--- a/internacional/Contraste_quimica.xlsx
+++ b/internacional/Contraste_quimica.xlsx
@@ -591,28 +591,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Agentes oxidantes y reductores</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>8.5</v>
       </c>
+      <c r="I2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -620,9 +626,15 @@
       <c r="P2" t="n">
         <v>1</v>
       </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
       <c r="U2" t="n">
         <v>1</v>
       </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
@@ -633,9 +645,6 @@
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
         <v>1</v>
       </c>
       <c r="AB2" t="n">
@@ -654,7 +663,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agentes oxidantes y reductores</t>
+          <t>Autoionización del agua, Kw y cálculo de pH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -663,13 +672,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
         <v>8.5</v>
@@ -678,13 +684,10 @@
         <v>9.5</v>
       </c>
       <c r="L3" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -708,6 +711,9 @@
         <v>1</v>
       </c>
       <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
         <v>1</v>
       </c>
       <c r="AB3" t="n">
@@ -726,7 +732,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Autoionización del agua, Kw y cálculo de pH</t>
+          <t>Catalizadores</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -735,33 +741,30 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.5</v>
       </c>
       <c r="G4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>11</v>
       </c>
       <c r="M4" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
       <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
@@ -795,7 +798,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Catalizadores</t>
+          <t>Celdas galvánicas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -804,27 +807,27 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>10.5</v>
       </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
@@ -858,7 +861,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Celdas galvánicas</t>
+          <t>Metales, cerámicas y materiales compuestos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -867,19 +870,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
+      <c r="L6" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M6" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -887,22 +896,16 @@
       <c r="R6" t="n">
         <v>1</v>
       </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="n">
         <v>1</v>
       </c>
       <c r="AB6" t="n">
@@ -921,7 +924,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Metales, cerámicas y materiales compuestos</t>
+          <t>Composición porcentual y fórmulas empírica y molecular</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -935,31 +938,19 @@
       <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
       <c r="G7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="L7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
+        <v>11</v>
+      </c>
+      <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
@@ -968,23 +959,17 @@
       <c r="Z7" t="n">
         <v>1</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1</v>
-      </c>
       <c r="AC7" t="n">
         <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Composición porcentual y fórmulas empírica y molecular</t>
+          <t>Conservación de la masa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -998,18 +983,48 @@
       <c r="D8" t="n">
         <v>10</v>
       </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
       <c r="G8" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
       <c r="U8" t="n">
         <v>1</v>
       </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
@@ -1019,17 +1034,23 @@
       <c r="Z8" t="n">
         <v>1</v>
       </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
       <c r="AC8" t="n">
         <v>1</v>
       </c>
       <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Conservación de la masa</t>
+          <t>Cromatografía</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1043,29 +1064,17 @@
       <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8</v>
-      </c>
       <c r="G9" t="n">
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="L9" t="n">
         <v>9.5</v>
       </c>
       <c r="M9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1073,9 +1082,6 @@
       <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
       <c r="U9" t="n">
         <v>1</v>
       </c>
@@ -1091,23 +1097,14 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cromatografía</t>
+          <t>Diagramas de fases</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1121,47 +1118,20 @@
       <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="G10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M10" t="n">
         <v>9.5</v>
       </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AA10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Diagramas de fases</t>
+          <t>Ecuación de los gases ideales y volumen molar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1175,20 +1145,53 @@
       <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="M11" t="n">
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="n">
         <v>9.5</v>
       </c>
-      <c r="V11" t="n">
+      <c r="L11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1</v>
       </c>
       <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ecuación de los gases ideales y volumen molar</t>
+          <t>Ecuación de Nernst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1197,58 +1200,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ecuación de Nernst</t>
+          <t>Ecuaciones y reacciones nucleares</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1257,19 +1221,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ecuaciones y reacciones nucleares</t>
+          <t>El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1283,17 +1250,59 @@
       <c r="D14" t="n">
         <v>10</v>
       </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
       <c r="G14" t="n">
         <v>8.5</v>
       </c>
+      <c r="L14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
       <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>El carbono y las moléculas orgánicas</t>
+          <t>Electrólisis y celdas electrolíticas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1308,21 +1317,21 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G15" t="n">
         <v>8.5</v>
       </c>
-      <c r="L15" t="n">
-        <v>9.5</v>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
         <v>1</v>
       </c>
       <c r="W15" t="n">
@@ -1356,7 +1365,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Electrólisis y celdas electrolíticas</t>
+          <t>Electrolitos fuertes y débiles</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1365,13 +1374,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
         <v>8.5</v>
@@ -1379,16 +1388,22 @@
       <c r="I16" t="n">
         <v>8</v>
       </c>
+      <c r="L16" t="n">
+        <v>11</v>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
       <c r="O16" t="n">
         <v>1</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
@@ -1397,9 +1412,6 @@
       <c r="Z16" t="n">
         <v>1</v>
       </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
       <c r="AB16" t="n">
         <v>1</v>
       </c>
@@ -1407,16 +1419,13 @@
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Electrolitos fuertes y débiles</t>
+          <t>Energía de activación y perfil energético</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1425,24 +1434,18 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G17" t="n">
         <v>8.5</v>
       </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
       <c r="L17" t="n">
-        <v>11</v>
-      </c>
-      <c r="M17" t="n">
         <v>9.5</v>
       </c>
       <c r="O17" t="n">
@@ -1454,7 +1457,10 @@
       <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
@@ -1470,13 +1476,16 @@
         <v>1</v>
       </c>
       <c r="AD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Energía de activación y perfil energético</t>
+          <t>Energía de enlace</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1520,7 +1529,7 @@
       <c r="Z18" t="n">
         <v>1</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AA18" t="n">
         <v>1</v>
       </c>
       <c r="AC18" t="n">
@@ -1536,7 +1545,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Energía de enlace</t>
+          <t>Energía reticular y ciclo de Born-Haber</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1550,53 +1559,20 @@
       <c r="D19" t="n">
         <v>10</v>
       </c>
-      <c r="F19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>8.5</v>
-      </c>
       <c r="L19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Energía reticular y ciclo de Born-Haber</t>
+          <t>Enlace químico</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1610,20 +1586,65 @@
       <c r="D20" t="n">
         <v>10</v>
       </c>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9</v>
+      </c>
       <c r="L20" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
       <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Enlace químico</t>
+          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1643,14 +1664,11 @@
       <c r="G21" t="n">
         <v>8.5</v>
       </c>
-      <c r="J21" t="n">
-        <v>9</v>
-      </c>
       <c r="L21" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M21" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -1658,9 +1676,6 @@
       <c r="P21" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
@@ -1677,6 +1692,9 @@
         <v>1</v>
       </c>
       <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1</v>
       </c>
       <c r="AB21" t="n">
@@ -1695,7 +1713,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
+          <t>Equilibrio químico dinámico</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1704,22 +1722,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G22" t="n">
         <v>8.5</v>
       </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
       <c r="L22" t="n">
         <v>11</v>
       </c>
       <c r="M22" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -1764,7 +1785,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Equilibrio químico dinámico</t>
+          <t>Equilibrio y rapidez en procesos industriales</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1773,10 +1794,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
         <v>10.5</v>
@@ -1787,9 +1808,6 @@
       <c r="L23" t="n">
         <v>11</v>
       </c>
-      <c r="M23" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
@@ -1799,22 +1817,10 @@
       <c r="U23" t="n">
         <v>1</v>
       </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
       <c r="Y23" t="n">
         <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
         <v>1</v>
       </c>
       <c r="AB23" t="n">
@@ -1833,7 +1839,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Equilibrio y rapidez en procesos industriales</t>
+          <t>Esterificación e hidrólisis</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1842,52 +1848,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
         <v>10.5</v>
       </c>
-      <c r="G24" t="n">
-        <v>8.5</v>
-      </c>
       <c r="L24" t="n">
         <v>11</v>
       </c>
+      <c r="M24" t="n">
+        <v>7</v>
+      </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
       <c r="Y24" t="n">
         <v>1</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1</v>
-      </c>
       <c r="AC24" t="n">
         <v>1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Esterificación e hidrólisis</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1901,13 +1901,19 @@
       <c r="D25" t="n">
         <v>11</v>
       </c>
-      <c r="F25" t="n">
-        <v>10.5</v>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>9.5</v>
       </c>
       <c r="L25" t="n">
-        <v>11</v>
-      </c>
-      <c r="O25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7</v>
+      </c>
+      <c r="R25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
@@ -1922,17 +1928,20 @@
       <c r="Z25" t="n">
         <v>1</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>1</v>
       </c>
       <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Fuerza de ácidos y bases: Ka y Kb</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1941,13 +1950,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I26" t="n">
         <v>9.5</v>
@@ -1955,15 +1967,30 @@
       <c r="L26" t="n">
         <v>9.5</v>
       </c>
+      <c r="M26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y26" t="n">
         <v>1</v>
       </c>
@@ -1971,6 +1998,12 @@
         <v>1</v>
       </c>
       <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1</v>
       </c>
       <c r="AD26" t="n">
@@ -1983,7 +2016,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fuerza de ácidos y bases: Ka y Kb</t>
+          <t>Grupos funcionales</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1992,10 +2025,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
@@ -2003,14 +2036,11 @@
       <c r="G27" t="n">
         <v>8.5</v>
       </c>
-      <c r="I27" t="n">
-        <v>9.5</v>
-      </c>
       <c r="L27" t="n">
         <v>9.5</v>
       </c>
       <c r="M27" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -2018,13 +2048,7 @@
       <c r="P27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
       <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
         <v>1</v>
       </c>
       <c r="W27" t="n">
@@ -2058,7 +2082,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grupos funcionales</t>
+          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2081,6 +2105,9 @@
       <c r="L28" t="n">
         <v>9.5</v>
       </c>
+      <c r="M28" t="n">
+        <v>7</v>
+      </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
@@ -2103,9 +2130,6 @@
         <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB28" t="n">
         <v>1</v>
       </c>
       <c r="AC28" t="n">
@@ -2121,7 +2145,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
+          <t>Hidrocarburos aromáticos</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2136,13 +2160,13 @@
         <v>11</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G29" t="n">
         <v>8.5</v>
       </c>
       <c r="L29" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -2153,9 +2177,6 @@
       <c r="U29" t="n">
         <v>1</v>
       </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
@@ -2168,20 +2189,14 @@
       <c r="AA29" t="n">
         <v>1</v>
       </c>
-      <c r="AC29" t="n">
-        <v>1</v>
-      </c>
       <c r="AD29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hidrocarburos aromáticos</t>
+          <t>Indicadores ácido-base</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2190,30 +2205,45 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" t="n">
+        <v>9</v>
       </c>
       <c r="L30" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="P30" t="n">
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
       </c>
-      <c r="X30" t="n">
+      <c r="W30" t="n">
         <v>1</v>
       </c>
       <c r="Y30" t="n">
@@ -2222,17 +2252,20 @@
       <c r="Z30" t="n">
         <v>1</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>1</v>
       </c>
       <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Indicadores ácido-base</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2241,48 +2274,39 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
       </c>
-      <c r="G31" t="n">
-        <v>6</v>
-      </c>
-      <c r="I31" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>9</v>
-      </c>
-      <c r="K31" t="n">
-        <v>9</v>
-      </c>
       <c r="L31" t="n">
-        <v>9.5</v>
+        <v>11</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
       <c r="Y31" t="n">
         <v>1</v>
       </c>
       <c r="Z31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
         <v>1</v>
       </c>
       <c r="AC31" t="n">
@@ -2298,7 +2322,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Leyes de los gases</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2312,31 +2336,25 @@
       <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="F32" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" t="n">
-        <v>11</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="n">
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V32" t="n">
         <v>1</v>
       </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1</v>
-      </c>
       <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1</v>
       </c>
       <c r="AC32" t="n">
@@ -2352,7 +2370,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2366,56 +2384,26 @@
       <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="G33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>11</v>
+      <c r="I33" t="n">
+        <v>7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
       </c>
       <c r="M33" t="n">
         <v>9.5</v>
       </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Neutralización y reacciones de los ácidos</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2424,28 +2412,76 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
       </c>
       <c r="I34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>9</v>
+      </c>
+      <c r="K34" t="n">
+        <v>9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M34" t="n">
         <v>7</v>
       </c>
-      <c r="M34" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V34" t="n">
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1</v>
       </c>
       <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Neutralización y reacciones de los ácidos</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2454,25 +2490,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
-      </c>
-      <c r="I35" t="n">
-        <v>8</v>
-      </c>
-      <c r="J35" t="n">
-        <v>9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="L35" t="n">
         <v>9.5</v>
@@ -2483,19 +2510,13 @@
       <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
       <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
         <v>1</v>
       </c>
       <c r="Y35" t="n">
@@ -2520,7 +2541,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Oxidación y reducción</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2529,29 +2550,47 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9</v>
       </c>
       <c r="L36" t="n">
         <v>9.5</v>
       </c>
+      <c r="M36" t="n">
+        <v>7</v>
+      </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
       </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
@@ -2562,6 +2601,9 @@
         <v>1</v>
       </c>
       <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
         <v>1</v>
       </c>
       <c r="AB36" t="n">
@@ -2580,7 +2622,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oxidación y reducción</t>
+          <t>Polimerización por adición y por condensación</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2589,51 +2631,24 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
-      </c>
-      <c r="G37" t="n">
-        <v>6</v>
-      </c>
-      <c r="I37" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="L37" t="n">
         <v>9.5</v>
       </c>
-      <c r="M37" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
       <c r="U37" t="n">
         <v>1</v>
       </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
       <c r="W37" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" t="n">
         <v>1</v>
       </c>
       <c r="Y37" t="n">
@@ -2661,7 +2676,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Polimerización por adición y por condensación</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2676,11 +2691,14 @@
         <v>11</v>
       </c>
       <c r="F38" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="L38" t="n">
         <v>9.5</v>
       </c>
+      <c r="M38" t="n">
+        <v>7</v>
+      </c>
       <c r="O38" t="n">
         <v>1</v>
       </c>
@@ -2690,32 +2708,20 @@
       <c r="W38" t="n">
         <v>1</v>
       </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
-      <c r="AA38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
       <c r="AC38" t="n">
         <v>1</v>
       </c>
       <c r="AD38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2724,40 +2730,64 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D39" t="n">
+        <v>9</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L39" t="n">
         <v>11</v>
       </c>
-      <c r="D39" t="n">
-        <v>11</v>
-      </c>
-      <c r="F39" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" t="n">
-        <v>9.5</v>
+      <c r="M39" t="n">
+        <v>7</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
       <c r="U39" t="n">
         <v>1</v>
       </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
       <c r="Z39" t="n">
         <v>1</v>
       </c>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
       <c r="AC39" t="n">
         <v>1</v>
       </c>
       <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Química verde y economía atómica</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2771,22 +2801,25 @@
       <c r="D40" t="n">
         <v>11</v>
       </c>
-      <c r="F40" t="n">
-        <v>8</v>
-      </c>
       <c r="G40" t="n">
         <v>8.5</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" t="n">
         <v>9.5</v>
       </c>
-      <c r="O40" t="n">
-        <v>1</v>
+      <c r="M40" t="n">
+        <v>9.5</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="n">
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
         <v>1</v>
       </c>
       <c r="W40" t="n">
@@ -2805,9 +2838,6 @@
         <v>1</v>
       </c>
       <c r="AC40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD40" t="n">
         <v>1</v>
       </c>
       <c r="AE40" t="n">
@@ -2817,7 +2847,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Química verde y economía atómica</t>
+          <t>Reacciones de precipitación e identificación de iones</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2826,45 +2856,48 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10.5</v>
       </c>
       <c r="G41" t="n">
         <v>8.5</v>
       </c>
+      <c r="I41" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L41" t="n">
         <v>9.5</v>
       </c>
       <c r="M41" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P41" t="n">
+        <v>7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
       <c r="Y41" t="n">
         <v>1</v>
       </c>
       <c r="Z41" t="n">
         <v>1</v>
       </c>
-      <c r="AB41" t="n">
-        <v>1</v>
-      </c>
       <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1</v>
       </c>
       <c r="AE41" t="n">
@@ -2874,7 +2907,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Reacciones de precipitación e identificación de iones</t>
+          <t>Reacciones exotérmicas y endotérmicas</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2883,39 +2916,69 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K42" t="n">
         <v>9</v>
-      </c>
-      <c r="D42" t="n">
-        <v>9</v>
-      </c>
-      <c r="F42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G42" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I42" t="n">
-        <v>9.5</v>
       </c>
       <c r="L42" t="n">
         <v>9.5</v>
       </c>
+      <c r="M42" t="n">
+        <v>7</v>
+      </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="R42" t="n">
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>1</v>
       </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
       <c r="W42" t="n">
         <v>1</v>
       </c>
+      <c r="X42" t="n">
+        <v>1</v>
+      </c>
       <c r="Y42" t="n">
         <v>1</v>
       </c>
       <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1</v>
       </c>
       <c r="AC42" t="n">
@@ -2931,7 +2994,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Reacciones exotérmicas y endotérmicas</t>
+          <t>Reacciones orgánicas características</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2940,51 +3003,24 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
-      </c>
-      <c r="G43" t="n">
-        <v>6</v>
-      </c>
-      <c r="I43" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" t="n">
-        <v>9</v>
-      </c>
-      <c r="K43" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="L43" t="n">
         <v>9.5</v>
       </c>
       <c r="M43" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
       <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="W43" t="n">
@@ -3018,7 +3054,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Reacciones orgánicas características</t>
+          <t>Reactivo limitante y en exceso</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3027,39 +3063,33 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F44" t="n">
         <v>10.5</v>
       </c>
+      <c r="G44" t="n">
+        <v>8.5</v>
+      </c>
       <c r="L44" t="n">
         <v>9.5</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
       <c r="U44" t="n">
         <v>1</v>
       </c>
-      <c r="W44" t="n">
-        <v>1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
       <c r="Y44" t="n">
         <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB44" t="n">
         <v>1</v>
       </c>
       <c r="AC44" t="n">
@@ -3075,7 +3105,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Reactivo limitante y en exceso</t>
+          <t>Redes covalentes y alótropos del carbono</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3090,7 +3120,7 @@
         <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
         <v>8.5</v>
@@ -3098,6 +3128,9 @@
       <c r="L45" t="n">
         <v>9.5</v>
       </c>
+      <c r="M45" t="n">
+        <v>7</v>
+      </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
@@ -3107,26 +3140,23 @@
       <c r="U45" t="n">
         <v>1</v>
       </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
       <c r="Y45" t="n">
         <v>1</v>
       </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
-      <c r="AC45" t="n">
-        <v>1</v>
-      </c>
       <c r="AD45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Redes covalentes y alótropos del carbono</t>
+          <t>Semivida, series de desintegración y residuos radiactivos</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3146,35 +3176,59 @@
       <c r="G46" t="n">
         <v>8.5</v>
       </c>
+      <c r="I46" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L46" t="n">
         <v>9.5</v>
       </c>
+      <c r="M46" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
       <c r="U46" t="n">
         <v>1</v>
       </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
       <c r="W46" t="n">
         <v>1</v>
       </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
       <c r="Y46" t="n">
         <v>1</v>
       </c>
       <c r="Z46" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1</v>
+      </c>
       <c r="AD46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Semivida, series de desintegración y residuos radiactivos</t>
+          <t>Teoría cinética de los gases</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3183,22 +3237,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G47" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I47" t="n">
         <v>9.5</v>
       </c>
-      <c r="L47" t="n">
-        <v>9.5</v>
+      <c r="J47" t="n">
+        <v>7</v>
       </c>
       <c r="M47" t="n">
         <v>9.5</v>
@@ -3212,18 +3266,12 @@
       <c r="R47" t="n">
         <v>1</v>
       </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
-      <c r="X47" t="n">
-        <v>1</v>
-      </c>
       <c r="Y47" t="n">
         <v>1</v>
       </c>
@@ -3231,6 +3279,9 @@
         <v>1</v>
       </c>
       <c r="AA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
         <v>1</v>
       </c>
       <c r="AC47" t="n">
@@ -3246,7 +3297,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Síntesis química y rutas de reacción</t>
+          <t>Teoría de colisiones</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3255,21 +3306,39 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9</v>
       </c>
       <c r="F48" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8.5</v>
       </c>
       <c r="L48" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>7</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
       </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
       <c r="U48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
         <v>1</v>
       </c>
       <c r="W48" t="n">
@@ -3303,7 +3372,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Teoría cinética de los gases</t>
+          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3318,16 +3387,22 @@
         <v>9</v>
       </c>
       <c r="F49" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" t="n">
+        <v>9</v>
+      </c>
+      <c r="L49" t="n">
         <v>9.5</v>
       </c>
       <c r="M49" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -3335,7 +3410,10 @@
       <c r="P49" t="n">
         <v>1</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
         <v>1</v>
       </c>
       <c r="V49" t="n">
@@ -3344,13 +3422,13 @@
       <c r="W49" t="n">
         <v>1</v>
       </c>
+      <c r="X49" t="n">
+        <v>1</v>
+      </c>
       <c r="Y49" t="n">
         <v>1</v>
       </c>
       <c r="Z49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA49" t="n">
         <v>1</v>
       </c>
       <c r="AB49" t="n">
@@ -3369,7 +3447,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Teoría de colisiones</t>
+          <t>Valoración ácido-base</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3383,49 +3461,25 @@
       <c r="D50" t="n">
         <v>9</v>
       </c>
-      <c r="E50" t="n">
-        <v>9</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8</v>
-      </c>
-      <c r="G50" t="n">
-        <v>8.5</v>
+      <c r="I50" t="n">
+        <v>9.5</v>
       </c>
       <c r="L50" t="n">
         <v>9.5</v>
       </c>
-      <c r="M50" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="n">
-        <v>1</v>
-      </c>
       <c r="W50" t="n">
         <v>1</v>
       </c>
-      <c r="X50" t="n">
-        <v>1</v>
-      </c>
       <c r="Y50" t="n">
         <v>1</v>
       </c>
       <c r="Z50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA50" t="n">
         <v>1</v>
       </c>
       <c r="AB50" t="n">
@@ -3444,7 +3498,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
+          <t>Medición de la velocidad de reacción</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3453,56 +3507,35 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
-      </c>
-      <c r="F51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G51" t="n">
         <v>8.5</v>
       </c>
-      <c r="I51" t="n">
-        <v>8</v>
-      </c>
-      <c r="J51" t="n">
-        <v>9</v>
-      </c>
       <c r="L51" t="n">
         <v>9.5</v>
       </c>
-      <c r="M51" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
       <c r="U51" t="n">
         <v>1</v>
       </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
       <c r="W51" t="n">
         <v>1</v>
       </c>
-      <c r="X51" t="n">
-        <v>1</v>
-      </c>
       <c r="Y51" t="n">
         <v>1</v>
       </c>
       <c r="Z51" t="n">
         <v>1</v>
       </c>
+      <c r="AA51" t="n">
+        <v>1</v>
+      </c>
       <c r="AB51" t="n">
         <v>1</v>
       </c>
@@ -3510,40 +3543,19 @@
         <v>1</v>
       </c>
       <c r="AD51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Valoración ácido-base</t>
+          <t>Espectrometría de masas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>alineado</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>9</v>
-      </c>
-      <c r="D52" t="n">
-        <v>9</v>
-      </c>
-      <c r="I52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1</v>
+          <t>no_aplica</t>
+        </is>
       </c>
       <c r="W52" t="n">
         <v>1</v>
@@ -3552,49 +3564,19 @@
         <v>1</v>
       </c>
       <c r="Z52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE52" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Medición de la velocidad de reacción</t>
+          <t>Técnicas para determinar estructuras orgánicas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>alineado</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>10</v>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="G53" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L53" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1</v>
+          <t>no_aplica</t>
+        </is>
       </c>
       <c r="W53" t="n">
         <v>1</v>
@@ -3605,68 +3587,80 @@
       <c r="Z53" t="n">
         <v>1</v>
       </c>
-      <c r="AA53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1</v>
-      </c>
       <c r="AC53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD53" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Espectrometría de masas</t>
+          <t>Disolución y rapidez de disolución</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>no_aplica</t>
-        </is>
-      </c>
-      <c r="W54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z54" t="n">
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Técnicas para determinar estructuras orgánicas</t>
+          <t>Minerales: composición y estructura cristalina</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>no_aplica</t>
-        </is>
-      </c>
-      <c r="W55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y55" t="n">
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>9</v>
+      </c>
+      <c r="L55" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD55" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Disolución y rapidez de disolución</t>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3675,54 +3669,123 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
       </c>
       <c r="G56" t="n">
         <v>6</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="I56" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>9</v>
+      </c>
+      <c r="M56" t="n">
+        <v>7</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" t="n">
         <v>1</v>
       </c>
       <c r="AC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Minerales: composición y estructura cristalina</t>
+          <t>Ácidos y bases: propiedades</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>9</v>
       </c>
       <c r="F57" t="n">
         <v>8</v>
       </c>
+      <c r="G57" t="n">
+        <v>6</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5</v>
+      </c>
       <c r="J57" t="n">
         <v>9</v>
       </c>
+      <c r="K57" t="n">
+        <v>9</v>
+      </c>
       <c r="L57" t="n">
         <v>9.5</v>
       </c>
+      <c r="M57" t="n">
+        <v>7</v>
+      </c>
       <c r="O57" t="n">
         <v>1</v>
       </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
       <c r="S57" t="n">
         <v>1</v>
       </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
       <c r="U57" t="n">
         <v>1</v>
       </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AC57" t="n">
         <v>1</v>
       </c>
       <c r="AD57" t="n">
@@ -3732,29 +3795,38 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+          <t>Aminoácidos y estructura de las proteínas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D58" t="n">
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G58" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I58" t="n">
         <v>9.5</v>
       </c>
-      <c r="K58" t="n">
+      <c r="J58" t="n">
         <v>9</v>
       </c>
+      <c r="L58" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
@@ -3764,7 +3836,16 @@
       <c r="R58" t="n">
         <v>1</v>
       </c>
-      <c r="T58" t="n">
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>1</v>
       </c>
       <c r="X58" t="n">
@@ -3774,6 +3855,12 @@
         <v>1</v>
       </c>
       <c r="Z58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB58" t="n">
         <v>1</v>
       </c>
       <c r="AC58" t="n">
@@ -3789,7 +3876,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ácidos y bases: propiedades</t>
+          <t>Átomo y partículas subatómicas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3798,10 +3885,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E59" t="n">
+        <v>8</v>
       </c>
       <c r="F59" t="n">
         <v>8</v>
@@ -3810,19 +3900,22 @@
         <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L59" t="n">
         <v>9.5</v>
       </c>
       <c r="M59" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
       <c r="O59" t="n">
         <v>1</v>
@@ -3833,9 +3926,6 @@
       <c r="R59" t="n">
         <v>1</v>
       </c>
-      <c r="S59" t="n">
-        <v>1</v>
-      </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
@@ -3848,6 +3938,9 @@
       <c r="W59" t="n">
         <v>1</v>
       </c>
+      <c r="X59" t="n">
+        <v>1</v>
+      </c>
       <c r="Y59" t="n">
         <v>1</v>
       </c>
@@ -3858,13 +3951,16 @@
         <v>1</v>
       </c>
       <c r="AD59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE59" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Aminoácidos y estructura de las proteínas</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3873,28 +3969,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
         <v>9</v>
       </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
       <c r="F60" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G60" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L60" t="n">
         <v>9.5</v>
       </c>
       <c r="M60" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -3905,9 +4004,6 @@
       <c r="R60" t="n">
         <v>1</v>
       </c>
-      <c r="S60" t="n">
-        <v>1</v>
-      </c>
       <c r="U60" t="n">
         <v>1</v>
       </c>
@@ -3936,16 +4032,13 @@
         <v>1</v>
       </c>
       <c r="AD60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE60" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Átomo y partículas subatómicas</t>
+          <t>Cambios físicos y químicos</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3954,34 +4047,34 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I61" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>7</v>
+      </c>
+      <c r="K61" t="n">
         <v>8</v>
-      </c>
-      <c r="K61" t="n">
-        <v>9</v>
       </c>
       <c r="L61" t="n">
         <v>9.5</v>
       </c>
       <c r="M61" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O61" t="n">
         <v>1</v>
@@ -3992,41 +4085,38 @@
       <c r="R61" t="n">
         <v>1</v>
       </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
         <v>1</v>
       </c>
-      <c r="V61" t="n">
-        <v>1</v>
-      </c>
       <c r="W61" t="n">
         <v>1</v>
       </c>
-      <c r="X61" t="n">
-        <v>1</v>
-      </c>
       <c r="Y61" t="n">
         <v>1</v>
       </c>
       <c r="Z61" t="n">
         <v>1</v>
       </c>
+      <c r="AB61" t="n">
+        <v>1</v>
+      </c>
       <c r="AC61" t="n">
         <v>1</v>
       </c>
       <c r="AD61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE61" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Combustibles fósiles y biocombustibles</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4035,28 +4125,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F62" t="n">
         <v>8</v>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>9</v>
       </c>
       <c r="L62" t="n">
         <v>9.5</v>
       </c>
       <c r="M62" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
@@ -4064,7 +4151,7 @@
       <c r="P62" t="n">
         <v>1</v>
       </c>
-      <c r="R62" t="n">
+      <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
@@ -4085,9 +4172,6 @@
       <c r="Z62" t="n">
         <v>1</v>
       </c>
-      <c r="AA62" t="n">
-        <v>1</v>
-      </c>
       <c r="AB62" t="n">
         <v>1</v>
       </c>
@@ -4095,13 +4179,16 @@
         <v>1</v>
       </c>
       <c r="AD62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE62" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cambios físicos y químicos</t>
+          <t>Combustión</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4110,50 +4197,47 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F63" t="n">
         <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I63" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>9</v>
       </c>
-      <c r="K63" t="n">
-        <v>9</v>
-      </c>
       <c r="L63" t="n">
         <v>9.5</v>
       </c>
+      <c r="M63" t="n">
+        <v>7</v>
+      </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
       <c r="P63" t="n">
         <v>1</v>
       </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
       <c r="S63" t="n">
         <v>1</v>
       </c>
-      <c r="T63" t="n">
-        <v>1</v>
-      </c>
       <c r="U63" t="n">
         <v>1</v>
       </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
       <c r="W63" t="n">
         <v>1</v>
       </c>
@@ -4170,13 +4254,16 @@
         <v>1</v>
       </c>
       <c r="AD63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Combustibles fósiles y biocombustibles</t>
+          <t>Composición del aire y contaminantes atmosféricos</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4196,6 +4283,9 @@
       <c r="G64" t="n">
         <v>8.5</v>
       </c>
+      <c r="I64" t="n">
+        <v>5</v>
+      </c>
       <c r="K64" t="n">
         <v>9</v>
       </c>
@@ -4203,7 +4293,7 @@
         <v>9.5</v>
       </c>
       <c r="M64" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -4217,9 +4307,6 @@
       <c r="U64" t="n">
         <v>1</v>
       </c>
-      <c r="V64" t="n">
-        <v>1</v>
-      </c>
       <c r="W64" t="n">
         <v>1</v>
       </c>
@@ -4230,12 +4317,6 @@
         <v>1</v>
       </c>
       <c r="Z64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC64" t="n">
         <v>1</v>
       </c>
       <c r="AD64" t="n">
@@ -4248,7 +4329,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Combustión</t>
+          <t>Soluto, disolvente y concentración</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4257,31 +4338,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
         <v>9</v>
       </c>
-      <c r="E65" t="n">
-        <v>8</v>
-      </c>
       <c r="F65" t="n">
         <v>8</v>
       </c>
       <c r="G65" t="n">
-        <v>6</v>
-      </c>
-      <c r="I65" t="n">
-        <v>5</v>
-      </c>
-      <c r="J65" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="L65" t="n">
         <v>9.5</v>
       </c>
       <c r="M65" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -4289,9 +4361,6 @@
       <c r="P65" t="n">
         <v>1</v>
       </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
       <c r="U65" t="n">
         <v>1</v>
       </c>
@@ -4307,6 +4376,9 @@
       <c r="Z65" t="n">
         <v>1</v>
       </c>
+      <c r="AA65" t="n">
+        <v>1</v>
+      </c>
       <c r="AB65" t="n">
         <v>1</v>
       </c>
@@ -4314,16 +4386,13 @@
         <v>1</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE65" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Composición del aire y contaminantes atmosféricos</t>
+          <t>Configuración electrónica</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4332,11 +4401,14 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
         <v>10</v>
       </c>
+      <c r="E66" t="n">
+        <v>9</v>
+      </c>
       <c r="F66" t="n">
         <v>8</v>
       </c>
@@ -4344,21 +4416,30 @@
         <v>8.5</v>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>9.5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>9</v>
       </c>
       <c r="K66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L66" t="n">
         <v>9.5</v>
       </c>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
       <c r="O66" t="n">
         <v>1</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
       </c>
-      <c r="T66" t="n">
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
         <v>1</v>
       </c>
       <c r="U66" t="n">
@@ -4374,6 +4455,12 @@
         <v>1</v>
       </c>
       <c r="Z66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC66" t="n">
         <v>1</v>
       </c>
       <c r="AD66" t="n">
@@ -4386,7 +4473,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Soluto, disolvente y concentración</t>
+          <t>Densidad y flotación</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4395,7 +4482,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
         <v>9</v>
@@ -4406,11 +4493,14 @@
       <c r="G67" t="n">
         <v>8.5</v>
       </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
       <c r="L67" t="n">
         <v>9.5</v>
       </c>
       <c r="M67" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -4421,25 +4511,10 @@
       <c r="U67" t="n">
         <v>1</v>
       </c>
-      <c r="V67" t="n">
-        <v>1</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1</v>
-      </c>
       <c r="Y67" t="n">
         <v>1</v>
       </c>
       <c r="Z67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC67" t="n">
         <v>1</v>
       </c>
       <c r="AD67" t="n">
@@ -4449,7 +4524,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Configuración electrónica</t>
+          <t>Disoluciones, coloides y suspensiones</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4458,54 +4533,21 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
         <v>10</v>
       </c>
-      <c r="E68" t="n">
-        <v>9</v>
-      </c>
       <c r="F68" t="n">
         <v>8</v>
       </c>
-      <c r="G68" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I68" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J68" t="n">
-        <v>9</v>
-      </c>
-      <c r="L68" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N68" t="n">
-        <v>1</v>
+      <c r="M68" t="n">
+        <v>7</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="P68" t="n">
-        <v>1</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S68" t="n">
-        <v>1</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1</v>
-      </c>
-      <c r="X68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y68" t="n">
+      <c r="V68" t="n">
         <v>1</v>
       </c>
       <c r="Z68" t="n">
@@ -4515,19 +4557,13 @@
         <v>1</v>
       </c>
       <c r="AC68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE68" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Densidad y flotación</t>
+          <t>Ecuación química y su balanceo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4536,43 +4572,82 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
         <v>9</v>
       </c>
+      <c r="E69" t="n">
+        <v>8</v>
+      </c>
       <c r="F69" t="n">
         <v>8</v>
       </c>
       <c r="G69" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I69" t="n">
+        <v>7</v>
+      </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
+      <c r="K69" t="n">
+        <v>9</v>
       </c>
       <c r="L69" t="n">
         <v>9.5</v>
       </c>
+      <c r="M69" t="n">
+        <v>7</v>
+      </c>
       <c r="O69" t="n">
         <v>1</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
       <c r="U69" t="n">
         <v>1</v>
       </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1</v>
+      </c>
       <c r="Y69" t="n">
         <v>1</v>
       </c>
       <c r="Z69" t="n">
         <v>1</v>
       </c>
+      <c r="AB69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1</v>
+      </c>
       <c r="AD69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE69" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Disoluciones, coloides y suspensiones</t>
+          <t>Electronegatividad y polaridad de enlace</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4581,37 +4656,49 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
         <v>10</v>
       </c>
       <c r="F70" t="n">
-        <v>8</v>
-      </c>
-      <c r="M70" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="L70" t="n">
+        <v>11</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="V70" t="n">
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y70" t="n">
         <v>1</v>
       </c>
       <c r="Z70" t="n">
         <v>1</v>
       </c>
-      <c r="AA70" t="n">
+      <c r="AB70" t="n">
         <v>1</v>
       </c>
       <c r="AC70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD70" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ecuación química y su balanceo</t>
+          <t>Electrones de valencia y regla del octeto</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4623,29 +4710,23 @@
         <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>9</v>
-      </c>
-      <c r="E71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G71" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
-      </c>
-      <c r="K71" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J71" t="n">
         <v>9</v>
       </c>
       <c r="L71" t="n">
         <v>9.5</v>
       </c>
-      <c r="M71" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O71" t="n">
         <v>1</v>
       </c>
@@ -4655,21 +4736,15 @@
       <c r="R71" t="n">
         <v>1</v>
       </c>
-      <c r="T71" t="n">
+      <c r="S71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
         <v>1</v>
       </c>
-      <c r="V71" t="n">
-        <v>1</v>
-      </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
-      <c r="X71" t="n">
-        <v>1</v>
-      </c>
       <c r="Y71" t="n">
         <v>1</v>
       </c>
@@ -4683,16 +4758,13 @@
         <v>1</v>
       </c>
       <c r="AD71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE71" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Electronegatividad y polaridad de enlace</t>
+          <t>Enlace covalente</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4707,23 +4779,44 @@
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I72" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>9</v>
       </c>
       <c r="L72" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M72" t="n">
+        <v>9.5</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
       </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
       <c r="U72" t="n">
         <v>1</v>
       </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
-      <c r="X72" t="n">
-        <v>1</v>
-      </c>
       <c r="Y72" t="n">
         <v>1</v>
       </c>
@@ -4737,13 +4830,16 @@
         <v>1</v>
       </c>
       <c r="AD72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE72" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Electrones de valencia y regla del octeto</t>
+          <t>Enlace iónico</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4752,13 +4848,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
         <v>10</v>
       </c>
       <c r="F73" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G73" t="n">
         <v>8.5</v>
@@ -4772,6 +4868,9 @@
       <c r="L73" t="n">
         <v>9.5</v>
       </c>
+      <c r="M73" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
@@ -4785,6 +4884,9 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
         <v>1</v>
       </c>
       <c r="W73" t="n">
@@ -4809,7 +4911,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enlace covalente</t>
+          <t>Enlace metálico</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4838,9 +4940,6 @@
       <c r="L74" t="n">
         <v>9.5</v>
       </c>
-      <c r="M74" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
@@ -4856,10 +4955,10 @@
       <c r="U74" t="n">
         <v>1</v>
       </c>
-      <c r="V74" t="n">
-        <v>1</v>
-      </c>
       <c r="W74" t="n">
+        <v>1</v>
+      </c>
+      <c r="X74" t="n">
         <v>1</v>
       </c>
       <c r="Y74" t="n">
@@ -4884,7 +4983,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Enlace iónico</t>
+          <t>Escala de pH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4893,28 +4992,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
         <v>8</v>
       </c>
       <c r="G75" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I75" t="n">
         <v>9.5</v>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>9</v>
       </c>
       <c r="L75" t="n">
         <v>9.5</v>
       </c>
       <c r="M75" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -4925,7 +5024,7 @@
       <c r="R75" t="n">
         <v>1</v>
       </c>
-      <c r="S75" t="n">
+      <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
@@ -4937,6 +5036,9 @@
       <c r="W75" t="n">
         <v>1</v>
       </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
       <c r="Y75" t="n">
         <v>1</v>
       </c>
@@ -4950,13 +5052,16 @@
         <v>1</v>
       </c>
       <c r="AD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE75" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Enlace metálico</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4965,26 +5070,32 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
         <v>10</v>
       </c>
+      <c r="E76" t="n">
+        <v>2</v>
+      </c>
       <c r="F76" t="n">
         <v>8</v>
       </c>
       <c r="G76" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
         <v>9.5</v>
       </c>
       <c r="J76" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L76" t="n">
         <v>9.5</v>
       </c>
+      <c r="M76" t="n">
+        <v>7</v>
+      </c>
       <c r="O76" t="n">
         <v>1</v>
       </c>
@@ -4994,24 +5105,18 @@
       <c r="R76" t="n">
         <v>1</v>
       </c>
-      <c r="S76" t="n">
-        <v>1</v>
-      </c>
       <c r="U76" t="n">
         <v>1</v>
       </c>
-      <c r="W76" t="n">
-        <v>1</v>
-      </c>
-      <c r="X76" t="n">
-        <v>1</v>
-      </c>
       <c r="Y76" t="n">
         <v>1</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
+      <c r="AA76" t="n">
+        <v>1</v>
+      </c>
       <c r="AB76" t="n">
         <v>1</v>
       </c>
@@ -5019,16 +5124,13 @@
         <v>1</v>
       </c>
       <c r="AD76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE76" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Escala de pH</t>
+          <t>Estequiometría</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5037,22 +5139,22 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F77" t="n">
         <v>8</v>
       </c>
       <c r="G77" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I77" t="n">
         <v>9.5</v>
       </c>
-      <c r="K77" t="n">
-        <v>9</v>
+      <c r="J77" t="n">
+        <v>7</v>
       </c>
       <c r="L77" t="n">
         <v>9.5</v>
@@ -5069,9 +5171,6 @@
       <c r="R77" t="n">
         <v>1</v>
       </c>
-      <c r="T77" t="n">
-        <v>1</v>
-      </c>
       <c r="U77" t="n">
         <v>1</v>
       </c>
@@ -5088,6 +5187,9 @@
         <v>1</v>
       </c>
       <c r="Z77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA77" t="n">
         <v>1</v>
       </c>
       <c r="AB77" t="n">
@@ -5106,7 +5208,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Notación y estructuras de Lewis</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5115,22 +5217,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D78" t="n">
         <v>10</v>
       </c>
-      <c r="E78" t="n">
-        <v>2</v>
-      </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
-      </c>
-      <c r="I78" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="L78" t="n">
         <v>9.5</v>
@@ -5141,19 +5237,19 @@
       <c r="P78" t="n">
         <v>1</v>
       </c>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
       <c r="U78" t="n">
         <v>1</v>
       </c>
+      <c r="W78" t="n">
+        <v>1</v>
+      </c>
+      <c r="X78" t="n">
+        <v>1</v>
+      </c>
       <c r="Y78" t="n">
         <v>1</v>
       </c>
       <c r="Z78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA78" t="n">
         <v>1</v>
       </c>
       <c r="AB78" t="n">
@@ -5169,7 +5265,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5178,19 +5274,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D79" t="n">
         <v>10</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G79" t="n">
         <v>8.5</v>
       </c>
-      <c r="I79" t="n">
-        <v>9.5</v>
+      <c r="J79" t="n">
+        <v>7</v>
       </c>
       <c r="L79" t="n">
         <v>9.5</v>
@@ -5204,9 +5300,6 @@
       <c r="P79" t="n">
         <v>1</v>
       </c>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
       <c r="U79" t="n">
         <v>1</v>
       </c>
@@ -5244,7 +5337,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Notación y estructuras de Lewis</t>
+          <t>Fuerzas intermoleculares y propiedades físicas</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5259,11 +5352,14 @@
         <v>10</v>
       </c>
       <c r="F80" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G80" t="n">
         <v>8.5</v>
       </c>
+      <c r="I80" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L80" t="n">
         <v>9.5</v>
       </c>
@@ -5273,6 +5369,9 @@
       <c r="P80" t="n">
         <v>1</v>
       </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
       <c r="U80" t="n">
         <v>1</v>
       </c>
@@ -5288,6 +5387,9 @@
       <c r="Z80" t="n">
         <v>1</v>
       </c>
+      <c r="AA80" t="n">
+        <v>1</v>
+      </c>
       <c r="AB80" t="n">
         <v>1</v>
       </c>
@@ -5295,13 +5397,16 @@
         <v>1</v>
       </c>
       <c r="AD80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE80" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares</t>
+          <t>Geometría molecular (RPECV)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5315,21 +5420,15 @@
       <c r="D81" t="n">
         <v>10</v>
       </c>
-      <c r="F81" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G81" t="n">
         <v>8.5</v>
       </c>
       <c r="L81" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M81" t="n">
         <v>9.5</v>
       </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
       <c r="P81" t="n">
         <v>1</v>
       </c>
@@ -5349,9 +5448,6 @@
         <v>1</v>
       </c>
       <c r="Z81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA81" t="n">
         <v>1</v>
       </c>
       <c r="AB81" t="n">
@@ -5370,7 +5466,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares y propiedades físicas</t>
+          <t>Iones</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5379,7 +5475,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
         <v>10</v>
@@ -5391,11 +5487,20 @@
         <v>8.5</v>
       </c>
       <c r="I82" t="n">
-        <v>9.5</v>
+        <v>8</v>
+      </c>
+      <c r="J82" t="n">
+        <v>7</v>
+      </c>
+      <c r="K82" t="n">
+        <v>9</v>
       </c>
       <c r="L82" t="n">
         <v>9.5</v>
       </c>
+      <c r="M82" t="n">
+        <v>7</v>
+      </c>
       <c r="O82" t="n">
         <v>1</v>
       </c>
@@ -5405,9 +5510,15 @@
       <c r="R82" t="n">
         <v>1</v>
       </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
       <c r="U82" t="n">
         <v>1</v>
       </c>
+      <c r="V82" t="n">
+        <v>1</v>
+      </c>
       <c r="W82" t="n">
         <v>1</v>
       </c>
@@ -5420,26 +5531,17 @@
       <c r="Z82" t="n">
         <v>1</v>
       </c>
-      <c r="AA82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>1</v>
-      </c>
       <c r="AC82" t="n">
         <v>1</v>
       </c>
       <c r="AD82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE82" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Geometría molecular (RPECV)</t>
+          <t>Isótopos</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5448,16 +5550,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
         <v>10</v>
       </c>
+      <c r="E83" t="n">
+        <v>8</v>
+      </c>
       <c r="G83" t="n">
         <v>8.5</v>
       </c>
+      <c r="I83" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L83" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M83" t="n">
         <v>9.5</v>
@@ -5465,6 +5573,9 @@
       <c r="P83" t="n">
         <v>1</v>
       </c>
+      <c r="R83" t="n">
+        <v>1</v>
+      </c>
       <c r="U83" t="n">
         <v>1</v>
       </c>
@@ -5474,32 +5585,23 @@
       <c r="W83" t="n">
         <v>1</v>
       </c>
-      <c r="X83" t="n">
-        <v>1</v>
-      </c>
       <c r="Y83" t="n">
         <v>1</v>
       </c>
       <c r="Z83" t="n">
         <v>1</v>
       </c>
-      <c r="AB83" t="n">
-        <v>1</v>
-      </c>
       <c r="AC83" t="n">
         <v>1</v>
       </c>
       <c r="AD83" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE83" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Iones</t>
+          <t>Masa atómica relativa</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5513,46 +5615,22 @@
       <c r="D84" t="n">
         <v>10</v>
       </c>
-      <c r="F84" t="n">
-        <v>8</v>
-      </c>
       <c r="G84" t="n">
         <v>8.5</v>
       </c>
-      <c r="I84" t="n">
-        <v>8</v>
-      </c>
-      <c r="K84" t="n">
-        <v>9</v>
-      </c>
       <c r="L84" t="n">
         <v>9.5</v>
       </c>
       <c r="M84" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P84" t="n">
         <v>1</v>
       </c>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
-      <c r="T84" t="n">
-        <v>1</v>
-      </c>
       <c r="U84" t="n">
         <v>1</v>
       </c>
-      <c r="V84" t="n">
-        <v>1</v>
-      </c>
       <c r="W84" t="n">
-        <v>1</v>
-      </c>
-      <c r="X84" t="n">
         <v>1</v>
       </c>
       <c r="Y84" t="n">
@@ -5571,7 +5649,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Isótopos</t>
+          <t>Masa molar</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5580,12 +5658,12 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D85" t="n">
         <v>10</v>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>8</v>
       </c>
       <c r="G85" t="n">
@@ -5600,6 +5678,9 @@
       <c r="M85" t="n">
         <v>9.5</v>
       </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
       <c r="P85" t="n">
         <v>1</v>
       </c>
@@ -5615,10 +5696,16 @@
       <c r="W85" t="n">
         <v>1</v>
       </c>
+      <c r="X85" t="n">
+        <v>1</v>
+      </c>
       <c r="Y85" t="n">
         <v>1</v>
       </c>
       <c r="Z85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB85" t="n">
         <v>1</v>
       </c>
       <c r="AC85" t="n">
@@ -5631,7 +5718,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Masa atómica relativa</t>
+          <t>Materia y materiales</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5640,33 +5727,63 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="I86" t="n">
+        <v>6</v>
+      </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
+      <c r="K86" t="n">
+        <v>8</v>
       </c>
       <c r="L86" t="n">
         <v>9.5</v>
       </c>
+      <c r="M86" t="n">
+        <v>7</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
       <c r="P86" t="n">
         <v>1</v>
       </c>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
       <c r="U86" t="n">
         <v>1</v>
       </c>
       <c r="W86" t="n">
         <v>1</v>
       </c>
+      <c r="X86" t="n">
+        <v>1</v>
+      </c>
       <c r="Y86" t="n">
         <v>1</v>
       </c>
       <c r="Z86" t="n">
         <v>1</v>
       </c>
-      <c r="AC86" t="n">
+      <c r="AA86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB86" t="n">
         <v>1</v>
       </c>
       <c r="AD86" t="n">
@@ -5676,7 +5793,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Masa molar</t>
+          <t>Reutilización y reciclaje de materiales</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5685,10 +5802,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F87" t="n">
         <v>8</v>
@@ -5697,13 +5814,19 @@
         <v>8.5</v>
       </c>
       <c r="I87" t="n">
-        <v>9.5</v>
+        <v>8</v>
+      </c>
+      <c r="J87" t="n">
+        <v>9</v>
+      </c>
+      <c r="K87" t="n">
+        <v>8</v>
       </c>
       <c r="L87" t="n">
         <v>9.5</v>
       </c>
       <c r="M87" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O87" t="n">
         <v>1</v>
@@ -5714,38 +5837,35 @@
       <c r="R87" t="n">
         <v>1</v>
       </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
       <c r="U87" t="n">
         <v>1</v>
       </c>
       <c r="V87" t="n">
         <v>1</v>
       </c>
-      <c r="W87" t="n">
-        <v>1</v>
-      </c>
-      <c r="X87" t="n">
-        <v>1</v>
-      </c>
       <c r="Y87" t="n">
         <v>1</v>
       </c>
       <c r="Z87" t="n">
         <v>1</v>
       </c>
-      <c r="AB87" t="n">
-        <v>1</v>
-      </c>
       <c r="AC87" t="n">
         <v>1</v>
       </c>
       <c r="AD87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE87" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Materia y materiales</t>
+          <t>Mezclas homogéneas y heterogéneas</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5757,23 +5877,29 @@
         <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F88" t="n">
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I88" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J88" t="n">
+        <v>7</v>
       </c>
       <c r="L88" t="n">
         <v>9.5</v>
       </c>
+      <c r="M88" t="n">
+        <v>7</v>
+      </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
@@ -5789,16 +5915,10 @@
       <c r="W88" t="n">
         <v>1</v>
       </c>
-      <c r="X88" t="n">
-        <v>1</v>
-      </c>
       <c r="Y88" t="n">
         <v>1</v>
       </c>
       <c r="Z88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA88" t="n">
         <v>1</v>
       </c>
       <c r="AB88" t="n">
@@ -5811,7 +5931,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Reutilización y reciclaje de materiales</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5820,28 +5940,34 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D89" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4</v>
       </c>
       <c r="F89" t="n">
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I89" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>7</v>
+      </c>
+      <c r="K89" t="n">
         <v>8</v>
-      </c>
-      <c r="J89" t="n">
-        <v>9</v>
       </c>
       <c r="L89" t="n">
         <v>9.5</v>
       </c>
       <c r="M89" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
@@ -5852,19 +5978,25 @@
       <c r="R89" t="n">
         <v>1</v>
       </c>
-      <c r="S89" t="n">
-        <v>1</v>
-      </c>
       <c r="U89" t="n">
         <v>1</v>
       </c>
       <c r="V89" t="n">
         <v>1</v>
       </c>
+      <c r="W89" t="n">
+        <v>1</v>
+      </c>
       <c r="Y89" t="n">
         <v>1</v>
       </c>
       <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB89" t="n">
         <v>1</v>
       </c>
       <c r="AC89" t="n">
@@ -5880,7 +6012,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Mezclas homogéneas y heterogéneas</t>
+          <t>Modelo mecanocuántico y orbitales atómicos</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5889,58 +6021,37 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
         <v>10</v>
       </c>
-      <c r="E90" t="n">
-        <v>6</v>
-      </c>
-      <c r="F90" t="n">
-        <v>8</v>
-      </c>
-      <c r="G90" t="n">
-        <v>6</v>
-      </c>
-      <c r="I90" t="n">
-        <v>4</v>
-      </c>
       <c r="L90" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O90" t="n">
-        <v>1</v>
-      </c>
-      <c r="P90" t="n">
-        <v>1</v>
-      </c>
-      <c r="R90" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U90" t="n">
         <v>1</v>
       </c>
-      <c r="W90" t="n">
-        <v>1</v>
-      </c>
       <c r="Y90" t="n">
         <v>1</v>
       </c>
       <c r="Z90" t="n">
         <v>1</v>
       </c>
-      <c r="AB90" t="n">
+      <c r="AC90" t="n">
         <v>1</v>
       </c>
       <c r="AD90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE90" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Evolución de los modelos atómicos</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5949,28 +6060,31 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
         <v>10</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G91" t="n">
         <v>6</v>
       </c>
-      <c r="I91" t="n">
-        <v>9.5</v>
+      <c r="J91" t="n">
+        <v>9</v>
+      </c>
+      <c r="K91" t="n">
+        <v>8</v>
       </c>
       <c r="L91" t="n">
         <v>9.5</v>
       </c>
       <c r="M91" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -5978,7 +6092,7 @@
       <c r="P91" t="n">
         <v>1</v>
       </c>
-      <c r="R91" t="n">
+      <c r="S91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
@@ -5994,12 +6108,6 @@
         <v>1</v>
       </c>
       <c r="Z91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB91" t="n">
         <v>1</v>
       </c>
       <c r="AC91" t="n">
@@ -6015,7 +6123,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Modelo mecanocuántico y orbitales atómicos</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6024,37 +6132,67 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D92" t="n">
         <v>10</v>
       </c>
+      <c r="F92" t="n">
+        <v>8</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I92" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L92" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M92" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
       </c>
       <c r="U92" t="n">
         <v>1</v>
       </c>
+      <c r="V92" t="n">
+        <v>1</v>
+      </c>
+      <c r="W92" t="n">
+        <v>1</v>
+      </c>
+      <c r="X92" t="n">
+        <v>1</v>
+      </c>
       <c r="Y92" t="n">
         <v>1</v>
       </c>
       <c r="Z92" t="n">
         <v>1</v>
       </c>
+      <c r="AB92" t="n">
+        <v>1</v>
+      </c>
       <c r="AC92" t="n">
         <v>1</v>
       </c>
       <c r="AD92" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE92" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Evolución de los modelos atómicos</t>
+          <t>Molaridad y unidades químicas de concentración</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6063,22 +6201,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D93" t="n">
-        <v>10</v>
-      </c>
-      <c r="E93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F93" t="n">
         <v>10.5</v>
       </c>
-      <c r="G93" t="n">
-        <v>6</v>
-      </c>
-      <c r="J93" t="n">
-        <v>9</v>
+      <c r="I93" t="n">
+        <v>9.5</v>
       </c>
       <c r="L93" t="n">
         <v>9.5</v>
@@ -6089,10 +6221,7 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="P93" t="n">
-        <v>1</v>
-      </c>
-      <c r="S93" t="n">
+      <c r="R93" t="n">
         <v>1</v>
       </c>
       <c r="U93" t="n">
@@ -6104,10 +6233,16 @@
       <c r="W93" t="n">
         <v>1</v>
       </c>
+      <c r="X93" t="n">
+        <v>1</v>
+      </c>
       <c r="Y93" t="n">
         <v>1</v>
       </c>
       <c r="Z93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB93" t="n">
         <v>1</v>
       </c>
       <c r="AC93" t="n">
@@ -6123,7 +6258,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Moléculas y fórmulas químicas</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6132,25 +6267,34 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
         <v>10</v>
       </c>
+      <c r="E94" t="n">
+        <v>7</v>
+      </c>
       <c r="F94" t="n">
         <v>8</v>
       </c>
       <c r="G94" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I94" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="J94" t="n">
+        <v>7</v>
+      </c>
+      <c r="K94" t="n">
+        <v>8</v>
       </c>
       <c r="L94" t="n">
         <v>9.5</v>
       </c>
       <c r="M94" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -6158,13 +6302,10 @@
       <c r="P94" t="n">
         <v>1</v>
       </c>
-      <c r="R94" t="n">
+      <c r="T94" t="n">
         <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>1</v>
-      </c>
-      <c r="V94" t="n">
         <v>1</v>
       </c>
       <c r="W94" t="n">
@@ -6192,7 +6333,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Molaridad y unidades químicas de concentración</t>
+          <t>Número de oxidación</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6201,13 +6342,13 @@
         </is>
       </c>
       <c r="C95" t="n">
+        <v>5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="F95" t="n">
         <v>8</v>
-      </c>
-      <c r="D95" t="n">
-        <v>9</v>
-      </c>
-      <c r="F95" t="n">
-        <v>10.5</v>
       </c>
       <c r="I95" t="n">
         <v>9.5</v>
@@ -6215,9 +6356,6 @@
       <c r="L95" t="n">
         <v>9.5</v>
       </c>
-      <c r="M95" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O95" t="n">
         <v>1</v>
       </c>
@@ -6225,12 +6363,6 @@
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>1</v>
-      </c>
-      <c r="V95" t="n">
-        <v>1</v>
-      </c>
-      <c r="W95" t="n">
         <v>1</v>
       </c>
       <c r="X95" t="n">
@@ -6258,7 +6390,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Moléculas y fórmulas químicas</t>
+          <t>Números cuánticos</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6272,62 +6404,23 @@
       <c r="D96" t="n">
         <v>10</v>
       </c>
-      <c r="E96" t="n">
-        <v>7</v>
-      </c>
-      <c r="F96" t="n">
-        <v>8</v>
-      </c>
-      <c r="G96" t="n">
-        <v>6</v>
-      </c>
-      <c r="I96" t="n">
-        <v>7</v>
-      </c>
-      <c r="K96" t="n">
-        <v>9</v>
-      </c>
       <c r="L96" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O96" t="n">
-        <v>1</v>
-      </c>
-      <c r="P96" t="n">
-        <v>1</v>
-      </c>
-      <c r="T96" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U96" t="n">
         <v>1</v>
       </c>
-      <c r="W96" t="n">
-        <v>1</v>
-      </c>
-      <c r="X96" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>1</v>
-      </c>
       <c r="AD96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE96" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Número de oxidación</t>
+          <t>Oxidación y corrosión de los metales</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6336,30 +6429,45 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D97" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F97" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="I97" t="n">
         <v>9.5</v>
       </c>
+      <c r="J97" t="n">
+        <v>9</v>
+      </c>
+      <c r="K97" t="n">
+        <v>9</v>
+      </c>
       <c r="L97" t="n">
         <v>9.5</v>
       </c>
+      <c r="M97" t="n">
+        <v>7</v>
+      </c>
       <c r="O97" t="n">
         <v>1</v>
       </c>
       <c r="R97" t="n">
         <v>1</v>
       </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" t="n">
+        <v>1</v>
+      </c>
       <c r="U97" t="n">
         <v>1</v>
       </c>
-      <c r="X97" t="n">
+      <c r="W97" t="n">
         <v>1</v>
       </c>
       <c r="Y97" t="n">
@@ -6368,23 +6476,17 @@
       <c r="Z97" t="n">
         <v>1</v>
       </c>
-      <c r="AB97" t="n">
-        <v>1</v>
-      </c>
       <c r="AC97" t="n">
         <v>1</v>
       </c>
       <c r="AD97" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE97" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Números cuánticos</t>
+          <t>Polaridad molecular</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6393,15 +6495,51 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
         <v>10</v>
       </c>
+      <c r="F98" t="n">
+        <v>8</v>
+      </c>
+      <c r="I98" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L98" t="n">
         <v>11</v>
       </c>
+      <c r="M98" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1</v>
+      </c>
       <c r="U98" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1</v>
+      </c>
+      <c r="W98" t="n">
+        <v>1</v>
+      </c>
+      <c r="X98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC98" t="n">
         <v>1</v>
       </c>
       <c r="AD98" t="n">
@@ -6414,7 +6552,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Oxidación y corrosión de los metales</t>
+          <t>Proceso de disolución y solvatación</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6426,45 +6564,27 @@
         <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F99" t="n">
         <v>10.5</v>
       </c>
-      <c r="I99" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J99" t="n">
-        <v>9</v>
-      </c>
-      <c r="K99" t="n">
-        <v>9</v>
-      </c>
-      <c r="L99" t="n">
-        <v>9.5</v>
+      <c r="G99" t="n">
+        <v>3</v>
+      </c>
+      <c r="M99" t="n">
+        <v>7</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="R99" t="n">
-        <v>1</v>
-      </c>
-      <c r="S99" t="n">
-        <v>1</v>
-      </c>
-      <c r="T99" t="n">
-        <v>1</v>
-      </c>
-      <c r="U99" t="n">
+      <c r="V99" t="n">
         <v>1</v>
       </c>
       <c r="W99" t="n">
         <v>1</v>
       </c>
-      <c r="Y99" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z99" t="n">
+      <c r="AA99" t="n">
         <v>1</v>
       </c>
       <c r="AC99" t="n">
@@ -6477,7 +6597,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Polaridad molecular</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6486,30 +6606,18 @@
         </is>
       </c>
       <c r="C100" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" t="n">
+        <v>11</v>
+      </c>
+      <c r="G100" t="n">
         <v>6</v>
-      </c>
-      <c r="D100" t="n">
-        <v>10</v>
-      </c>
-      <c r="F100" t="n">
-        <v>8</v>
-      </c>
-      <c r="I100" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L100" t="n">
-        <v>11</v>
       </c>
       <c r="M100" t="n">
         <v>9.5</v>
       </c>
-      <c r="O100" t="n">
-        <v>1</v>
-      </c>
-      <c r="R100" t="n">
-        <v>1</v>
-      </c>
-      <c r="U100" t="n">
+      <c r="P100" t="n">
         <v>1</v>
       </c>
       <c r="V100" t="n">
@@ -6518,9 +6626,6 @@
       <c r="W100" t="n">
         <v>1</v>
       </c>
-      <c r="X100" t="n">
-        <v>1</v>
-      </c>
       <c r="Y100" t="n">
         <v>1</v>
       </c>
@@ -6534,16 +6639,13 @@
         <v>1</v>
       </c>
       <c r="AD100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE100" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Proceso de disolución y solvatación</t>
+          <t>Propiedades coligativas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6552,43 +6654,31 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D101" t="n">
         <v>10</v>
       </c>
-      <c r="F101" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G101" t="n">
-        <v>3</v>
-      </c>
-      <c r="M101" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
-        <v>1</v>
-      </c>
-      <c r="W101" t="n">
+      <c r="Z101" t="n">
         <v>1</v>
       </c>
       <c r="AA101" t="n">
         <v>1</v>
       </c>
+      <c r="AB101" t="n">
+        <v>1</v>
+      </c>
       <c r="AC101" t="n">
         <v>1</v>
       </c>
-      <c r="AD101" t="n">
+      <c r="AE101" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Propiedades físicas de los materiales</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6597,21 +6687,42 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
         <v>11</v>
       </c>
+      <c r="E102" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" t="n">
+        <v>8</v>
+      </c>
       <c r="G102" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="I102" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J102" t="n">
+        <v>7</v>
+      </c>
+      <c r="L102" t="n">
+        <v>9.5</v>
       </c>
       <c r="M102" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
       </c>
-      <c r="V102" t="n">
+      <c r="R102" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" t="n">
         <v>1</v>
       </c>
       <c r="W102" t="n">
@@ -6623,20 +6734,20 @@
       <c r="Z102" t="n">
         <v>1</v>
       </c>
-      <c r="AB102" t="n">
-        <v>1</v>
-      </c>
       <c r="AC102" t="n">
         <v>1</v>
       </c>
       <c r="AD102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE102" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Propiedades físicas y químicas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6645,21 +6756,69 @@
         </is>
       </c>
       <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>9</v>
+      </c>
+      <c r="F103" t="n">
         <v>8</v>
       </c>
-      <c r="D103" t="n">
-        <v>10</v>
+      <c r="G103" t="n">
+        <v>6</v>
+      </c>
+      <c r="I103" t="n">
+        <v>6</v>
+      </c>
+      <c r="J103" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" t="n">
+        <v>8</v>
+      </c>
+      <c r="L103" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M103" t="n">
+        <v>7</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>1</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" t="n">
+        <v>1</v>
+      </c>
+      <c r="V103" t="n">
+        <v>1</v>
+      </c>
+      <c r="W103" t="n">
+        <v>1</v>
+      </c>
+      <c r="X103" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>1</v>
       </c>
       <c r="Z103" t="n">
         <v>1</v>
       </c>
-      <c r="AA103" t="n">
-        <v>1</v>
-      </c>
       <c r="AB103" t="n">
         <v>1</v>
       </c>
       <c r="AC103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD103" t="n">
         <v>1</v>
       </c>
       <c r="AE103" t="n">
@@ -6669,7 +6828,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Propiedades físicas de los materiales</t>
+          <t>Propiedades periódicas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6678,26 +6837,38 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F104" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I104" t="n">
         <v>9.5</v>
       </c>
+      <c r="J104" t="n">
+        <v>9</v>
+      </c>
+      <c r="K104" t="n">
+        <v>8</v>
+      </c>
       <c r="L104" t="n">
         <v>9.5</v>
       </c>
+      <c r="M104" t="n">
+        <v>7</v>
+      </c>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
       <c r="O104" t="n">
         <v>1</v>
       </c>
@@ -6707,16 +6878,28 @@
       <c r="R104" t="n">
         <v>1</v>
       </c>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
       <c r="U104" t="n">
         <v>1</v>
       </c>
       <c r="W104" t="n">
         <v>1</v>
       </c>
+      <c r="X104" t="n">
+        <v>1</v>
+      </c>
       <c r="Y104" t="n">
         <v>1</v>
       </c>
       <c r="Z104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB104" t="n">
         <v>1</v>
       </c>
       <c r="AC104" t="n">
@@ -6732,7 +6915,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Propiedades físicas y químicas</t>
+          <t>Propiedades singulares del agua</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6741,56 +6924,32 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
         <v>9</v>
       </c>
-      <c r="F105" t="n">
-        <v>8</v>
-      </c>
       <c r="G105" t="n">
         <v>6</v>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
-      </c>
-      <c r="K105" t="n">
+        <v>3</v>
+      </c>
+      <c r="J105" t="n">
         <v>9</v>
       </c>
       <c r="L105" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M105" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O105" t="n">
-        <v>1</v>
-      </c>
-      <c r="P105" t="n">
-        <v>1</v>
-      </c>
-      <c r="R105" t="n">
-        <v>1</v>
-      </c>
-      <c r="T105" t="n">
+        <v>11</v>
+      </c>
+      <c r="S105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="n">
         <v>1</v>
       </c>
-      <c r="V105" t="n">
-        <v>1</v>
-      </c>
       <c r="W105" t="n">
         <v>1</v>
       </c>
-      <c r="X105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>1</v>
-      </c>
       <c r="Z105" t="n">
         <v>1</v>
       </c>
@@ -6801,16 +6960,13 @@
         <v>1</v>
       </c>
       <c r="AD105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE105" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Propiedades periódicas</t>
+          <t>Química de los carbohidratos</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6819,47 +6975,35 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D106" t="n">
         <v>10</v>
       </c>
-      <c r="E106" t="n">
-        <v>9</v>
-      </c>
       <c r="F106" t="n">
         <v>10.5</v>
       </c>
-      <c r="G106" t="n">
-        <v>6</v>
-      </c>
       <c r="I106" t="n">
         <v>9.5</v>
       </c>
-      <c r="J106" t="n">
-        <v>9</v>
-      </c>
       <c r="L106" t="n">
         <v>9.5</v>
       </c>
-      <c r="N106" t="n">
-        <v>1</v>
+      <c r="M106" t="n">
+        <v>9.5</v>
       </c>
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="P106" t="n">
-        <v>1</v>
-      </c>
       <c r="R106" t="n">
         <v>1</v>
       </c>
-      <c r="S106" t="n">
-        <v>1</v>
-      </c>
       <c r="U106" t="n">
         <v>1</v>
       </c>
+      <c r="V106" t="n">
+        <v>1</v>
+      </c>
       <c r="W106" t="n">
         <v>1</v>
       </c>
@@ -6873,25 +7017,13 @@
         <v>1</v>
       </c>
       <c r="AA106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE106" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Propiedades singulares del agua</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6900,39 +7032,33 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D107" t="n">
-        <v>9</v>
-      </c>
-      <c r="G107" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="F107" t="n">
+        <v>10.5</v>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
-      </c>
-      <c r="J107" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="L107" t="n">
-        <v>11</v>
-      </c>
-      <c r="S107" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="R107" t="n">
         <v>1</v>
       </c>
       <c r="U107" t="n">
         <v>1</v>
       </c>
-      <c r="W107" t="n">
-        <v>1</v>
-      </c>
       <c r="Z107" t="n">
         <v>1</v>
       </c>
-      <c r="AB107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC107" t="n">
+      <c r="AA107" t="n">
         <v>1</v>
       </c>
       <c r="AD107" t="n">
@@ -6942,7 +7068,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Química de los carbohidratos</t>
+          <t>Química descriptiva de los elementos</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6951,38 +7077,44 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
         <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G108" t="n">
+        <v>6</v>
       </c>
       <c r="I108" t="n">
         <v>9.5</v>
       </c>
+      <c r="J108" t="n">
+        <v>9</v>
+      </c>
       <c r="L108" t="n">
         <v>9.5</v>
       </c>
       <c r="M108" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O108" t="n">
         <v>1</v>
       </c>
+      <c r="P108" t="n">
+        <v>1</v>
+      </c>
       <c r="R108" t="n">
         <v>1</v>
       </c>
+      <c r="S108" t="n">
+        <v>1</v>
+      </c>
       <c r="U108" t="n">
         <v>1</v>
       </c>
-      <c r="V108" t="n">
-        <v>1</v>
-      </c>
-      <c r="W108" t="n">
-        <v>1</v>
-      </c>
       <c r="X108" t="n">
         <v>1</v>
       </c>
@@ -6993,13 +7125,22 @@
         <v>1</v>
       </c>
       <c r="AA108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE108" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Radiactividad y emisiones nucleares</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7008,43 +7149,34 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D109" t="n">
         <v>10</v>
       </c>
-      <c r="F109" t="n">
-        <v>10.5</v>
+      <c r="E109" t="n">
+        <v>8</v>
+      </c>
+      <c r="G109" t="n">
+        <v>8.5</v>
       </c>
       <c r="I109" t="n">
         <v>9.5</v>
       </c>
-      <c r="L109" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O109" t="n">
-        <v>1</v>
-      </c>
       <c r="R109" t="n">
         <v>1</v>
       </c>
-      <c r="U109" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD109" t="n">
+      <c r="W109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC109" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Química descriptiva de los elementos</t>
+          <t>Factores que afectan la rapidez de reacción</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7053,41 +7185,44 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D110" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E110" t="n">
+        <v>9</v>
       </c>
       <c r="F110" t="n">
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>6</v>
-      </c>
-      <c r="I110" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J110" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="L110" t="n">
         <v>9.5</v>
       </c>
+      <c r="M110" t="n">
+        <v>7</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1</v>
+      </c>
       <c r="O110" t="n">
         <v>1</v>
       </c>
       <c r="P110" t="n">
         <v>1</v>
       </c>
-      <c r="R110" t="n">
-        <v>1</v>
-      </c>
-      <c r="S110" t="n">
-        <v>1</v>
-      </c>
       <c r="U110" t="n">
         <v>1</v>
       </c>
+      <c r="V110" t="n">
+        <v>1</v>
+      </c>
+      <c r="W110" t="n">
+        <v>1</v>
+      </c>
       <c r="X110" t="n">
         <v>1</v>
       </c>
@@ -7098,6 +7233,9 @@
         <v>1</v>
       </c>
       <c r="AA110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB110" t="n">
         <v>1</v>
       </c>
       <c r="AC110" t="n">
@@ -7113,7 +7251,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Radiactividad y emisiones nucleares</t>
+          <t>Reacción química y sus evidencias</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7122,34 +7260,79 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
         <v>10</v>
       </c>
       <c r="E111" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" t="n">
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="I111" t="n">
+        <v>5</v>
+      </c>
+      <c r="J111" t="n">
+        <v>7</v>
+      </c>
+      <c r="K111" t="n">
+        <v>9</v>
+      </c>
+      <c r="L111" t="n">
         <v>9.5</v>
       </c>
+      <c r="M111" t="n">
+        <v>7</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
       <c r="R111" t="n">
         <v>1</v>
       </c>
+      <c r="S111" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" t="n">
+        <v>1</v>
+      </c>
       <c r="W111" t="n">
         <v>1</v>
       </c>
+      <c r="Y111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>1</v>
+      </c>
       <c r="AC111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE111" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Factores que afectan la rapidez de reacción</t>
+          <t>Métodos físicos de separación de mezclas</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7158,28 +7341,31 @@
         </is>
       </c>
       <c r="C112" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="n">
         <v>6</v>
-      </c>
-      <c r="D112" t="n">
-        <v>9</v>
-      </c>
-      <c r="E112" t="n">
-        <v>9</v>
       </c>
       <c r="F112" t="n">
         <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>8.5</v>
+        <v>3</v>
+      </c>
+      <c r="I112" t="n">
+        <v>4</v>
+      </c>
+      <c r="J112" t="n">
+        <v>7</v>
       </c>
       <c r="L112" t="n">
         <v>9.5</v>
       </c>
       <c r="M112" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N112" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O112" t="n">
         <v>1</v>
@@ -7187,6 +7373,9 @@
       <c r="P112" t="n">
         <v>1</v>
       </c>
+      <c r="R112" t="n">
+        <v>1</v>
+      </c>
       <c r="U112" t="n">
         <v>1</v>
       </c>
@@ -7196,19 +7385,10 @@
       <c r="W112" t="n">
         <v>1</v>
       </c>
-      <c r="X112" t="n">
-        <v>1</v>
-      </c>
       <c r="Y112" t="n">
         <v>1</v>
       </c>
       <c r="Z112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB112" t="n">
         <v>1</v>
       </c>
       <c r="AC112" t="n">
@@ -7224,7 +7404,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Reacción química y sus evidencias</t>
+          <t>Sólidos cristalinos y amorfos</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7233,46 +7413,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
         <v>10</v>
       </c>
-      <c r="E113" t="n">
-        <v>5</v>
-      </c>
-      <c r="F113" t="n">
-        <v>8</v>
-      </c>
-      <c r="G113" t="n">
-        <v>3</v>
-      </c>
-      <c r="I113" t="n">
-        <v>5</v>
-      </c>
-      <c r="J113" t="n">
-        <v>9</v>
-      </c>
-      <c r="K113" t="n">
-        <v>9</v>
-      </c>
       <c r="L113" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O113" t="n">
-        <v>1</v>
-      </c>
-      <c r="P113" t="n">
-        <v>1</v>
-      </c>
-      <c r="R113" t="n">
-        <v>1</v>
-      </c>
-      <c r="S113" t="n">
-        <v>1</v>
-      </c>
-      <c r="T113" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U113" t="n">
         <v>1</v>
@@ -7286,6 +7433,9 @@
       <c r="Z113" t="n">
         <v>1</v>
       </c>
+      <c r="AA113" t="n">
+        <v>1</v>
+      </c>
       <c r="AB113" t="n">
         <v>1</v>
       </c>
@@ -7293,16 +7443,13 @@
         <v>1</v>
       </c>
       <c r="AD113" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE113" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Métodos físicos de separación de mezclas</t>
+          <t>Solubilidad y disoluciones saturadas</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7311,14 +7458,11 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
         <v>10</v>
       </c>
-      <c r="E114" t="n">
-        <v>6</v>
-      </c>
       <c r="F114" t="n">
         <v>8</v>
       </c>
@@ -7328,6 +7472,9 @@
       <c r="I114" t="n">
         <v>4</v>
       </c>
+      <c r="J114" t="n">
+        <v>7</v>
+      </c>
       <c r="L114" t="n">
         <v>9.5</v>
       </c>
@@ -7337,9 +7484,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="P114" t="n">
-        <v>1</v>
-      </c>
       <c r="R114" t="n">
         <v>1</v>
       </c>
@@ -7352,10 +7496,16 @@
       <c r="W114" t="n">
         <v>1</v>
       </c>
+      <c r="X114" t="n">
+        <v>1</v>
+      </c>
       <c r="Y114" t="n">
         <v>1</v>
       </c>
       <c r="Z114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA114" t="n">
         <v>1</v>
       </c>
       <c r="AC114" t="n">
@@ -7371,7 +7521,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sólidos cristalinos y amorfos</t>
+          <t>Sustancias puras: elementos y compuestos</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7383,14 +7533,53 @@
         <v>8</v>
       </c>
       <c r="D115" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E115" t="n">
+        <v>6</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8</v>
+      </c>
+      <c r="G115" t="n">
+        <v>6</v>
+      </c>
+      <c r="I115" t="n">
+        <v>7</v>
+      </c>
+      <c r="J115" t="n">
+        <v>7</v>
+      </c>
+      <c r="K115" t="n">
+        <v>8</v>
       </c>
       <c r="L115" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M115" t="n">
+        <v>7</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1</v>
       </c>
       <c r="U115" t="n">
         <v>1</v>
       </c>
+      <c r="V115" t="n">
+        <v>1</v>
+      </c>
       <c r="W115" t="n">
         <v>1</v>
       </c>
@@ -7398,12 +7587,6 @@
         <v>1</v>
       </c>
       <c r="Z115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB115" t="n">
         <v>1</v>
       </c>
       <c r="AC115" t="n">
@@ -7416,7 +7599,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Solubilidad y disoluciones saturadas</t>
+          <t>Organización de la tabla periódica</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7425,30 +7608,51 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D116" t="n">
         <v>10</v>
       </c>
+      <c r="E116" t="n">
+        <v>9</v>
+      </c>
       <c r="F116" t="n">
         <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I116" t="n">
-        <v>4</v>
+        <v>9.5</v>
+      </c>
+      <c r="J116" t="n">
+        <v>7</v>
+      </c>
+      <c r="K116" t="n">
+        <v>8</v>
       </c>
       <c r="L116" t="n">
         <v>9.5</v>
       </c>
       <c r="M116" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
       </c>
       <c r="O116" t="n">
         <v>1</v>
       </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
       <c r="R116" t="n">
+        <v>1</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" t="n">
         <v>1</v>
       </c>
       <c r="U116" t="n">
@@ -7485,7 +7689,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sustancias puras: elementos y compuestos</t>
+          <t>Tipo de enlace y propiedades de las sustancias</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7494,34 +7698,28 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>9</v>
-      </c>
-      <c r="E117" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F117" t="n">
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J117" t="n">
         <v>9</v>
       </c>
-      <c r="K117" t="n">
-        <v>9</v>
-      </c>
       <c r="L117" t="n">
         <v>9.5</v>
       </c>
       <c r="M117" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
@@ -7535,9 +7733,6 @@
       <c r="S117" t="n">
         <v>1</v>
       </c>
-      <c r="T117" t="n">
-        <v>1</v>
-      </c>
       <c r="U117" t="n">
         <v>1</v>
       </c>
@@ -7547,23 +7742,35 @@
       <c r="W117" t="n">
         <v>1</v>
       </c>
+      <c r="X117" t="n">
+        <v>1</v>
+      </c>
       <c r="Y117" t="n">
         <v>1</v>
       </c>
       <c r="Z117" t="n">
         <v>1</v>
       </c>
+      <c r="AA117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>1</v>
+      </c>
       <c r="AC117" t="n">
         <v>1</v>
       </c>
       <c r="AD117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE117" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Organización de la tabla periódica</t>
+          <t>Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7572,7 +7779,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D118" t="n">
         <v>10</v>
@@ -7587,10 +7794,7 @@
         <v>6</v>
       </c>
       <c r="I118" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J118" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K118" t="n">
         <v>9</v>
@@ -7598,9 +7802,6 @@
       <c r="L118" t="n">
         <v>9.5</v>
       </c>
-      <c r="M118" t="n">
-        <v>9.5</v>
-      </c>
       <c r="N118" t="n">
         <v>1</v>
       </c>
@@ -7610,50 +7811,32 @@
       <c r="P118" t="n">
         <v>1</v>
       </c>
-      <c r="R118" t="n">
-        <v>1</v>
-      </c>
-      <c r="S118" t="n">
-        <v>1</v>
-      </c>
       <c r="T118" t="n">
         <v>1</v>
       </c>
       <c r="U118" t="n">
         <v>1</v>
       </c>
-      <c r="V118" t="n">
-        <v>1</v>
-      </c>
       <c r="W118" t="n">
         <v>1</v>
       </c>
       <c r="X118" t="n">
         <v>1</v>
       </c>
-      <c r="Y118" t="n">
-        <v>1</v>
-      </c>
       <c r="Z118" t="n">
         <v>1</v>
       </c>
-      <c r="AA118" t="n">
-        <v>1</v>
-      </c>
       <c r="AC118" t="n">
         <v>1</v>
       </c>
       <c r="AD118" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE118" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Tipo de enlace y propiedades de las sustancias</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7662,7 +7845,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
         <v>10</v>
@@ -7673,17 +7856,8 @@
       <c r="G119" t="n">
         <v>8.5</v>
       </c>
-      <c r="I119" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J119" t="n">
-        <v>9</v>
-      </c>
-      <c r="L119" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M119" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O119" t="n">
         <v>1</v>
@@ -7691,15 +7865,6 @@
       <c r="P119" t="n">
         <v>1</v>
       </c>
-      <c r="R119" t="n">
-        <v>1</v>
-      </c>
-      <c r="S119" t="n">
-        <v>1</v>
-      </c>
-      <c r="U119" t="n">
-        <v>1</v>
-      </c>
       <c r="V119" t="n">
         <v>1</v>
       </c>
@@ -7715,16 +7880,7 @@
       <c r="Z119" t="n">
         <v>1</v>
       </c>
-      <c r="AA119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB119" t="n">
-        <v>1</v>
-      </c>
       <c r="AC119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD119" t="n">
         <v>1</v>
       </c>
       <c r="AE119" t="n">
@@ -7734,49 +7890,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Clasificación de las reacciones químicas</t>
+          <t>Constante de equilibrio</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D120" t="n">
-        <v>10</v>
-      </c>
-      <c r="E120" t="n">
         <v>9</v>
       </c>
-      <c r="F120" t="n">
-        <v>8</v>
-      </c>
-      <c r="G120" t="n">
-        <v>6</v>
-      </c>
-      <c r="I120" t="n">
-        <v>7</v>
-      </c>
-      <c r="K120" t="n">
-        <v>9</v>
-      </c>
       <c r="L120" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N120" t="n">
-        <v>1</v>
-      </c>
-      <c r="O120" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" t="n">
-        <v>1</v>
-      </c>
-      <c r="T120" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U120" t="n">
         <v>1</v>
@@ -7787,64 +7916,58 @@
       <c r="X120" t="n">
         <v>1</v>
       </c>
+      <c r="Y120" t="n">
+        <v>1</v>
+      </c>
       <c r="Z120" t="n">
         <v>1</v>
       </c>
+      <c r="AA120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>1</v>
+      </c>
       <c r="AC120" t="n">
         <v>1</v>
       </c>
       <c r="AD120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE120" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D121" t="n">
         <v>10</v>
       </c>
-      <c r="F121" t="n">
-        <v>8</v>
-      </c>
-      <c r="G121" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M121" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O121" t="n">
-        <v>1</v>
-      </c>
-      <c r="P121" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" t="n">
-        <v>1</v>
-      </c>
-      <c r="W121" t="n">
-        <v>1</v>
-      </c>
-      <c r="X121" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z121" t="n">
+      <c r="J121" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB121" t="n">
         <v>1</v>
       </c>
       <c r="AC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD121" t="n">
         <v>1</v>
       </c>
       <c r="AE121" t="n">
@@ -7854,7 +7977,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Constante de equilibrio</t>
+          <t>Hidrólisis de sales y disoluciones amortiguadoras</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7874,16 +7997,10 @@
       <c r="U122" t="n">
         <v>1</v>
       </c>
-      <c r="W122" t="n">
-        <v>1</v>
-      </c>
       <c r="X122" t="n">
         <v>1</v>
       </c>
       <c r="Y122" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z122" t="n">
         <v>1</v>
       </c>
       <c r="AA122" t="n">
@@ -7905,7 +8022,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Energía de Gibbs y espontaneidad</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7919,26 +8036,32 @@
       <c r="D123" t="n">
         <v>10</v>
       </c>
+      <c r="W123" t="n">
+        <v>1</v>
+      </c>
+      <c r="X123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>1</v>
+      </c>
       <c r="AA123" t="n">
         <v>1</v>
       </c>
       <c r="AB123" t="n">
         <v>1</v>
       </c>
-      <c r="AC123" t="n">
-        <v>1</v>
-      </c>
       <c r="AD123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE123" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Hidrólisis de sales y disoluciones amortiguadoras</t>
+          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7947,10 +8070,10 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L124" t="n">
         <v>11</v>
@@ -7961,18 +8084,6 @@
       <c r="X124" t="n">
         <v>1</v>
       </c>
-      <c r="Y124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC124" t="n">
-        <v>1</v>
-      </c>
       <c r="AD124" t="n">
         <v>1</v>
       </c>
@@ -7983,7 +8094,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Energía de Gibbs y espontaneidad</t>
+          <t>Entropía</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7997,19 +8108,10 @@
       <c r="D125" t="n">
         <v>10</v>
       </c>
-      <c r="W125" t="n">
-        <v>1</v>
-      </c>
       <c r="X125" t="n">
         <v>1</v>
       </c>
       <c r="Y125" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA125" t="n">
         <v>1</v>
       </c>
       <c r="AB125" t="n">
@@ -8022,7 +8124,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
+          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8036,26 +8138,20 @@
       <c r="D126" t="n">
         <v>10</v>
       </c>
-      <c r="L126" t="n">
-        <v>11</v>
-      </c>
-      <c r="U126" t="n">
-        <v>1</v>
-      </c>
-      <c r="X126" t="n">
+      <c r="Y126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z126" t="n">
         <v>1</v>
       </c>
       <c r="AD126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE126" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Entropía</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8069,23 +8165,35 @@
       <c r="D127" t="n">
         <v>10</v>
       </c>
-      <c r="X127" t="n">
+      <c r="I127" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1</v>
+      </c>
+      <c r="W127" t="n">
         <v>1</v>
       </c>
       <c r="Y127" t="n">
         <v>1</v>
       </c>
-      <c r="AB127" t="n">
+      <c r="Z127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC127" t="n">
         <v>1</v>
       </c>
       <c r="AD127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE127" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8099,20 +8207,41 @@
       <c r="D128" t="n">
         <v>10</v>
       </c>
+      <c r="L128" t="n">
+        <v>11</v>
+      </c>
+      <c r="M128" t="n">
+        <v>7</v>
+      </c>
+      <c r="U128" t="n">
+        <v>1</v>
+      </c>
+      <c r="X128" t="n">
+        <v>1</v>
+      </c>
       <c r="Y128" t="n">
         <v>1</v>
       </c>
       <c r="Z128" t="n">
         <v>1</v>
       </c>
+      <c r="AA128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>1</v>
+      </c>
       <c r="AD128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE128" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8121,18 +8250,18 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D129" t="n">
-        <v>10</v>
-      </c>
-      <c r="I129" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R129" t="n">
-        <v>1</v>
-      </c>
-      <c r="W129" t="n">
+        <v>11</v>
+      </c>
+      <c r="L129" t="n">
+        <v>11</v>
+      </c>
+      <c r="U129" t="n">
+        <v>1</v>
+      </c>
+      <c r="X129" t="n">
         <v>1</v>
       </c>
       <c r="Y129" t="n">
@@ -8141,20 +8270,14 @@
       <c r="Z129" t="n">
         <v>1</v>
       </c>
-      <c r="AC129" t="n">
-        <v>1</v>
-      </c>
       <c r="AD129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE129" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Hibridación de orbitales</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8183,12 +8306,6 @@
       <c r="Z130" t="n">
         <v>1</v>
       </c>
-      <c r="AA130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>1</v>
-      </c>
       <c r="AD130" t="n">
         <v>1</v>
       </c>
@@ -8199,7 +8316,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Fundamentos de la reactividad orgánica</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8208,17 +8325,32 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D131" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="G131" t="n">
+        <v>8.5</v>
       </c>
       <c r="L131" t="n">
         <v>11</v>
       </c>
+      <c r="M131" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P131" t="n">
+        <v>1</v>
+      </c>
       <c r="U131" t="n">
         <v>1</v>
       </c>
+      <c r="V131" t="n">
+        <v>1</v>
+      </c>
+      <c r="W131" t="n">
+        <v>1</v>
+      </c>
       <c r="X131" t="n">
         <v>1</v>
       </c>
@@ -8228,14 +8360,26 @@
       <c r="Z131" t="n">
         <v>1</v>
       </c>
+      <c r="AA131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1</v>
+      </c>
       <c r="AD131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE131" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Hibridación de orbitales</t>
+          <t>Ley de velocidad, orden de reacción y ecuación de Arrhenius</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8264,6 +8408,12 @@
       <c r="Z132" t="n">
         <v>1</v>
       </c>
+      <c r="AB132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1</v>
+      </c>
       <c r="AD132" t="n">
         <v>1</v>
       </c>
@@ -8274,7 +8424,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ley de velocidad, orden de reacción y ecuación de Arrhenius</t>
+          <t>Mecanismos de reacción</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8288,12 +8438,6 @@
       <c r="D133" t="n">
         <v>10</v>
       </c>
-      <c r="L133" t="n">
-        <v>11</v>
-      </c>
-      <c r="U133" t="n">
-        <v>1</v>
-      </c>
       <c r="X133" t="n">
         <v>1</v>
       </c>
@@ -8303,23 +8447,17 @@
       <c r="Z133" t="n">
         <v>1</v>
       </c>
-      <c r="AB133" t="n">
-        <v>1</v>
-      </c>
       <c r="AC133" t="n">
         <v>1</v>
       </c>
       <c r="AD133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE133" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Leyes de los gases</t>
+          <t>Nanomateriales y manufactura molecular</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8328,33 +8466,21 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D134" t="n">
-        <v>10</v>
-      </c>
-      <c r="M134" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V134" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="G134" t="n">
+        <v>8.5</v>
       </c>
       <c r="W134" t="n">
         <v>1</v>
       </c>
+      <c r="Y134" t="n">
+        <v>1</v>
+      </c>
       <c r="Z134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD134" t="n">
         <v>1</v>
       </c>
       <c r="AE134" t="n">
@@ -8364,7 +8490,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Mecanismos de reacción</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8373,10 +8499,31 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D135" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F135" t="n">
+        <v>8</v>
+      </c>
+      <c r="G135" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I135" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
+      <c r="R135" t="n">
+        <v>1</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1</v>
       </c>
       <c r="X135" t="n">
         <v>1</v>
@@ -8387,17 +8534,23 @@
       <c r="Z135" t="n">
         <v>1</v>
       </c>
+      <c r="AB135" t="n">
+        <v>1</v>
+      </c>
       <c r="AC135" t="n">
         <v>1</v>
       </c>
       <c r="AD135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE135" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nanomateriales y manufactura molecular</t>
+          <t>Producto de solubilidad (Kps)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8411,16 +8564,13 @@
       <c r="D136" t="n">
         <v>11</v>
       </c>
-      <c r="G136" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W136" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z136" t="n">
+      <c r="X136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="n">
         <v>1</v>
       </c>
       <c r="AE136" t="n">
@@ -8430,7 +8580,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Producto de solubilidad (Kps)</t>
+          <t>Química de los ácidos nucleicos</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8439,28 +8589,28 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D137" t="n">
-        <v>11</v>
-      </c>
-      <c r="X137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE137" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB137" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Química de los ácidos nucleicos</t>
+          <t>Rendimiento de una reacción</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8474,23 +8624,38 @@
       <c r="D138" t="n">
         <v>10</v>
       </c>
+      <c r="F138" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1</v>
+      </c>
+      <c r="X138" t="n">
+        <v>1</v>
+      </c>
       <c r="Y138" t="n">
         <v>1</v>
       </c>
       <c r="Z138" t="n">
         <v>1</v>
       </c>
-      <c r="AA138" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB138" t="n">
+      <c r="AC138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE138" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Rendimiento de una reacción</t>
+          <t>Resonancia y carga formal</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8504,38 +8669,23 @@
       <c r="D139" t="n">
         <v>10</v>
       </c>
-      <c r="F139" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O139" t="n">
-        <v>1</v>
-      </c>
-      <c r="W139" t="n">
-        <v>1</v>
-      </c>
       <c r="X139" t="n">
         <v>1</v>
       </c>
       <c r="Y139" t="n">
         <v>1</v>
       </c>
-      <c r="Z139" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC139" t="n">
+      <c r="AA139" t="n">
         <v>1</v>
       </c>
       <c r="AD139" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE139" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Resonancia y carga formal</t>
+          <t>Síntesis química y rutas de reacción</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8549,16 +8699,43 @@
       <c r="D140" t="n">
         <v>10</v>
       </c>
+      <c r="F140" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L140" t="n">
+        <v>11</v>
+      </c>
+      <c r="O140" t="n">
+        <v>1</v>
+      </c>
+      <c r="U140" t="n">
+        <v>1</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1</v>
+      </c>
       <c r="X140" t="n">
         <v>1</v>
       </c>
       <c r="Y140" t="n">
         <v>1</v>
       </c>
+      <c r="Z140" t="n">
+        <v>1</v>
+      </c>
       <c r="AA140" t="n">
         <v>1</v>
       </c>
+      <c r="AB140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1</v>
+      </c>
       <c r="AD140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE140" t="n">
         <v>1</v>
       </c>
     </row>

--- a/internacional/Contraste_quimica.xlsx
+++ b/internacional/Contraste_quimica.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE140"/>
+  <dimension ref="A1:AE141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3807,22 +3807,16 @@
         <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F58" t="n">
         <v>10.5</v>
       </c>
-      <c r="G58" t="n">
-        <v>8.5</v>
-      </c>
       <c r="I58" t="n">
         <v>9.5</v>
       </c>
-      <c r="J58" t="n">
-        <v>9</v>
-      </c>
       <c r="L58" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M58" t="n">
         <v>9.5</v>
@@ -3830,15 +3824,9 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
       <c r="R58" t="n">
         <v>1</v>
       </c>
-      <c r="S58" t="n">
-        <v>1</v>
-      </c>
       <c r="U58" t="n">
         <v>1</v>
       </c>
@@ -3863,13 +3851,7 @@
       <c r="AB58" t="n">
         <v>1</v>
       </c>
-      <c r="AC58" t="n">
-        <v>1</v>
-      </c>
       <c r="AD58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4286,24 +4268,15 @@
       <c r="I64" t="n">
         <v>5</v>
       </c>
-      <c r="K64" t="n">
-        <v>9</v>
-      </c>
       <c r="L64" t="n">
         <v>9.5</v>
       </c>
-      <c r="M64" t="n">
-        <v>7</v>
-      </c>
       <c r="O64" t="n">
         <v>1</v>
       </c>
       <c r="P64" t="n">
         <v>1</v>
       </c>
-      <c r="T64" t="n">
-        <v>1</v>
-      </c>
       <c r="U64" t="n">
         <v>1</v>
       </c>
@@ -4311,9 +4284,6 @@
         <v>1</v>
       </c>
       <c r="X64" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y64" t="n">
         <v>1</v>
       </c>
       <c r="Z64" t="n">
@@ -4392,7 +4362,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Configuración electrónica</t>
+          <t>Densidad y flotación</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4401,12 +4371,9 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
-      </c>
-      <c r="E66" t="n">
         <v>9</v>
       </c>
       <c r="F66" t="n">
@@ -4415,20 +4382,14 @@
       <c r="G66" t="n">
         <v>8.5</v>
       </c>
-      <c r="I66" t="n">
-        <v>9.5</v>
-      </c>
       <c r="J66" t="n">
-        <v>9</v>
-      </c>
-      <c r="K66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L66" t="n">
         <v>9.5</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
+      <c r="M66" t="n">
+        <v>7</v>
       </c>
       <c r="O66" t="n">
         <v>1</v>
@@ -4436,44 +4397,23 @@
       <c r="P66" t="n">
         <v>1</v>
       </c>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1</v>
-      </c>
       <c r="U66" t="n">
         <v>1</v>
       </c>
-      <c r="W66" t="n">
-        <v>1</v>
-      </c>
-      <c r="X66" t="n">
-        <v>1</v>
-      </c>
       <c r="Y66" t="n">
         <v>1</v>
       </c>
       <c r="Z66" t="n">
         <v>1</v>
       </c>
-      <c r="AA66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1</v>
-      </c>
       <c r="AD66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE66" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Densidad y flotación</t>
+          <t>Disoluciones, coloides y suspensiones</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4482,49 +4422,37 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F67" t="n">
         <v>8</v>
       </c>
-      <c r="G67" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J67" t="n">
-        <v>7</v>
-      </c>
-      <c r="L67" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M67" t="n">
         <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="P67" t="n">
-        <v>1</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y67" t="n">
+      <c r="V67" t="n">
         <v>1</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
-      <c r="AD67" t="n">
+      <c r="AA67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC67" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Disoluciones, coloides y suspensiones</t>
+          <t>Distribución electrónica por niveles (modelo de capas)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4533,30 +4461,66 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
         <v>10</v>
       </c>
+      <c r="E68" t="n">
+        <v>9</v>
+      </c>
       <c r="F68" t="n">
         <v>8</v>
       </c>
-      <c r="M68" t="n">
-        <v>7</v>
+      <c r="G68" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>9</v>
+      </c>
+      <c r="K68" t="n">
+        <v>8</v>
+      </c>
+      <c r="L68" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="V68" t="n">
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="n">
         <v>1</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
       </c>
-      <c r="AA68" t="n">
-        <v>1</v>
-      </c>
       <c r="AC68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD68" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7890,7 +7854,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Constante de equilibrio</t>
+          <t>Configuración electrónica por orbitales</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7899,10 +7863,10 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L120" t="n">
         <v>11</v>
@@ -7919,13 +7883,7 @@
       <c r="Y120" t="n">
         <v>1</v>
       </c>
-      <c r="Z120" t="n">
-        <v>1</v>
-      </c>
       <c r="AA120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB120" t="n">
         <v>1</v>
       </c>
       <c r="AC120" t="n">
@@ -7941,7 +7899,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Constante de equilibrio</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7950,13 +7908,28 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
-      </c>
-      <c r="J121" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="L121" t="n">
+        <v>11</v>
+      </c>
+      <c r="U121" t="n">
+        <v>1</v>
+      </c>
+      <c r="W121" t="n">
+        <v>1</v>
+      </c>
+      <c r="X121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" t="n">
         <v>1</v>
@@ -7977,7 +7950,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Hidrólisis de sales y disoluciones amortiguadoras</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7986,22 +7959,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D122" t="n">
-        <v>9</v>
-      </c>
-      <c r="L122" t="n">
-        <v>11</v>
-      </c>
-      <c r="U122" t="n">
-        <v>1</v>
-      </c>
-      <c r="X122" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="J122" t="n">
+        <v>7</v>
       </c>
       <c r="AA122" t="n">
         <v>1</v>
@@ -8022,7 +7986,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Energía de Gibbs y espontaneidad</t>
+          <t>Hidrólisis de sales y disoluciones amortiguadoras</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8031,12 +7995,15 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
-      </c>
-      <c r="W123" t="n">
+        <v>9</v>
+      </c>
+      <c r="L123" t="n">
+        <v>11</v>
+      </c>
+      <c r="U123" t="n">
         <v>1</v>
       </c>
       <c r="X123" t="n">
@@ -8045,23 +8012,26 @@
       <c r="Y123" t="n">
         <v>1</v>
       </c>
-      <c r="Z123" t="n">
-        <v>1</v>
-      </c>
       <c r="AA123" t="n">
         <v>1</v>
       </c>
       <c r="AB123" t="n">
         <v>1</v>
       </c>
+      <c r="AC123" t="n">
+        <v>1</v>
+      </c>
       <c r="AD123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE123" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
+          <t>Energía de Gibbs y espontaneidad</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8075,26 +8045,32 @@
       <c r="D124" t="n">
         <v>10</v>
       </c>
-      <c r="L124" t="n">
-        <v>11</v>
-      </c>
-      <c r="U124" t="n">
+      <c r="W124" t="n">
         <v>1</v>
       </c>
       <c r="X124" t="n">
         <v>1</v>
       </c>
+      <c r="Y124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>1</v>
+      </c>
       <c r="AD124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE124" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Entropía</t>
+          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8108,23 +8084,26 @@
       <c r="D125" t="n">
         <v>10</v>
       </c>
+      <c r="L125" t="n">
+        <v>11</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
+      </c>
       <c r="X125" t="n">
         <v>1</v>
       </c>
-      <c r="Y125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>1</v>
-      </c>
       <c r="AD125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE125" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
+          <t>Entropía</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8138,10 +8117,13 @@
       <c r="D126" t="n">
         <v>10</v>
       </c>
+      <c r="X126" t="n">
+        <v>1</v>
+      </c>
       <c r="Y126" t="n">
         <v>1</v>
       </c>
-      <c r="Z126" t="n">
+      <c r="AB126" t="n">
         <v>1</v>
       </c>
       <c r="AD126" t="n">
@@ -8151,7 +8133,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8165,35 +8147,20 @@
       <c r="D127" t="n">
         <v>10</v>
       </c>
-      <c r="I127" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R127" t="n">
-        <v>1</v>
-      </c>
-      <c r="W127" t="n">
-        <v>1</v>
-      </c>
       <c r="Y127" t="n">
         <v>1</v>
       </c>
       <c r="Z127" t="n">
         <v>1</v>
       </c>
-      <c r="AC127" t="n">
-        <v>1</v>
-      </c>
       <c r="AD127" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE127" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8207,25 +8174,19 @@
       <c r="D128" t="n">
         <v>10</v>
       </c>
-      <c r="L128" t="n">
-        <v>11</v>
-      </c>
-      <c r="M128" t="n">
-        <v>7</v>
-      </c>
-      <c r="U128" t="n">
-        <v>1</v>
-      </c>
-      <c r="X128" t="n">
+      <c r="I128" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1</v>
+      </c>
+      <c r="W128" t="n">
         <v>1</v>
       </c>
       <c r="Y128" t="n">
         <v>1</v>
       </c>
       <c r="Z128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA128" t="n">
         <v>1</v>
       </c>
       <c r="AC128" t="n">
@@ -8241,7 +8202,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Fundamentos de la reactividad orgánica</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8250,14 +8211,17 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L129" t="n">
         <v>11</v>
       </c>
+      <c r="M129" t="n">
+        <v>7</v>
+      </c>
       <c r="U129" t="n">
         <v>1</v>
       </c>
@@ -8270,14 +8234,23 @@
       <c r="Z129" t="n">
         <v>1</v>
       </c>
+      <c r="AA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1</v>
+      </c>
       <c r="AD129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE129" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Hibridación de orbitales</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8286,10 +8259,10 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L130" t="n">
         <v>11</v>
@@ -8309,14 +8282,11 @@
       <c r="AD130" t="n">
         <v>1</v>
       </c>
-      <c r="AE130" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Hibridación de orbitales</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8330,27 +8300,12 @@
       <c r="D131" t="n">
         <v>10</v>
       </c>
-      <c r="G131" t="n">
-        <v>8.5</v>
-      </c>
       <c r="L131" t="n">
         <v>11</v>
       </c>
-      <c r="M131" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P131" t="n">
-        <v>1</v>
-      </c>
       <c r="U131" t="n">
         <v>1</v>
       </c>
-      <c r="V131" t="n">
-        <v>1</v>
-      </c>
-      <c r="W131" t="n">
-        <v>1</v>
-      </c>
       <c r="X131" t="n">
         <v>1</v>
       </c>
@@ -8358,15 +8313,6 @@
         <v>1</v>
       </c>
       <c r="Z131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC131" t="n">
         <v>1</v>
       </c>
       <c r="AD131" t="n">
@@ -8379,7 +8325,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ley de velocidad, orden de reacción y ecuación de Arrhenius</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8393,12 +8339,27 @@
       <c r="D132" t="n">
         <v>10</v>
       </c>
+      <c r="G132" t="n">
+        <v>8.5</v>
+      </c>
       <c r="L132" t="n">
         <v>11</v>
       </c>
+      <c r="M132" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
       <c r="U132" t="n">
         <v>1</v>
       </c>
+      <c r="V132" t="n">
+        <v>1</v>
+      </c>
+      <c r="W132" t="n">
+        <v>1</v>
+      </c>
       <c r="X132" t="n">
         <v>1</v>
       </c>
@@ -8406,6 +8367,9 @@
         <v>1</v>
       </c>
       <c r="Z132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" t="n">
         <v>1</v>
       </c>
       <c r="AB132" t="n">
@@ -8424,7 +8388,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Mecanismos de reacción</t>
+          <t>Ley de velocidad, orden de reacción y ecuación de Arrhenius</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8438,6 +8402,12 @@
       <c r="D133" t="n">
         <v>10</v>
       </c>
+      <c r="L133" t="n">
+        <v>11</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1</v>
+      </c>
       <c r="X133" t="n">
         <v>1</v>
       </c>
@@ -8447,17 +8417,23 @@
       <c r="Z133" t="n">
         <v>1</v>
       </c>
+      <c r="AB133" t="n">
+        <v>1</v>
+      </c>
       <c r="AC133" t="n">
         <v>1</v>
       </c>
       <c r="AD133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE133" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Nanomateriales y manufactura molecular</t>
+          <t>Mecanismos de reacción</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8466,15 +8442,12 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D134" t="n">
-        <v>11</v>
-      </c>
-      <c r="G134" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W134" t="n">
+        <v>10</v>
+      </c>
+      <c r="X134" t="n">
         <v>1</v>
       </c>
       <c r="Y134" t="n">
@@ -8483,14 +8456,17 @@
       <c r="Z134" t="n">
         <v>1</v>
       </c>
-      <c r="AE134" t="n">
+      <c r="AC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD134" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Nanomateriales y manufactura molecular</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8504,43 +8480,16 @@
       <c r="D135" t="n">
         <v>11</v>
       </c>
-      <c r="F135" t="n">
-        <v>8</v>
-      </c>
       <c r="G135" t="n">
         <v>8.5</v>
       </c>
-      <c r="I135" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O135" t="n">
-        <v>1</v>
-      </c>
-      <c r="P135" t="n">
-        <v>1</v>
-      </c>
-      <c r="R135" t="n">
-        <v>1</v>
-      </c>
       <c r="W135" t="n">
         <v>1</v>
       </c>
-      <c r="X135" t="n">
-        <v>1</v>
-      </c>
       <c r="Y135" t="n">
         <v>1</v>
       </c>
       <c r="Z135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD135" t="n">
         <v>1</v>
       </c>
       <c r="AE135" t="n">
@@ -8550,7 +8499,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Producto de solubilidad (Kps)</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8564,7 +8513,37 @@
       <c r="D136" t="n">
         <v>11</v>
       </c>
+      <c r="F136" t="n">
+        <v>8</v>
+      </c>
+      <c r="G136" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I136" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" t="n">
+        <v>1</v>
+      </c>
       <c r="X136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB136" t="n">
         <v>1</v>
       </c>
       <c r="AC136" t="n">
@@ -8580,7 +8559,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Química de los ácidos nucleicos</t>
+          <t>Producto de solubilidad (Kps)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8589,28 +8568,28 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D137" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB137" t="n">
+        <v>11</v>
+      </c>
+      <c r="X137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE137" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Rendimiento de una reacción</t>
+          <t>Química de los ácidos nucleicos</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8624,38 +8603,23 @@
       <c r="D138" t="n">
         <v>10</v>
       </c>
-      <c r="F138" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O138" t="n">
-        <v>1</v>
-      </c>
-      <c r="W138" t="n">
-        <v>1</v>
-      </c>
-      <c r="X138" t="n">
-        <v>1</v>
-      </c>
       <c r="Y138" t="n">
         <v>1</v>
       </c>
       <c r="Z138" t="n">
         <v>1</v>
       </c>
-      <c r="AC138" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD138" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE138" t="n">
+      <c r="AA138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB138" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Resonancia y carga formal</t>
+          <t>Rendimiento de una reacción</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8669,23 +8633,38 @@
       <c r="D139" t="n">
         <v>10</v>
       </c>
+      <c r="F139" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="W139" t="n">
+        <v>1</v>
+      </c>
       <c r="X139" t="n">
         <v>1</v>
       </c>
       <c r="Y139" t="n">
         <v>1</v>
       </c>
-      <c r="AA139" t="n">
+      <c r="Z139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC139" t="n">
         <v>1</v>
       </c>
       <c r="AD139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE139" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Síntesis química y rutas de reacción</t>
+          <t>Resonancia y carga formal</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8699,43 +8678,73 @@
       <c r="D140" t="n">
         <v>10</v>
       </c>
-      <c r="F140" t="n">
+      <c r="X140" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Síntesis química y rutas de reacción</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>solo_especializacion</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>10</v>
+      </c>
+      <c r="D141" t="n">
+        <v>10</v>
+      </c>
+      <c r="F141" t="n">
         <v>10.5</v>
       </c>
-      <c r="L140" t="n">
+      <c r="L141" t="n">
         <v>11</v>
       </c>
-      <c r="O140" t="n">
-        <v>1</v>
-      </c>
-      <c r="U140" t="n">
-        <v>1</v>
-      </c>
-      <c r="W140" t="n">
-        <v>1</v>
-      </c>
-      <c r="X140" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE140" t="n">
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="U141" t="n">
+        <v>1</v>
+      </c>
+      <c r="W141" t="n">
+        <v>1</v>
+      </c>
+      <c r="X141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE141" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8750,7 +8759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -14643,6 +14652,48 @@
       </c>
       <c r="J140">
         <f>Datos!B140</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <f>Datos!A141</f>
+        <v/>
+      </c>
+      <c r="B141">
+        <f>IF(Datos!C141="","",Datos!C141)</f>
+        <v/>
+      </c>
+      <c r="C141">
+        <f>COUNT(Datos!E141:M141)</f>
+        <v/>
+      </c>
+      <c r="D141">
+        <f>IF(C141=0,"",MEDIAN(Datos!E141:M141))</f>
+        <v/>
+      </c>
+      <c r="E141">
+        <f>COUNT(Datos!W141:AE141)</f>
+        <v/>
+      </c>
+      <c r="F141">
+        <f>IF(OR(B141="",D141=""),"",B141-D141)</f>
+        <v/>
+      </c>
+      <c r="G141">
+        <f>IF(Datos!D141="","",Datos!D141)</f>
+        <v/>
+      </c>
+      <c r="H141">
+        <f>COUNT(Datos!N141:V141)</f>
+        <v/>
+      </c>
+      <c r="I141">
+        <f>IF(B141="",IF(C141&gt;=5,"falta en SV",""),IF(G141="",IF(H141&gt;=5,"no retomado en 9-11","previo"),IF(B141&lt;9,"retomado",IF(AND(C141&lt;=1,E141&gt;=3),"solo especializacion",IF(F141="","coherente",IF(F141&lt;=-1.5,"SV adelantado",IF(F141&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J141">
+        <f>Datos!B141</f>
         <v/>
       </c>
     </row>
@@ -14682,7 +14733,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(Datos!B2:B140,A2)</f>
+        <f>COUNTIF(Datos!B2:B141,A2)</f>
         <v/>
       </c>
     </row>
@@ -14693,7 +14744,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Datos!B2:B140,A3)</f>
+        <f>COUNTIF(Datos!B2:B141,A3)</f>
         <v/>
       </c>
     </row>
@@ -14704,7 +14755,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Datos!B2:B140,A4)</f>
+        <f>COUNTIF(Datos!B2:B141,A4)</f>
         <v/>
       </c>
     </row>
@@ -14715,7 +14766,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(Datos!B2:B140,A5)</f>
+        <f>COUNTIF(Datos!B2:B141,A5)</f>
         <v/>
       </c>
     </row>
@@ -14726,7 +14777,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(Datos!B2:B140,A6)</f>
+        <f>COUNTIF(Datos!B2:B141,A6)</f>
         <v/>
       </c>
     </row>
@@ -14737,7 +14788,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(Datos!B2:B140,A7)</f>
+        <f>COUNTIF(Datos!B2:B141,A7)</f>
         <v/>
       </c>
     </row>
@@ -14748,7 +14799,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(Datos!B2:B140,A8)</f>
+        <f>COUNTIF(Datos!B2:B141,A8)</f>
         <v/>
       </c>
     </row>
@@ -14759,7 +14810,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF(Datos!B2:B140,A9)</f>
+        <f>COUNTIF(Datos!B2:B141,A9)</f>
         <v/>
       </c>
     </row>
@@ -14770,7 +14821,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>COUNTIF(Datos!B2:B140,A10)</f>
+        <f>COUNTIF(Datos!B2:B141,A10)</f>
         <v/>
       </c>
     </row>

--- a/internacional/Contraste_quimica.xlsx
+++ b/internacional/Contraste_quimica.xlsx
@@ -4362,7 +4362,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Densidad y flotación</t>
+          <t>Configuración electrónica por orbitales</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4371,49 +4371,37 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
-      </c>
-      <c r="F66" t="n">
-        <v>8</v>
-      </c>
-      <c r="G66" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L66" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M66" t="n">
-        <v>7</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U66" t="n">
         <v>1</v>
       </c>
+      <c r="X66" t="n">
+        <v>1</v>
+      </c>
       <c r="Y66" t="n">
         <v>1</v>
       </c>
-      <c r="Z66" t="n">
+      <c r="AC66" t="n">
         <v>1</v>
       </c>
       <c r="AD66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Disoluciones, coloides y suspensiones</t>
+          <t>Densidad y flotación</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4422,37 +4410,49 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F67" t="n">
         <v>8</v>
       </c>
+      <c r="G67" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
+      <c r="L67" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M67" t="n">
         <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="V67" t="n">
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="n">
         <v>1</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
-      <c r="AA67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC67" t="n">
+      <c r="AD67" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Distribución electrónica por niveles (modelo de capas)</t>
+          <t>Disoluciones, coloides y suspensiones</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4461,73 +4461,37 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
         <v>10</v>
       </c>
-      <c r="E68" t="n">
-        <v>9</v>
-      </c>
       <c r="F68" t="n">
         <v>8</v>
       </c>
-      <c r="G68" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I68" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J68" t="n">
-        <v>9</v>
-      </c>
-      <c r="K68" t="n">
-        <v>8</v>
-      </c>
-      <c r="L68" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N68" t="n">
-        <v>1</v>
+      <c r="M68" t="n">
+        <v>7</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="P68" t="n">
-        <v>1</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S68" t="n">
-        <v>1</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1</v>
-      </c>
-      <c r="X68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y68" t="n">
+      <c r="V68" t="n">
         <v>1</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
       </c>
+      <c r="AA68" t="n">
+        <v>1</v>
+      </c>
       <c r="AC68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD68" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ecuación química y su balanceo</t>
+          <t>Distribución electrónica por niveles (modelo de capas)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4536,34 +4500,34 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="n">
         <v>9</v>
-      </c>
-      <c r="E69" t="n">
-        <v>8</v>
       </c>
       <c r="F69" t="n">
         <v>8</v>
       </c>
       <c r="G69" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L69" t="n">
         <v>9.5</v>
       </c>
-      <c r="M69" t="n">
-        <v>7</v>
+      <c r="N69" t="n">
+        <v>1</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
@@ -4574,15 +4538,12 @@
       <c r="R69" t="n">
         <v>1</v>
       </c>
-      <c r="T69" t="n">
+      <c r="S69" t="n">
         <v>1</v>
       </c>
       <c r="U69" t="n">
         <v>1</v>
       </c>
-      <c r="V69" t="n">
-        <v>1</v>
-      </c>
       <c r="W69" t="n">
         <v>1</v>
       </c>
@@ -4595,23 +4556,20 @@
       <c r="Z69" t="n">
         <v>1</v>
       </c>
-      <c r="AB69" t="n">
+      <c r="AA69" t="n">
         <v>1</v>
       </c>
       <c r="AC69" t="n">
         <v>1</v>
       </c>
       <c r="AD69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE69" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Electronegatividad y polaridad de enlace</t>
+          <t>Ecuación química y su balanceo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4623,20 +4581,50 @@
         <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E70" t="n">
+        <v>8</v>
       </c>
       <c r="F70" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G70" t="n">
+        <v>6</v>
+      </c>
+      <c r="I70" t="n">
+        <v>7</v>
+      </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
+      <c r="K70" t="n">
+        <v>9</v>
       </c>
       <c r="L70" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M70" t="n">
+        <v>7</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
       <c r="U70" t="n">
         <v>1</v>
       </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
@@ -4656,13 +4644,16 @@
         <v>1</v>
       </c>
       <c r="AD70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE70" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Electrones de valencia y regla del octeto</t>
+          <t>Electronegatividad y polaridad de enlace</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4679,34 +4670,19 @@
       <c r="F71" t="n">
         <v>10.5</v>
       </c>
-      <c r="G71" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I71" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J71" t="n">
-        <v>9</v>
-      </c>
       <c r="L71" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
       </c>
-      <c r="P71" t="n">
-        <v>1</v>
-      </c>
-      <c r="R71" t="n">
-        <v>1</v>
-      </c>
-      <c r="S71" t="n">
-        <v>1</v>
-      </c>
       <c r="U71" t="n">
         <v>1</v>
       </c>
       <c r="W71" t="n">
+        <v>1</v>
+      </c>
+      <c r="X71" t="n">
         <v>1</v>
       </c>
       <c r="Y71" t="n">
@@ -4728,7 +4704,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Enlace covalente</t>
+          <t>Electrones de valencia y regla del octeto</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4743,7 +4719,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G72" t="n">
         <v>8.5</v>
@@ -4757,9 +4733,6 @@
       <c r="L72" t="n">
         <v>9.5</v>
       </c>
-      <c r="M72" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O72" t="n">
         <v>1</v>
       </c>
@@ -4775,9 +4748,6 @@
       <c r="U72" t="n">
         <v>1</v>
       </c>
-      <c r="V72" t="n">
-        <v>1</v>
-      </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
@@ -4794,16 +4764,13 @@
         <v>1</v>
       </c>
       <c r="AD72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE72" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Enlace iónico</t>
+          <t>Enlace covalente</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4812,7 +4779,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D73" t="n">
         <v>10</v>
@@ -4871,11 +4838,14 @@
       <c r="AD73" t="n">
         <v>1</v>
       </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enlace metálico</t>
+          <t>Enlace iónico</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4884,7 +4854,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
         <v>10</v>
@@ -4904,6 +4874,9 @@
       <c r="L74" t="n">
         <v>9.5</v>
       </c>
+      <c r="M74" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
@@ -4919,12 +4892,12 @@
       <c r="U74" t="n">
         <v>1</v>
       </c>
+      <c r="V74" t="n">
+        <v>1</v>
+      </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
-      <c r="X74" t="n">
-        <v>1</v>
-      </c>
       <c r="Y74" t="n">
         <v>1</v>
       </c>
@@ -4938,16 +4911,13 @@
         <v>1</v>
       </c>
       <c r="AD74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE74" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Escala de pH</t>
+          <t>Enlace metálico</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4956,29 +4926,26 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F75" t="n">
         <v>8</v>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I75" t="n">
         <v>9.5</v>
       </c>
-      <c r="K75" t="n">
+      <c r="J75" t="n">
         <v>9</v>
       </c>
       <c r="L75" t="n">
         <v>9.5</v>
       </c>
-      <c r="M75" t="n">
-        <v>7</v>
-      </c>
       <c r="O75" t="n">
         <v>1</v>
       </c>
@@ -4988,13 +4955,10 @@
       <c r="R75" t="n">
         <v>1</v>
       </c>
-      <c r="T75" t="n">
+      <c r="S75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>1</v>
-      </c>
-      <c r="V75" t="n">
         <v>1</v>
       </c>
       <c r="W75" t="n">
@@ -5025,7 +4989,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Escala de pH</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5034,25 +4998,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
-      </c>
-      <c r="E76" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
         <v>8</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I76" t="n">
         <v>9.5</v>
       </c>
-      <c r="J76" t="n">
-        <v>7</v>
+      <c r="K76" t="n">
+        <v>9</v>
       </c>
       <c r="L76" t="n">
         <v>9.5</v>
@@ -5069,18 +5030,27 @@
       <c r="R76" t="n">
         <v>1</v>
       </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
       <c r="U76" t="n">
         <v>1</v>
       </c>
+      <c r="V76" t="n">
+        <v>1</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1</v>
+      </c>
       <c r="Y76" t="n">
         <v>1</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
-      <c r="AA76" t="n">
-        <v>1</v>
-      </c>
       <c r="AB76" t="n">
         <v>1</v>
       </c>
@@ -5088,13 +5058,16 @@
         <v>1</v>
       </c>
       <c r="AD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE76" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,16 +5076,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
         <v>10</v>
       </c>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
       <c r="F77" t="n">
         <v>8</v>
       </c>
       <c r="G77" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
         <v>9.5</v>
@@ -5124,7 +5100,7 @@
         <v>9.5</v>
       </c>
       <c r="M77" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
@@ -5138,15 +5114,6 @@
       <c r="U77" t="n">
         <v>1</v>
       </c>
-      <c r="V77" t="n">
-        <v>1</v>
-      </c>
-      <c r="W77" t="n">
-        <v>1</v>
-      </c>
-      <c r="X77" t="n">
-        <v>1</v>
-      </c>
       <c r="Y77" t="n">
         <v>1</v>
       </c>
@@ -5163,16 +5130,13 @@
         <v>1</v>
       </c>
       <c r="AD77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE77" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Notación y estructuras de Lewis</t>
+          <t>Estequiometría</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5181,29 +5145,44 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D78" t="n">
         <v>10</v>
       </c>
       <c r="F78" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G78" t="n">
         <v>8.5</v>
       </c>
+      <c r="I78" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
       <c r="L78" t="n">
         <v>9.5</v>
       </c>
+      <c r="M78" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
       <c r="P78" t="n">
         <v>1</v>
       </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
       <c r="U78" t="n">
         <v>1</v>
       </c>
+      <c r="V78" t="n">
+        <v>1</v>
+      </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
@@ -5216,6 +5195,9 @@
       <c r="Z78" t="n">
         <v>1</v>
       </c>
+      <c r="AA78" t="n">
+        <v>1</v>
+      </c>
       <c r="AB78" t="n">
         <v>1</v>
       </c>
@@ -5223,13 +5205,16 @@
         <v>1</v>
       </c>
       <c r="AD78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE78" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares</t>
+          <t>Notación y estructuras de Lewis</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5249,15 +5234,9 @@
       <c r="G79" t="n">
         <v>8.5</v>
       </c>
-      <c r="J79" t="n">
-        <v>7</v>
-      </c>
       <c r="L79" t="n">
         <v>9.5</v>
       </c>
-      <c r="M79" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O79" t="n">
         <v>1</v>
       </c>
@@ -5267,9 +5246,6 @@
       <c r="U79" t="n">
         <v>1</v>
       </c>
-      <c r="V79" t="n">
-        <v>1</v>
-      </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
@@ -5282,9 +5258,6 @@
       <c r="Z79" t="n">
         <v>1</v>
       </c>
-      <c r="AA79" t="n">
-        <v>1</v>
-      </c>
       <c r="AB79" t="n">
         <v>1</v>
       </c>
@@ -5292,16 +5265,13 @@
         <v>1</v>
       </c>
       <c r="AD79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE79" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares y propiedades físicas</t>
+          <t>Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5316,27 +5286,30 @@
         <v>10</v>
       </c>
       <c r="F80" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G80" t="n">
         <v>8.5</v>
       </c>
-      <c r="I80" t="n">
-        <v>9.5</v>
+      <c r="J80" t="n">
+        <v>7</v>
       </c>
       <c r="L80" t="n">
         <v>9.5</v>
       </c>
+      <c r="M80" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O80" t="n">
         <v>1</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
       <c r="U80" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" t="n">
         <v>1</v>
       </c>
       <c r="W80" t="n">
@@ -5370,7 +5343,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Geometría molecular (RPECV)</t>
+          <t>Fuerzas intermoleculares y propiedades físicas</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5384,24 +5357,30 @@
       <c r="D81" t="n">
         <v>10</v>
       </c>
+      <c r="F81" t="n">
+        <v>8</v>
+      </c>
       <c r="G81" t="n">
         <v>8.5</v>
       </c>
+      <c r="I81" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L81" t="n">
-        <v>11</v>
-      </c>
-      <c r="M81" t="n">
         <v>9.5</v>
       </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
       <c r="P81" t="n">
         <v>1</v>
       </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
       <c r="U81" t="n">
         <v>1</v>
       </c>
-      <c r="V81" t="n">
-        <v>1</v>
-      </c>
       <c r="W81" t="n">
         <v>1</v>
       </c>
@@ -5412,6 +5391,9 @@
         <v>1</v>
       </c>
       <c r="Z81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA81" t="n">
         <v>1</v>
       </c>
       <c r="AB81" t="n">
@@ -5430,7 +5412,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Iones</t>
+          <t>Geometría molecular (RPECV)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5439,44 +5421,23 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
         <v>10</v>
       </c>
-      <c r="F82" t="n">
-        <v>8</v>
-      </c>
       <c r="G82" t="n">
         <v>8.5</v>
       </c>
-      <c r="I82" t="n">
-        <v>8</v>
-      </c>
-      <c r="J82" t="n">
-        <v>7</v>
-      </c>
-      <c r="K82" t="n">
-        <v>9</v>
-      </c>
       <c r="L82" t="n">
+        <v>11</v>
+      </c>
+      <c r="M82" t="n">
         <v>9.5</v>
       </c>
-      <c r="M82" t="n">
-        <v>7</v>
-      </c>
-      <c r="O82" t="n">
-        <v>1</v>
-      </c>
       <c r="P82" t="n">
         <v>1</v>
       </c>
-      <c r="R82" t="n">
-        <v>1</v>
-      </c>
-      <c r="T82" t="n">
-        <v>1</v>
-      </c>
       <c r="U82" t="n">
         <v>1</v>
       </c>
@@ -5495,17 +5456,23 @@
       <c r="Z82" t="n">
         <v>1</v>
       </c>
+      <c r="AB82" t="n">
+        <v>1</v>
+      </c>
       <c r="AC82" t="n">
         <v>1</v>
       </c>
       <c r="AD82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE82" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Isótopos</t>
+          <t>Iones</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5519,20 +5486,29 @@
       <c r="D83" t="n">
         <v>10</v>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>8</v>
       </c>
       <c r="G83" t="n">
         <v>8.5</v>
       </c>
       <c r="I83" t="n">
-        <v>9.5</v>
+        <v>8</v>
+      </c>
+      <c r="J83" t="n">
+        <v>7</v>
+      </c>
+      <c r="K83" t="n">
+        <v>9</v>
       </c>
       <c r="L83" t="n">
         <v>9.5</v>
       </c>
       <c r="M83" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
       </c>
       <c r="P83" t="n">
         <v>1</v>
@@ -5540,6 +5516,9 @@
       <c r="R83" t="n">
         <v>1</v>
       </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
       <c r="U83" t="n">
         <v>1</v>
       </c>
@@ -5547,6 +5526,9 @@
         <v>1</v>
       </c>
       <c r="W83" t="n">
+        <v>1</v>
+      </c>
+      <c r="X83" t="n">
         <v>1</v>
       </c>
       <c r="Y83" t="n">
@@ -5565,7 +5547,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Masa atómica relativa</t>
+          <t>Isótopos</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5579,19 +5561,31 @@
       <c r="D84" t="n">
         <v>10</v>
       </c>
+      <c r="E84" t="n">
+        <v>8</v>
+      </c>
       <c r="G84" t="n">
         <v>8.5</v>
       </c>
+      <c r="I84" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L84" t="n">
         <v>9.5</v>
       </c>
       <c r="M84" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="P84" t="n">
         <v>1</v>
       </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
       <c r="U84" t="n">
+        <v>1</v>
+      </c>
+      <c r="V84" t="n">
         <v>1</v>
       </c>
       <c r="W84" t="n">
@@ -5613,7 +5607,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Masa molar</t>
+          <t>Masa atómica relativa</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5622,54 +5616,33 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D85" t="n">
         <v>10</v>
       </c>
-      <c r="F85" t="n">
-        <v>8</v>
-      </c>
       <c r="G85" t="n">
         <v>8.5</v>
       </c>
-      <c r="I85" t="n">
-        <v>9.5</v>
-      </c>
       <c r="L85" t="n">
         <v>9.5</v>
       </c>
       <c r="M85" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P85" t="n">
         <v>1</v>
       </c>
-      <c r="R85" t="n">
-        <v>1</v>
-      </c>
       <c r="U85" t="n">
         <v>1</v>
       </c>
-      <c r="V85" t="n">
-        <v>1</v>
-      </c>
       <c r="W85" t="n">
         <v>1</v>
       </c>
-      <c r="X85" t="n">
-        <v>1</v>
-      </c>
       <c r="Y85" t="n">
         <v>1</v>
       </c>
       <c r="Z85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB85" t="n">
         <v>1</v>
       </c>
       <c r="AC85" t="n">
@@ -5682,7 +5655,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Materia y materiales</t>
+          <t>Masa molar</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5691,34 +5664,25 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D86" t="n">
-        <v>11</v>
-      </c>
-      <c r="E86" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F86" t="n">
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I86" t="n">
-        <v>6</v>
-      </c>
-      <c r="J86" t="n">
-        <v>7</v>
-      </c>
-      <c r="K86" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="L86" t="n">
         <v>9.5</v>
       </c>
       <c r="M86" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
@@ -5732,6 +5696,9 @@
       <c r="U86" t="n">
         <v>1</v>
       </c>
+      <c r="V86" t="n">
+        <v>1</v>
+      </c>
       <c r="W86" t="n">
         <v>1</v>
       </c>
@@ -5744,10 +5711,10 @@
       <c r="Z86" t="n">
         <v>1</v>
       </c>
-      <c r="AA86" t="n">
-        <v>1</v>
-      </c>
       <c r="AB86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC86" t="n">
         <v>1</v>
       </c>
       <c r="AD86" t="n">
@@ -5757,7 +5724,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Reutilización y reciclaje de materiales</t>
+          <t>Materia y materiales</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5771,17 +5738,20 @@
       <c r="D87" t="n">
         <v>11</v>
       </c>
+      <c r="E87" t="n">
+        <v>2</v>
+      </c>
       <c r="F87" t="n">
         <v>8</v>
       </c>
       <c r="G87" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K87" t="n">
         <v>8</v>
@@ -5801,13 +5771,13 @@
       <c r="R87" t="n">
         <v>1</v>
       </c>
-      <c r="S87" t="n">
-        <v>1</v>
-      </c>
       <c r="U87" t="n">
         <v>1</v>
       </c>
-      <c r="V87" t="n">
+      <c r="W87" t="n">
+        <v>1</v>
+      </c>
+      <c r="X87" t="n">
         <v>1</v>
       </c>
       <c r="Y87" t="n">
@@ -5816,20 +5786,20 @@
       <c r="Z87" t="n">
         <v>1</v>
       </c>
-      <c r="AC87" t="n">
+      <c r="AA87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB87" t="n">
         <v>1</v>
       </c>
       <c r="AD87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE87" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mezclas homogéneas y heterogéneas</t>
+          <t>Reutilización y reciclaje de materiales</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5841,22 +5811,22 @@
         <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>10</v>
-      </c>
-      <c r="E88" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="K88" t="n">
+        <v>8</v>
       </c>
       <c r="L88" t="n">
         <v>9.5</v>
@@ -5873,10 +5843,13 @@
       <c r="R88" t="n">
         <v>1</v>
       </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
       <c r="U88" t="n">
         <v>1</v>
       </c>
-      <c r="W88" t="n">
+      <c r="V88" t="n">
         <v>1</v>
       </c>
       <c r="Y88" t="n">
@@ -5885,17 +5858,20 @@
       <c r="Z88" t="n">
         <v>1</v>
       </c>
-      <c r="AB88" t="n">
+      <c r="AC88" t="n">
         <v>1</v>
       </c>
       <c r="AD88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE88" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Mezclas homogéneas y heterogéneas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5904,13 +5880,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
         <v>10</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F89" t="n">
         <v>8</v>
@@ -5919,14 +5895,11 @@
         <v>6</v>
       </c>
       <c r="I89" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>7</v>
       </c>
-      <c r="K89" t="n">
-        <v>8</v>
-      </c>
       <c r="L89" t="n">
         <v>9.5</v>
       </c>
@@ -5945,9 +5918,6 @@
       <c r="U89" t="n">
         <v>1</v>
       </c>
-      <c r="V89" t="n">
-        <v>1</v>
-      </c>
       <c r="W89" t="n">
         <v>1</v>
       </c>
@@ -5957,26 +5927,17 @@
       <c r="Z89" t="n">
         <v>1</v>
       </c>
-      <c r="AA89" t="n">
-        <v>1</v>
-      </c>
       <c r="AB89" t="n">
         <v>1</v>
       </c>
-      <c r="AC89" t="n">
-        <v>1</v>
-      </c>
       <c r="AD89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE89" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Modelo mecanocuántico y orbitales atómicos</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5985,21 +5946,63 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
         <v>10</v>
       </c>
+      <c r="E90" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" t="n">
+        <v>8</v>
+      </c>
+      <c r="G90" t="n">
+        <v>6</v>
+      </c>
+      <c r="I90" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>7</v>
+      </c>
+      <c r="K90" t="n">
+        <v>8</v>
+      </c>
       <c r="L90" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M90" t="n">
+        <v>7</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" t="n">
+        <v>1</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1</v>
       </c>
       <c r="U90" t="n">
         <v>1</v>
       </c>
+      <c r="V90" t="n">
+        <v>1</v>
+      </c>
+      <c r="W90" t="n">
+        <v>1</v>
+      </c>
       <c r="Y90" t="n">
         <v>1</v>
       </c>
       <c r="Z90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB90" t="n">
         <v>1</v>
       </c>
       <c r="AC90" t="n">
@@ -6015,7 +6018,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Evolución de los modelos atómicos</t>
+          <t>Modelo mecanocuántico y orbitales atómicos</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6029,43 +6032,10 @@
       <c r="D91" t="n">
         <v>10</v>
       </c>
-      <c r="E91" t="n">
-        <v>8</v>
-      </c>
-      <c r="F91" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G91" t="n">
-        <v>6</v>
-      </c>
-      <c r="J91" t="n">
-        <v>9</v>
-      </c>
-      <c r="K91" t="n">
-        <v>8</v>
-      </c>
       <c r="L91" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M91" t="n">
-        <v>7</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="S91" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="n">
-        <v>1</v>
-      </c>
-      <c r="W91" t="n">
         <v>1</v>
       </c>
       <c r="Y91" t="n">
@@ -6087,7 +6057,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Evolución de los modelos atómicos</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6096,25 +6066,31 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
         <v>10</v>
       </c>
+      <c r="E92" t="n">
+        <v>8</v>
+      </c>
       <c r="F92" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6</v>
+      </c>
+      <c r="J92" t="n">
+        <v>9</v>
+      </c>
+      <c r="K92" t="n">
         <v>8</v>
-      </c>
-      <c r="G92" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I92" t="n">
-        <v>9.5</v>
       </c>
       <c r="L92" t="n">
         <v>9.5</v>
       </c>
       <c r="M92" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
@@ -6122,7 +6098,7 @@
       <c r="P92" t="n">
         <v>1</v>
       </c>
-      <c r="R92" t="n">
+      <c r="S92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
@@ -6134,29 +6110,26 @@
       <c r="W92" t="n">
         <v>1</v>
       </c>
-      <c r="X92" t="n">
-        <v>1</v>
-      </c>
       <c r="Y92" t="n">
         <v>1</v>
       </c>
       <c r="Z92" t="n">
         <v>1</v>
       </c>
-      <c r="AB92" t="n">
-        <v>1</v>
-      </c>
       <c r="AC92" t="n">
         <v>1</v>
       </c>
       <c r="AD92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE92" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Molaridad y unidades químicas de concentración</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6168,10 +6141,13 @@
         <v>8</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8.5</v>
       </c>
       <c r="I93" t="n">
         <v>9.5</v>
@@ -6185,6 +6161,9 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
       <c r="R93" t="n">
         <v>1</v>
       </c>
@@ -6213,16 +6192,13 @@
         <v>1</v>
       </c>
       <c r="AD93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE93" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Moléculas y fórmulas químicas</t>
+          <t>Molaridad y unidades químicas de concentración</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6231,47 +6207,35 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
-      </c>
-      <c r="E94" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F94" t="n">
-        <v>8</v>
-      </c>
-      <c r="G94" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="I94" t="n">
-        <v>7</v>
-      </c>
-      <c r="J94" t="n">
-        <v>7</v>
-      </c>
-      <c r="K94" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="L94" t="n">
         <v>9.5</v>
       </c>
       <c r="M94" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="P94" t="n">
-        <v>1</v>
-      </c>
-      <c r="T94" t="n">
+      <c r="R94" t="n">
         <v>1</v>
       </c>
       <c r="U94" t="n">
         <v>1</v>
       </c>
+      <c r="V94" t="n">
+        <v>1</v>
+      </c>
       <c r="W94" t="n">
         <v>1</v>
       </c>
@@ -6291,13 +6255,16 @@
         <v>1</v>
       </c>
       <c r="AD94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE94" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Número de oxidación</t>
+          <t>Moléculas y fórmulas químicas</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6311,24 +6278,45 @@
       <c r="D95" t="n">
         <v>10</v>
       </c>
+      <c r="E95" t="n">
+        <v>7</v>
+      </c>
       <c r="F95" t="n">
         <v>8</v>
       </c>
+      <c r="G95" t="n">
+        <v>6</v>
+      </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="J95" t="n">
+        <v>7</v>
+      </c>
+      <c r="K95" t="n">
+        <v>8</v>
       </c>
       <c r="L95" t="n">
         <v>9.5</v>
       </c>
+      <c r="M95" t="n">
+        <v>7</v>
+      </c>
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="R95" t="n">
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" t="n">
         <v>1</v>
       </c>
       <c r="U95" t="n">
         <v>1</v>
       </c>
+      <c r="W95" t="n">
+        <v>1</v>
+      </c>
       <c r="X95" t="n">
         <v>1</v>
       </c>
@@ -6345,16 +6333,13 @@
         <v>1</v>
       </c>
       <c r="AD95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE95" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Números cuánticos</t>
+          <t>Número de oxidación</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6368,10 +6353,37 @@
       <c r="D96" t="n">
         <v>10</v>
       </c>
+      <c r="F96" t="n">
+        <v>8</v>
+      </c>
+      <c r="I96" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L96" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+      <c r="R96" t="n">
+        <v>1</v>
       </c>
       <c r="U96" t="n">
+        <v>1</v>
+      </c>
+      <c r="X96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC96" t="n">
         <v>1</v>
       </c>
       <c r="AD96" t="n">
@@ -6384,7 +6396,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Oxidación y corrosión de los metales</t>
+          <t>Números cuánticos</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6393,64 +6405,28 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
+        <v>10</v>
+      </c>
+      <c r="L97" t="n">
         <v>11</v>
       </c>
-      <c r="F97" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I97" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J97" t="n">
-        <v>9</v>
-      </c>
-      <c r="K97" t="n">
-        <v>9</v>
-      </c>
-      <c r="L97" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M97" t="n">
-        <v>7</v>
-      </c>
-      <c r="O97" t="n">
-        <v>1</v>
-      </c>
-      <c r="R97" t="n">
-        <v>1</v>
-      </c>
-      <c r="S97" t="n">
-        <v>1</v>
-      </c>
-      <c r="T97" t="n">
-        <v>1</v>
-      </c>
       <c r="U97" t="n">
         <v>1</v>
       </c>
-      <c r="W97" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC97" t="n">
-        <v>1</v>
-      </c>
       <c r="AD97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE97" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Polaridad molecular</t>
+          <t>Oxidación y corrosión de los metales</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6459,22 +6435,28 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="I98" t="n">
         <v>9.5</v>
       </c>
+      <c r="J98" t="n">
+        <v>9</v>
+      </c>
+      <c r="K98" t="n">
+        <v>9</v>
+      </c>
       <c r="L98" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M98" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O98" t="n">
         <v>1</v>
@@ -6482,41 +6464,35 @@
       <c r="R98" t="n">
         <v>1</v>
       </c>
+      <c r="S98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
+        <v>1</v>
+      </c>
       <c r="U98" t="n">
         <v>1</v>
       </c>
-      <c r="V98" t="n">
-        <v>1</v>
-      </c>
       <c r="W98" t="n">
         <v>1</v>
       </c>
-      <c r="X98" t="n">
-        <v>1</v>
-      </c>
       <c r="Y98" t="n">
         <v>1</v>
       </c>
       <c r="Z98" t="n">
         <v>1</v>
       </c>
-      <c r="AB98" t="n">
-        <v>1</v>
-      </c>
       <c r="AC98" t="n">
         <v>1</v>
       </c>
       <c r="AD98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE98" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Proceso de disolución y solvatación</t>
+          <t>Polaridad molecular</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6525,43 +6501,64 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
         <v>10</v>
       </c>
       <c r="F99" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G99" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="I99" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L99" t="n">
+        <v>11</v>
       </c>
       <c r="M99" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
       </c>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
       <c r="V99" t="n">
         <v>1</v>
       </c>
       <c r="W99" t="n">
         <v>1</v>
       </c>
-      <c r="AA99" t="n">
+      <c r="X99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB99" t="n">
         <v>1</v>
       </c>
       <c r="AC99" t="n">
         <v>1</v>
       </c>
       <c r="AD99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE99" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Proceso de disolución y solvatación</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6570,18 +6567,21 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D100" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F100" t="n">
+        <v>10.5</v>
       </c>
       <c r="G100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M100" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P100" t="n">
+        <v>7</v>
+      </c>
+      <c r="O100" t="n">
         <v>1</v>
       </c>
       <c r="V100" t="n">
@@ -6590,13 +6590,7 @@
       <c r="W100" t="n">
         <v>1</v>
       </c>
-      <c r="Y100" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB100" t="n">
+      <c r="AA100" t="n">
         <v>1</v>
       </c>
       <c r="AC100" t="n">
@@ -6609,7 +6603,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6621,28 +6615,43 @@
         <v>8</v>
       </c>
       <c r="D101" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G101" t="n">
+        <v>6</v>
+      </c>
+      <c r="M101" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>1</v>
       </c>
       <c r="Z101" t="n">
         <v>1</v>
       </c>
-      <c r="AA101" t="n">
-        <v>1</v>
-      </c>
       <c r="AB101" t="n">
         <v>1</v>
       </c>
       <c r="AC101" t="n">
         <v>1</v>
       </c>
-      <c r="AE101" t="n">
+      <c r="AD101" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Propiedades físicas de los materiales</t>
+          <t>Propiedades coligativas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6651,57 +6660,21 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D102" t="n">
-        <v>11</v>
-      </c>
-      <c r="E102" t="n">
-        <v>2</v>
-      </c>
-      <c r="F102" t="n">
-        <v>8</v>
-      </c>
-      <c r="G102" t="n">
-        <v>2</v>
-      </c>
-      <c r="I102" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J102" t="n">
-        <v>7</v>
-      </c>
-      <c r="L102" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M102" t="n">
-        <v>7</v>
-      </c>
-      <c r="O102" t="n">
-        <v>1</v>
-      </c>
-      <c r="P102" t="n">
-        <v>1</v>
-      </c>
-      <c r="R102" t="n">
-        <v>1</v>
-      </c>
-      <c r="U102" t="n">
-        <v>1</v>
-      </c>
-      <c r="W102" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Z102" t="n">
         <v>1</v>
       </c>
+      <c r="AA102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>1</v>
+      </c>
       <c r="AC102" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD102" t="n">
         <v>1</v>
       </c>
       <c r="AE102" t="n">
@@ -6711,7 +6684,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Propiedades físicas y químicas</t>
+          <t>Propiedades físicas de los materiales</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6723,23 +6696,23 @@
         <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2</v>
       </c>
       <c r="F103" t="n">
         <v>8</v>
       </c>
       <c r="G103" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I103" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="J103" t="n">
         <v>7</v>
       </c>
-      <c r="K103" t="n">
-        <v>8</v>
-      </c>
       <c r="L103" t="n">
         <v>9.5</v>
       </c>
@@ -6755,28 +6728,16 @@
       <c r="R103" t="n">
         <v>1</v>
       </c>
-      <c r="T103" t="n">
-        <v>1</v>
-      </c>
       <c r="U103" t="n">
         <v>1</v>
       </c>
-      <c r="V103" t="n">
-        <v>1</v>
-      </c>
       <c r="W103" t="n">
         <v>1</v>
       </c>
-      <c r="X103" t="n">
-        <v>1</v>
-      </c>
       <c r="Y103" t="n">
         <v>1</v>
       </c>
       <c r="Z103" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB103" t="n">
         <v>1</v>
       </c>
       <c r="AC103" t="n">
@@ -6792,7 +6753,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Propiedades periódicas</t>
+          <t>Propiedades físicas y químicas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6801,25 +6762,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>10</v>
-      </c>
-      <c r="E104" t="n">
         <v>9</v>
       </c>
       <c r="F104" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G104" t="n">
         <v>6</v>
       </c>
       <c r="I104" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="J104" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K104" t="n">
         <v>8</v>
@@ -6830,9 +6788,6 @@
       <c r="M104" t="n">
         <v>7</v>
       </c>
-      <c r="N104" t="n">
-        <v>1</v>
-      </c>
       <c r="O104" t="n">
         <v>1</v>
       </c>
@@ -6842,12 +6797,15 @@
       <c r="R104" t="n">
         <v>1</v>
       </c>
-      <c r="S104" t="n">
+      <c r="T104" t="n">
         <v>1</v>
       </c>
       <c r="U104" t="n">
         <v>1</v>
       </c>
+      <c r="V104" t="n">
+        <v>1</v>
+      </c>
       <c r="W104" t="n">
         <v>1</v>
       </c>
@@ -6858,9 +6816,6 @@
         <v>1</v>
       </c>
       <c r="Z104" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA104" t="n">
         <v>1</v>
       </c>
       <c r="AB104" t="n">
@@ -6879,7 +6834,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Propiedades singulares del agua</t>
+          <t>Propiedades periódicas</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6888,22 +6843,46 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="n">
         <v>9</v>
+      </c>
+      <c r="F105" t="n">
+        <v>10.5</v>
       </c>
       <c r="G105" t="n">
         <v>6</v>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J105" t="n">
         <v>9</v>
       </c>
+      <c r="K105" t="n">
+        <v>8</v>
+      </c>
       <c r="L105" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M105" t="n">
+        <v>7</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
@@ -6914,9 +6893,18 @@
       <c r="W105" t="n">
         <v>1</v>
       </c>
+      <c r="X105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1</v>
+      </c>
       <c r="Z105" t="n">
         <v>1</v>
       </c>
+      <c r="AA105" t="n">
+        <v>1</v>
+      </c>
       <c r="AB105" t="n">
         <v>1</v>
       </c>
@@ -6924,13 +6912,16 @@
         <v>1</v>
       </c>
       <c r="AD105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE105" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Química de los carbohidratos</t>
+          <t>Propiedades singulares del agua</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6939,55 +6930,49 @@
         </is>
       </c>
       <c r="C106" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" t="n">
+        <v>9</v>
+      </c>
+      <c r="G106" t="n">
         <v>6</v>
       </c>
-      <c r="D106" t="n">
-        <v>10</v>
-      </c>
-      <c r="F106" t="n">
-        <v>10.5</v>
-      </c>
       <c r="I106" t="n">
-        <v>9.5</v>
+        <v>3</v>
+      </c>
+      <c r="J106" t="n">
+        <v>9</v>
       </c>
       <c r="L106" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M106" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O106" t="n">
-        <v>1</v>
-      </c>
-      <c r="R106" t="n">
+        <v>11</v>
+      </c>
+      <c r="S106" t="n">
         <v>1</v>
       </c>
       <c r="U106" t="n">
         <v>1</v>
       </c>
-      <c r="V106" t="n">
-        <v>1</v>
-      </c>
       <c r="W106" t="n">
         <v>1</v>
       </c>
-      <c r="X106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>1</v>
-      </c>
       <c r="Z106" t="n">
         <v>1</v>
       </c>
-      <c r="AA106" t="n">
+      <c r="AB106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD106" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Química de los carbohidratos</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7010,6 +6995,9 @@
       <c r="L107" t="n">
         <v>9.5</v>
       </c>
+      <c r="M107" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O107" t="n">
         <v>1</v>
       </c>
@@ -7019,20 +7007,29 @@
       <c r="U107" t="n">
         <v>1</v>
       </c>
+      <c r="V107" t="n">
+        <v>1</v>
+      </c>
+      <c r="W107" t="n">
+        <v>1</v>
+      </c>
+      <c r="X107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>1</v>
+      </c>
       <c r="Z107" t="n">
         <v>1</v>
       </c>
       <c r="AA107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD107" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Química descriptiva de los elementos</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7041,70 +7038,43 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D108" t="n">
         <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>8</v>
-      </c>
-      <c r="G108" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="I108" t="n">
         <v>9.5</v>
       </c>
-      <c r="J108" t="n">
-        <v>9</v>
-      </c>
       <c r="L108" t="n">
         <v>9.5</v>
       </c>
-      <c r="M108" t="n">
-        <v>7</v>
-      </c>
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="P108" t="n">
-        <v>1</v>
-      </c>
       <c r="R108" t="n">
         <v>1</v>
       </c>
-      <c r="S108" t="n">
-        <v>1</v>
-      </c>
       <c r="U108" t="n">
         <v>1</v>
       </c>
-      <c r="X108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>1</v>
-      </c>
       <c r="Z108" t="n">
         <v>1</v>
       </c>
       <c r="AA108" t="n">
         <v>1</v>
       </c>
-      <c r="AC108" t="n">
-        <v>1</v>
-      </c>
       <c r="AD108" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE108" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Radiactividad y emisiones nucleares</t>
+          <t>Química descriptiva de los elementos</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7118,29 +7088,65 @@
       <c r="D109" t="n">
         <v>10</v>
       </c>
-      <c r="E109" t="n">
+      <c r="F109" t="n">
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I109" t="n">
         <v>9.5</v>
       </c>
+      <c r="J109" t="n">
+        <v>9</v>
+      </c>
+      <c r="L109" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M109" t="n">
+        <v>7</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
       <c r="R109" t="n">
         <v>1</v>
       </c>
-      <c r="W109" t="n">
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" t="n">
+        <v>1</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA109" t="n">
         <v>1</v>
       </c>
       <c r="AC109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE109" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Factores que afectan la rapidez de reacción</t>
+          <t>Radiactividad y emisiones nucleares</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7149,73 +7155,34 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E110" t="n">
-        <v>9</v>
-      </c>
-      <c r="F110" t="n">
         <v>8</v>
       </c>
       <c r="G110" t="n">
         <v>8.5</v>
       </c>
-      <c r="L110" t="n">
+      <c r="I110" t="n">
         <v>9.5</v>
       </c>
-      <c r="M110" t="n">
-        <v>7</v>
-      </c>
-      <c r="N110" t="n">
-        <v>1</v>
-      </c>
-      <c r="O110" t="n">
-        <v>1</v>
-      </c>
-      <c r="P110" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" t="n">
-        <v>1</v>
-      </c>
-      <c r="V110" t="n">
+      <c r="R110" t="n">
         <v>1</v>
       </c>
       <c r="W110" t="n">
         <v>1</v>
       </c>
-      <c r="X110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB110" t="n">
-        <v>1</v>
-      </c>
       <c r="AC110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE110" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Reacción química y sus evidencias</t>
+          <t>Factores que afectan la rapidez de reacción</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7224,28 +7191,19 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E111" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F111" t="n">
         <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
-      </c>
-      <c r="I111" t="n">
-        <v>5</v>
-      </c>
-      <c r="J111" t="n">
-        <v>7</v>
-      </c>
-      <c r="K111" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="L111" t="n">
         <v>9.5</v>
@@ -7253,31 +7211,34 @@
       <c r="M111" t="n">
         <v>7</v>
       </c>
+      <c r="N111" t="n">
+        <v>1</v>
+      </c>
       <c r="O111" t="n">
         <v>1</v>
       </c>
       <c r="P111" t="n">
         <v>1</v>
       </c>
-      <c r="R111" t="n">
-        <v>1</v>
-      </c>
-      <c r="S111" t="n">
-        <v>1</v>
-      </c>
-      <c r="T111" t="n">
-        <v>1</v>
-      </c>
       <c r="U111" t="n">
         <v>1</v>
       </c>
+      <c r="V111" t="n">
+        <v>1</v>
+      </c>
       <c r="W111" t="n">
         <v>1</v>
       </c>
+      <c r="X111" t="n">
+        <v>1</v>
+      </c>
       <c r="Y111" t="n">
         <v>1</v>
       </c>
       <c r="Z111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA111" t="n">
         <v>1</v>
       </c>
       <c r="AB111" t="n">
@@ -7296,7 +7257,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Métodos físicos de separación de mezclas</t>
+          <t>Reacción química y sus evidencias</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7311,7 +7272,7 @@
         <v>10</v>
       </c>
       <c r="E112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F112" t="n">
         <v>8</v>
@@ -7320,11 +7281,14 @@
         <v>3</v>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
         <v>7</v>
       </c>
+      <c r="K112" t="n">
+        <v>9</v>
+      </c>
       <c r="L112" t="n">
         <v>9.5</v>
       </c>
@@ -7340,12 +7304,15 @@
       <c r="R112" t="n">
         <v>1</v>
       </c>
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="n">
+        <v>1</v>
+      </c>
       <c r="U112" t="n">
         <v>1</v>
       </c>
-      <c r="V112" t="n">
-        <v>1</v>
-      </c>
       <c r="W112" t="n">
         <v>1</v>
       </c>
@@ -7353,6 +7320,9 @@
         <v>1</v>
       </c>
       <c r="Z112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB112" t="n">
         <v>1</v>
       </c>
       <c r="AC112" t="n">
@@ -7368,7 +7338,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sólidos cristalinos y amorfos</t>
+          <t>Métodos físicos de separación de mezclas</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7377,17 +7347,47 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
         <v>10</v>
       </c>
+      <c r="E113" t="n">
+        <v>6</v>
+      </c>
+      <c r="F113" t="n">
+        <v>8</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3</v>
+      </c>
+      <c r="I113" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" t="n">
+        <v>7</v>
+      </c>
       <c r="L113" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M113" t="n">
+        <v>7</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1</v>
+      </c>
+      <c r="P113" t="n">
+        <v>1</v>
+      </c>
+      <c r="R113" t="n">
+        <v>1</v>
       </c>
       <c r="U113" t="n">
         <v>1</v>
       </c>
+      <c r="V113" t="n">
+        <v>1</v>
+      </c>
       <c r="W113" t="n">
         <v>1</v>
       </c>
@@ -7397,23 +7397,20 @@
       <c r="Z113" t="n">
         <v>1</v>
       </c>
-      <c r="AA113" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB113" t="n">
-        <v>1</v>
-      </c>
       <c r="AC113" t="n">
         <v>1</v>
       </c>
       <c r="AD113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE113" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Solubilidad y disoluciones saturadas</t>
+          <t>Sólidos cristalinos y amorfos</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7422,47 +7419,20 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D114" t="n">
         <v>10</v>
       </c>
-      <c r="F114" t="n">
-        <v>8</v>
-      </c>
-      <c r="G114" t="n">
-        <v>3</v>
-      </c>
-      <c r="I114" t="n">
-        <v>4</v>
-      </c>
-      <c r="J114" t="n">
-        <v>7</v>
-      </c>
       <c r="L114" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M114" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O114" t="n">
-        <v>1</v>
-      </c>
-      <c r="R114" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U114" t="n">
         <v>1</v>
       </c>
-      <c r="V114" t="n">
-        <v>1</v>
-      </c>
       <c r="W114" t="n">
         <v>1</v>
       </c>
-      <c r="X114" t="n">
-        <v>1</v>
-      </c>
       <c r="Y114" t="n">
         <v>1</v>
       </c>
@@ -7472,20 +7442,20 @@
       <c r="AA114" t="n">
         <v>1</v>
       </c>
+      <c r="AB114" t="n">
+        <v>1</v>
+      </c>
       <c r="AC114" t="n">
         <v>1</v>
       </c>
       <c r="AD114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE114" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sustancias puras: elementos y compuestos</t>
+          <t>Solubilidad y disoluciones saturadas</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7494,50 +7464,35 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
-        <v>9</v>
-      </c>
-      <c r="E115" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F115" t="n">
         <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I115" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
         <v>7</v>
       </c>
-      <c r="K115" t="n">
-        <v>8</v>
-      </c>
       <c r="L115" t="n">
         <v>9.5</v>
       </c>
       <c r="M115" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="P115" t="n">
-        <v>1</v>
-      </c>
       <c r="R115" t="n">
         <v>1</v>
       </c>
-      <c r="S115" t="n">
-        <v>1</v>
-      </c>
-      <c r="T115" t="n">
-        <v>1</v>
-      </c>
       <c r="U115" t="n">
         <v>1</v>
       </c>
@@ -7547,23 +7502,32 @@
       <c r="W115" t="n">
         <v>1</v>
       </c>
+      <c r="X115" t="n">
+        <v>1</v>
+      </c>
       <c r="Y115" t="n">
         <v>1</v>
       </c>
       <c r="Z115" t="n">
         <v>1</v>
       </c>
+      <c r="AA115" t="n">
+        <v>1</v>
+      </c>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE115" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Organización de la tabla periódica</t>
+          <t>Sustancias puras: elementos y compuestos</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7572,13 +7536,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E116" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F116" t="n">
         <v>8</v>
@@ -7587,7 +7551,7 @@
         <v>6</v>
       </c>
       <c r="I116" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="J116" t="n">
         <v>7</v>
@@ -7601,9 +7565,6 @@
       <c r="M116" t="n">
         <v>7</v>
       </c>
-      <c r="N116" t="n">
-        <v>1</v>
-      </c>
       <c r="O116" t="n">
         <v>1</v>
       </c>
@@ -7628,32 +7589,23 @@
       <c r="W116" t="n">
         <v>1</v>
       </c>
-      <c r="X116" t="n">
-        <v>1</v>
-      </c>
       <c r="Y116" t="n">
         <v>1</v>
       </c>
       <c r="Z116" t="n">
         <v>1</v>
       </c>
-      <c r="AA116" t="n">
-        <v>1</v>
-      </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE116" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Tipo de enlace y propiedades de las sustancias</t>
+          <t>Organización de la tabla periódica</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7662,22 +7614,28 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D117" t="n">
         <v>10</v>
       </c>
+      <c r="E117" t="n">
+        <v>9</v>
+      </c>
       <c r="F117" t="n">
         <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I117" t="n">
         <v>9.5</v>
       </c>
       <c r="J117" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K117" t="n">
+        <v>8</v>
       </c>
       <c r="L117" t="n">
         <v>9.5</v>
@@ -7685,6 +7643,9 @@
       <c r="M117" t="n">
         <v>7</v>
       </c>
+      <c r="N117" t="n">
+        <v>1</v>
+      </c>
       <c r="O117" t="n">
         <v>1</v>
       </c>
@@ -7697,6 +7658,9 @@
       <c r="S117" t="n">
         <v>1</v>
       </c>
+      <c r="T117" t="n">
+        <v>1</v>
+      </c>
       <c r="U117" t="n">
         <v>1</v>
       </c>
@@ -7716,9 +7680,6 @@
         <v>1</v>
       </c>
       <c r="AA117" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB117" t="n">
         <v>1</v>
       </c>
       <c r="AC117" t="n">
@@ -7734,7 +7695,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Clasificación de las reacciones químicas</t>
+          <t>Tipo de enlace y propiedades de las sustancias</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7748,26 +7709,23 @@
       <c r="D118" t="n">
         <v>10</v>
       </c>
-      <c r="E118" t="n">
-        <v>9</v>
-      </c>
       <c r="F118" t="n">
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I118" t="n">
-        <v>7</v>
-      </c>
-      <c r="K118" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J118" t="n">
         <v>9</v>
       </c>
       <c r="L118" t="n">
         <v>9.5</v>
       </c>
-      <c r="N118" t="n">
-        <v>1</v>
+      <c r="M118" t="n">
+        <v>7</v>
       </c>
       <c r="O118" t="n">
         <v>1</v>
@@ -7775,32 +7733,50 @@
       <c r="P118" t="n">
         <v>1</v>
       </c>
-      <c r="T118" t="n">
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" t="n">
         <v>1</v>
       </c>
       <c r="U118" t="n">
         <v>1</v>
       </c>
+      <c r="V118" t="n">
+        <v>1</v>
+      </c>
       <c r="W118" t="n">
         <v>1</v>
       </c>
       <c r="X118" t="n">
         <v>1</v>
       </c>
+      <c r="Y118" t="n">
+        <v>1</v>
+      </c>
       <c r="Z118" t="n">
         <v>1</v>
       </c>
+      <c r="AA118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1</v>
+      </c>
       <c r="AC118" t="n">
         <v>1</v>
       </c>
       <c r="AD118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE118" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7809,27 +7785,42 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D119" t="n">
         <v>10</v>
       </c>
+      <c r="E119" t="n">
+        <v>9</v>
+      </c>
       <c r="F119" t="n">
         <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M119" t="n">
+        <v>6</v>
+      </c>
+      <c r="I119" t="n">
         <v>7</v>
       </c>
+      <c r="K119" t="n">
+        <v>9</v>
+      </c>
+      <c r="L119" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1</v>
+      </c>
       <c r="O119" t="n">
         <v>1</v>
       </c>
       <c r="P119" t="n">
         <v>1</v>
       </c>
-      <c r="V119" t="n">
+      <c r="T119" t="n">
+        <v>1</v>
+      </c>
+      <c r="U119" t="n">
         <v>1</v>
       </c>
       <c r="W119" t="n">
@@ -7838,40 +7829,49 @@
       <c r="X119" t="n">
         <v>1</v>
       </c>
-      <c r="Y119" t="n">
-        <v>1</v>
-      </c>
       <c r="Z119" t="n">
         <v>1</v>
       </c>
       <c r="AC119" t="n">
         <v>1</v>
       </c>
-      <c r="AE119" t="n">
+      <c r="AD119" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Configuración electrónica por orbitales</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
         <v>10</v>
       </c>
-      <c r="L120" t="n">
-        <v>11</v>
-      </c>
-      <c r="U120" t="n">
+      <c r="F120" t="n">
+        <v>8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M120" t="n">
+        <v>7</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" t="n">
+        <v>1</v>
+      </c>
+      <c r="V120" t="n">
         <v>1</v>
       </c>
       <c r="W120" t="n">
@@ -7883,13 +7883,10 @@
       <c r="Y120" t="n">
         <v>1</v>
       </c>
-      <c r="AA120" t="n">
+      <c r="Z120" t="n">
         <v>1</v>
       </c>
       <c r="AC120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD120" t="n">
         <v>1</v>
       </c>
       <c r="AE120" t="n">

--- a/internacional/Contraste_quimica.xlsx
+++ b/internacional/Contraste_quimica.xlsx
@@ -767,7 +767,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Metales, cerámicas y materiales compuestos</t>
+          <t>Autoionización del agua, Kw y cálculo de pH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -776,27 +776,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="L4" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
         <v>7</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
@@ -808,12 +805,21 @@
       <c r="V4" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
       <c r="AB4" t="n">
         <v>1</v>
       </c>
@@ -827,11 +833,11 @@
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -843,7 +849,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Conservación de la masa</t>
+          <t>Celdas galvánicas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -852,31 +858,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I5" t="n">
         <v>8</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9.5</v>
       </c>
       <c r="M5" t="n">
         <v>7</v>
@@ -884,30 +875,27 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
       <c r="AB5" t="n">
         <v>1</v>
       </c>
@@ -921,7 +909,7 @@
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -937,7 +925,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>El carbono y las moléculas orgánicas</t>
+          <t>Metales, cerámicas y materiales compuestos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -955,7 +943,10 @@
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>9.5</v>
@@ -966,16 +957,13 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
@@ -984,9 +972,6 @@
       <c r="Z6" t="n">
         <v>1</v>
       </c>
-      <c r="AA6" t="n">
-        <v>1</v>
-      </c>
       <c r="AB6" t="n">
         <v>1</v>
       </c>
@@ -1000,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1016,7 +1001,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Electrólisis y celdas electrolíticas</t>
+          <t>Conservación de la masa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1025,19 +1010,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
       <c r="F7" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.5</v>
       </c>
       <c r="M7" t="n">
         <v>7</v>
@@ -1048,19 +1045,25 @@
       <c r="P7" t="n">
         <v>1</v>
       </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
       <c r="Y7" t="n">
         <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
         <v>1</v>
       </c>
       <c r="AB7" t="n">
@@ -1080,7 +1083,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1092,7 +1095,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Electrolitos fuertes y débiles</t>
+          <t>El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1101,10 +1104,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
@@ -1112,11 +1115,8 @@
       <c r="G8" t="n">
         <v>8.5</v>
       </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
         <v>7</v>
@@ -1130,7 +1130,10 @@
       <c r="U8" t="n">
         <v>1</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
@@ -1139,6 +1142,9 @@
       <c r="Z8" t="n">
         <v>1</v>
       </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
       <c r="AB8" t="n">
         <v>1</v>
       </c>
@@ -1148,8 +1154,11 @@
       <c r="AD8" t="n">
         <v>1</v>
       </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1165,7 +1174,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Energía de activación y perfil energético</t>
+          <t>Electrólisis y celdas electrolíticas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1174,7 +1183,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
@@ -1185,8 +1194,11 @@
       <c r="G9" t="n">
         <v>8.5</v>
       </c>
-      <c r="L9" t="n">
-        <v>9.5</v>
+      <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1194,9 +1206,6 @@
       <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
@@ -1207,6 +1216,9 @@
         <v>1</v>
       </c>
       <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
@@ -1226,7 +1238,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1238,7 +1250,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Enlace químico</t>
+          <t>Electrolitos fuertes y débiles</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1247,10 +1259,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
@@ -1258,60 +1270,48 @@
       <c r="G10" t="n">
         <v>8.5</v>
       </c>
-      <c r="J10" t="n">
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
         <v>9</v>
       </c>
-      <c r="L10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>10</v>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
+          <t>Energía de activación y perfil energético</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1332,22 +1332,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G11" t="n">
         <v>8.5</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
-      </c>
-      <c r="M11" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1358,9 +1355,6 @@
       <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V11" t="n">
-        <v>1</v>
-      </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
@@ -1371,9 +1365,6 @@
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
         <v>1</v>
       </c>
       <c r="AB11" t="n">
@@ -1393,7 +1384,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -1405,7 +1396,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Equilibrio químico dinámico</t>
+          <t>Energía de enlace</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1414,10 +1405,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
         <v>10.5</v>
@@ -1425,14 +1416,8 @@
       <c r="G12" t="n">
         <v>8.5</v>
       </c>
-      <c r="K12" t="n">
-        <v>8</v>
-      </c>
       <c r="L12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M12" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1443,9 +1428,6 @@
       <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
@@ -1461,9 +1443,6 @@
       <c r="AA12" t="n">
         <v>1</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
       <c r="AC12" t="n">
         <v>1</v>
       </c>
@@ -1474,11 +1453,11 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -1490,7 +1469,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Equilibrio y rapidez en procesos industriales</t>
+          <t>Enlace químico</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1499,19 +1478,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>8.5</v>
       </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
       <c r="L13" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1519,7 +1504,19 @@
       <c r="P13" t="n">
         <v>1</v>
       </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
       <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="n">
@@ -1545,19 +1542,19 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fuerza de ácidos y bases: Ka y Kb</t>
+          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1566,10 +1563,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
@@ -1577,11 +1574,8 @@
       <c r="G14" t="n">
         <v>8.5</v>
       </c>
-      <c r="I14" t="n">
-        <v>9.5</v>
-      </c>
       <c r="L14" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M14" t="n">
         <v>7</v>
@@ -1592,9 +1586,6 @@
       <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
       <c r="U14" t="n">
         <v>1</v>
       </c>
@@ -1629,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -1645,7 +1636,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Equilibrio químico dinámico</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1654,32 +1645,71 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11</v>
+      </c>
+      <c r="M15" t="n">
         <v>7</v>
       </c>
-      <c r="J15" t="n">
-        <v>7</v>
-      </c>
-      <c r="M15" t="n">
-        <v>9.5</v>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
       </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
       <c r="AC15" t="n">
         <v>1</v>
       </c>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
       <c r="AF15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -1691,7 +1721,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Neutralización y reacciones de los ácidos</t>
+          <t>Equilibrio y rapidez en procesos industriales</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1706,25 +1736,13 @@
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="L16" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1732,21 +1750,9 @@
       <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
       <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
       <c r="Y16" t="n">
         <v>1</v>
       </c>
@@ -1766,23 +1772,23 @@
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Esterificación e hidrólisis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1791,7 +1797,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
@@ -1799,43 +1805,31 @@
       <c r="F17" t="n">
         <v>10.5</v>
       </c>
-      <c r="G17" t="n">
-        <v>8.5</v>
-      </c>
       <c r="L17" t="n">
-        <v>9.5</v>
+        <v>11</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
       <c r="Y17" t="n">
         <v>1</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
       <c r="AC17" t="n">
         <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE17" t="n">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
@@ -1843,7 +1837,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -1855,7 +1849,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Fuerza de ácidos y bases: Ka y Kb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1870,13 +1864,16 @@
         <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
         <v>8.5</v>
       </c>
+      <c r="I18" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L18" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M18" t="n">
         <v>7</v>
@@ -1887,7 +1884,13 @@
       <c r="P18" t="n">
         <v>1</v>
       </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
       <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
         <v>1</v>
       </c>
       <c r="W18" t="n">
@@ -1934,7 +1937,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Química de los carbohidratos</t>
+          <t>Grupos funcionales</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1943,35 +1946,32 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>9.5</v>
+        <v>8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.5</v>
       </c>
       <c r="L19" t="n">
         <v>9.5</v>
       </c>
       <c r="M19" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
+      <c r="P19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
       <c r="W19" t="n">
         <v>1</v>
       </c>
@@ -1987,12 +1987,24 @@
       <c r="AA19" t="n">
         <v>1</v>
       </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
       <c r="AF19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2004,7 +2016,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Radiactividad y emisiones nucleares</t>
+          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2013,35 +2025,62 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="n">
+        <v>11</v>
+      </c>
+      <c r="F20" t="n">
         <v>8</v>
       </c>
       <c r="G20" t="n">
         <v>8.5</v>
       </c>
-      <c r="I20" t="n">
+      <c r="L20" t="n">
         <v>9.5</v>
       </c>
-      <c r="R20" t="n">
+      <c r="M20" t="n">
+        <v>7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
         <v>1</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
       <c r="AC20" t="n">
         <v>1</v>
       </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
       <c r="AF20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -2053,7 +2092,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Factores que afectan la rapidez de reacción</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2062,41 +2101,26 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
-      </c>
-      <c r="E21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
-      <c r="G21" t="n">
-        <v>8.5</v>
-      </c>
       <c r="L21" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M21" t="n">
         <v>7</v>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
@@ -2112,9 +2136,6 @@
       <c r="AA21" t="n">
         <v>1</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
       <c r="AC21" t="n">
         <v>1</v>
       </c>
@@ -2125,11 +2146,11 @@
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2141,7 +2162,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reacciones exotérmicas y endotérmicas</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2155,73 +2176,19 @@
       <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>8</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6</v>
-      </c>
       <c r="I22" t="n">
         <v>7</v>
       </c>
       <c r="J22" t="n">
         <v>7</v>
       </c>
-      <c r="K22" t="n">
-        <v>9</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>9.5</v>
       </c>
-      <c r="M22" t="n">
-        <v>7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="W22" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
@@ -2241,7 +2208,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Redes covalentes y alótropos del carbono</t>
+          <t>Neutralización y reacciones de los ácidos</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2250,16 +2217,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>9</v>
       </c>
       <c r="L23" t="n">
         <v>9.5</v>
@@ -2273,6 +2249,15 @@
       <c r="P23" t="n">
         <v>1</v>
       </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
@@ -2285,11 +2270,20 @@
       <c r="Z23" t="n">
         <v>1</v>
       </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
       <c r="AD23" t="n">
         <v>1</v>
       </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
       <c r="AF23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -2305,7 +2299,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Teoría cinética de los gases</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2314,50 +2308,41 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
         <v>10.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
-      </c>
-      <c r="I24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L24" t="n">
         <v>9.5</v>
       </c>
-      <c r="J24" t="n">
-        <v>7</v>
-      </c>
-      <c r="M24" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="U24" t="n">
         <v>1</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
       <c r="Y24" t="n">
         <v>1</v>
       </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
-      <c r="AA24" t="n">
-        <v>1</v>
-      </c>
       <c r="AB24" t="n">
         <v>1</v>
       </c>
@@ -2371,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -2387,7 +2372,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Teoría de colisiones</t>
+          <t>Oxidación y reducción</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2396,19 +2381,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9</v>
       </c>
       <c r="L25" t="n">
         <v>9.5</v>
@@ -2416,15 +2404,18 @@
       <c r="M25" t="n">
         <v>7</v>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
@@ -2459,7 +2450,7 @@
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -2468,14 +2459,14 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2484,23 +2475,14 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
-      <c r="G26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I26" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>9</v>
-      </c>
       <c r="L26" t="n">
         <v>9.5</v>
       </c>
@@ -2510,48 +2492,27 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1</v>
-      </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1</v>
-      </c>
       <c r="AC26" t="n">
         <v>1</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
       <c r="AF26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -2563,12 +2524,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Autoionización del agua, Kw y cálculo de pH</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2577,28 +2538,25 @@
       <c r="D27" t="n">
         <v>9</v>
       </c>
+      <c r="F27" t="n">
+        <v>10.5</v>
+      </c>
       <c r="G27" t="n">
         <v>8.5</v>
       </c>
-      <c r="I27" t="n">
-        <v>9.5</v>
-      </c>
       <c r="L27" t="n">
         <v>11</v>
       </c>
       <c r="M27" t="n">
         <v>7</v>
       </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
       <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
         <v>1</v>
       </c>
       <c r="W27" t="n">
@@ -2633,7 +2591,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -2645,82 +2603,61 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cambios físicos y químicos</t>
+          <t>Química de los carbohidratos</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
       <c r="F28" t="n">
-        <v>8</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="I28" t="n">
         <v>9.5</v>
       </c>
-      <c r="J28" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" t="n">
-        <v>8</v>
-      </c>
       <c r="L28" t="n">
         <v>9.5</v>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
       <c r="Y28" t="n">
         <v>1</v>
       </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD28" t="n">
+      <c r="AA28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -2729,153 +2666,120 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Catalizadores</t>
+          <t>Química verde y economía atómica</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="F29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8</v>
       </c>
       <c r="L29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
         <v>11</v>
       </c>
-      <c r="M29" t="n">
-        <v>7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>10</v>
-      </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Celdas galvánicas</t>
+          <t>Radiactividad y emisiones nucleares</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
-      </c>
-      <c r="F30" t="n">
-        <v>10.5</v>
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8.5</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
-      </c>
-      <c r="M30" t="n">
-        <v>7</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
       <c r="W30" t="n">
         <v>1</v>
       </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1</v>
-      </c>
       <c r="AC30" t="n">
         <v>1</v>
       </c>
-      <c r="AD30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1</v>
-      </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -2884,32 +2788,47 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Composición porcentual y fórmulas empírica y molecular</t>
+          <t>Factores que afectan la rapidez de reacción</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
       </c>
       <c r="G31" t="n">
         <v>8.5</v>
       </c>
       <c r="L31" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2917,23 +2836,38 @@
       <c r="U31" t="n">
         <v>1</v>
       </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
       <c r="Y31" t="n">
         <v>1</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
       </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1</v>
+      </c>
       <c r="AC31" t="n">
         <v>1</v>
       </c>
       <c r="AD31" t="n">
         <v>1</v>
       </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
       <c r="AF31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2942,29 +2876,32 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cromatografía</t>
+          <t>Reacciones de precipitación e identificación de iones</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10.5</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I32" t="n">
         <v>9.5</v>
@@ -2975,7 +2912,7 @@
       <c r="M32" t="n">
         <v>7</v>
       </c>
-      <c r="P32" t="n">
+      <c r="O32" t="n">
         <v>1</v>
       </c>
       <c r="R32" t="n">
@@ -2984,9 +2921,6 @@
       <c r="U32" t="n">
         <v>1</v>
       </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
       <c r="W32" t="n">
         <v>1</v>
       </c>
@@ -2996,7 +2930,13 @@
       <c r="Z32" t="n">
         <v>1</v>
       </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
       <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
@@ -3016,27 +2956,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Diagramas de fases</t>
+          <t>Reacciones exotérmicas y endotérmicas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
         <v>10</v>
       </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>9</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M33" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
       <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
@@ -3044,48 +3044,63 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Redes covalentes y alótropos del carbono</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
         <v>10</v>
       </c>
-      <c r="J34" t="n">
+      <c r="F34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M34" t="n">
         <v>7</v>
       </c>
-      <c r="AA34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC34" t="n">
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
@@ -3093,24 +3108,24 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Energía de enlace</t>
+          <t>Semivida, series de desintegración y residuos radiactivos</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -3120,23 +3135,35 @@
         <v>10</v>
       </c>
       <c r="F35" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>8.5</v>
       </c>
+      <c r="I35" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L35" t="n">
         <v>9.5</v>
       </c>
+      <c r="M35" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
       <c r="U35" t="n">
         <v>1</v>
       </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
       <c r="W35" t="n">
         <v>1</v>
       </c>
@@ -3162,35 +3189,62 @@
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Espectrometría de masas</t>
+          <t>Teoría cinética de los gases</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="M36" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
       </c>
       <c r="W36" t="n">
         <v>1</v>
@@ -3201,79 +3255,154 @@
       <c r="Z36" t="n">
         <v>1</v>
       </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>10</v>
+      </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Técnicas para determinar estructuras orgánicas</t>
+          <t>Teoría de colisiones</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="E37" t="n">
+        <v>9</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>7</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
       </c>
       <c r="W37" t="n">
         <v>1</v>
       </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
       <c r="Y37" t="n">
         <v>1</v>
       </c>
       <c r="Z37" t="n">
         <v>1</v>
       </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
       <c r="AC37" t="n">
         <v>1</v>
       </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>10</v>
+      </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Esterificación e hidrólisis</t>
+          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F38" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>9</v>
       </c>
       <c r="L38" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M38" t="n">
         <v>7</v>
@@ -3281,30 +3410,48 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
       <c r="U38" t="n">
         <v>1</v>
       </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
       <c r="W38" t="n">
         <v>1</v>
       </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
       <c r="Y38" t="n">
         <v>1</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
       <c r="AC38" t="n">
         <v>1</v>
       </c>
       <c r="AD38" t="n">
         <v>1</v>
       </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
       <c r="AF38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -3316,27 +3463,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fundamentos de la reactividad orgánica</t>
+          <t>Técnicas para determinar estructuras orgánicas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" t="n">
         <v>11</v>
       </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="X39" t="n">
+      <c r="W39" t="n">
         <v>1</v>
       </c>
       <c r="Y39" t="n">
@@ -3345,191 +3486,128 @@
       <c r="Z39" t="n">
         <v>1</v>
       </c>
-      <c r="AD39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>11</v>
+      <c r="AC39" t="n">
+        <v>1</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Grupos funcionales</t>
+          <t>Disolución y rapidez de disolución</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
-      </c>
-      <c r="F40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L40" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>7</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
-      <c r="AB40" t="n">
-        <v>1</v>
-      </c>
       <c r="AC40" t="n">
         <v>1</v>
       </c>
-      <c r="AD40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1</v>
-      </c>
       <c r="AF40" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
+          <t>Minerales: composición y estructura cristalina</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
-      </c>
-      <c r="D41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F41" t="n">
         <v>8</v>
       </c>
-      <c r="G41" t="n">
-        <v>8.5</v>
+      <c r="J41" t="n">
+        <v>9</v>
       </c>
       <c r="L41" t="n">
         <v>9.5</v>
       </c>
-      <c r="M41" t="n">
-        <v>7</v>
-      </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="P41" t="n">
+      <c r="S41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
-      <c r="W41" t="n">
-        <v>1</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
       <c r="Z41" t="n">
         <v>1</v>
       </c>
       <c r="AA41" t="n">
         <v>1</v>
       </c>
-      <c r="AC41" t="n">
-        <v>1</v>
-      </c>
       <c r="AD41" t="n">
         <v>1</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1</v>
-      </c>
       <c r="AF41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
         <v>10</v>
@@ -3537,8 +3615,14 @@
       <c r="F42" t="n">
         <v>8</v>
       </c>
-      <c r="L42" t="n">
-        <v>11</v>
+      <c r="G42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>9</v>
       </c>
       <c r="M42" t="n">
         <v>7</v>
@@ -3546,10 +3630,13 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="U42" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" t="n">
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="X42" t="n">
@@ -3561,9 +3648,6 @@
       <c r="Z42" t="n">
         <v>1</v>
       </c>
-      <c r="AA42" t="n">
-        <v>1</v>
-      </c>
       <c r="AC42" t="n">
         <v>1</v>
       </c>
@@ -3574,41 +3658,44 @@
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Oxidación y corrosión de los metales</t>
+          <t>Ácidos y bases: propiedades</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J43" t="n">
         <v>9</v>
@@ -3625,6 +3712,9 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
       <c r="R43" t="n">
         <v>1</v>
       </c>
@@ -3637,6 +3727,9 @@
       <c r="U43" t="n">
         <v>1</v>
       </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
       <c r="W43" t="n">
         <v>1</v>
       </c>
@@ -3653,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3662,26 +3755,29 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Oxidación y reducción</t>
+          <t>Átomo y partículas subatómicas</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -3690,10 +3786,13 @@
         <v>6</v>
       </c>
       <c r="I44" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" t="n">
         <v>7</v>
       </c>
-      <c r="J44" t="n">
-        <v>9</v>
+      <c r="K44" t="n">
+        <v>8</v>
       </c>
       <c r="L44" t="n">
         <v>9.5</v>
@@ -3701,6 +3800,9 @@
       <c r="M44" t="n">
         <v>7</v>
       </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
@@ -3710,7 +3812,7 @@
       <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
@@ -3731,12 +3833,6 @@
       <c r="Z44" t="n">
         <v>1</v>
       </c>
-      <c r="AA44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1</v>
-      </c>
       <c r="AC44" t="n">
         <v>1</v>
       </c>
@@ -3747,39 +3843,51 @@
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
       </c>
       <c r="F45" t="n">
         <v>8</v>
       </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
       <c r="L45" t="n">
         <v>9.5</v>
       </c>
@@ -3789,15 +3897,36 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
       <c r="U45" t="n">
         <v>1</v>
       </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
+      <c r="X45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1</v>
+      </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
+      <c r="AA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1</v>
+      </c>
       <c r="AC45" t="n">
         <v>1</v>
       </c>
@@ -3805,65 +3934,98 @@
         <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Cambios físicos y químicos</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>10</v>
       </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
       <c r="F46" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
       </c>
       <c r="I46" t="n">
         <v>9.5</v>
       </c>
+      <c r="J46" t="n">
+        <v>7</v>
+      </c>
+      <c r="K46" t="n">
+        <v>8</v>
+      </c>
       <c r="L46" t="n">
         <v>9.5</v>
       </c>
+      <c r="M46" t="n">
+        <v>7</v>
+      </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
       <c r="R46" t="n">
         <v>1</v>
       </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
       <c r="U46" t="n">
         <v>1</v>
       </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1</v>
+      </c>
       <c r="Z46" t="n">
         <v>1</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
         <v>1</v>
       </c>
       <c r="AD46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3872,38 +4034,41 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Química verde y economía atómica</t>
+          <t>Catalizadores</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" t="n">
         <v>11</v>
       </c>
-      <c r="D47" t="n">
-        <v>11</v>
-      </c>
-      <c r="G47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K47" t="n">
-        <v>8</v>
-      </c>
-      <c r="L47" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M47" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3911,9 +4076,6 @@
       <c r="U47" t="n">
         <v>1</v>
       </c>
-      <c r="V47" t="n">
-        <v>1</v>
-      </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
@@ -3926,54 +4088,60 @@
       <c r="Z47" t="n">
         <v>1</v>
       </c>
+      <c r="AA47" t="n">
+        <v>1</v>
+      </c>
       <c r="AB47" t="n">
         <v>1</v>
       </c>
       <c r="AC47" t="n">
         <v>1</v>
       </c>
+      <c r="AD47" t="n">
+        <v>1</v>
+      </c>
       <c r="AE47" t="n">
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Reacciones de precipitación e identificación de iones</t>
+          <t>Combustibles fósiles y biocombustibles</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
         <v>9</v>
       </c>
       <c r="F48" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I48" t="n">
-        <v>9.5</v>
+        <v>6</v>
+      </c>
+      <c r="K48" t="n">
+        <v>9</v>
       </c>
       <c r="L48" t="n">
         <v>9.5</v>
@@ -3984,21 +4152,33 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="R48" t="n">
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>1</v>
       </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
       <c r="W48" t="n">
         <v>1</v>
       </c>
+      <c r="X48" t="n">
+        <v>1</v>
+      </c>
       <c r="Y48" t="n">
         <v>1</v>
       </c>
       <c r="Z48" t="n">
         <v>1</v>
       </c>
+      <c r="AB48" t="n">
+        <v>1</v>
+      </c>
       <c r="AC48" t="n">
         <v>1</v>
       </c>
@@ -4009,54 +4189,84 @@
         <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rendimiento de una reacción</t>
+          <t>Combustión</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>9</v>
+      </c>
+      <c r="E49" t="n">
         <v>8</v>
       </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
       <c r="F49" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>9</v>
+      </c>
+      <c r="L49" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>7</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
-      <c r="X49" t="n">
-        <v>1</v>
-      </c>
       <c r="Y49" t="n">
         <v>1</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
+      <c r="AB49" t="n">
+        <v>1</v>
+      </c>
       <c r="AC49" t="n">
         <v>1</v>
       </c>
@@ -4067,7 +4277,7 @@
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -4076,26 +4286,26 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Semivida, series de desintegración y residuos radiactivos</t>
+          <t>Composición del aire y contaminantes atmosféricos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F50" t="n">
         <v>8</v>
@@ -4104,47 +4314,29 @@
         <v>8.5</v>
       </c>
       <c r="I50" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="L50" t="n">
         <v>9.5</v>
       </c>
-      <c r="M50" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O50" t="n">
         <v>1</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
       <c r="U50" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="n">
-        <v>1</v>
-      </c>
       <c r="W50" t="n">
         <v>1</v>
       </c>
       <c r="X50" t="n">
         <v>1</v>
       </c>
-      <c r="Y50" t="n">
-        <v>1</v>
-      </c>
       <c r="Z50" t="n">
         <v>1</v>
       </c>
-      <c r="AA50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1</v>
-      </c>
       <c r="AD50" t="n">
         <v>1</v>
       </c>
@@ -4152,43 +4344,79 @@
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Disolución y rapidez de disolución</t>
+          <t>Soluto, disolvente y concentración</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M51" t="n">
+        <v>7</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" t="n">
         <v>1</v>
       </c>
+      <c r="AB51" t="n">
+        <v>1</v>
+      </c>
       <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
         <v>1</v>
       </c>
       <c r="AF51" t="n">
@@ -4201,110 +4429,104 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Minerales: composición y estructura cristalina</t>
+          <t>Configuración electrónica por orbitales</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
-      </c>
-      <c r="F52" t="n">
-        <v>8</v>
-      </c>
-      <c r="J52" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
       </c>
       <c r="L52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U52" t="n">
         <v>1</v>
       </c>
-      <c r="Z52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA52" t="n">
+      <c r="X52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC52" t="n">
         <v>1</v>
       </c>
       <c r="AD52" t="n">
         <v>1</v>
       </c>
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
       <c r="AF52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+          <t>Cromatografía</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
         <v>10</v>
       </c>
-      <c r="F53" t="n">
-        <v>8</v>
-      </c>
       <c r="G53" t="n">
         <v>6</v>
       </c>
       <c r="I53" t="n">
         <v>9.5</v>
       </c>
-      <c r="K53" t="n">
-        <v>9</v>
+      <c r="L53" t="n">
+        <v>9.5</v>
       </c>
       <c r="M53" t="n">
         <v>7</v>
       </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
       </c>
-      <c r="T53" t="n">
-        <v>1</v>
-      </c>
-      <c r="X53" t="n">
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>1</v>
       </c>
       <c r="Y53" t="n">
@@ -4313,33 +4535,27 @@
       <c r="Z53" t="n">
         <v>1</v>
       </c>
-      <c r="AC53" t="n">
-        <v>1</v>
-      </c>
       <c r="AD53" t="n">
         <v>1</v>
       </c>
-      <c r="AE53" t="n">
-        <v>1</v>
-      </c>
       <c r="AF53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ácidos y bases: propiedades</t>
+          <t>Densidad y flotación</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4348,7 +4564,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
         <v>9</v>
@@ -4360,13 +4576,10 @@
         <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>9</v>
-      </c>
-      <c r="K54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L54" t="n">
         <v>9.5</v>
@@ -4380,38 +4593,20 @@
       <c r="P54" t="n">
         <v>1</v>
       </c>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
       <c r="U54" t="n">
         <v>1</v>
       </c>
-      <c r="V54" t="n">
-        <v>1</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1</v>
-      </c>
       <c r="Y54" t="n">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
-      <c r="AC54" t="n">
-        <v>1</v>
-      </c>
       <c r="AD54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -4427,7 +4622,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Átomo y partículas subatómicas</t>
+          <t>Disoluciones, coloides y suspensiones</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4436,79 +4631,34 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
-      </c>
-      <c r="E55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
         <v>8</v>
       </c>
-      <c r="G55" t="n">
-        <v>6</v>
-      </c>
-      <c r="I55" t="n">
-        <v>8</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7</v>
-      </c>
-      <c r="K55" t="n">
-        <v>8</v>
-      </c>
-      <c r="L55" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M55" t="n">
         <v>7</v>
       </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1</v>
-      </c>
       <c r="V55" t="n">
         <v>1</v>
       </c>
-      <c r="W55" t="n">
-        <v>1</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1</v>
-      </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
       <c r="AC55" t="n">
         <v>1</v>
       </c>
-      <c r="AD55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1</v>
-      </c>
       <c r="AF55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4524,7 +4674,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Distribución electrónica por niveles (modelo de capas)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4539,25 +4689,28 @@
         <v>9</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J56" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="K56" t="n">
+        <v>8</v>
       </c>
       <c r="L56" t="n">
         <v>9.5</v>
       </c>
-      <c r="M56" t="n">
-        <v>7</v>
+      <c r="N56" t="n">
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -4568,12 +4721,12 @@
       <c r="R56" t="n">
         <v>1</v>
       </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
       <c r="U56" t="n">
         <v>1</v>
       </c>
-      <c r="V56" t="n">
-        <v>1</v>
-      </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
@@ -4589,9 +4742,6 @@
       <c r="AA56" t="n">
         <v>1</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1</v>
-      </c>
       <c r="AC56" t="n">
         <v>1</v>
       </c>
@@ -4599,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4615,7 +4765,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Combustibles fósiles y biocombustibles</t>
+          <t>Ecuación química y su balanceo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4624,17 +4774,26 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
         <v>9</v>
       </c>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
       <c r="F57" t="n">
         <v>8</v>
       </c>
       <c r="G57" t="n">
         <v>6</v>
       </c>
+      <c r="I57" t="n">
+        <v>7</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7</v>
+      </c>
       <c r="K57" t="n">
         <v>9</v>
       </c>
@@ -4650,6 +4809,9 @@
       <c r="P57" t="n">
         <v>1</v>
       </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
@@ -4700,7 +4862,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Combustión</t>
+          <t>Electronegatividad y polaridad de enlace</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4709,70 +4871,46 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
-      </c>
-      <c r="E58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
-      </c>
-      <c r="G58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>11</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="n">
         <v>6</v>
-      </c>
-      <c r="I58" t="n">
-        <v>5</v>
-      </c>
-      <c r="J58" t="n">
-        <v>9</v>
-      </c>
-      <c r="L58" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
-      <c r="S58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>7</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -4788,7 +4926,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Composición del aire y contaminantes atmosféricos</t>
+          <t>Electrones de valencia y regla del octeto</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4797,19 +4935,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G59" t="n">
         <v>8.5</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>9.5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>9</v>
       </c>
       <c r="L59" t="n">
         <v>9.5</v>
@@ -4820,26 +4961,35 @@
       <c r="P59" t="n">
         <v>1</v>
       </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
       <c r="U59" t="n">
         <v>1</v>
       </c>
       <c r="W59" t="n">
         <v>1</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Y59" t="n">
         <v>1</v>
       </c>
       <c r="Z59" t="n">
         <v>1</v>
       </c>
+      <c r="AB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1</v>
+      </c>
       <c r="AD59" t="n">
         <v>1</v>
       </c>
-      <c r="AE59" t="n">
-        <v>1</v>
-      </c>
       <c r="AF59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -4855,7 +5005,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Soluto, disolvente y concentración</t>
+          <t>Enlace covalente</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4864,10 +5014,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
         <v>8</v>
@@ -4875,11 +5025,17 @@
       <c r="G60" t="n">
         <v>8.5</v>
       </c>
+      <c r="I60" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J60" t="n">
+        <v>9</v>
+      </c>
       <c r="L60" t="n">
         <v>9.5</v>
       </c>
       <c r="M60" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
@@ -4887,6 +5043,12 @@
       <c r="P60" t="n">
         <v>1</v>
       </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
       <c r="U60" t="n">
         <v>1</v>
       </c>
@@ -4902,9 +5064,6 @@
       <c r="Z60" t="n">
         <v>1</v>
       </c>
-      <c r="AA60" t="n">
-        <v>1</v>
-      </c>
       <c r="AB60" t="n">
         <v>1</v>
       </c>
@@ -4914,8 +5073,11 @@
       <c r="AD60" t="n">
         <v>1</v>
       </c>
+      <c r="AE60" t="n">
+        <v>1</v>
+      </c>
       <c r="AF60" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -4931,7 +5093,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Configuración electrónica por orbitales</t>
+          <t>Enlace iónico</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4945,25 +5107,58 @@
       <c r="D61" t="n">
         <v>10</v>
       </c>
+      <c r="F61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I61" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>9</v>
+      </c>
       <c r="L61" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
       </c>
       <c r="U61" t="n">
         <v>1</v>
       </c>
-      <c r="X61" t="n">
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>1</v>
       </c>
       <c r="Y61" t="n">
         <v>1</v>
       </c>
+      <c r="Z61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1</v>
+      </c>
       <c r="AC61" t="n">
         <v>1</v>
       </c>
       <c r="AD61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE61" t="n">
         <v>1</v>
       </c>
       <c r="AF61" t="n">
@@ -4983,7 +5178,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Densidad y flotación</t>
+          <t>Enlace metálico</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4992,49 +5187,67 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F62" t="n">
         <v>8</v>
       </c>
       <c r="G62" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L62" t="n">
         <v>9.5</v>
       </c>
-      <c r="M62" t="n">
-        <v>7</v>
-      </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
       <c r="P62" t="n">
         <v>1</v>
       </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
       <c r="U62" t="n">
         <v>1</v>
       </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1</v>
+      </c>
       <c r="Y62" t="n">
         <v>1</v>
       </c>
       <c r="Z62" t="n">
         <v>1</v>
       </c>
+      <c r="AB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1</v>
+      </c>
       <c r="AD62" t="n">
         <v>1</v>
       </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
       <c r="AF62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -5050,7 +5263,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Disoluciones, coloides y suspensiones</t>
+          <t>Escala de pH</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5059,34 +5272,73 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>8</v>
       </c>
+      <c r="G63" t="n">
+        <v>6</v>
+      </c>
+      <c r="I63" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>9</v>
+      </c>
+      <c r="L63" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M63" t="n">
         <v>7</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
       <c r="V63" t="n">
         <v>1</v>
       </c>
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1</v>
+      </c>
       <c r="Z63" t="n">
         <v>1</v>
       </c>
-      <c r="AA63" t="n">
+      <c r="AB63" t="n">
         <v>1</v>
       </c>
       <c r="AC63" t="n">
         <v>1</v>
       </c>
+      <c r="AD63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
       <c r="AF63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -5102,7 +5354,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Distribución electrónica por niveles (modelo de capas)</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5117,28 +5369,25 @@
         <v>9</v>
       </c>
       <c r="E64" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>8</v>
       </c>
       <c r="G64" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="I64" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
-        <v>9</v>
-      </c>
-      <c r="K64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L64" t="n">
         <v>9.5</v>
       </c>
-      <c r="N64" t="n">
-        <v>1</v>
+      <c r="M64" t="n">
+        <v>7</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -5149,18 +5398,9 @@
       <c r="R64" t="n">
         <v>1</v>
       </c>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
       <c r="U64" t="n">
         <v>1</v>
       </c>
-      <c r="W64" t="n">
-        <v>1</v>
-      </c>
-      <c r="X64" t="n">
-        <v>1</v>
-      </c>
       <c r="Y64" t="n">
         <v>1</v>
       </c>
@@ -5170,6 +5410,9 @@
       <c r="AA64" t="n">
         <v>1</v>
       </c>
+      <c r="AB64" t="n">
+        <v>1</v>
+      </c>
       <c r="AC64" t="n">
         <v>1</v>
       </c>
@@ -5177,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -5193,7 +5436,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ecuación química y su balanceo</t>
+          <t>Estequiometría</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5202,34 +5445,28 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
-      </c>
-      <c r="E65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
         <v>8</v>
       </c>
       <c r="G65" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J65" t="n">
         <v>7</v>
       </c>
-      <c r="K65" t="n">
-        <v>9</v>
-      </c>
       <c r="L65" t="n">
         <v>9.5</v>
       </c>
       <c r="M65" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -5240,9 +5477,6 @@
       <c r="R65" t="n">
         <v>1</v>
       </c>
-      <c r="T65" t="n">
-        <v>1</v>
-      </c>
       <c r="U65" t="n">
         <v>1</v>
       </c>
@@ -5261,6 +5495,9 @@
       <c r="Z65" t="n">
         <v>1</v>
       </c>
+      <c r="AA65" t="n">
+        <v>1</v>
+      </c>
       <c r="AB65" t="n">
         <v>1</v>
       </c>
@@ -5274,7 +5511,7 @@
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5290,7 +5527,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Electronegatividad y polaridad de enlace</t>
+          <t>Notación y estructuras de Lewis</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5307,10 +5544,16 @@
       <c r="F66" t="n">
         <v>10.5</v>
       </c>
+      <c r="G66" t="n">
+        <v>8.5</v>
+      </c>
       <c r="L66" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
         <v>1</v>
       </c>
       <c r="U66" t="n">
@@ -5354,7 +5597,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Electrones de valencia y regla del octeto</t>
+          <t>Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5374,39 +5617,42 @@
       <c r="G67" t="n">
         <v>8.5</v>
       </c>
-      <c r="I67" t="n">
-        <v>9.5</v>
-      </c>
       <c r="J67" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L67" t="n">
         <v>9.5</v>
       </c>
+      <c r="M67" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
       <c r="P67" t="n">
         <v>1</v>
       </c>
-      <c r="R67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S67" t="n">
-        <v>1</v>
-      </c>
       <c r="U67" t="n">
         <v>1</v>
       </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
       <c r="W67" t="n">
         <v>1</v>
       </c>
+      <c r="X67" t="n">
+        <v>1</v>
+      </c>
       <c r="Y67" t="n">
         <v>1</v>
       </c>
       <c r="Z67" t="n">
         <v>1</v>
       </c>
+      <c r="AA67" t="n">
+        <v>1</v>
+      </c>
       <c r="AB67" t="n">
         <v>1</v>
       </c>
@@ -5414,6 +5660,9 @@
         <v>1</v>
       </c>
       <c r="AD67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
@@ -5433,7 +5682,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enlace covalente</t>
+          <t>Fuerzas intermoleculares y propiedades físicas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5442,7 +5691,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
         <v>10</v>
@@ -5456,15 +5705,9 @@
       <c r="I68" t="n">
         <v>9.5</v>
       </c>
-      <c r="J68" t="n">
-        <v>9</v>
-      </c>
       <c r="L68" t="n">
         <v>9.5</v>
       </c>
-      <c r="M68" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
@@ -5474,22 +5717,22 @@
       <c r="R68" t="n">
         <v>1</v>
       </c>
-      <c r="S68" t="n">
-        <v>1</v>
-      </c>
       <c r="U68" t="n">
         <v>1</v>
       </c>
-      <c r="V68" t="n">
-        <v>1</v>
-      </c>
       <c r="W68" t="n">
         <v>1</v>
       </c>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
       <c r="Y68" t="n">
         <v>1</v>
       </c>
       <c r="Z68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA68" t="n">
         <v>1</v>
       </c>
       <c r="AB68" t="n">
@@ -5521,7 +5764,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Enlace iónico</t>
+          <t>Geometría molecular (RPECV)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5530,41 +5773,23 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
         <v>10</v>
       </c>
-      <c r="F69" t="n">
-        <v>8</v>
-      </c>
       <c r="G69" t="n">
         <v>8.5</v>
       </c>
-      <c r="I69" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J69" t="n">
-        <v>9</v>
-      </c>
       <c r="L69" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M69" t="n">
         <v>9.5</v>
       </c>
-      <c r="O69" t="n">
-        <v>1</v>
-      </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
-      <c r="R69" t="n">
-        <v>1</v>
-      </c>
-      <c r="S69" t="n">
-        <v>1</v>
-      </c>
       <c r="U69" t="n">
         <v>1</v>
       </c>
@@ -5574,6 +5799,9 @@
       <c r="W69" t="n">
         <v>1</v>
       </c>
+      <c r="X69" t="n">
+        <v>1</v>
+      </c>
       <c r="Y69" t="n">
         <v>1</v>
       </c>
@@ -5589,8 +5817,11 @@
       <c r="AD69" t="n">
         <v>1</v>
       </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
       <c r="AF69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -5606,7 +5837,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Enlace metálico</t>
+          <t>Iones</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5615,7 +5846,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
         <v>10</v>
@@ -5627,14 +5858,20 @@
         <v>8.5</v>
       </c>
       <c r="I70" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="J70" t="n">
+        <v>7</v>
+      </c>
+      <c r="K70" t="n">
         <v>9</v>
       </c>
       <c r="L70" t="n">
         <v>9.5</v>
       </c>
+      <c r="M70" t="n">
+        <v>7</v>
+      </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
@@ -5644,12 +5881,15 @@
       <c r="R70" t="n">
         <v>1</v>
       </c>
-      <c r="S70" t="n">
+      <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
         <v>1</v>
       </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
@@ -5662,20 +5902,14 @@
       <c r="Z70" t="n">
         <v>1</v>
       </c>
-      <c r="AB70" t="n">
-        <v>1</v>
-      </c>
       <c r="AC70" t="n">
         <v>1</v>
       </c>
       <c r="AD70" t="n">
         <v>1</v>
       </c>
-      <c r="AE70" t="n">
-        <v>1</v>
-      </c>
       <c r="AF70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -5691,7 +5925,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Escala de pH</t>
+          <t>Isótopos</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5700,31 +5934,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>9</v>
-      </c>
-      <c r="F71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="n">
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I71" t="n">
         <v>9.5</v>
       </c>
-      <c r="K71" t="n">
-        <v>9</v>
-      </c>
       <c r="L71" t="n">
         <v>9.5</v>
       </c>
       <c r="M71" t="n">
-        <v>7</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5732,9 +5960,6 @@
       <c r="R71" t="n">
         <v>1</v>
       </c>
-      <c r="T71" t="n">
-        <v>1</v>
-      </c>
       <c r="U71" t="n">
         <v>1</v>
       </c>
@@ -5744,29 +5969,20 @@
       <c r="W71" t="n">
         <v>1</v>
       </c>
-      <c r="X71" t="n">
-        <v>1</v>
-      </c>
       <c r="Y71" t="n">
         <v>1</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
-      <c r="AB71" t="n">
-        <v>1</v>
-      </c>
       <c r="AC71" t="n">
         <v>1</v>
       </c>
       <c r="AD71" t="n">
         <v>1</v>
       </c>
-      <c r="AE71" t="n">
-        <v>1</v>
-      </c>
       <c r="AF71" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
@@ -5782,7 +5998,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Masa atómica relativa</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5791,25 +6007,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>9</v>
-      </c>
-      <c r="E72" t="n">
-        <v>2</v>
-      </c>
-      <c r="F72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
-      </c>
-      <c r="I72" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="L72" t="n">
         <v>9.5</v>
@@ -5817,30 +6021,21 @@
       <c r="M72" t="n">
         <v>7</v>
       </c>
-      <c r="O72" t="n">
-        <v>1</v>
-      </c>
       <c r="P72" t="n">
         <v>1</v>
       </c>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
       <c r="U72" t="n">
         <v>1</v>
       </c>
+      <c r="W72" t="n">
+        <v>1</v>
+      </c>
       <c r="Y72" t="n">
         <v>1</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
-      <c r="AA72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>1</v>
-      </c>
       <c r="AC72" t="n">
         <v>1</v>
       </c>
@@ -5848,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -5864,7 +6059,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Masa molar</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5887,9 +6082,6 @@
       <c r="I73" t="n">
         <v>9.5</v>
       </c>
-      <c r="J73" t="n">
-        <v>7</v>
-      </c>
       <c r="L73" t="n">
         <v>9.5</v>
       </c>
@@ -5923,9 +6115,6 @@
       <c r="Z73" t="n">
         <v>1</v>
       </c>
-      <c r="AA73" t="n">
-        <v>1</v>
-      </c>
       <c r="AB73" t="n">
         <v>1</v>
       </c>
@@ -5933,9 +6122,6 @@
         <v>1</v>
       </c>
       <c r="AD73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
@@ -5955,7 +6141,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Notación y estructuras de Lewis</t>
+          <t>Materia y materiales</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5964,26 +6150,44 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
         <v>10</v>
       </c>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
       <c r="F74" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G74" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6</v>
+      </c>
+      <c r="J74" t="n">
+        <v>7</v>
+      </c>
+      <c r="K74" t="n">
+        <v>8</v>
       </c>
       <c r="L74" t="n">
         <v>9.5</v>
       </c>
+      <c r="M74" t="n">
+        <v>7</v>
+      </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
       <c r="U74" t="n">
         <v>1</v>
       </c>
@@ -5999,17 +6203,17 @@
       <c r="Z74" t="n">
         <v>1</v>
       </c>
+      <c r="AA74" t="n">
+        <v>1</v>
+      </c>
       <c r="AB74" t="n">
         <v>1</v>
       </c>
-      <c r="AC74" t="n">
-        <v>1</v>
-      </c>
       <c r="AD74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
@@ -6025,7 +6229,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares</t>
+          <t>Reutilización y reciclaje de materiales</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6034,25 +6238,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F75" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G75" t="n">
         <v>8.5</v>
       </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
       <c r="J75" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="K75" t="n">
+        <v>8</v>
       </c>
       <c r="L75" t="n">
         <v>9.5</v>
       </c>
       <c r="M75" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -6060,30 +6270,24 @@
       <c r="P75" t="n">
         <v>1</v>
       </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
       <c r="U75" t="n">
         <v>1</v>
       </c>
       <c r="V75" t="n">
         <v>1</v>
       </c>
-      <c r="W75" t="n">
-        <v>1</v>
-      </c>
-      <c r="X75" t="n">
-        <v>1</v>
-      </c>
       <c r="Y75" t="n">
         <v>1</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
-      <c r="AA75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>1</v>
-      </c>
       <c r="AC75" t="n">
         <v>1</v>
       </c>
@@ -6094,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="AF75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
@@ -6110,7 +6314,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares y propiedades físicas</t>
+          <t>Mezclas homogéneas y heterogéneas</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6119,23 +6323,32 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
       </c>
       <c r="F76" t="n">
         <v>8</v>
       </c>
       <c r="G76" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I76" t="n">
-        <v>9.5</v>
+        <v>4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>7</v>
       </c>
       <c r="L76" t="n">
         <v>9.5</v>
       </c>
+      <c r="M76" t="n">
+        <v>7</v>
+      </c>
       <c r="O76" t="n">
         <v>1</v>
       </c>
@@ -6151,32 +6364,20 @@
       <c r="W76" t="n">
         <v>1</v>
       </c>
-      <c r="X76" t="n">
-        <v>1</v>
-      </c>
       <c r="Y76" t="n">
         <v>1</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
-      <c r="AA76" t="n">
-        <v>1</v>
-      </c>
       <c r="AB76" t="n">
         <v>1</v>
       </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
       <c r="AD76" t="n">
         <v>1</v>
       </c>
-      <c r="AE76" t="n">
-        <v>1</v>
-      </c>
       <c r="AF76" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -6192,7 +6393,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Geometría molecular (RPECV)</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6206,18 +6407,39 @@
       <c r="D77" t="n">
         <v>10</v>
       </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8</v>
+      </c>
       <c r="G77" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I77" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>7</v>
+      </c>
+      <c r="K77" t="n">
+        <v>8</v>
       </c>
       <c r="L77" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M77" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
       </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
       <c r="U77" t="n">
         <v>1</v>
       </c>
@@ -6227,13 +6449,13 @@
       <c r="W77" t="n">
         <v>1</v>
       </c>
-      <c r="X77" t="n">
-        <v>1</v>
-      </c>
       <c r="Y77" t="n">
         <v>1</v>
       </c>
       <c r="Z77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA77" t="n">
         <v>1</v>
       </c>
       <c r="AB77" t="n">
@@ -6265,7 +6487,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Iones</t>
+          <t>Modelo mecanocuántico y orbitales atómicos</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6279,51 +6501,12 @@
       <c r="D78" t="n">
         <v>10</v>
       </c>
-      <c r="F78" t="n">
-        <v>8</v>
-      </c>
-      <c r="G78" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I78" t="n">
-        <v>8</v>
-      </c>
-      <c r="J78" t="n">
-        <v>7</v>
-      </c>
-      <c r="K78" t="n">
-        <v>9</v>
-      </c>
       <c r="L78" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M78" t="n">
-        <v>7</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U78" t="n">
         <v>1</v>
       </c>
-      <c r="V78" t="n">
-        <v>1</v>
-      </c>
-      <c r="W78" t="n">
-        <v>1</v>
-      </c>
-      <c r="X78" t="n">
-        <v>1</v>
-      </c>
       <c r="Y78" t="n">
         <v>1</v>
       </c>
@@ -6334,6 +6517,9 @@
         <v>1</v>
       </c>
       <c r="AD78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
@@ -6353,7 +6539,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Isótopos</t>
+          <t>Evolución de los modelos atómicos</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6370,22 +6556,31 @@
       <c r="E79" t="n">
         <v>8</v>
       </c>
+      <c r="F79" t="n">
+        <v>10.5</v>
+      </c>
       <c r="G79" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I79" t="n">
-        <v>9.5</v>
+        <v>6</v>
+      </c>
+      <c r="J79" t="n">
+        <v>9</v>
+      </c>
+      <c r="K79" t="n">
+        <v>8</v>
       </c>
       <c r="L79" t="n">
         <v>9.5</v>
       </c>
       <c r="M79" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
       </c>
       <c r="P79" t="n">
         <v>1</v>
       </c>
-      <c r="R79" t="n">
+      <c r="S79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
@@ -6407,6 +6602,9 @@
         <v>1</v>
       </c>
       <c r="AD79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE79" t="n">
         <v>1</v>
       </c>
       <c r="AF79" t="n">
@@ -6426,7 +6624,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Masa atómica relativa</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6435,35 +6633,56 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D80" t="n">
         <v>10</v>
       </c>
+      <c r="F80" t="n">
+        <v>8</v>
+      </c>
       <c r="G80" t="n">
         <v>8.5</v>
       </c>
+      <c r="I80" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L80" t="n">
         <v>9.5</v>
       </c>
       <c r="M80" t="n">
-        <v>7</v>
+        <v>9.5</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
       <c r="U80" t="n">
         <v>1</v>
       </c>
+      <c r="V80" t="n">
+        <v>1</v>
+      </c>
       <c r="W80" t="n">
         <v>1</v>
       </c>
+      <c r="X80" t="n">
+        <v>1</v>
+      </c>
       <c r="Y80" t="n">
         <v>1</v>
       </c>
       <c r="Z80" t="n">
         <v>1</v>
       </c>
+      <c r="AB80" t="n">
+        <v>1</v>
+      </c>
       <c r="AC80" t="n">
         <v>1</v>
       </c>
@@ -6471,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="AF80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -6487,7 +6706,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Masa molar</t>
+          <t>Molaridad y unidades químicas de concentración</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6499,13 +6718,10 @@
         <v>8</v>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
-        <v>8</v>
-      </c>
-      <c r="G81" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="I81" t="n">
         <v>9.5</v>
@@ -6519,9 +6735,6 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
       <c r="R81" t="n">
         <v>1</v>
       </c>
@@ -6550,6 +6763,9 @@
         <v>1</v>
       </c>
       <c r="AD81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE81" t="n">
         <v>1</v>
       </c>
       <c r="AF81" t="n">
@@ -6569,7 +6785,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Materia y materiales</t>
+          <t>Moléculas y fórmulas químicas</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6578,22 +6794,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
         <v>10</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
         <v>7</v>
@@ -6613,7 +6829,7 @@
       <c r="P82" t="n">
         <v>1</v>
       </c>
-      <c r="R82" t="n">
+      <c r="T82" t="n">
         <v>1</v>
       </c>
       <c r="U82" t="n">
@@ -6631,17 +6847,17 @@
       <c r="Z82" t="n">
         <v>1</v>
       </c>
-      <c r="AA82" t="n">
-        <v>1</v>
-      </c>
       <c r="AB82" t="n">
         <v>1</v>
       </c>
+      <c r="AC82" t="n">
+        <v>1</v>
+      </c>
       <c r="AD82" t="n">
         <v>1</v>
       </c>
       <c r="AF82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
@@ -6657,7 +6873,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Reutilización y reciclaje de materiales</t>
+          <t>Número de oxidación</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6666,48 +6882,30 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>8</v>
       </c>
-      <c r="G83" t="n">
-        <v>8.5</v>
-      </c>
       <c r="I83" t="n">
-        <v>8</v>
-      </c>
-      <c r="J83" t="n">
-        <v>9</v>
-      </c>
-      <c r="K83" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="L83" t="n">
         <v>9.5</v>
       </c>
-      <c r="M83" t="n">
-        <v>7</v>
-      </c>
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="P83" t="n">
-        <v>1</v>
-      </c>
       <c r="R83" t="n">
         <v>1</v>
       </c>
-      <c r="S83" t="n">
-        <v>1</v>
-      </c>
       <c r="U83" t="n">
         <v>1</v>
       </c>
-      <c r="V83" t="n">
+      <c r="X83" t="n">
         <v>1</v>
       </c>
       <c r="Y83" t="n">
@@ -6716,6 +6914,9 @@
       <c r="Z83" t="n">
         <v>1</v>
       </c>
+      <c r="AB83" t="n">
+        <v>1</v>
+      </c>
       <c r="AC83" t="n">
         <v>1</v>
       </c>
@@ -6726,7 +6927,7 @@
         <v>1</v>
       </c>
       <c r="AF83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
@@ -6742,7 +6943,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mezclas homogéneas y heterogéneas</t>
+          <t>Números cuánticos</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6751,61 +6952,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
-        <v>9</v>
-      </c>
-      <c r="E84" t="n">
-        <v>6</v>
-      </c>
-      <c r="F84" t="n">
-        <v>8</v>
-      </c>
-      <c r="G84" t="n">
-        <v>6</v>
-      </c>
-      <c r="I84" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L84" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M84" t="n">
-        <v>7</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1</v>
-      </c>
-      <c r="P84" t="n">
-        <v>1</v>
-      </c>
-      <c r="R84" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U84" t="n">
         <v>1</v>
       </c>
-      <c r="W84" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>1</v>
-      </c>
       <c r="AD84" t="n">
         <v>1</v>
       </c>
+      <c r="AE84" t="n">
+        <v>1</v>
+      </c>
       <c r="AF84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -6821,7 +6986,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Oxidación y corrosión de los metales</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6830,28 +6995,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>10</v>
-      </c>
-      <c r="E85" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F85" t="n">
-        <v>8</v>
-      </c>
-      <c r="G85" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="I85" t="n">
         <v>9.5</v>
       </c>
       <c r="J85" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L85" t="n">
         <v>9.5</v>
@@ -6862,18 +7021,18 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="P85" t="n">
-        <v>1</v>
-      </c>
       <c r="R85" t="n">
         <v>1</v>
       </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
       <c r="U85" t="n">
         <v>1</v>
       </c>
-      <c r="V85" t="n">
-        <v>1</v>
-      </c>
       <c r="W85" t="n">
         <v>1</v>
       </c>
@@ -6883,23 +7042,14 @@
       <c r="Z85" t="n">
         <v>1</v>
       </c>
-      <c r="AA85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>1</v>
-      </c>
       <c r="AC85" t="n">
         <v>1</v>
       </c>
       <c r="AD85" t="n">
         <v>1</v>
       </c>
-      <c r="AE85" t="n">
-        <v>1</v>
-      </c>
       <c r="AF85" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
@@ -6908,14 +7058,14 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Modelo mecanocuántico y orbitales atómicos</t>
+          <t>Polaridad molecular</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6924,23 +7074,50 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D86" t="n">
         <v>10</v>
       </c>
+      <c r="F86" t="n">
+        <v>8</v>
+      </c>
+      <c r="I86" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L86" t="n">
         <v>11</v>
       </c>
+      <c r="M86" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
       <c r="U86" t="n">
         <v>1</v>
       </c>
+      <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1</v>
+      </c>
+      <c r="X86" t="n">
+        <v>1</v>
+      </c>
       <c r="Y86" t="n">
         <v>1</v>
       </c>
       <c r="Z86" t="n">
         <v>1</v>
       </c>
+      <c r="AB86" t="n">
+        <v>1</v>
+      </c>
       <c r="AC86" t="n">
         <v>1</v>
       </c>
@@ -6951,7 +7128,7 @@
         <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -6967,7 +7144,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Evolución de los modelos atómicos</t>
+          <t>Proceso de disolución y solvatación</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6976,28 +7153,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D87" t="n">
         <v>10</v>
       </c>
-      <c r="E87" t="n">
-        <v>8</v>
-      </c>
       <c r="F87" t="n">
         <v>10.5</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
-      </c>
-      <c r="J87" t="n">
-        <v>9</v>
-      </c>
-      <c r="K87" t="n">
-        <v>8</v>
-      </c>
-      <c r="L87" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="M87" t="n">
         <v>7</v>
@@ -7005,25 +7170,13 @@
       <c r="O87" t="n">
         <v>1</v>
       </c>
-      <c r="P87" t="n">
-        <v>1</v>
-      </c>
-      <c r="S87" t="n">
-        <v>1</v>
-      </c>
-      <c r="U87" t="n">
-        <v>1</v>
-      </c>
       <c r="V87" t="n">
         <v>1</v>
       </c>
       <c r="W87" t="n">
         <v>1</v>
       </c>
-      <c r="Y87" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z87" t="n">
+      <c r="AA87" t="n">
         <v>1</v>
       </c>
       <c r="AC87" t="n">
@@ -7032,11 +7185,8 @@
       <c r="AD87" t="n">
         <v>1</v>
       </c>
-      <c r="AE87" t="n">
-        <v>1</v>
-      </c>
       <c r="AF87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
@@ -7052,7 +7202,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7066,40 +7216,19 @@
       <c r="D88" t="n">
         <v>10</v>
       </c>
-      <c r="F88" t="n">
-        <v>8</v>
-      </c>
       <c r="G88" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I88" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L88" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="M88" t="n">
         <v>9.5</v>
       </c>
-      <c r="O88" t="n">
-        <v>1</v>
-      </c>
       <c r="P88" t="n">
         <v>1</v>
       </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
-      <c r="U88" t="n">
-        <v>1</v>
-      </c>
       <c r="V88" t="n">
         <v>1</v>
       </c>
       <c r="W88" t="n">
-        <v>1</v>
-      </c>
-      <c r="X88" t="n">
         <v>1</v>
       </c>
       <c r="Y88" t="n">
@@ -7134,7 +7263,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Molaridad y unidades químicas de concentración</t>
+          <t>Propiedades coligativas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7146,51 +7275,18 @@
         <v>8</v>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
-      </c>
-      <c r="F89" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I89" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L89" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M89" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O89" t="n">
-        <v>1</v>
-      </c>
-      <c r="R89" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" t="n">
-        <v>1</v>
-      </c>
-      <c r="V89" t="n">
-        <v>1</v>
-      </c>
-      <c r="W89" t="n">
-        <v>1</v>
-      </c>
-      <c r="X89" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Z89" t="n">
         <v>1</v>
       </c>
+      <c r="AA89" t="n">
+        <v>1</v>
+      </c>
       <c r="AB89" t="n">
         <v>1</v>
       </c>
       <c r="AC89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD89" t="n">
         <v>1</v>
       </c>
       <c r="AE89" t="n">
@@ -7213,7 +7309,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Moléculas y fórmulas químicas</t>
+          <t>Propiedades físicas de los materiales</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7222,29 +7318,26 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>10</v>
       </c>
       <c r="E90" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F90" t="n">
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J90" t="n">
         <v>7</v>
       </c>
-      <c r="K90" t="n">
-        <v>8</v>
-      </c>
       <c r="L90" t="n">
         <v>9.5</v>
       </c>
@@ -7257,7 +7350,7 @@
       <c r="P90" t="n">
         <v>1</v>
       </c>
-      <c r="T90" t="n">
+      <c r="R90" t="n">
         <v>1</v>
       </c>
       <c r="U90" t="n">
@@ -7266,26 +7359,23 @@
       <c r="W90" t="n">
         <v>1</v>
       </c>
-      <c r="X90" t="n">
-        <v>1</v>
-      </c>
       <c r="Y90" t="n">
         <v>1</v>
       </c>
       <c r="Z90" t="n">
         <v>1</v>
       </c>
-      <c r="AB90" t="n">
-        <v>1</v>
-      </c>
       <c r="AC90" t="n">
         <v>1</v>
       </c>
       <c r="AD90" t="n">
         <v>1</v>
       </c>
+      <c r="AE90" t="n">
+        <v>1</v>
+      </c>
       <c r="AF90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -7301,7 +7391,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Número de oxidación</t>
+          <t>Propiedades físicas y químicas</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7310,29 +7400,53 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F91" t="n">
         <v>8</v>
       </c>
+      <c r="G91" t="n">
+        <v>6</v>
+      </c>
       <c r="I91" t="n">
-        <v>9.5</v>
+        <v>6</v>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
+      </c>
+      <c r="K91" t="n">
+        <v>8</v>
       </c>
       <c r="L91" t="n">
         <v>9.5</v>
       </c>
+      <c r="M91" t="n">
+        <v>7</v>
+      </c>
       <c r="O91" t="n">
         <v>1</v>
       </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
       <c r="R91" t="n">
         <v>1</v>
       </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
       <c r="U91" t="n">
         <v>1</v>
       </c>
+      <c r="V91" t="n">
+        <v>1</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1</v>
+      </c>
       <c r="X91" t="n">
         <v>1</v>
       </c>
@@ -7355,7 +7469,7 @@
         <v>1</v>
       </c>
       <c r="AF91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
@@ -7371,7 +7485,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Números cuánticos</t>
+          <t>Propiedades periódicas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7385,10 +7499,67 @@
       <c r="D92" t="n">
         <v>10</v>
       </c>
+      <c r="E92" t="n">
+        <v>9</v>
+      </c>
+      <c r="F92" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6</v>
+      </c>
+      <c r="I92" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J92" t="n">
+        <v>9</v>
+      </c>
+      <c r="K92" t="n">
+        <v>8</v>
+      </c>
       <c r="L92" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M92" t="n">
+        <v>7</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
       </c>
       <c r="U92" t="n">
+        <v>1</v>
+      </c>
+      <c r="W92" t="n">
+        <v>1</v>
+      </c>
+      <c r="X92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC92" t="n">
         <v>1</v>
       </c>
       <c r="AD92" t="n">
@@ -7414,7 +7585,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Polaridad molecular</t>
+          <t>Propiedades singulares del agua</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7423,44 +7594,32 @@
         </is>
       </c>
       <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>9</v>
+      </c>
+      <c r="G93" t="n">
         <v>6</v>
       </c>
-      <c r="D93" t="n">
-        <v>10</v>
-      </c>
-      <c r="F93" t="n">
-        <v>8</v>
-      </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>9</v>
       </c>
       <c r="L93" t="n">
         <v>11</v>
       </c>
-      <c r="M93" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O93" t="n">
-        <v>1</v>
-      </c>
-      <c r="R93" t="n">
+      <c r="S93" t="n">
         <v>1</v>
       </c>
       <c r="U93" t="n">
         <v>1</v>
       </c>
-      <c r="V93" t="n">
-        <v>1</v>
-      </c>
       <c r="W93" t="n">
         <v>1</v>
       </c>
-      <c r="X93" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>1</v>
-      </c>
       <c r="Z93" t="n">
         <v>1</v>
       </c>
@@ -7473,11 +7632,8 @@
       <c r="AD93" t="n">
         <v>1</v>
       </c>
-      <c r="AE93" t="n">
-        <v>1</v>
-      </c>
       <c r="AF93" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -7493,7 +7649,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Proceso de disolución y solvatación</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7502,7 +7658,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D94" t="n">
         <v>10</v>
@@ -7510,32 +7666,32 @@
       <c r="F94" t="n">
         <v>10.5</v>
       </c>
-      <c r="G94" t="n">
-        <v>3</v>
-      </c>
-      <c r="M94" t="n">
-        <v>7</v>
+      <c r="I94" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L94" t="n">
+        <v>9.5</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="V94" t="n">
-        <v>1</v>
-      </c>
-      <c r="W94" t="n">
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z94" t="n">
         <v>1</v>
       </c>
       <c r="AA94" t="n">
         <v>1</v>
       </c>
-      <c r="AC94" t="n">
-        <v>1</v>
-      </c>
       <c r="AD94" t="n">
         <v>1</v>
       </c>
       <c r="AF94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -7544,14 +7700,14 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Química descriptiva de los elementos</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7560,24 +7716,45 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
         <v>10</v>
       </c>
+      <c r="F95" t="n">
+        <v>8</v>
+      </c>
       <c r="G95" t="n">
         <v>6</v>
       </c>
+      <c r="I95" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J95" t="n">
+        <v>9</v>
+      </c>
+      <c r="L95" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M95" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
       </c>
-      <c r="V95" t="n">
-        <v>1</v>
-      </c>
-      <c r="W95" t="n">
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" t="n">
+        <v>1</v>
+      </c>
+      <c r="X95" t="n">
         <v>1</v>
       </c>
       <c r="Y95" t="n">
@@ -7586,7 +7763,7 @@
       <c r="Z95" t="n">
         <v>1</v>
       </c>
-      <c r="AB95" t="n">
+      <c r="AA95" t="n">
         <v>1</v>
       </c>
       <c r="AC95" t="n">
@@ -7595,8 +7772,11 @@
       <c r="AD95" t="n">
         <v>1</v>
       </c>
+      <c r="AE95" t="n">
+        <v>1</v>
+      </c>
       <c r="AF95" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
@@ -7612,7 +7792,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Reacción química y sus evidencias</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7621,28 +7801,76 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
         <v>10</v>
       </c>
+      <c r="E96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" t="n">
+        <v>8</v>
+      </c>
+      <c r="G96" t="n">
+        <v>3</v>
+      </c>
+      <c r="I96" t="n">
+        <v>5</v>
+      </c>
+      <c r="J96" t="n">
+        <v>7</v>
+      </c>
+      <c r="K96" t="n">
+        <v>9</v>
+      </c>
+      <c r="L96" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M96" t="n">
+        <v>7</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" t="n">
+        <v>1</v>
+      </c>
+      <c r="W96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1</v>
+      </c>
       <c r="Z96" t="n">
         <v>1</v>
       </c>
-      <c r="AA96" t="n">
-        <v>1</v>
-      </c>
       <c r="AB96" t="n">
         <v>1</v>
       </c>
       <c r="AC96" t="n">
         <v>1</v>
       </c>
+      <c r="AD96" t="n">
+        <v>1</v>
+      </c>
       <c r="AE96" t="n">
         <v>1</v>
       </c>
       <c r="AF96" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
@@ -7658,7 +7886,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Propiedades físicas de los materiales</t>
+          <t>Rendimiento de una reacción</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7667,47 +7895,23 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D97" t="n">
         <v>10</v>
       </c>
-      <c r="E97" t="n">
-        <v>2</v>
-      </c>
       <c r="F97" t="n">
-        <v>8</v>
-      </c>
-      <c r="G97" t="n">
-        <v>2</v>
-      </c>
-      <c r="I97" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J97" t="n">
-        <v>7</v>
-      </c>
-      <c r="L97" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M97" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="P97" t="n">
-        <v>1</v>
-      </c>
-      <c r="R97" t="n">
-        <v>1</v>
-      </c>
-      <c r="U97" t="n">
-        <v>1</v>
-      </c>
       <c r="W97" t="n">
         <v>1</v>
       </c>
+      <c r="X97" t="n">
+        <v>1</v>
+      </c>
       <c r="Y97" t="n">
         <v>1</v>
       </c>
@@ -7724,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="AF97" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
@@ -7733,14 +7937,14 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Propiedades físicas y químicas</t>
+          <t>Métodos físicos de separación de mezclas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7752,23 +7956,23 @@
         <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E98" t="n">
+        <v>6</v>
       </c>
       <c r="F98" t="n">
         <v>8</v>
       </c>
       <c r="G98" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>7</v>
       </c>
-      <c r="K98" t="n">
-        <v>8</v>
-      </c>
       <c r="L98" t="n">
         <v>9.5</v>
       </c>
@@ -7784,9 +7988,6 @@
       <c r="R98" t="n">
         <v>1</v>
       </c>
-      <c r="T98" t="n">
-        <v>1</v>
-      </c>
       <c r="U98" t="n">
         <v>1</v>
       </c>
@@ -7796,16 +7997,10 @@
       <c r="W98" t="n">
         <v>1</v>
       </c>
-      <c r="X98" t="n">
-        <v>1</v>
-      </c>
       <c r="Y98" t="n">
         <v>1</v>
       </c>
       <c r="Z98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB98" t="n">
         <v>1</v>
       </c>
       <c r="AC98" t="n">
@@ -7834,7 +8029,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Propiedades periódicas</t>
+          <t>Sólidos cristalinos y amorfos</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7843,82 +8038,40 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D99" t="n">
         <v>10</v>
       </c>
-      <c r="E99" t="n">
-        <v>9</v>
-      </c>
-      <c r="F99" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G99" t="n">
-        <v>6</v>
-      </c>
-      <c r="I99" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J99" t="n">
-        <v>9</v>
-      </c>
-      <c r="K99" t="n">
+      <c r="L99" t="n">
+        <v>11</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
+      </c>
+      <c r="W99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="n">
         <v>8</v>
-      </c>
-      <c r="L99" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M99" t="n">
-        <v>7</v>
-      </c>
-      <c r="N99" t="n">
-        <v>1</v>
-      </c>
-      <c r="O99" t="n">
-        <v>1</v>
-      </c>
-      <c r="P99" t="n">
-        <v>1</v>
-      </c>
-      <c r="R99" t="n">
-        <v>1</v>
-      </c>
-      <c r="S99" t="n">
-        <v>1</v>
-      </c>
-      <c r="U99" t="n">
-        <v>1</v>
-      </c>
-      <c r="W99" t="n">
-        <v>1</v>
-      </c>
-      <c r="X99" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y99" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF99" t="n">
-        <v>5</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
@@ -7934,7 +8087,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Propiedades singulares del agua</t>
+          <t>Solubilidad y disoluciones saturadas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7946,39 +8099,60 @@
         <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F100" t="n">
+        <v>8</v>
       </c>
       <c r="G100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L100" t="n">
-        <v>11</v>
-      </c>
-      <c r="S100" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M100" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
+      <c r="R100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
         <v>1</v>
       </c>
+      <c r="V100" t="n">
+        <v>1</v>
+      </c>
       <c r="W100" t="n">
         <v>1</v>
       </c>
+      <c r="X100" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1</v>
+      </c>
       <c r="Z100" t="n">
         <v>1</v>
       </c>
-      <c r="AB100" t="n">
+      <c r="AA100" t="n">
         <v>1</v>
       </c>
       <c r="AC100" t="n">
         <v>1</v>
       </c>
       <c r="AD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE100" t="n">
         <v>1</v>
       </c>
       <c r="AF100" t="n">
@@ -7998,7 +8172,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Química descriptiva de los elementos</t>
+          <t>Sustancias puras: elementos y compuestos</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8010,7 +8184,10 @@
         <v>5</v>
       </c>
       <c r="D101" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E101" t="n">
+        <v>6</v>
       </c>
       <c r="F101" t="n">
         <v>8</v>
@@ -8019,10 +8196,13 @@
         <v>6</v>
       </c>
       <c r="I101" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="J101" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K101" t="n">
+        <v>8</v>
       </c>
       <c r="L101" t="n">
         <v>9.5</v>
@@ -8042,10 +8222,16 @@
       <c r="S101" t="n">
         <v>1</v>
       </c>
+      <c r="T101" t="n">
+        <v>1</v>
+      </c>
       <c r="U101" t="n">
         <v>1</v>
       </c>
-      <c r="X101" t="n">
+      <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="W101" t="n">
         <v>1</v>
       </c>
       <c r="Y101" t="n">
@@ -8054,20 +8240,14 @@
       <c r="Z101" t="n">
         <v>1</v>
       </c>
-      <c r="AA101" t="n">
-        <v>1</v>
-      </c>
       <c r="AC101" t="n">
         <v>1</v>
       </c>
       <c r="AD101" t="n">
         <v>1</v>
       </c>
-      <c r="AE101" t="n">
-        <v>1</v>
-      </c>
       <c r="AF101" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
@@ -8083,7 +8263,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Reacción química y sus evidencias</t>
+          <t>Organización de la tabla periódica</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8092,28 +8272,28 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D102" t="n">
         <v>10</v>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F102" t="n">
         <v>8</v>
       </c>
       <c r="G102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="J102" t="n">
         <v>7</v>
       </c>
       <c r="K102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L102" t="n">
         <v>9.5</v>
@@ -8121,6 +8301,9 @@
       <c r="M102" t="n">
         <v>7</v>
       </c>
+      <c r="N102" t="n">
+        <v>1</v>
+      </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
@@ -8139,16 +8322,22 @@
       <c r="U102" t="n">
         <v>1</v>
       </c>
+      <c r="V102" t="n">
+        <v>1</v>
+      </c>
       <c r="W102" t="n">
         <v>1</v>
       </c>
+      <c r="X102" t="n">
+        <v>1</v>
+      </c>
       <c r="Y102" t="n">
         <v>1</v>
       </c>
       <c r="Z102" t="n">
         <v>1</v>
       </c>
-      <c r="AB102" t="n">
+      <c r="AA102" t="n">
         <v>1</v>
       </c>
       <c r="AC102" t="n">
@@ -8161,7 +8350,7 @@
         <v>1</v>
       </c>
       <c r="AF102" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
@@ -8177,7 +8366,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Métodos físicos de separación de mezclas</t>
+          <t>Tipo de enlace y propiedades de las sustancias</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8186,25 +8375,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D103" t="n">
         <v>10</v>
       </c>
-      <c r="E103" t="n">
-        <v>6</v>
-      </c>
       <c r="F103" t="n">
         <v>8</v>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="J103" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L103" t="n">
         <v>9.5</v>
@@ -8221,6 +8407,9 @@
       <c r="R103" t="n">
         <v>1</v>
       </c>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
       <c r="U103" t="n">
         <v>1</v>
       </c>
@@ -8230,12 +8419,21 @@
       <c r="W103" t="n">
         <v>1</v>
       </c>
+      <c r="X103" t="n">
+        <v>1</v>
+      </c>
       <c r="Y103" t="n">
         <v>1</v>
       </c>
       <c r="Z103" t="n">
         <v>1</v>
       </c>
+      <c r="AA103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>1</v>
+      </c>
       <c r="AC103" t="n">
         <v>1</v>
       </c>
@@ -8246,7 +8444,7 @@
         <v>1</v>
       </c>
       <c r="AF103" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
@@ -8262,7 +8460,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sólidos cristalinos y amorfos</t>
+          <t>Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8271,13 +8469,40 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
         <v>10</v>
       </c>
+      <c r="E104" t="n">
+        <v>9</v>
+      </c>
+      <c r="F104" t="n">
+        <v>8</v>
+      </c>
+      <c r="G104" t="n">
+        <v>6</v>
+      </c>
+      <c r="I104" t="n">
+        <v>7</v>
+      </c>
+      <c r="K104" t="n">
+        <v>9</v>
+      </c>
       <c r="L104" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
+        <v>1</v>
       </c>
       <c r="U104" t="n">
         <v>1</v>
@@ -8285,18 +8510,12 @@
       <c r="W104" t="n">
         <v>1</v>
       </c>
-      <c r="Y104" t="n">
+      <c r="X104" t="n">
         <v>1</v>
       </c>
       <c r="Z104" t="n">
         <v>1</v>
       </c>
-      <c r="AA104" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>1</v>
-      </c>
       <c r="AC104" t="n">
         <v>1</v>
       </c>
@@ -8304,7 +8523,7 @@
         <v>1</v>
       </c>
       <c r="AF104" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
@@ -8320,7 +8539,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Solubilidad y disoluciones saturadas</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8338,27 +8557,15 @@
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
-      </c>
-      <c r="I105" t="n">
-        <v>4</v>
-      </c>
-      <c r="J105" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M105" t="n">
         <v>7</v>
       </c>
-      <c r="L105" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M105" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="R105" t="n">
-        <v>1</v>
-      </c>
-      <c r="U105" t="n">
+      <c r="P105" t="n">
         <v>1</v>
       </c>
       <c r="V105" t="n">
@@ -8376,13 +8583,7 @@
       <c r="Z105" t="n">
         <v>1</v>
       </c>
-      <c r="AA105" t="n">
-        <v>1</v>
-      </c>
       <c r="AC105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD105" t="n">
         <v>1</v>
       </c>
       <c r="AE105" t="n">
@@ -8405,82 +8606,31 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sustancias puras: elementos y compuestos</t>
+          <t>Diagramas de fases</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D106" t="n">
-        <v>9</v>
-      </c>
-      <c r="E106" t="n">
-        <v>6</v>
-      </c>
-      <c r="F106" t="n">
-        <v>8</v>
-      </c>
-      <c r="G106" t="n">
-        <v>6</v>
-      </c>
-      <c r="I106" t="n">
-        <v>7</v>
-      </c>
-      <c r="J106" t="n">
-        <v>7</v>
-      </c>
-      <c r="K106" t="n">
-        <v>8</v>
-      </c>
-      <c r="L106" t="n">
+        <v>10</v>
+      </c>
+      <c r="M106" t="n">
         <v>9.5</v>
       </c>
-      <c r="M106" t="n">
-        <v>7</v>
-      </c>
-      <c r="O106" t="n">
-        <v>1</v>
-      </c>
-      <c r="P106" t="n">
-        <v>1</v>
-      </c>
-      <c r="R106" t="n">
-        <v>1</v>
-      </c>
-      <c r="S106" t="n">
-        <v>1</v>
-      </c>
-      <c r="T106" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" t="n">
-        <v>1</v>
-      </c>
       <c r="V106" t="n">
         <v>1</v>
       </c>
-      <c r="W106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD106" t="n">
+      <c r="AA106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
@@ -8489,317 +8639,143 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Organización de la tabla periódica</t>
+          <t>Ecuación de Nernst</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D107" t="n">
         <v>10</v>
       </c>
-      <c r="E107" t="n">
-        <v>9</v>
-      </c>
-      <c r="F107" t="n">
-        <v>8</v>
-      </c>
-      <c r="G107" t="n">
-        <v>6</v>
-      </c>
-      <c r="I107" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J107" t="n">
-        <v>7</v>
-      </c>
-      <c r="K107" t="n">
-        <v>8</v>
-      </c>
-      <c r="L107" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M107" t="n">
-        <v>7</v>
-      </c>
-      <c r="N107" t="n">
-        <v>1</v>
-      </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
-      <c r="P107" t="n">
-        <v>1</v>
-      </c>
-      <c r="R107" t="n">
-        <v>1</v>
-      </c>
-      <c r="S107" t="n">
-        <v>1</v>
-      </c>
-      <c r="T107" t="n">
-        <v>1</v>
-      </c>
-      <c r="U107" t="n">
-        <v>1</v>
-      </c>
-      <c r="V107" t="n">
-        <v>1</v>
-      </c>
-      <c r="W107" t="n">
-        <v>1</v>
-      </c>
-      <c r="X107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>1</v>
-      </c>
       <c r="AD107" t="n">
         <v>1</v>
       </c>
-      <c r="AE107" t="n">
-        <v>1</v>
-      </c>
       <c r="AF107" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tipo de enlace y propiedades de las sustancias</t>
+          <t>Ecuaciones y reacciones nucleares</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D108" t="n">
         <v>10</v>
       </c>
-      <c r="F108" t="n">
-        <v>8</v>
-      </c>
       <c r="G108" t="n">
         <v>8.5</v>
       </c>
-      <c r="I108" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J108" t="n">
-        <v>9</v>
-      </c>
-      <c r="L108" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M108" t="n">
-        <v>7</v>
-      </c>
-      <c r="O108" t="n">
-        <v>1</v>
-      </c>
-      <c r="P108" t="n">
-        <v>1</v>
-      </c>
-      <c r="R108" t="n">
-        <v>1</v>
-      </c>
-      <c r="S108" t="n">
-        <v>1</v>
-      </c>
-      <c r="U108" t="n">
-        <v>1</v>
-      </c>
-      <c r="V108" t="n">
-        <v>1</v>
-      </c>
-      <c r="W108" t="n">
-        <v>1</v>
-      </c>
-      <c r="X108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA108" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB108" t="n">
-        <v>1</v>
-      </c>
       <c r="AC108" t="n">
         <v>1</v>
       </c>
-      <c r="AD108" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE108" t="n">
-        <v>1</v>
-      </c>
       <c r="AF108" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Clasificación de las reacciones químicas</t>
+          <t>Energía reticular y ciclo de Born-Haber</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D109" t="n">
         <v>10</v>
       </c>
-      <c r="E109" t="n">
-        <v>9</v>
-      </c>
-      <c r="F109" t="n">
-        <v>8</v>
-      </c>
-      <c r="G109" t="n">
-        <v>6</v>
-      </c>
-      <c r="I109" t="n">
-        <v>7</v>
-      </c>
-      <c r="K109" t="n">
-        <v>9</v>
-      </c>
       <c r="L109" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N109" t="n">
-        <v>1</v>
-      </c>
-      <c r="O109" t="n">
-        <v>1</v>
-      </c>
-      <c r="P109" t="n">
-        <v>1</v>
-      </c>
-      <c r="T109" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U109" t="n">
         <v>1</v>
       </c>
-      <c r="W109" t="n">
-        <v>1</v>
-      </c>
-      <c r="X109" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC109" t="n">
-        <v>1</v>
-      </c>
       <c r="AD109" t="n">
         <v>1</v>
       </c>
       <c r="AF109" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Leyes de los gases</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D110" t="n">
         <v>10</v>
       </c>
-      <c r="F110" t="n">
-        <v>8</v>
-      </c>
-      <c r="G110" t="n">
-        <v>8.5</v>
+      <c r="J110" t="n">
+        <v>7</v>
       </c>
       <c r="M110" t="n">
-        <v>7</v>
-      </c>
-      <c r="O110" t="n">
-        <v>1</v>
-      </c>
-      <c r="P110" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="V110" t="n">
         <v>1</v>
@@ -8807,130 +8783,193 @@
       <c r="W110" t="n">
         <v>1</v>
       </c>
-      <c r="X110" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>1</v>
-      </c>
       <c r="Z110" t="n">
         <v>1</v>
       </c>
+      <c r="AA110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>1</v>
+      </c>
       <c r="AC110" t="n">
         <v>1</v>
       </c>
+      <c r="AD110" t="n">
+        <v>1</v>
+      </c>
       <c r="AE110" t="n">
         <v>1</v>
       </c>
       <c r="AF110" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ecuación de Nernst</t>
+          <t>Composición porcentual y fórmulas empírica y molecular</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
         <v>10</v>
       </c>
+      <c r="G111" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L111" t="n">
+        <v>11</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" t="n">
+        <v>1</v>
+      </c>
+      <c r="W111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>1</v>
+      </c>
       <c r="AD111" t="n">
         <v>1</v>
       </c>
       <c r="AF111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ecuaciones y reacciones nucleares</t>
+          <t>Constante de equilibrio</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D112" t="n">
-        <v>10</v>
-      </c>
-      <c r="G112" t="n">
-        <v>8.5</v>
+        <v>9</v>
+      </c>
+      <c r="L112" t="n">
+        <v>11</v>
+      </c>
+      <c r="U112" t="n">
+        <v>1</v>
+      </c>
+      <c r="W112" t="n">
+        <v>1</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>1</v>
       </c>
       <c r="AC112" t="n">
         <v>1</v>
       </c>
+      <c r="AD112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1</v>
+      </c>
       <c r="AF112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Energía reticular y ciclo de Born-Haber</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
         <v>10</v>
       </c>
-      <c r="L113" t="n">
-        <v>11</v>
-      </c>
-      <c r="U113" t="n">
+      <c r="J113" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC113" t="n">
         <v>1</v>
       </c>
       <c r="AD113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE113" t="n">
         <v>1</v>
       </c>
       <c r="AF113" t="n">
@@ -8938,45 +8977,42 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Leyes de los gases</t>
+          <t>Hidrólisis de sales y disoluciones amortiguadoras</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D114" t="n">
-        <v>10</v>
-      </c>
-      <c r="J114" t="n">
-        <v>7</v>
-      </c>
-      <c r="M114" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V114" t="n">
-        <v>1</v>
-      </c>
-      <c r="W114" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z114" t="n">
+        <v>9</v>
+      </c>
+      <c r="L114" t="n">
+        <v>11</v>
+      </c>
+      <c r="U114" t="n">
+        <v>1</v>
+      </c>
+      <c r="X114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y114" t="n">
         <v>1</v>
       </c>
       <c r="AA114" t="n">
@@ -8995,23 +9031,23 @@
         <v>1</v>
       </c>
       <c r="AF114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Constante de equilibrio</t>
+          <t>Ecuación de los gases ideales y volumen molar</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9020,13 +9056,25 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D115" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8</v>
+      </c>
+      <c r="I115" t="n">
+        <v>9.5</v>
       </c>
       <c r="L115" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1</v>
       </c>
       <c r="U115" t="n">
         <v>1</v>
@@ -9034,9 +9082,6 @@
       <c r="W115" t="n">
         <v>1</v>
       </c>
-      <c r="X115" t="n">
-        <v>1</v>
-      </c>
       <c r="Y115" t="n">
         <v>1</v>
       </c>
@@ -9059,7 +9104,7 @@
         <v>1</v>
       </c>
       <c r="AF115" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG115" t="inlineStr">
         <is>
@@ -9075,7 +9120,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Hidrólisis de sales y disoluciones amortiguadoras</t>
+          <t>Energía de Gibbs y espontaneidad</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9089,10 +9134,7 @@
       <c r="D116" t="n">
         <v>9</v>
       </c>
-      <c r="L116" t="n">
-        <v>11</v>
-      </c>
-      <c r="U116" t="n">
+      <c r="W116" t="n">
         <v>1</v>
       </c>
       <c r="X116" t="n">
@@ -9101,23 +9143,20 @@
       <c r="Y116" t="n">
         <v>1</v>
       </c>
+      <c r="Z116" t="n">
+        <v>1</v>
+      </c>
       <c r="AA116" t="n">
         <v>1</v>
       </c>
       <c r="AB116" t="n">
         <v>1</v>
       </c>
-      <c r="AC116" t="n">
-        <v>1</v>
-      </c>
       <c r="AD116" t="n">
         <v>1</v>
       </c>
-      <c r="AE116" t="n">
-        <v>1</v>
-      </c>
       <c r="AF116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
@@ -9133,7 +9172,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ecuación de los gases ideales y volumen molar</t>
+          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9147,40 +9186,13 @@
       <c r="D117" t="n">
         <v>10</v>
       </c>
-      <c r="F117" t="n">
-        <v>8</v>
-      </c>
-      <c r="I117" t="n">
-        <v>9.5</v>
-      </c>
       <c r="L117" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O117" t="n">
-        <v>1</v>
-      </c>
-      <c r="R117" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U117" t="n">
         <v>1</v>
       </c>
-      <c r="W117" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y117" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA117" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB117" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC117" t="n">
+      <c r="X117" t="n">
         <v>1</v>
       </c>
       <c r="AD117" t="n">
@@ -9206,7 +9218,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Energía de Gibbs y espontaneidad</t>
+          <t>Entropía</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9215,24 +9227,15 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
-      </c>
-      <c r="W118" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X118" t="n">
         <v>1</v>
       </c>
       <c r="Y118" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA118" t="n">
         <v>1</v>
       </c>
       <c r="AB118" t="n">
@@ -9258,7 +9261,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
+          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9272,19 +9275,13 @@
       <c r="D119" t="n">
         <v>10</v>
       </c>
-      <c r="L119" t="n">
-        <v>11</v>
-      </c>
-      <c r="U119" t="n">
-        <v>1</v>
-      </c>
-      <c r="X119" t="n">
+      <c r="Y119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z119" t="n">
         <v>1</v>
       </c>
       <c r="AD119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE119" t="n">
         <v>1</v>
       </c>
       <c r="AF119" t="n">
@@ -9304,7 +9301,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Entropía</t>
+          <t>Espectrometría de masas</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9313,25 +9310,19 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D120" t="n">
-        <v>10</v>
-      </c>
-      <c r="X120" t="n">
+        <v>11</v>
+      </c>
+      <c r="W120" t="n">
         <v>1</v>
       </c>
       <c r="Y120" t="n">
         <v>1</v>
       </c>
-      <c r="AB120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>10</v>
+      <c r="Z120" t="n">
+        <v>1</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
@@ -9340,14 +9331,14 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9361,13 +9352,28 @@
       <c r="D121" t="n">
         <v>10</v>
       </c>
+      <c r="I121" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1</v>
+      </c>
+      <c r="W121" t="n">
+        <v>1</v>
+      </c>
       <c r="Y121" t="n">
         <v>1</v>
       </c>
       <c r="Z121" t="n">
         <v>1</v>
       </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
       <c r="AD121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE121" t="n">
         <v>1</v>
       </c>
       <c r="AF121" t="n">
@@ -9387,7 +9393,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9401,13 +9407,16 @@
       <c r="D122" t="n">
         <v>10</v>
       </c>
-      <c r="I122" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R122" t="n">
-        <v>1</v>
-      </c>
-      <c r="W122" t="n">
+      <c r="L122" t="n">
+        <v>11</v>
+      </c>
+      <c r="M122" t="n">
+        <v>7</v>
+      </c>
+      <c r="U122" t="n">
+        <v>1</v>
+      </c>
+      <c r="X122" t="n">
         <v>1</v>
       </c>
       <c r="Y122" t="n">
@@ -9416,6 +9425,9 @@
       <c r="Z122" t="n">
         <v>1</v>
       </c>
+      <c r="AA122" t="n">
+        <v>1</v>
+      </c>
       <c r="AC122" t="n">
         <v>1</v>
       </c>
@@ -9426,7 +9438,7 @@
         <v>1</v>
       </c>
       <c r="AF122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
@@ -9442,7 +9454,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9451,21 +9463,30 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G123" t="n">
+        <v>6</v>
+      </c>
+      <c r="I123" t="n">
+        <v>9.5</v>
       </c>
       <c r="L123" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M123" t="n">
         <v>7</v>
       </c>
+      <c r="R123" t="n">
+        <v>1</v>
+      </c>
       <c r="U123" t="n">
         <v>1</v>
       </c>
-      <c r="X123" t="n">
+      <c r="W123" t="n">
         <v>1</v>
       </c>
       <c r="Y123" t="n">
@@ -9475,9 +9496,6 @@
         <v>1</v>
       </c>
       <c r="AA123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC123" t="n">
         <v>1</v>
       </c>
       <c r="AD123" t="n">
@@ -9503,7 +9521,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9512,30 +9530,18 @@
         </is>
       </c>
       <c r="C124" t="n">
+        <v>5</v>
+      </c>
+      <c r="D124" t="n">
+        <v>10</v>
+      </c>
+      <c r="L124" t="n">
         <v>11</v>
       </c>
-      <c r="D124" t="n">
-        <v>11</v>
-      </c>
-      <c r="G124" t="n">
-        <v>6</v>
-      </c>
-      <c r="I124" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L124" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M124" t="n">
-        <v>7</v>
-      </c>
-      <c r="R124" t="n">
-        <v>1</v>
-      </c>
       <c r="U124" t="n">
         <v>1</v>
       </c>
-      <c r="W124" t="n">
+      <c r="X124" t="n">
         <v>1</v>
       </c>
       <c r="Y124" t="n">
@@ -9544,13 +9550,7 @@
       <c r="Z124" t="n">
         <v>1</v>
       </c>
-      <c r="AA124" t="n">
-        <v>1</v>
-      </c>
       <c r="AD124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE124" t="n">
         <v>1</v>
       </c>
       <c r="AF124" t="n">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">

--- a/internacional/Contraste_quimica.xlsx
+++ b/internacional/Contraste_quimica.xlsx
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D106" t="n">
         <v>10</v>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">

--- a/internacional/Contraste_quimica.xlsx
+++ b/internacional/Contraste_quimica.xlsx
@@ -626,6 +626,9 @@
       <c r="G2" t="n">
         <v>8.5</v>
       </c>
+      <c r="H2" t="n">
+        <v>7</v>
+      </c>
       <c r="I2" t="n">
         <v>9.5</v>
       </c>
@@ -945,6 +948,9 @@
       <c r="G6" t="n">
         <v>6</v>
       </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
       <c r="I6" t="n">
         <v>8</v>
       </c>
@@ -1024,6 +1030,9 @@
       <c r="G7" t="n">
         <v>6</v>
       </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
       <c r="I7" t="n">
         <v>2</v>
       </c>
@@ -1034,10 +1043,10 @@
         <v>9</v>
       </c>
       <c r="L7" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1194,6 +1203,9 @@
       <c r="G9" t="n">
         <v>8.5</v>
       </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
       <c r="I9" t="n">
         <v>8</v>
       </c>
@@ -1489,11 +1501,14 @@
       <c r="G13" t="n">
         <v>8.5</v>
       </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
       <c r="J13" t="n">
         <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M13" t="n">
         <v>9.5</v>
@@ -2092,7 +2107,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Indicadores ácido-base</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2101,41 +2116,56 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9</v>
+      </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
       <c r="Y21" t="n">
         <v>1</v>
       </c>
       <c r="Z21" t="n">
         <v>1</v>
       </c>
-      <c r="AA21" t="n">
-        <v>1</v>
-      </c>
       <c r="AC21" t="n">
         <v>1</v>
       </c>
@@ -2146,11 +2176,11 @@
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2162,7 +2192,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2176,19 +2206,43 @@
       <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="I22" t="n">
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11</v>
+      </c>
+      <c r="M22" t="n">
         <v>7</v>
       </c>
-      <c r="J22" t="n">
-        <v>7</v>
-      </c>
-      <c r="M22" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1</v>
       </c>
       <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
@@ -2196,7 +2250,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -2208,7 +2262,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Neutralización y reacciones de los ácidos</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2217,73 +2271,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
-      </c>
-      <c r="F23" t="n">
-        <v>8</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>9</v>
-      </c>
-      <c r="K23" t="n">
-        <v>9</v>
-      </c>
-      <c r="L23" t="n">
+        <v>7</v>
+      </c>
+      <c r="M23" t="n">
         <v>9.5</v>
       </c>
-      <c r="M23" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="V23" t="n">
         <v>1</v>
       </c>
       <c r="AC23" t="n">
         <v>1</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
       <c r="AF23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -2299,7 +2308,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Neutralización y reacciones de los ácidos</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2308,19 +2317,34 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="n">
         <v>7</v>
       </c>
-      <c r="D24" t="n">
-        <v>11</v>
-      </c>
-      <c r="F24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>8.5</v>
+      <c r="I24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
       </c>
       <c r="L24" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2328,15 +2352,21 @@
       <c r="P24" t="n">
         <v>1</v>
       </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
       <c r="Y24" t="n">
         <v>1</v>
       </c>
@@ -2356,11 +2386,11 @@
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -2372,7 +2402,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oxidación y reducción</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2381,47 +2411,29 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="L25" t="n">
         <v>9.5</v>
       </c>
-      <c r="M25" t="n">
-        <v>7</v>
-      </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
@@ -2432,9 +2444,6 @@
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA25" t="n">
         <v>1</v>
       </c>
       <c r="AB25" t="n">
@@ -2454,19 +2463,19 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
           <t>alineado</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Oxidación y reducción</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2475,16 +2484,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
       </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>9</v>
+      </c>
       <c r="L26" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M26" t="n">
         <v>7</v>
@@ -2492,19 +2513,46 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
       <c r="W26" t="n">
         <v>1</v>
       </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
+      <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
       <c r="AC26" t="n">
         <v>1</v>
       </c>
       <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
@@ -2512,19 +2560,19 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2533,19 +2581,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>8.5</v>
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>7</v>
       </c>
       <c r="L27" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M27" t="n">
         <v>7</v>
@@ -2553,41 +2601,23 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
       <c r="U27" t="n">
         <v>1</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1</v>
-      </c>
       <c r="Z27" t="n">
         <v>1</v>
       </c>
-      <c r="AA27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1</v>
-      </c>
       <c r="AC27" t="n">
         <v>1</v>
       </c>
       <c r="AD27" t="n">
         <v>1</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1</v>
-      </c>
       <c r="AF27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2603,7 +2633,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Química de los carbohidratos</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2612,35 +2642,32 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
         <v>10.5</v>
       </c>
-      <c r="I28" t="n">
-        <v>9.5</v>
+      <c r="G28" t="n">
+        <v>8.5</v>
       </c>
       <c r="L28" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M28" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
+      <c r="P28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
       <c r="W28" t="n">
         <v>1</v>
       </c>
@@ -2656,12 +2683,24 @@
       <c r="AA28" t="n">
         <v>1</v>
       </c>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -2673,7 +2712,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Química verde y economía atómica</t>
+          <t>Química de los carbohidratos</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2682,16 +2721,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
-      </c>
-      <c r="G29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>9.5</v>
       </c>
       <c r="L29" t="n">
         <v>9.5</v>
@@ -2699,7 +2738,10 @@
       <c r="M29" t="n">
         <v>9.5</v>
       </c>
-      <c r="P29" t="n">
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
@@ -2720,21 +2762,15 @@
       <c r="Z29" t="n">
         <v>1</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="AA29" t="n">
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -2818,11 +2854,14 @@
       <c r="G31" t="n">
         <v>8.5</v>
       </c>
+      <c r="H31" t="n">
+        <v>7</v>
+      </c>
       <c r="L31" t="n">
         <v>9.5</v>
       </c>
       <c r="M31" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
@@ -2903,6 +2942,9 @@
       <c r="G32" t="n">
         <v>8.5</v>
       </c>
+      <c r="H32" t="n">
+        <v>7</v>
+      </c>
       <c r="I32" t="n">
         <v>9.5</v>
       </c>
@@ -2944,7 +2986,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -2979,6 +3021,9 @@
       <c r="G33" t="n">
         <v>6</v>
       </c>
+      <c r="H33" t="n">
+        <v>7</v>
+      </c>
       <c r="I33" t="n">
         <v>7</v>
       </c>
@@ -3229,10 +3274,10 @@
         <v>9.5</v>
       </c>
       <c r="J36" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
@@ -3463,12 +3508,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Técnicas para determinar estructuras orgánicas</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3477,6 +3522,27 @@
       <c r="D39" t="n">
         <v>11</v>
       </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
       <c r="W39" t="n">
         <v>1</v>
       </c>
@@ -3486,8 +3552,17 @@
       <c r="Z39" t="n">
         <v>1</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1</v>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>11</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3496,7 +3571,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
@@ -3520,6 +3595,21 @@
       <c r="G40" t="n">
         <v>6</v>
       </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.5</v>
+      </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
@@ -3557,6 +3647,9 @@
       <c r="F41" t="n">
         <v>8</v>
       </c>
+      <c r="H41" t="n">
+        <v>7</v>
+      </c>
       <c r="J41" t="n">
         <v>9</v>
       </c>
@@ -3694,20 +3787,23 @@
       <c r="G43" t="n">
         <v>6</v>
       </c>
+      <c r="H43" t="n">
+        <v>7</v>
+      </c>
       <c r="I43" t="n">
         <v>5</v>
       </c>
       <c r="J43" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="K43" t="n">
         <v>9</v>
       </c>
       <c r="L43" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3785,6 +3881,9 @@
       <c r="G44" t="n">
         <v>6</v>
       </c>
+      <c r="H44" t="n">
+        <v>7</v>
+      </c>
       <c r="I44" t="n">
         <v>8</v>
       </c>
@@ -3792,10 +3891,10 @@
         <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L44" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M44" t="n">
         <v>7</v>
@@ -3882,17 +3981,23 @@
       <c r="G45" t="n">
         <v>2</v>
       </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
       <c r="I45" t="n">
         <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M45" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3973,20 +4078,23 @@
       <c r="G46" t="n">
         <v>2</v>
       </c>
+      <c r="H46" t="n">
+        <v>3</v>
+      </c>
       <c r="I46" t="n">
         <v>9.5</v>
       </c>
       <c r="J46" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L46" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M46" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -4140,8 +4248,11 @@
       <c r="G48" t="n">
         <v>6</v>
       </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
       <c r="K48" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
         <v>9.5</v>
@@ -4228,17 +4339,20 @@
       <c r="G49" t="n">
         <v>6</v>
       </c>
+      <c r="H49" t="n">
+        <v>3</v>
+      </c>
       <c r="I49" t="n">
         <v>5</v>
       </c>
       <c r="J49" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="L49" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -4313,9 +4427,15 @@
       <c r="G50" t="n">
         <v>8.5</v>
       </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
       <c r="I50" t="n">
         <v>5</v>
       </c>
+      <c r="J50" t="n">
+        <v>2.5</v>
+      </c>
       <c r="L50" t="n">
         <v>9.5</v>
       </c>
@@ -4375,13 +4495,22 @@
         <v>9</v>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>8.5</v>
       </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>6</v>
+      </c>
       <c r="L51" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M51" t="n">
         <v>7</v>
@@ -4505,11 +4634,14 @@
       <c r="G53" t="n">
         <v>6</v>
       </c>
+      <c r="H53" t="n">
+        <v>7</v>
+      </c>
       <c r="I53" t="n">
         <v>9.5</v>
       </c>
       <c r="L53" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M53" t="n">
         <v>7</v>
@@ -4543,7 +4675,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
@@ -4575,14 +4707,20 @@
       <c r="G54" t="n">
         <v>6</v>
       </c>
+      <c r="H54" t="n">
+        <v>7</v>
+      </c>
       <c r="I54" t="n">
         <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6</v>
       </c>
       <c r="L54" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M54" t="n">
         <v>7</v>
@@ -4639,6 +4777,12 @@
       <c r="F55" t="n">
         <v>8</v>
       </c>
+      <c r="H55" t="n">
+        <v>7</v>
+      </c>
+      <c r="L55" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M55" t="n">
         <v>7</v>
       </c>
@@ -4788,17 +4932,20 @@
       <c r="G57" t="n">
         <v>6</v>
       </c>
+      <c r="H57" t="n">
+        <v>7</v>
+      </c>
       <c r="I57" t="n">
         <v>7</v>
       </c>
       <c r="J57" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K57" t="n">
         <v>9</v>
       </c>
       <c r="L57" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
@@ -5198,6 +5345,9 @@
       <c r="G62" t="n">
         <v>8.5</v>
       </c>
+      <c r="H62" t="n">
+        <v>7</v>
+      </c>
       <c r="I62" t="n">
         <v>9.5</v>
       </c>
@@ -5283,17 +5433,23 @@
       <c r="G63" t="n">
         <v>6</v>
       </c>
+      <c r="H63" t="n">
+        <v>7</v>
+      </c>
       <c r="I63" t="n">
         <v>9.5</v>
       </c>
+      <c r="J63" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K63" t="n">
         <v>9</v>
       </c>
       <c r="L63" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M63" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
@@ -5377,17 +5533,23 @@
       <c r="G64" t="n">
         <v>2</v>
       </c>
+      <c r="H64" t="n">
+        <v>2</v>
+      </c>
       <c r="I64" t="n">
         <v>3</v>
       </c>
       <c r="J64" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K64" t="n">
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M64" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -5702,6 +5864,9 @@
       <c r="G68" t="n">
         <v>8.5</v>
       </c>
+      <c r="H68" t="n">
+        <v>7</v>
+      </c>
       <c r="I68" t="n">
         <v>9.5</v>
       </c>
@@ -5867,7 +6032,7 @@
         <v>9</v>
       </c>
       <c r="L70" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M70" t="n">
         <v>7</v>
@@ -5949,7 +6114,7 @@
         <v>9.5</v>
       </c>
       <c r="L71" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M71" t="n">
         <v>9.5</v>
@@ -6016,7 +6181,7 @@
         <v>8.5</v>
       </c>
       <c r="L72" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M72" t="n">
         <v>7</v>
@@ -6159,25 +6324,28 @@
         <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G74" t="n">
         <v>2</v>
       </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
       <c r="I74" t="n">
         <v>6</v>
       </c>
       <c r="J74" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K74" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L74" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="M74" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -6249,17 +6417,20 @@
       <c r="G75" t="n">
         <v>8.5</v>
       </c>
+      <c r="H75" t="n">
+        <v>7</v>
+      </c>
       <c r="I75" t="n">
         <v>8</v>
       </c>
       <c r="J75" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="K75" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L75" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M75" t="n">
         <v>7</v>
@@ -6332,22 +6503,28 @@
         <v>6</v>
       </c>
       <c r="F76" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
         <v>6</v>
       </c>
+      <c r="H76" t="n">
+        <v>2</v>
+      </c>
       <c r="I76" t="n">
         <v>4</v>
       </c>
       <c r="J76" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
       </c>
       <c r="L76" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="M76" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
@@ -6416,6 +6593,9 @@
       <c r="G77" t="n">
         <v>6</v>
       </c>
+      <c r="H77" t="n">
+        <v>7</v>
+      </c>
       <c r="I77" t="n">
         <v>9.5</v>
       </c>
@@ -6423,10 +6603,10 @@
         <v>7</v>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L77" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M77" t="n">
         <v>7</v>
@@ -6569,7 +6749,7 @@
         <v>8</v>
       </c>
       <c r="L79" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M79" t="n">
         <v>7</v>
@@ -6808,6 +6988,9 @@
       <c r="G82" t="n">
         <v>6</v>
       </c>
+      <c r="H82" t="n">
+        <v>7</v>
+      </c>
       <c r="I82" t="n">
         <v>7</v>
       </c>
@@ -6815,10 +6998,10 @@
         <v>7</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L82" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M82" t="n">
         <v>7</v>
@@ -7003,6 +7186,9 @@
       <c r="F85" t="n">
         <v>10.5</v>
       </c>
+      <c r="H85" t="n">
+        <v>3</v>
+      </c>
       <c r="I85" t="n">
         <v>9.5</v>
       </c>
@@ -7016,7 +7202,7 @@
         <v>9.5</v>
       </c>
       <c r="M85" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
@@ -7085,6 +7271,9 @@
       <c r="I86" t="n">
         <v>9.5</v>
       </c>
+      <c r="K86" t="n">
+        <v>6</v>
+      </c>
       <c r="L86" t="n">
         <v>11</v>
       </c>
@@ -7164,6 +7353,12 @@
       <c r="G87" t="n">
         <v>3</v>
       </c>
+      <c r="H87" t="n">
+        <v>7</v>
+      </c>
+      <c r="K87" t="n">
+        <v>6</v>
+      </c>
       <c r="M87" t="n">
         <v>7</v>
       </c>
@@ -7219,6 +7414,9 @@
       <c r="G88" t="n">
         <v>6</v>
       </c>
+      <c r="K88" t="n">
+        <v>4</v>
+      </c>
       <c r="M88" t="n">
         <v>9.5</v>
       </c>
@@ -7327,22 +7525,28 @@
         <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G90" t="n">
         <v>2</v>
       </c>
+      <c r="H90" t="n">
+        <v>2</v>
+      </c>
       <c r="I90" t="n">
         <v>9.5</v>
       </c>
       <c r="J90" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2</v>
       </c>
       <c r="L90" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
@@ -7406,25 +7610,28 @@
         <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G91" t="n">
         <v>6</v>
       </c>
+      <c r="H91" t="n">
+        <v>2</v>
+      </c>
       <c r="I91" t="n">
         <v>6</v>
       </c>
       <c r="J91" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K91" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L91" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M91" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -7599,15 +7806,24 @@
       <c r="D93" t="n">
         <v>9</v>
       </c>
+      <c r="F93" t="n">
+        <v>5</v>
+      </c>
       <c r="G93" t="n">
         <v>6</v>
       </c>
+      <c r="H93" t="n">
+        <v>7</v>
+      </c>
       <c r="I93" t="n">
         <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>9</v>
       </c>
+      <c r="K93" t="n">
+        <v>2</v>
+      </c>
       <c r="L93" t="n">
         <v>11</v>
       </c>
@@ -7727,6 +7943,9 @@
       <c r="G95" t="n">
         <v>6</v>
       </c>
+      <c r="H95" t="n">
+        <v>7</v>
+      </c>
       <c r="I95" t="n">
         <v>9.5</v>
       </c>
@@ -7815,20 +8034,23 @@
       <c r="G96" t="n">
         <v>3</v>
       </c>
+      <c r="H96" t="n">
+        <v>5</v>
+      </c>
       <c r="I96" t="n">
         <v>5</v>
       </c>
       <c r="J96" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K96" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L96" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M96" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -7962,22 +8184,28 @@
         <v>6</v>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G98" t="n">
         <v>3</v>
       </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
       <c r="I98" t="n">
         <v>4</v>
       </c>
       <c r="J98" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>6</v>
       </c>
       <c r="L98" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M98" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O98" t="n">
         <v>1</v>
@@ -8107,17 +8335,23 @@
       <c r="G100" t="n">
         <v>3</v>
       </c>
+      <c r="H100" t="n">
+        <v>2</v>
+      </c>
       <c r="I100" t="n">
         <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K100" t="n">
+        <v>6</v>
       </c>
       <c r="L100" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M100" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="O100" t="n">
         <v>1</v>
@@ -8195,6 +8429,9 @@
       <c r="G101" t="n">
         <v>6</v>
       </c>
+      <c r="H101" t="n">
+        <v>7</v>
+      </c>
       <c r="I101" t="n">
         <v>7</v>
       </c>
@@ -8202,13 +8439,13 @@
         <v>7</v>
       </c>
       <c r="K101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L101" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M101" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O101" t="n">
         <v>1</v>
@@ -8286,6 +8523,9 @@
       <c r="G102" t="n">
         <v>6</v>
       </c>
+      <c r="H102" t="n">
+        <v>3</v>
+      </c>
       <c r="I102" t="n">
         <v>9.5</v>
       </c>
@@ -8296,7 +8536,7 @@
         <v>8</v>
       </c>
       <c r="L102" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M102" t="n">
         <v>7</v>
@@ -8386,6 +8626,9 @@
       <c r="G103" t="n">
         <v>8.5</v>
       </c>
+      <c r="H103" t="n">
+        <v>7</v>
+      </c>
       <c r="I103" t="n">
         <v>9.5</v>
       </c>
@@ -8483,6 +8726,9 @@
       <c r="G104" t="n">
         <v>6</v>
       </c>
+      <c r="H104" t="n">
+        <v>7</v>
+      </c>
       <c r="I104" t="n">
         <v>7</v>
       </c>
@@ -8490,7 +8736,7 @@
         <v>9</v>
       </c>
       <c r="L104" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="N104" t="n">
         <v>1</v>
@@ -8554,11 +8800,20 @@
         <v>10</v>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G105" t="n">
         <v>8.5</v>
       </c>
+      <c r="H105" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2</v>
+      </c>
+      <c r="L105" t="n">
+        <v>5</v>
+      </c>
       <c r="M105" t="n">
         <v>7</v>
       </c>
@@ -8697,6 +8952,9 @@
       <c r="G108" t="n">
         <v>8.5</v>
       </c>
+      <c r="L108" t="n">
+        <v>7.5</v>
+      </c>
       <c r="AC108" t="n">
         <v>1</v>
       </c>
@@ -8772,7 +9030,7 @@
         <v>10</v>
       </c>
       <c r="J110" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="M110" t="n">
         <v>9.5</v>
@@ -8957,6 +9215,9 @@
       <c r="J113" t="n">
         <v>7</v>
       </c>
+      <c r="L113" t="n">
+        <v>7.5</v>
+      </c>
       <c r="AA113" t="n">
         <v>1</v>
       </c>
@@ -8982,7 +9243,7 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
@@ -9352,6 +9613,9 @@
       <c r="D121" t="n">
         <v>10</v>
       </c>
+      <c r="H121" t="n">
+        <v>7</v>
+      </c>
       <c r="I121" t="n">
         <v>9.5</v>
       </c>
@@ -9393,7 +9657,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Técnicas para determinar estructuras orgánicas</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9402,21 +9666,12 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D122" t="n">
-        <v>10</v>
-      </c>
-      <c r="L122" t="n">
         <v>11</v>
       </c>
-      <c r="M122" t="n">
-        <v>7</v>
-      </c>
-      <c r="U122" t="n">
-        <v>1</v>
-      </c>
-      <c r="X122" t="n">
+      <c r="W122" t="n">
         <v>1</v>
       </c>
       <c r="Y122" t="n">
@@ -9425,21 +9680,9 @@
       <c r="Z122" t="n">
         <v>1</v>
       </c>
-      <c r="AA122" t="n">
-        <v>1</v>
-      </c>
       <c r="AC122" t="n">
         <v>1</v>
       </c>
-      <c r="AD122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF122" t="n">
-        <v>11</v>
-      </c>
       <c r="AG122" t="inlineStr">
         <is>
           <t>solo_especializacion</t>
@@ -9447,14 +9690,14 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9463,30 +9706,21 @@
         </is>
       </c>
       <c r="C123" t="n">
+        <v>10</v>
+      </c>
+      <c r="D123" t="n">
+        <v>10</v>
+      </c>
+      <c r="L123" t="n">
         <v>11</v>
-      </c>
-      <c r="D123" t="n">
-        <v>11</v>
-      </c>
-      <c r="G123" t="n">
-        <v>6</v>
-      </c>
-      <c r="I123" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L123" t="n">
-        <v>9.5</v>
       </c>
       <c r="M123" t="n">
         <v>7</v>
       </c>
-      <c r="R123" t="n">
-        <v>1</v>
-      </c>
       <c r="U123" t="n">
         <v>1</v>
       </c>
-      <c r="W123" t="n">
+      <c r="X123" t="n">
         <v>1</v>
       </c>
       <c r="Y123" t="n">
@@ -9496,6 +9730,9 @@
         <v>1</v>
       </c>
       <c r="AA123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC123" t="n">
         <v>1</v>
       </c>
       <c r="AD123" t="n">
@@ -9686,7 +9923,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Indicadores ácido-base</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9695,53 +9932,47 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D127" t="n">
-        <v>9</v>
-      </c>
-      <c r="F127" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G127" t="n">
-        <v>6</v>
-      </c>
-      <c r="I127" t="n">
-        <v>5</v>
-      </c>
-      <c r="J127" t="n">
-        <v>9</v>
-      </c>
-      <c r="K127" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="L127" t="n">
+        <v>11</v>
+      </c>
+      <c r="M127" t="n">
         <v>9.5</v>
       </c>
-      <c r="M127" t="n">
-        <v>7</v>
-      </c>
-      <c r="O127" t="n">
-        <v>1</v>
-      </c>
-      <c r="S127" t="n">
-        <v>1</v>
-      </c>
-      <c r="T127" t="n">
+      <c r="P127" t="n">
         <v>1</v>
       </c>
       <c r="U127" t="n">
         <v>1</v>
       </c>
+      <c r="V127" t="n">
+        <v>1</v>
+      </c>
       <c r="W127" t="n">
         <v>1</v>
       </c>
+      <c r="X127" t="n">
+        <v>1</v>
+      </c>
       <c r="Y127" t="n">
         <v>1</v>
       </c>
       <c r="Z127" t="n">
         <v>1</v>
       </c>
+      <c r="AA127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>1</v>
+      </c>
       <c r="AC127" t="n">
         <v>1</v>
       </c>
@@ -9752,7 +9983,7 @@
         <v>1</v>
       </c>
       <c r="AF127" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
@@ -9768,7 +9999,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Ley de velocidad, orden de reacción y ecuación de Arrhenius</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9777,32 +10008,17 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D128" t="n">
-        <v>10</v>
-      </c>
-      <c r="G128" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L128" t="n">
         <v>11</v>
       </c>
-      <c r="M128" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P128" t="n">
-        <v>1</v>
-      </c>
       <c r="U128" t="n">
         <v>1</v>
       </c>
-      <c r="V128" t="n">
-        <v>1</v>
-      </c>
-      <c r="W128" t="n">
-        <v>1</v>
-      </c>
       <c r="X128" t="n">
         <v>1</v>
       </c>
@@ -9810,9 +10026,6 @@
         <v>1</v>
       </c>
       <c r="Z128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA128" t="n">
         <v>1</v>
       </c>
       <c r="AB128" t="n">
@@ -9844,7 +10057,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ley de velocidad, orden de reacción y ecuación de Arrhenius</t>
+          <t>Mecanismos de reacción</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9853,16 +10066,10 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D129" t="n">
-        <v>9</v>
-      </c>
-      <c r="L129" t="n">
-        <v>11</v>
-      </c>
-      <c r="U129" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X129" t="n">
         <v>1</v>
@@ -9873,16 +10080,10 @@
       <c r="Z129" t="n">
         <v>1</v>
       </c>
-      <c r="AB129" t="n">
-        <v>1</v>
-      </c>
       <c r="AC129" t="n">
         <v>1</v>
       </c>
       <c r="AD129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE129" t="n">
         <v>1</v>
       </c>
       <c r="AF129" t="n">
@@ -9902,7 +10103,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mecanismos de reacción</t>
+          <t>Nanomateriales y manufactura molecular</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9911,12 +10112,15 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D130" t="n">
-        <v>10</v>
-      </c>
-      <c r="X130" t="n">
+        <v>11</v>
+      </c>
+      <c r="G130" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W130" t="n">
         <v>1</v>
       </c>
       <c r="Y130" t="n">
@@ -9925,14 +10129,11 @@
       <c r="Z130" t="n">
         <v>1</v>
       </c>
-      <c r="AC130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD130" t="n">
+      <c r="AE130" t="n">
         <v>1</v>
       </c>
       <c r="AF130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
@@ -9948,7 +10149,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Nanomateriales y manufactura molecular</t>
+          <t>Polimerización por adición y por condensación</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9962,8 +10163,17 @@
       <c r="D131" t="n">
         <v>11</v>
       </c>
-      <c r="G131" t="n">
-        <v>8.5</v>
+      <c r="F131" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L131" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" t="n">
+        <v>1</v>
       </c>
       <c r="W131" t="n">
         <v>1</v>
@@ -9972,6 +10182,18 @@
         <v>1</v>
       </c>
       <c r="Z131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD131" t="n">
         <v>1</v>
       </c>
       <c r="AE131" t="n">
@@ -9994,7 +10216,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Polimerización por adición y por condensación</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10003,33 +10225,39 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F132" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L132" t="n">
+        <v>8</v>
+      </c>
+      <c r="G132" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I132" t="n">
         <v>9.5</v>
       </c>
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="U132" t="n">
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="R132" t="n">
         <v>1</v>
       </c>
       <c r="W132" t="n">
         <v>1</v>
       </c>
+      <c r="X132" t="n">
+        <v>1</v>
+      </c>
       <c r="Y132" t="n">
         <v>1</v>
       </c>
       <c r="Z132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA132" t="n">
         <v>1</v>
       </c>
       <c r="AB132" t="n">
@@ -10061,7 +10289,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Producto de solubilidad (Kps)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10075,37 +10303,7 @@
       <c r="D133" t="n">
         <v>10</v>
       </c>
-      <c r="F133" t="n">
-        <v>8</v>
-      </c>
-      <c r="G133" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I133" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O133" t="n">
-        <v>1</v>
-      </c>
-      <c r="P133" t="n">
-        <v>1</v>
-      </c>
-      <c r="R133" t="n">
-        <v>1</v>
-      </c>
-      <c r="W133" t="n">
-        <v>1</v>
-      </c>
       <c r="X133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB133" t="n">
         <v>1</v>
       </c>
       <c r="AC133" t="n">
@@ -10134,7 +10332,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Producto de solubilidad (Kps)</t>
+          <t>Química de los ácidos nucleicos</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10148,20 +10346,20 @@
       <c r="D134" t="n">
         <v>10</v>
       </c>
-      <c r="X134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE134" t="n">
+      <c r="Y134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" t="n">
         <v>1</v>
       </c>
       <c r="AF134" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
@@ -10177,7 +10375,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Química de los ácidos nucleicos</t>
+          <t>Química verde y economía atómica</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10186,10 +10384,40 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D135" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G135" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H135" t="n">
+        <v>7</v>
+      </c>
+      <c r="K135" t="n">
+        <v>4</v>
+      </c>
+      <c r="L135" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M135" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" t="n">
+        <v>1</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1</v>
+      </c>
+      <c r="X135" t="n">
+        <v>1</v>
       </c>
       <c r="Y135" t="n">
         <v>1</v>
@@ -10197,23 +10425,26 @@
       <c r="Z135" t="n">
         <v>1</v>
       </c>
-      <c r="AA135" t="n">
-        <v>1</v>
-      </c>
       <c r="AB135" t="n">
         <v>1</v>
       </c>
+      <c r="AC135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1</v>
+      </c>
       <c r="AF135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>

--- a/internacional/Contraste_quimica.xlsx
+++ b/internacional/Contraste_quimica.xlsx
@@ -3508,77 +3508,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Disolución y rapidez de disolución</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
         <v>6</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
-      </c>
-      <c r="I39" t="n">
-        <v>9.5</v>
+        <v>2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M39" t="n">
-        <v>7</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AA39" t="n">
         <v>1</v>
       </c>
-      <c r="AD39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE39" t="n">
+      <c r="AC39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Disolución y rapidez de disolución</t>
+          <t>Minerales: composición y estructura cristalina</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3587,41 +3572,44 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="G40" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L40" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" t="n">
         <v>1</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AD40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3633,7 +3621,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Minerales: composición y estructura cristalina</t>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3642,44 +3630,62 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
       </c>
       <c r="F41" t="n">
         <v>8</v>
       </c>
-      <c r="H41" t="n">
+      <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>9</v>
+      </c>
+      <c r="M41" t="n">
         <v>7</v>
       </c>
-      <c r="J41" t="n">
-        <v>9</v>
-      </c>
-      <c r="L41" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
         <v>1</v>
       </c>
       <c r="Z41" t="n">
         <v>1</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AC41" t="n">
         <v>1</v>
       </c>
       <c r="AD41" t="n">
         <v>1</v>
       </c>
+      <c r="AE41" t="n">
+        <v>1</v>
+      </c>
       <c r="AF41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -3691,19 +3697,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+          <t>Ácidos y bases: propiedades</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F42" t="n">
         <v>8</v>
@@ -3711,14 +3717,23 @@
       <c r="G42" t="n">
         <v>6</v>
       </c>
+      <c r="H42" t="n">
+        <v>7</v>
+      </c>
       <c r="I42" t="n">
-        <v>9.5</v>
+        <v>5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.5</v>
       </c>
       <c r="K42" t="n">
         <v>9</v>
       </c>
+      <c r="L42" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -3729,10 +3744,19 @@
       <c r="R42" t="n">
         <v>1</v>
       </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
-      <c r="X42" t="n">
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>1</v>
       </c>
       <c r="Y42" t="n">
@@ -3745,9 +3769,6 @@
         <v>1</v>
       </c>
       <c r="AD42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
@@ -3760,14 +3781,14 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ácidos y bases: propiedades</t>
+          <t>Átomo y partículas subatómicas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3776,11 +3797,14 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
         <v>9</v>
       </c>
+      <c r="E43" t="n">
+        <v>8</v>
+      </c>
       <c r="F43" t="n">
         <v>8</v>
       </c>
@@ -3791,19 +3815,22 @@
         <v>7</v>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
         <v>7.5</v>
       </c>
       <c r="M43" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3814,9 +3841,6 @@
       <c r="R43" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="n">
-        <v>1</v>
-      </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
@@ -3829,6 +3853,9 @@
       <c r="W43" t="n">
         <v>1</v>
       </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
       <c r="Y43" t="n">
         <v>1</v>
       </c>
@@ -3841,8 +3868,11 @@
       <c r="AD43" t="n">
         <v>1</v>
       </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
       <c r="AF43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3858,7 +3888,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Átomo y partículas subatómicas</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3867,40 +3897,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>7</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
@@ -3911,9 +3938,6 @@
       <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
       <c r="U44" t="n">
         <v>1</v>
       </c>
@@ -3932,17 +3956,20 @@
       <c r="Z44" t="n">
         <v>1</v>
       </c>
+      <c r="AA44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1</v>
+      </c>
       <c r="AC44" t="n">
         <v>1</v>
       </c>
       <c r="AD44" t="n">
         <v>1</v>
       </c>
-      <c r="AE44" t="n">
-        <v>1</v>
-      </c>
       <c r="AF44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3958,7 +3985,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Cambios físicos y químicos</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3970,7 +3997,7 @@
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
@@ -3982,22 +4009,22 @@
         <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J45" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M45" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -4008,25 +4035,22 @@
       <c r="R45" t="n">
         <v>1</v>
       </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
       <c r="U45" t="n">
         <v>1</v>
       </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
       <c r="W45" t="n">
         <v>1</v>
       </c>
-      <c r="X45" t="n">
-        <v>1</v>
-      </c>
       <c r="Y45" t="n">
         <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA45" t="n">
         <v>1</v>
       </c>
       <c r="AB45" t="n">
@@ -4048,14 +4072,14 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cambios físicos y químicos</t>
+          <t>Catalizadores</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4064,37 +4088,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
         <v>10</v>
       </c>
-      <c r="E46" t="n">
-        <v>2</v>
-      </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" t="n">
-        <v>3</v>
-      </c>
-      <c r="I46" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L46" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="M46" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -4102,27 +4111,24 @@
       <c r="P46" t="n">
         <v>1</v>
       </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
       <c r="U46" t="n">
         <v>1</v>
       </c>
       <c r="W46" t="n">
         <v>1</v>
       </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
       <c r="Y46" t="n">
         <v>1</v>
       </c>
       <c r="Z46" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" t="n">
+        <v>1</v>
+      </c>
       <c r="AB46" t="n">
         <v>1</v>
       </c>
@@ -4132,8 +4138,11 @@
       <c r="AD46" t="n">
         <v>1</v>
       </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
       <c r="AF46" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -4142,14 +4151,14 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Catalizadores</t>
+          <t>Combustibles fósiles y biocombustibles</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4158,19 +4167,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G47" t="n">
         <v>6</v>
       </c>
+      <c r="H47" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
       <c r="L47" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M47" t="n">
         <v>7</v>
@@ -4181,9 +4196,15 @@
       <c r="P47" t="n">
         <v>1</v>
       </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
       <c r="U47" t="n">
         <v>1</v>
       </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
       <c r="W47" t="n">
         <v>1</v>
       </c>
@@ -4196,9 +4217,6 @@
       <c r="Z47" t="n">
         <v>1</v>
       </c>
-      <c r="AA47" t="n">
-        <v>1</v>
-      </c>
       <c r="AB47" t="n">
         <v>1</v>
       </c>
@@ -4212,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -4221,14 +4239,14 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Combustibles fósiles y biocombustibles</t>
+          <t>Combustión</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4242,6 +4260,9 @@
       <c r="D48" t="n">
         <v>9</v>
       </c>
+      <c r="E48" t="n">
+        <v>8</v>
+      </c>
       <c r="F48" t="n">
         <v>8</v>
       </c>
@@ -4251,14 +4272,17 @@
       <c r="H48" t="n">
         <v>3</v>
       </c>
-      <c r="K48" t="n">
-        <v>2</v>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4.5</v>
       </c>
       <c r="L48" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M48" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
@@ -4266,7 +4290,7 @@
       <c r="P48" t="n">
         <v>1</v>
       </c>
-      <c r="T48" t="n">
+      <c r="S48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
@@ -4276,9 +4300,6 @@
         <v>1</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
-      </c>
-      <c r="X48" t="n">
         <v>1</v>
       </c>
       <c r="Y48" t="n">
@@ -4316,7 +4337,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Combustión</t>
+          <t>Composición del aire y contaminantes atmosféricos</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4325,34 +4346,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
         <v>9</v>
       </c>
-      <c r="E49" t="n">
-        <v>8</v>
-      </c>
       <c r="F49" t="n">
         <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
         <v>5</v>
       </c>
       <c r="J49" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="L49" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
@@ -4360,28 +4375,16 @@
       <c r="P49" t="n">
         <v>1</v>
       </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
       <c r="U49" t="n">
         <v>1</v>
       </c>
-      <c r="V49" t="n">
-        <v>1</v>
-      </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="X49" t="n">
         <v>1</v>
       </c>
       <c r="Z49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC49" t="n">
         <v>1</v>
       </c>
       <c r="AD49" t="n">
@@ -4407,7 +4410,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Composición del aire y contaminantes atmosféricos</t>
+          <t>Soluto, disolvente y concentración</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4422,7 +4425,7 @@
         <v>9</v>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
         <v>8.5</v>
@@ -4430,14 +4433,17 @@
       <c r="H50" t="n">
         <v>2</v>
       </c>
-      <c r="I50" t="n">
-        <v>5</v>
-      </c>
       <c r="J50" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6</v>
       </c>
       <c r="L50" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
@@ -4448,23 +4454,32 @@
       <c r="U50" t="n">
         <v>1</v>
       </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
       <c r="W50" t="n">
         <v>1</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Y50" t="n">
         <v>1</v>
       </c>
       <c r="Z50" t="n">
         <v>1</v>
       </c>
+      <c r="AA50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1</v>
+      </c>
       <c r="AD50" t="n">
         <v>1</v>
       </c>
-      <c r="AE50" t="n">
-        <v>1</v>
-      </c>
       <c r="AF50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -4480,7 +4495,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Soluto, disolvente y concentración</t>
+          <t>Configuración electrónica por orbitales</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4489,67 +4504,34 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
-      </c>
-      <c r="F51" t="n">
+        <v>10</v>
+      </c>
+      <c r="L51" t="n">
+        <v>11</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="n">
         <v>5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K51" t="n">
-        <v>6</v>
-      </c>
-      <c r="L51" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>7</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>3</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -4565,7 +4547,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Configuración electrónica por orbitales</t>
+          <t>Cromatografía</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4574,50 +4556,68 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D52" t="n">
         <v>10</v>
       </c>
+      <c r="G52" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>7</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L52" t="n">
-        <v>11</v>
+        <v>7.5</v>
+      </c>
+      <c r="M52" t="n">
+        <v>7</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
       </c>
       <c r="U52" t="n">
         <v>1</v>
       </c>
-      <c r="X52" t="n">
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>1</v>
       </c>
       <c r="Y52" t="n">
         <v>1</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="Z52" t="n">
         <v>1</v>
       </c>
       <c r="AD52" t="n">
         <v>1</v>
       </c>
-      <c r="AE52" t="n">
-        <v>1</v>
-      </c>
       <c r="AF52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cromatografía</t>
+          <t>Densidad y flotación</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4626,10 +4626,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8</v>
       </c>
       <c r="G53" t="n">
         <v>6</v>
@@ -4638,7 +4641,13 @@
         <v>7</v>
       </c>
       <c r="I53" t="n">
-        <v>9.5</v>
+        <v>2</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>6</v>
       </c>
       <c r="L53" t="n">
         <v>7.5</v>
@@ -4646,21 +4655,15 @@
       <c r="M53" t="n">
         <v>7</v>
       </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
       <c r="U53" t="n">
         <v>1</v>
       </c>
-      <c r="V53" t="n">
-        <v>1</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1</v>
-      </c>
       <c r="Y53" t="n">
         <v>1</v>
       </c>
@@ -4671,23 +4674,23 @@
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Densidad y flotación</t>
+          <t>Disoluciones, coloides y suspensiones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4696,29 +4699,17 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F54" t="n">
         <v>8</v>
       </c>
-      <c r="G54" t="n">
-        <v>6</v>
-      </c>
       <c r="H54" t="n">
         <v>7</v>
       </c>
-      <c r="I54" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K54" t="n">
-        <v>6</v>
-      </c>
       <c r="L54" t="n">
         <v>7.5</v>
       </c>
@@ -4728,23 +4719,20 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y54" t="n">
+      <c r="V54" t="n">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
         <v>1</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" t="n">
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -4760,7 +4748,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Disoluciones, coloides y suspensiones</t>
+          <t>Distribución electrónica por niveles (modelo de capas)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4769,27 +4757,57 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9</v>
       </c>
       <c r="F55" t="n">
         <v>8</v>
       </c>
-      <c r="H55" t="n">
-        <v>7</v>
+      <c r="G55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>8</v>
       </c>
       <c r="L55" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M55" t="n">
-        <v>7</v>
+        <v>9.5</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="V55" t="n">
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
@@ -4801,8 +4819,11 @@
       <c r="AC55" t="n">
         <v>1</v>
       </c>
+      <c r="AD55" t="n">
+        <v>1</v>
+      </c>
       <c r="AF55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4818,7 +4839,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Distribución electrónica por niveles (modelo de capas)</t>
+          <t>Ecuación química y su balanceo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4827,34 +4848,37 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
         <v>9</v>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>7</v>
       </c>
       <c r="I56" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="J56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K56" t="n">
         <v>9</v>
       </c>
-      <c r="K56" t="n">
-        <v>8</v>
-      </c>
       <c r="L56" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
+        <v>7.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>7</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -4865,12 +4889,15 @@
       <c r="R56" t="n">
         <v>1</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
         <v>1</v>
       </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
@@ -4883,7 +4910,7 @@
       <c r="Z56" t="n">
         <v>1</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AB56" t="n">
         <v>1</v>
       </c>
       <c r="AC56" t="n">
@@ -4892,8 +4919,11 @@
       <c r="AD56" t="n">
         <v>1</v>
       </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
       <c r="AF56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4909,7 +4939,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ecuación química y su balanceo</t>
+          <t>Electronegatividad y polaridad de enlace</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4921,79 +4951,43 @@
         <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
-      </c>
-      <c r="E57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
-      </c>
-      <c r="G57" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L57" t="n">
+        <v>11</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="n">
         <v>6</v>
-      </c>
-      <c r="H57" t="n">
-        <v>7</v>
-      </c>
-      <c r="I57" t="n">
-        <v>7</v>
-      </c>
-      <c r="J57" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K57" t="n">
-        <v>9</v>
-      </c>
-      <c r="L57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M57" t="n">
-        <v>7</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>7</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -5009,7 +5003,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Electronegatividad y polaridad de enlace</t>
+          <t>Electrones de valencia y regla del octeto</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5026,19 +5020,34 @@
       <c r="F58" t="n">
         <v>10.5</v>
       </c>
+      <c r="G58" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>9</v>
+      </c>
       <c r="L58" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
       <c r="U58" t="n">
         <v>1</v>
       </c>
       <c r="W58" t="n">
-        <v>1</v>
-      </c>
-      <c r="X58" t="n">
         <v>1</v>
       </c>
       <c r="Y58" t="n">
@@ -5073,7 +5082,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Electrones de valencia y regla del octeto</t>
+          <t>Enlace covalente</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5088,7 +5097,7 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G59" t="n">
         <v>8.5</v>
@@ -5102,6 +5111,9 @@
       <c r="L59" t="n">
         <v>9.5</v>
       </c>
+      <c r="M59" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
@@ -5117,6 +5129,9 @@
       <c r="U59" t="n">
         <v>1</v>
       </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
       <c r="W59" t="n">
         <v>1</v>
       </c>
@@ -5133,6 +5148,9 @@
         <v>1</v>
       </c>
       <c r="AD59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE59" t="n">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
@@ -5152,7 +5170,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enlace covalente</t>
+          <t>Enlace iónico</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5161,7 +5179,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
         <v>10</v>
@@ -5220,11 +5238,8 @@
       <c r="AD60" t="n">
         <v>1</v>
       </c>
-      <c r="AE60" t="n">
-        <v>1</v>
-      </c>
       <c r="AF60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -5240,7 +5255,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enlace iónico</t>
+          <t>Enlace metálico</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5249,7 +5264,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
         <v>10</v>
@@ -5260,6 +5275,9 @@
       <c r="G61" t="n">
         <v>8.5</v>
       </c>
+      <c r="H61" t="n">
+        <v>7</v>
+      </c>
       <c r="I61" t="n">
         <v>9.5</v>
       </c>
@@ -5269,9 +5287,6 @@
       <c r="L61" t="n">
         <v>9.5</v>
       </c>
-      <c r="M61" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O61" t="n">
         <v>1</v>
       </c>
@@ -5287,12 +5302,12 @@
       <c r="U61" t="n">
         <v>1</v>
       </c>
-      <c r="V61" t="n">
-        <v>1</v>
-      </c>
       <c r="W61" t="n">
         <v>1</v>
       </c>
+      <c r="X61" t="n">
+        <v>1</v>
+      </c>
       <c r="Y61" t="n">
         <v>1</v>
       </c>
@@ -5308,8 +5323,11 @@
       <c r="AD61" t="n">
         <v>1</v>
       </c>
+      <c r="AE61" t="n">
+        <v>1</v>
+      </c>
       <c r="AF61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -5325,7 +5343,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enlace metálico</t>
+          <t>Escala de pH</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5334,16 +5352,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F62" t="n">
         <v>8</v>
       </c>
       <c r="G62" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H62" t="n">
         <v>7</v>
@@ -5352,10 +5370,16 @@
         <v>9.5</v>
       </c>
       <c r="J62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K62" t="n">
         <v>9</v>
       </c>
       <c r="L62" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4.5</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
@@ -5366,12 +5390,15 @@
       <c r="R62" t="n">
         <v>1</v>
       </c>
-      <c r="S62" t="n">
+      <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
         <v>1</v>
       </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
       <c r="W62" t="n">
         <v>1</v>
       </c>
@@ -5397,7 +5424,7 @@
         <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -5413,7 +5440,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Escala de pH</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5422,34 +5449,37 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
         <v>9</v>
       </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
       <c r="F63" t="n">
         <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M63" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
@@ -5460,27 +5490,18 @@
       <c r="R63" t="n">
         <v>1</v>
       </c>
-      <c r="T63" t="n">
-        <v>1</v>
-      </c>
       <c r="U63" t="n">
         <v>1</v>
       </c>
-      <c r="V63" t="n">
-        <v>1</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1</v>
-      </c>
-      <c r="X63" t="n">
-        <v>1</v>
-      </c>
       <c r="Y63" t="n">
         <v>1</v>
       </c>
       <c r="Z63" t="n">
         <v>1</v>
       </c>
+      <c r="AA63" t="n">
+        <v>1</v>
+      </c>
       <c r="AB63" t="n">
         <v>1</v>
       </c>
@@ -5490,11 +5511,8 @@
       <c r="AD63" t="n">
         <v>1</v>
       </c>
-      <c r="AE63" t="n">
-        <v>1</v>
-      </c>
       <c r="AF63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -5510,7 +5528,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Estequiometría</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5519,37 +5537,28 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
-      </c>
-      <c r="E64" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>8</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
-      </c>
-      <c r="H64" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J64" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L64" t="n">
-        <v>4</v>
+        <v>9.5</v>
       </c>
       <c r="M64" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -5563,6 +5572,15 @@
       <c r="U64" t="n">
         <v>1</v>
       </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1</v>
+      </c>
       <c r="Y64" t="n">
         <v>1</v>
       </c>
@@ -5581,8 +5599,11 @@
       <c r="AD64" t="n">
         <v>1</v>
       </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
       <c r="AF64" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -5598,7 +5619,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Notación y estructuras de Lewis</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5607,44 +5628,29 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
         <v>10</v>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G65" t="n">
         <v>8.5</v>
       </c>
-      <c r="I65" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J65" t="n">
-        <v>7</v>
-      </c>
       <c r="L65" t="n">
         <v>9.5</v>
       </c>
-      <c r="M65" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
       </c>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
       <c r="U65" t="n">
         <v>1</v>
       </c>
-      <c r="V65" t="n">
-        <v>1</v>
-      </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
@@ -5657,9 +5663,6 @@
       <c r="Z65" t="n">
         <v>1</v>
       </c>
-      <c r="AA65" t="n">
-        <v>1</v>
-      </c>
       <c r="AB65" t="n">
         <v>1</v>
       </c>
@@ -5669,11 +5672,8 @@
       <c r="AD65" t="n">
         <v>1</v>
       </c>
-      <c r="AE65" t="n">
-        <v>1</v>
-      </c>
       <c r="AF65" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Notación y estructuras de Lewis</t>
+          <t>Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,9 +5709,15 @@
       <c r="G66" t="n">
         <v>8.5</v>
       </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
       <c r="L66" t="n">
         <v>9.5</v>
       </c>
+      <c r="M66" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O66" t="n">
         <v>1</v>
       </c>
@@ -5721,6 +5727,9 @@
       <c r="U66" t="n">
         <v>1</v>
       </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
       <c r="W66" t="n">
         <v>1</v>
       </c>
@@ -5733,6 +5742,9 @@
       <c r="Z66" t="n">
         <v>1</v>
       </c>
+      <c r="AA66" t="n">
+        <v>1</v>
+      </c>
       <c r="AB66" t="n">
         <v>1</v>
       </c>
@@ -5740,6 +5752,9 @@
         <v>1</v>
       </c>
       <c r="AD66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
@@ -5759,7 +5774,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares</t>
+          <t>Fuerzas intermoleculares y propiedades físicas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5768,36 +5783,36 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
         <v>10</v>
       </c>
       <c r="F67" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G67" t="n">
         <v>8.5</v>
       </c>
-      <c r="J67" t="n">
+      <c r="H67" t="n">
         <v>7</v>
+      </c>
+      <c r="I67" t="n">
+        <v>9.5</v>
       </c>
       <c r="L67" t="n">
         <v>9.5</v>
       </c>
-      <c r="M67" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
       <c r="P67" t="n">
         <v>1</v>
       </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
       <c r="U67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" t="n">
         <v>1</v>
       </c>
       <c r="W67" t="n">
@@ -5844,7 +5859,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares y propiedades físicas</t>
+          <t>Geometría molecular (RPECV)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5853,38 +5868,29 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
         <v>10</v>
       </c>
-      <c r="F68" t="n">
-        <v>8</v>
-      </c>
       <c r="G68" t="n">
         <v>8.5</v>
       </c>
-      <c r="H68" t="n">
-        <v>7</v>
-      </c>
-      <c r="I68" t="n">
+      <c r="L68" t="n">
+        <v>11</v>
+      </c>
+      <c r="M68" t="n">
         <v>9.5</v>
       </c>
-      <c r="L68" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1</v>
-      </c>
       <c r="P68" t="n">
         <v>1</v>
       </c>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
       <c r="U68" t="n">
         <v>1</v>
       </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
       <c r="W68" t="n">
         <v>1</v>
       </c>
@@ -5895,9 +5901,6 @@
         <v>1</v>
       </c>
       <c r="Z68" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA68" t="n">
         <v>1</v>
       </c>
       <c r="AB68" t="n">
@@ -5929,7 +5932,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Geometría molecular (RPECV)</t>
+          <t>Iones</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5938,23 +5941,44 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
         <v>10</v>
       </c>
+      <c r="F69" t="n">
+        <v>8</v>
+      </c>
       <c r="G69" t="n">
         <v>8.5</v>
       </c>
+      <c r="I69" t="n">
+        <v>8</v>
+      </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
+      <c r="K69" t="n">
+        <v>9</v>
+      </c>
       <c r="L69" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="M69" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
       <c r="U69" t="n">
         <v>1</v>
       </c>
@@ -5973,20 +5997,14 @@
       <c r="Z69" t="n">
         <v>1</v>
       </c>
-      <c r="AB69" t="n">
-        <v>1</v>
-      </c>
       <c r="AC69" t="n">
         <v>1</v>
       </c>
       <c r="AD69" t="n">
         <v>1</v>
       </c>
-      <c r="AE69" t="n">
-        <v>1</v>
-      </c>
       <c r="AF69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -6002,7 +6020,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Iones</t>
+          <t>Isótopos</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6016,29 +6034,20 @@
       <c r="D70" t="n">
         <v>10</v>
       </c>
-      <c r="F70" t="n">
+      <c r="E70" t="n">
         <v>8</v>
       </c>
       <c r="G70" t="n">
         <v>8.5</v>
       </c>
       <c r="I70" t="n">
-        <v>8</v>
-      </c>
-      <c r="J70" t="n">
-        <v>7</v>
-      </c>
-      <c r="K70" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="L70" t="n">
         <v>7.5</v>
       </c>
       <c r="M70" t="n">
-        <v>7</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
@@ -6046,9 +6055,6 @@
       <c r="R70" t="n">
         <v>1</v>
       </c>
-      <c r="T70" t="n">
-        <v>1</v>
-      </c>
       <c r="U70" t="n">
         <v>1</v>
       </c>
@@ -6056,9 +6062,6 @@
         <v>1</v>
       </c>
       <c r="W70" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" t="n">
         <v>1</v>
       </c>
       <c r="Y70" t="n">
@@ -6090,7 +6093,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Isótopos</t>
+          <t>Masa atómica relativa</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6104,31 +6107,19 @@
       <c r="D71" t="n">
         <v>10</v>
       </c>
-      <c r="E71" t="n">
-        <v>8</v>
-      </c>
       <c r="G71" t="n">
         <v>8.5</v>
       </c>
-      <c r="I71" t="n">
-        <v>9.5</v>
-      </c>
       <c r="L71" t="n">
         <v>7.5</v>
       </c>
       <c r="M71" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
       </c>
-      <c r="R71" t="n">
-        <v>1</v>
-      </c>
       <c r="U71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" t="n">
         <v>1</v>
       </c>
       <c r="W71" t="n">
@@ -6163,7 +6154,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Masa atómica relativa</t>
+          <t>Masa molar</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6172,35 +6163,56 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
         <v>10</v>
       </c>
+      <c r="F72" t="n">
+        <v>8</v>
+      </c>
       <c r="G72" t="n">
         <v>8.5</v>
       </c>
+      <c r="I72" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L72" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M72" t="n">
-        <v>7</v>
+        <v>9.5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
       </c>
       <c r="P72" t="n">
         <v>1</v>
       </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
       <c r="U72" t="n">
         <v>1</v>
       </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
       <c r="W72" t="n">
         <v>1</v>
       </c>
+      <c r="X72" t="n">
+        <v>1</v>
+      </c>
       <c r="Y72" t="n">
         <v>1</v>
       </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
+      <c r="AB72" t="n">
+        <v>1</v>
+      </c>
       <c r="AC72" t="n">
         <v>1</v>
       </c>
@@ -6208,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="AF72" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -6224,7 +6236,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Masa molar</t>
+          <t>Materia y materiales</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6233,25 +6245,37 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
         <v>10</v>
       </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G73" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>9.5</v>
+        <v>6</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2</v>
       </c>
       <c r="L73" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="M73" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -6265,9 +6289,6 @@
       <c r="U73" t="n">
         <v>1</v>
       </c>
-      <c r="V73" t="n">
-        <v>1</v>
-      </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
@@ -6280,17 +6301,17 @@
       <c r="Z73" t="n">
         <v>1</v>
       </c>
+      <c r="AA73" t="n">
+        <v>1</v>
+      </c>
       <c r="AB73" t="n">
         <v>1</v>
       </c>
-      <c r="AC73" t="n">
-        <v>1</v>
-      </c>
       <c r="AD73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -6306,7 +6327,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Materia y materiales</t>
+          <t>Reutilización y reciclaje de materiales</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6318,34 +6339,31 @@
         <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F74" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J74" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K74" t="n">
         <v>2</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M74" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -6356,13 +6374,13 @@
       <c r="R74" t="n">
         <v>1</v>
       </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
       <c r="U74" t="n">
         <v>1</v>
       </c>
-      <c r="W74" t="n">
-        <v>1</v>
-      </c>
-      <c r="X74" t="n">
+      <c r="V74" t="n">
         <v>1</v>
       </c>
       <c r="Y74" t="n">
@@ -6371,13 +6389,13 @@
       <c r="Z74" t="n">
         <v>1</v>
       </c>
-      <c r="AA74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB74" t="n">
+      <c r="AC74" t="n">
         <v>1</v>
       </c>
       <c r="AD74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
@@ -6397,7 +6415,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Reutilización y reciclaje de materiales</t>
+          <t>Mezclas homogéneas y heterogéneas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6409,19 +6427,22 @@
         <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
       </c>
       <c r="F75" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
         <v>4.5</v>
@@ -6430,10 +6451,10 @@
         <v>2</v>
       </c>
       <c r="L75" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M75" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -6444,13 +6465,10 @@
       <c r="R75" t="n">
         <v>1</v>
       </c>
-      <c r="S75" t="n">
-        <v>1</v>
-      </c>
       <c r="U75" t="n">
         <v>1</v>
       </c>
-      <c r="V75" t="n">
+      <c r="W75" t="n">
         <v>1</v>
       </c>
       <c r="Y75" t="n">
@@ -6459,13 +6477,10 @@
       <c r="Z75" t="n">
         <v>1</v>
       </c>
-      <c r="AC75" t="n">
+      <c r="AB75" t="n">
         <v>1</v>
       </c>
       <c r="AD75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE75" t="n">
         <v>1</v>
       </c>
       <c r="AF75" t="n">
@@ -6485,7 +6500,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mezclas homogéneas y heterogéneas</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6494,37 +6509,37 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G76" t="n">
         <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I76" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J76" t="n">
+        <v>7</v>
+      </c>
+      <c r="K76" t="n">
         <v>4</v>
       </c>
-      <c r="J76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K76" t="n">
-        <v>2</v>
-      </c>
       <c r="L76" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M76" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
@@ -6538,6 +6553,9 @@
       <c r="U76" t="n">
         <v>1</v>
       </c>
+      <c r="V76" t="n">
+        <v>1</v>
+      </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
@@ -6547,14 +6565,23 @@
       <c r="Z76" t="n">
         <v>1</v>
       </c>
+      <c r="AA76" t="n">
+        <v>1</v>
+      </c>
       <c r="AB76" t="n">
         <v>1</v>
       </c>
+      <c r="AC76" t="n">
+        <v>1</v>
+      </c>
       <c r="AD76" t="n">
         <v>1</v>
       </c>
+      <c r="AE76" t="n">
+        <v>1</v>
+      </c>
       <c r="AF76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -6570,7 +6597,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Modelo mecanocuántico y orbitales atómicos</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6579,68 +6606,23 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
         <v>10</v>
       </c>
-      <c r="E77" t="n">
-        <v>4</v>
-      </c>
-      <c r="F77" t="n">
-        <v>8</v>
-      </c>
-      <c r="G77" t="n">
-        <v>6</v>
-      </c>
-      <c r="H77" t="n">
-        <v>7</v>
-      </c>
-      <c r="I77" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J77" t="n">
-        <v>7</v>
-      </c>
-      <c r="K77" t="n">
-        <v>4</v>
-      </c>
       <c r="L77" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M77" t="n">
-        <v>7</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
-      </c>
-      <c r="P77" t="n">
-        <v>1</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U77" t="n">
         <v>1</v>
       </c>
-      <c r="V77" t="n">
-        <v>1</v>
-      </c>
-      <c r="W77" t="n">
-        <v>1</v>
-      </c>
       <c r="Y77" t="n">
         <v>1</v>
       </c>
       <c r="Z77" t="n">
         <v>1</v>
       </c>
-      <c r="AA77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>1</v>
-      </c>
       <c r="AC77" t="n">
         <v>1</v>
       </c>
@@ -6651,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="AF77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -6667,7 +6649,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Modelo mecanocuántico y orbitales atómicos</t>
+          <t>Evolución de los modelos atómicos</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6681,10 +6663,43 @@
       <c r="D78" t="n">
         <v>10</v>
       </c>
+      <c r="E78" t="n">
+        <v>8</v>
+      </c>
+      <c r="F78" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>6</v>
+      </c>
+      <c r="J78" t="n">
+        <v>9</v>
+      </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
       <c r="L78" t="n">
-        <v>11</v>
+        <v>7.5</v>
+      </c>
+      <c r="M78" t="n">
+        <v>7</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
       </c>
       <c r="U78" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1</v>
+      </c>
+      <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="Y78" t="n">
@@ -6719,7 +6734,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Evolución de los modelos atómicos</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6728,67 +6743,64 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D79" t="n">
         <v>10</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>8</v>
       </c>
-      <c r="F79" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G79" t="n">
-        <v>6</v>
-      </c>
-      <c r="J79" t="n">
-        <v>9</v>
-      </c>
-      <c r="K79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I79" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L79" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M79" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="n">
         <v>8</v>
-      </c>
-      <c r="L79" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M79" t="n">
-        <v>7</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-      <c r="S79" t="n">
-        <v>1</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1</v>
-      </c>
-      <c r="V79" t="n">
-        <v>1</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>5</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -6804,7 +6816,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Molaridad y unidades químicas de concentración</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6816,13 +6828,10 @@
         <v>8</v>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F80" t="n">
-        <v>8</v>
-      </c>
-      <c r="G80" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="I80" t="n">
         <v>9.5</v>
@@ -6836,9 +6845,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
       <c r="R80" t="n">
         <v>1</v>
       </c>
@@ -6867,6 +6873,9 @@
         <v>1</v>
       </c>
       <c r="AD80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE80" t="n">
         <v>1</v>
       </c>
       <c r="AF80" t="n">
@@ -6886,7 +6895,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Molaridad y unidades químicas de concentración</t>
+          <t>Moléculas y fórmulas químicas</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6895,35 +6904,50 @@
         </is>
       </c>
       <c r="C81" t="n">
+        <v>5</v>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="n">
+        <v>7</v>
+      </c>
+      <c r="F81" t="n">
         <v>8</v>
       </c>
-      <c r="D81" t="n">
-        <v>9</v>
-      </c>
-      <c r="F81" t="n">
-        <v>10.5</v>
+      <c r="G81" t="n">
+        <v>6</v>
+      </c>
+      <c r="H81" t="n">
+        <v>7</v>
       </c>
       <c r="I81" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="J81" t="n">
+        <v>7</v>
+      </c>
+      <c r="K81" t="n">
+        <v>6</v>
       </c>
       <c r="L81" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M81" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="R81" t="n">
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
         <v>1</v>
       </c>
       <c r="U81" t="n">
         <v>1</v>
       </c>
-      <c r="V81" t="n">
-        <v>1</v>
-      </c>
       <c r="W81" t="n">
         <v>1</v>
       </c>
@@ -6945,11 +6969,8 @@
       <c r="AD81" t="n">
         <v>1</v>
       </c>
-      <c r="AE81" t="n">
-        <v>1</v>
-      </c>
       <c r="AF81" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
@@ -6965,7 +6986,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Moléculas y fórmulas químicas</t>
+          <t>Número de oxidación</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6979,48 +7000,24 @@
       <c r="D82" t="n">
         <v>10</v>
       </c>
-      <c r="E82" t="n">
-        <v>7</v>
-      </c>
       <c r="F82" t="n">
         <v>8</v>
       </c>
-      <c r="G82" t="n">
-        <v>6</v>
-      </c>
-      <c r="H82" t="n">
-        <v>7</v>
-      </c>
       <c r="I82" t="n">
-        <v>7</v>
-      </c>
-      <c r="J82" t="n">
-        <v>7</v>
-      </c>
-      <c r="K82" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="L82" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M82" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
-      <c r="T82" t="n">
+      <c r="R82" t="n">
         <v>1</v>
       </c>
       <c r="U82" t="n">
         <v>1</v>
       </c>
-      <c r="W82" t="n">
-        <v>1</v>
-      </c>
       <c r="X82" t="n">
         <v>1</v>
       </c>
@@ -7037,6 +7034,9 @@
         <v>1</v>
       </c>
       <c r="AD82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE82" t="n">
         <v>1</v>
       </c>
       <c r="AF82" t="n">
@@ -7056,7 +7056,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Número de oxidación</t>
+          <t>Números cuánticos</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7070,37 +7070,10 @@
       <c r="D83" t="n">
         <v>10</v>
       </c>
-      <c r="F83" t="n">
-        <v>8</v>
-      </c>
-      <c r="I83" t="n">
-        <v>9.5</v>
-      </c>
       <c r="L83" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O83" t="n">
-        <v>1</v>
-      </c>
-      <c r="R83" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U83" t="n">
-        <v>1</v>
-      </c>
-      <c r="X83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC83" t="n">
         <v>1</v>
       </c>
       <c r="AD83" t="n">
@@ -7126,7 +7099,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Números cuánticos</t>
+          <t>Oxidación y corrosión de los metales</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7135,26 +7108,65 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D84" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F84" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J84" t="n">
+        <v>9</v>
+      </c>
+      <c r="K84" t="n">
+        <v>9</v>
       </c>
       <c r="L84" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="n">
         <v>11</v>
       </c>
-      <c r="U84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>5</v>
-      </c>
       <c r="AG84" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -7162,14 +7174,14 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Oxidación y corrosión de los metales</t>
+          <t>Polaridad molecular</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7178,64 +7190,64 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F85" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H85" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I85" t="n">
         <v>9.5</v>
       </c>
-      <c r="J85" t="n">
-        <v>9</v>
-      </c>
       <c r="K85" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L85" t="n">
+        <v>11</v>
+      </c>
+      <c r="M85" t="n">
         <v>9.5</v>
       </c>
-      <c r="M85" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O85" t="n">
         <v>1</v>
       </c>
       <c r="R85" t="n">
         <v>1</v>
       </c>
-      <c r="S85" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" t="n">
-        <v>1</v>
-      </c>
       <c r="U85" t="n">
         <v>1</v>
       </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
       <c r="W85" t="n">
         <v>1</v>
       </c>
+      <c r="X85" t="n">
+        <v>1</v>
+      </c>
       <c r="Y85" t="n">
         <v>1</v>
       </c>
       <c r="Z85" t="n">
         <v>1</v>
       </c>
+      <c r="AB85" t="n">
+        <v>1</v>
+      </c>
       <c r="AC85" t="n">
         <v>1</v>
       </c>
       <c r="AD85" t="n">
         <v>1</v>
       </c>
+      <c r="AE85" t="n">
+        <v>1</v>
+      </c>
       <c r="AF85" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
@@ -7244,14 +7256,14 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Polaridad molecular</t>
+          <t>Proceso de disolución y solvatación</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7260,51 +7272,36 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
         <v>10</v>
       </c>
       <c r="F86" t="n">
-        <v>8</v>
-      </c>
-      <c r="I86" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>3</v>
+      </c>
+      <c r="H86" t="n">
+        <v>7</v>
       </c>
       <c r="K86" t="n">
         <v>6</v>
       </c>
-      <c r="L86" t="n">
-        <v>11</v>
-      </c>
       <c r="M86" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
-      <c r="U86" t="n">
-        <v>1</v>
-      </c>
       <c r="V86" t="n">
         <v>1</v>
       </c>
       <c r="W86" t="n">
         <v>1</v>
       </c>
-      <c r="X86" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB86" t="n">
+      <c r="AA86" t="n">
         <v>1</v>
       </c>
       <c r="AC86" t="n">
@@ -7313,11 +7310,8 @@
       <c r="AD86" t="n">
         <v>1</v>
       </c>
-      <c r="AE86" t="n">
-        <v>1</v>
-      </c>
       <c r="AF86" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -7333,7 +7327,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Proceso de disolución y solvatación</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7342,27 +7336,21 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D87" t="n">
         <v>10</v>
       </c>
-      <c r="F87" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G87" t="n">
-        <v>3</v>
-      </c>
-      <c r="H87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M87" t="n">
-        <v>7</v>
-      </c>
-      <c r="O87" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P87" t="n">
         <v>1</v>
       </c>
       <c r="V87" t="n">
@@ -7371,7 +7359,13 @@
       <c r="W87" t="n">
         <v>1</v>
       </c>
-      <c r="AA87" t="n">
+      <c r="Y87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB87" t="n">
         <v>1</v>
       </c>
       <c r="AC87" t="n">
@@ -7397,7 +7391,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Propiedades coligativas</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7411,37 +7405,19 @@
       <c r="D88" t="n">
         <v>10</v>
       </c>
-      <c r="G88" t="n">
-        <v>6</v>
-      </c>
-      <c r="K88" t="n">
-        <v>4</v>
-      </c>
-      <c r="M88" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P88" t="n">
-        <v>1</v>
-      </c>
-      <c r="V88" t="n">
-        <v>1</v>
-      </c>
-      <c r="W88" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>1</v>
-      </c>
       <c r="Z88" t="n">
         <v>1</v>
       </c>
+      <c r="AA88" t="n">
+        <v>1</v>
+      </c>
       <c r="AB88" t="n">
         <v>1</v>
       </c>
       <c r="AC88" t="n">
         <v>1</v>
       </c>
-      <c r="AD88" t="n">
+      <c r="AE88" t="n">
         <v>1</v>
       </c>
       <c r="AF88" t="n">
@@ -7461,7 +7437,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Propiedades físicas de los materiales</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7470,28 +7446,70 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
         <v>10</v>
       </c>
+      <c r="E89" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" t="n">
+        <v>5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" t="n">
+        <v>3</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1</v>
+      </c>
       <c r="Z89" t="n">
         <v>1</v>
       </c>
-      <c r="AA89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>1</v>
-      </c>
       <c r="AC89" t="n">
         <v>1</v>
       </c>
+      <c r="AD89" t="n">
+        <v>1</v>
+      </c>
       <c r="AE89" t="n">
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -7507,7 +7525,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Propiedades físicas de los materiales</t>
+          <t>Propiedades físicas y químicas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7519,22 +7537,19 @@
         <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>10</v>
-      </c>
-      <c r="E90" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H90" t="n">
         <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="J90" t="n">
         <v>2.5</v>
@@ -7543,10 +7558,10 @@
         <v>2</v>
       </c>
       <c r="L90" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M90" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
@@ -7557,16 +7572,28 @@
       <c r="R90" t="n">
         <v>1</v>
       </c>
+      <c r="T90" t="n">
+        <v>1</v>
+      </c>
       <c r="U90" t="n">
         <v>1</v>
       </c>
+      <c r="V90" t="n">
+        <v>1</v>
+      </c>
       <c r="W90" t="n">
         <v>1</v>
       </c>
+      <c r="X90" t="n">
+        <v>1</v>
+      </c>
       <c r="Y90" t="n">
         <v>1</v>
       </c>
       <c r="Z90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB90" t="n">
         <v>1</v>
       </c>
       <c r="AC90" t="n">
@@ -7595,7 +7622,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Propiedades físicas y químicas</t>
+          <t>Propiedades periódicas</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7604,34 +7631,37 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="n">
         <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="G91" t="n">
         <v>6</v>
       </c>
-      <c r="H91" t="n">
-        <v>2</v>
-      </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="J91" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="K91" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L91" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M91" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
@@ -7642,15 +7672,12 @@
       <c r="R91" t="n">
         <v>1</v>
       </c>
-      <c r="T91" t="n">
+      <c r="S91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
         <v>1</v>
       </c>
-      <c r="V91" t="n">
-        <v>1</v>
-      </c>
       <c r="W91" t="n">
         <v>1</v>
       </c>
@@ -7663,6 +7690,9 @@
       <c r="Z91" t="n">
         <v>1</v>
       </c>
+      <c r="AA91" t="n">
+        <v>1</v>
+      </c>
       <c r="AB91" t="n">
         <v>1</v>
       </c>
@@ -7676,7 +7706,7 @@
         <v>1</v>
       </c>
       <c r="AF91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
@@ -7692,7 +7722,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Propiedades periódicas</t>
+          <t>Propiedades singulares del agua</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7701,46 +7731,31 @@
         </is>
       </c>
       <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>9</v>
+      </c>
+      <c r="F92" t="n">
         <v>5</v>
-      </c>
-      <c r="D92" t="n">
-        <v>10</v>
-      </c>
-      <c r="E92" t="n">
-        <v>9</v>
-      </c>
-      <c r="F92" t="n">
-        <v>10.5</v>
       </c>
       <c r="G92" t="n">
         <v>6</v>
       </c>
+      <c r="H92" t="n">
+        <v>7</v>
+      </c>
       <c r="I92" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
         <v>9</v>
       </c>
       <c r="K92" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M92" t="n">
-        <v>7</v>
-      </c>
-      <c r="N92" t="n">
-        <v>1</v>
-      </c>
-      <c r="O92" t="n">
-        <v>1</v>
-      </c>
-      <c r="P92" t="n">
-        <v>1</v>
-      </c>
-      <c r="R92" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="S92" t="n">
         <v>1</v>
@@ -7751,18 +7766,9 @@
       <c r="W92" t="n">
         <v>1</v>
       </c>
-      <c r="X92" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>1</v>
-      </c>
       <c r="Z92" t="n">
         <v>1</v>
       </c>
-      <c r="AA92" t="n">
-        <v>1</v>
-      </c>
       <c r="AB92" t="n">
         <v>1</v>
       </c>
@@ -7772,11 +7778,8 @@
       <c r="AD92" t="n">
         <v>1</v>
       </c>
-      <c r="AE92" t="n">
-        <v>1</v>
-      </c>
       <c r="AF92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
@@ -7792,7 +7795,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Propiedades singulares del agua</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7801,55 +7804,40 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
-        <v>5</v>
-      </c>
-      <c r="G93" t="n">
-        <v>6</v>
-      </c>
-      <c r="H93" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
-      </c>
-      <c r="J93" t="n">
-        <v>9</v>
-      </c>
-      <c r="K93" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="L93" t="n">
-        <v>11</v>
-      </c>
-      <c r="S93" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" t="n">
         <v>1</v>
       </c>
       <c r="U93" t="n">
         <v>1</v>
       </c>
-      <c r="W93" t="n">
-        <v>1</v>
-      </c>
       <c r="Z93" t="n">
         <v>1</v>
       </c>
-      <c r="AB93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC93" t="n">
+      <c r="AA93" t="n">
         <v>1</v>
       </c>
       <c r="AD93" t="n">
         <v>1</v>
       </c>
       <c r="AF93" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -7858,14 +7846,14 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Química descriptiva de los elementos</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7874,40 +7862,70 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
         <v>10</v>
       </c>
       <c r="F94" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G94" t="n">
+        <v>6</v>
+      </c>
+      <c r="H94" t="n">
+        <v>7</v>
       </c>
       <c r="I94" t="n">
         <v>9.5</v>
       </c>
+      <c r="J94" t="n">
+        <v>9</v>
+      </c>
       <c r="L94" t="n">
         <v>9.5</v>
       </c>
+      <c r="M94" t="n">
+        <v>7</v>
+      </c>
       <c r="O94" t="n">
         <v>1</v>
       </c>
+      <c r="P94" t="n">
+        <v>1</v>
+      </c>
       <c r="R94" t="n">
         <v>1</v>
       </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
       <c r="U94" t="n">
         <v>1</v>
       </c>
+      <c r="X94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>1</v>
+      </c>
       <c r="Z94" t="n">
         <v>1</v>
       </c>
       <c r="AA94" t="n">
         <v>1</v>
       </c>
+      <c r="AC94" t="n">
+        <v>1</v>
+      </c>
       <c r="AD94" t="n">
         <v>1</v>
       </c>
+      <c r="AE94" t="n">
+        <v>1</v>
+      </c>
       <c r="AF94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -7916,14 +7934,14 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Química descriptiva de los elementos</t>
+          <t>Reacción química y sus evidencias</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7932,31 +7950,37 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>10</v>
       </c>
+      <c r="E95" t="n">
+        <v>5</v>
+      </c>
       <c r="F95" t="n">
         <v>8</v>
       </c>
       <c r="G95" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H95" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>9</v>
+        <v>4.5</v>
+      </c>
+      <c r="K95" t="n">
+        <v>4</v>
       </c>
       <c r="L95" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M95" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -7970,10 +7994,13 @@
       <c r="S95" t="n">
         <v>1</v>
       </c>
+      <c r="T95" t="n">
+        <v>1</v>
+      </c>
       <c r="U95" t="n">
         <v>1</v>
       </c>
-      <c r="X95" t="n">
+      <c r="W95" t="n">
         <v>1</v>
       </c>
       <c r="Y95" t="n">
@@ -7982,7 +8009,7 @@
       <c r="Z95" t="n">
         <v>1</v>
       </c>
-      <c r="AA95" t="n">
+      <c r="AB95" t="n">
         <v>1</v>
       </c>
       <c r="AC95" t="n">
@@ -7995,7 +8022,7 @@
         <v>1</v>
       </c>
       <c r="AF95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
@@ -8011,7 +8038,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Reacción química y sus evidencias</t>
+          <t>Rendimiento de una reacción</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8020,68 +8047,29 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D96" t="n">
         <v>10</v>
       </c>
-      <c r="E96" t="n">
-        <v>5</v>
-      </c>
       <c r="F96" t="n">
-        <v>8</v>
-      </c>
-      <c r="G96" t="n">
-        <v>3</v>
-      </c>
-      <c r="H96" t="n">
-        <v>5</v>
-      </c>
-      <c r="I96" t="n">
-        <v>5</v>
-      </c>
-      <c r="J96" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K96" t="n">
-        <v>4</v>
-      </c>
-      <c r="L96" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M96" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="P96" t="n">
-        <v>1</v>
-      </c>
-      <c r="R96" t="n">
-        <v>1</v>
-      </c>
-      <c r="S96" t="n">
-        <v>1</v>
-      </c>
-      <c r="T96" t="n">
-        <v>1</v>
-      </c>
-      <c r="U96" t="n">
-        <v>1</v>
-      </c>
       <c r="W96" t="n">
         <v>1</v>
       </c>
+      <c r="X96" t="n">
+        <v>1</v>
+      </c>
       <c r="Y96" t="n">
         <v>1</v>
       </c>
       <c r="Z96" t="n">
         <v>1</v>
       </c>
-      <c r="AB96" t="n">
-        <v>1</v>
-      </c>
       <c r="AC96" t="n">
         <v>1</v>
       </c>
@@ -8092,7 +8080,7 @@
         <v>1</v>
       </c>
       <c r="AF96" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
@@ -8101,14 +8089,14 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Rendimiento de una reacción</t>
+          <t>Métodos físicos de separación de mezclas</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8117,23 +8105,56 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>10</v>
       </c>
+      <c r="E97" t="n">
+        <v>6</v>
+      </c>
       <c r="F97" t="n">
-        <v>10.5</v>
+        <v>5</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" t="n">
+        <v>4</v>
+      </c>
+      <c r="J97" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K97" t="n">
+        <v>6</v>
+      </c>
+      <c r="L97" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M97" t="n">
+        <v>2.5</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
       </c>
+      <c r="P97" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" t="n">
+        <v>1</v>
+      </c>
       <c r="W97" t="n">
         <v>1</v>
       </c>
-      <c r="X97" t="n">
-        <v>1</v>
-      </c>
       <c r="Y97" t="n">
         <v>1</v>
       </c>
@@ -8150,7 +8171,7 @@
         <v>1</v>
       </c>
       <c r="AF97" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
@@ -8159,14 +8180,14 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Métodos físicos de separación de mezclas</t>
+          <t>Sólidos cristalinos y amorfos</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8175,53 +8196,17 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D98" t="n">
         <v>10</v>
       </c>
-      <c r="E98" t="n">
-        <v>6</v>
-      </c>
-      <c r="F98" t="n">
-        <v>5</v>
-      </c>
-      <c r="G98" t="n">
-        <v>3</v>
-      </c>
-      <c r="H98" t="n">
-        <v>2</v>
-      </c>
-      <c r="I98" t="n">
-        <v>4</v>
-      </c>
-      <c r="J98" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K98" t="n">
-        <v>6</v>
-      </c>
       <c r="L98" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M98" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O98" t="n">
-        <v>1</v>
-      </c>
-      <c r="P98" t="n">
-        <v>1</v>
-      </c>
-      <c r="R98" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U98" t="n">
         <v>1</v>
       </c>
-      <c r="V98" t="n">
-        <v>1</v>
-      </c>
       <c r="W98" t="n">
         <v>1</v>
       </c>
@@ -8231,17 +8216,20 @@
       <c r="Z98" t="n">
         <v>1</v>
       </c>
+      <c r="AA98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>1</v>
+      </c>
       <c r="AC98" t="n">
         <v>1</v>
       </c>
       <c r="AD98" t="n">
         <v>1</v>
       </c>
-      <c r="AE98" t="n">
-        <v>1</v>
-      </c>
       <c r="AF98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
@@ -8257,7 +8245,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sólidos cristalinos y amorfos</t>
+          <t>Solubilidad y disoluciones saturadas</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8266,20 +8254,53 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
         <v>10</v>
       </c>
+      <c r="F99" t="n">
+        <v>8</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" t="n">
+        <v>4</v>
+      </c>
+      <c r="J99" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K99" t="n">
+        <v>6</v>
+      </c>
       <c r="L99" t="n">
-        <v>11</v>
+        <v>7.5</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1</v>
       </c>
       <c r="U99" t="n">
         <v>1</v>
       </c>
+      <c r="V99" t="n">
+        <v>1</v>
+      </c>
       <c r="W99" t="n">
         <v>1</v>
       </c>
+      <c r="X99" t="n">
+        <v>1</v>
+      </c>
       <c r="Y99" t="n">
         <v>1</v>
       </c>
@@ -8289,17 +8310,17 @@
       <c r="AA99" t="n">
         <v>1</v>
       </c>
-      <c r="AB99" t="n">
-        <v>1</v>
-      </c>
       <c r="AC99" t="n">
         <v>1</v>
       </c>
       <c r="AD99" t="n">
         <v>1</v>
       </c>
+      <c r="AE99" t="n">
+        <v>1</v>
+      </c>
       <c r="AF99" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
@@ -8315,7 +8336,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Solubilidad y disoluciones saturadas</t>
+          <t>Sustancias puras: elementos y compuestos</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8324,25 +8345,28 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D100" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E100" t="n">
+        <v>6</v>
       </c>
       <c r="F100" t="n">
         <v>8</v>
       </c>
       <c r="G100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J100" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K100" t="n">
         <v>6</v>
@@ -8356,9 +8380,18 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
+      <c r="P100" t="n">
+        <v>1</v>
+      </c>
       <c r="R100" t="n">
         <v>1</v>
       </c>
+      <c r="S100" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" t="n">
+        <v>1</v>
+      </c>
       <c r="U100" t="n">
         <v>1</v>
       </c>
@@ -8368,29 +8401,20 @@
       <c r="W100" t="n">
         <v>1</v>
       </c>
-      <c r="X100" t="n">
-        <v>1</v>
-      </c>
       <c r="Y100" t="n">
         <v>1</v>
       </c>
       <c r="Z100" t="n">
         <v>1</v>
       </c>
-      <c r="AA100" t="n">
-        <v>1</v>
-      </c>
       <c r="AC100" t="n">
         <v>1</v>
       </c>
       <c r="AD100" t="n">
         <v>1</v>
       </c>
-      <c r="AE100" t="n">
-        <v>1</v>
-      </c>
       <c r="AF100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
@@ -8406,7 +8430,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sustancias puras: elementos y compuestos</t>
+          <t>Organización de la tabla periódica</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8418,10 +8442,10 @@
         <v>5</v>
       </c>
       <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="n">
         <v>9</v>
-      </c>
-      <c r="E101" t="n">
-        <v>6</v>
       </c>
       <c r="F101" t="n">
         <v>8</v>
@@ -8430,22 +8454,25 @@
         <v>6</v>
       </c>
       <c r="H101" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I101" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J101" t="n">
         <v>7</v>
       </c>
       <c r="K101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L101" t="n">
         <v>7.5</v>
       </c>
       <c r="M101" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
       </c>
       <c r="O101" t="n">
         <v>1</v>
@@ -8471,20 +8498,29 @@
       <c r="W101" t="n">
         <v>1</v>
       </c>
+      <c r="X101" t="n">
+        <v>1</v>
+      </c>
       <c r="Y101" t="n">
         <v>1</v>
       </c>
       <c r="Z101" t="n">
         <v>1</v>
       </c>
+      <c r="AA101" t="n">
+        <v>1</v>
+      </c>
       <c r="AC101" t="n">
         <v>1</v>
       </c>
       <c r="AD101" t="n">
         <v>1</v>
       </c>
+      <c r="AE101" t="n">
+        <v>1</v>
+      </c>
       <c r="AF101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
@@ -8500,7 +8536,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Organización de la tabla periódica</t>
+          <t>Tipo de enlace y propiedades de las sustancias</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8509,41 +8545,32 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D102" t="n">
         <v>10</v>
       </c>
-      <c r="E102" t="n">
-        <v>9</v>
-      </c>
       <c r="F102" t="n">
         <v>8</v>
       </c>
       <c r="G102" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I102" t="n">
         <v>9.5</v>
       </c>
       <c r="J102" t="n">
-        <v>7</v>
-      </c>
-      <c r="K102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L102" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M102" t="n">
         <v>7</v>
       </c>
-      <c r="N102" t="n">
-        <v>1</v>
-      </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
@@ -8556,9 +8583,6 @@
       <c r="S102" t="n">
         <v>1</v>
       </c>
-      <c r="T102" t="n">
-        <v>1</v>
-      </c>
       <c r="U102" t="n">
         <v>1</v>
       </c>
@@ -8580,6 +8604,9 @@
       <c r="AA102" t="n">
         <v>1</v>
       </c>
+      <c r="AB102" t="n">
+        <v>1</v>
+      </c>
       <c r="AC102" t="n">
         <v>1</v>
       </c>
@@ -8590,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="AF102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
@@ -8606,7 +8633,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tipo de enlace y propiedades de las sustancias</t>
+          <t>Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8620,26 +8647,29 @@
       <c r="D103" t="n">
         <v>10</v>
       </c>
+      <c r="E103" t="n">
+        <v>9</v>
+      </c>
       <c r="F103" t="n">
         <v>8</v>
       </c>
       <c r="G103" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H103" t="n">
         <v>7</v>
       </c>
       <c r="I103" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J103" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" t="n">
         <v>9</v>
       </c>
       <c r="L103" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M103" t="n">
-        <v>7</v>
+        <v>7.5</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
@@ -8647,43 +8677,25 @@
       <c r="P103" t="n">
         <v>1</v>
       </c>
-      <c r="R103" t="n">
-        <v>1</v>
-      </c>
-      <c r="S103" t="n">
+      <c r="T103" t="n">
         <v>1</v>
       </c>
       <c r="U103" t="n">
         <v>1</v>
       </c>
-      <c r="V103" t="n">
-        <v>1</v>
-      </c>
       <c r="W103" t="n">
         <v>1</v>
       </c>
       <c r="X103" t="n">
         <v>1</v>
       </c>
-      <c r="Y103" t="n">
-        <v>1</v>
-      </c>
       <c r="Z103" t="n">
         <v>1</v>
       </c>
-      <c r="AA103" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB103" t="n">
-        <v>1</v>
-      </c>
       <c r="AC103" t="n">
         <v>1</v>
       </c>
       <c r="AD103" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE103" t="n">
         <v>1</v>
       </c>
       <c r="AF103" t="n">
@@ -8703,7 +8715,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Clasificación de las reacciones químicas</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8712,45 +8724,36 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
         <v>10</v>
       </c>
-      <c r="E104" t="n">
-        <v>9</v>
-      </c>
       <c r="F104" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G104" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="K104" t="n">
+        <v>2</v>
+      </c>
+      <c r="L104" t="n">
+        <v>5</v>
+      </c>
+      <c r="M104" t="n">
         <v>7</v>
       </c>
-      <c r="I104" t="n">
-        <v>7</v>
-      </c>
-      <c r="K104" t="n">
-        <v>9</v>
-      </c>
-      <c r="L104" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N104" t="n">
-        <v>1</v>
-      </c>
       <c r="O104" t="n">
         <v>1</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
       </c>
-      <c r="T104" t="n">
-        <v>1</v>
-      </c>
-      <c r="U104" t="n">
+      <c r="V104" t="n">
         <v>1</v>
       </c>
       <c r="W104" t="n">
@@ -8759,17 +8762,20 @@
       <c r="X104" t="n">
         <v>1</v>
       </c>
+      <c r="Y104" t="n">
+        <v>1</v>
+      </c>
       <c r="Z104" t="n">
         <v>1</v>
       </c>
       <c r="AC104" t="n">
         <v>1</v>
       </c>
-      <c r="AD104" t="n">
+      <c r="AE104" t="n">
         <v>1</v>
       </c>
       <c r="AF104" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
@@ -8785,83 +8791,47 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Diagramas de fases</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D105" t="n">
         <v>10</v>
       </c>
-      <c r="F105" t="n">
-        <v>5</v>
-      </c>
-      <c r="G105" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H105" t="n">
-        <v>2</v>
-      </c>
-      <c r="K105" t="n">
-        <v>2</v>
-      </c>
-      <c r="L105" t="n">
-        <v>5</v>
-      </c>
       <c r="M105" t="n">
-        <v>7</v>
-      </c>
-      <c r="O105" t="n">
-        <v>1</v>
-      </c>
-      <c r="P105" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="V105" t="n">
         <v>1</v>
       </c>
-      <c r="W105" t="n">
-        <v>1</v>
-      </c>
-      <c r="X105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE105" t="n">
+      <c r="AA105" t="n">
         <v>1</v>
       </c>
       <c r="AF105" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Diagramas de fases</t>
+          <t>Ecuación de Nernst</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8875,17 +8845,11 @@
       <c r="D106" t="n">
         <v>10</v>
       </c>
-      <c r="M106" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA106" t="n">
+      <c r="AD106" t="n">
         <v>1</v>
       </c>
       <c r="AF106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
@@ -8901,7 +8865,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ecuación de Nernst</t>
+          <t>Ecuaciones y reacciones nucleares</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8915,11 +8879,17 @@
       <c r="D107" t="n">
         <v>10</v>
       </c>
-      <c r="AD107" t="n">
+      <c r="G107" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L107" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC107" t="n">
         <v>1</v>
       </c>
       <c r="AF107" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
@@ -8935,7 +8905,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ecuaciones y reacciones nucleares</t>
+          <t>Energía reticular y ciclo de Born-Haber</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8949,13 +8919,13 @@
       <c r="D108" t="n">
         <v>10</v>
       </c>
-      <c r="G108" t="n">
-        <v>8.5</v>
-      </c>
       <c r="L108" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AC108" t="n">
+        <v>11</v>
+      </c>
+      <c r="U108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="n">
         <v>1</v>
       </c>
       <c r="AF108" t="n">
@@ -8975,7 +8945,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Energía reticular y ciclo de Born-Haber</t>
+          <t>Leyes de los gases</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8989,13 +8959,34 @@
       <c r="D109" t="n">
         <v>10</v>
       </c>
-      <c r="L109" t="n">
-        <v>11</v>
-      </c>
-      <c r="U109" t="n">
+      <c r="J109" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M109" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V109" t="n">
+        <v>1</v>
+      </c>
+      <c r="W109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC109" t="n">
         <v>1</v>
       </c>
       <c r="AD109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE109" t="n">
         <v>1</v>
       </c>
       <c r="AF109" t="n">
@@ -9015,48 +9006,45 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Leyes de los gases</t>
+          <t>Composición porcentual y fórmulas empírica y molecular</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D110" t="n">
         <v>10</v>
       </c>
-      <c r="J110" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M110" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V110" t="n">
+      <c r="G110" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L110" t="n">
+        <v>11</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1</v>
+      </c>
+      <c r="U110" t="n">
         <v>1</v>
       </c>
       <c r="W110" t="n">
         <v>1</v>
       </c>
+      <c r="Y110" t="n">
+        <v>1</v>
+      </c>
       <c r="Z110" t="n">
         <v>1</v>
       </c>
-      <c r="AA110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB110" t="n">
-        <v>1</v>
-      </c>
       <c r="AC110" t="n">
         <v>1</v>
       </c>
       <c r="AD110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE110" t="n">
         <v>1</v>
       </c>
       <c r="AF110" t="n">
@@ -9064,19 +9052,19 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Composición porcentual y fórmulas empírica y molecular</t>
+          <t>Constante de equilibrio</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9085,44 +9073,50 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D111" t="n">
-        <v>10</v>
-      </c>
-      <c r="G111" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L111" t="n">
         <v>11</v>
       </c>
-      <c r="P111" t="n">
-        <v>1</v>
-      </c>
       <c r="U111" t="n">
         <v>1</v>
       </c>
       <c r="W111" t="n">
         <v>1</v>
       </c>
+      <c r="X111" t="n">
+        <v>1</v>
+      </c>
       <c r="Y111" t="n">
         <v>1</v>
       </c>
       <c r="Z111" t="n">
         <v>1</v>
       </c>
+      <c r="AA111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>1</v>
+      </c>
       <c r="AC111" t="n">
         <v>1</v>
       </c>
       <c r="AD111" t="n">
         <v>1</v>
       </c>
+      <c r="AE111" t="n">
+        <v>1</v>
+      </c>
       <c r="AF111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
@@ -9134,7 +9128,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Constante de equilibrio</t>
+          <t>Mezclas de gases, difusión y gases reales</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9143,28 +9137,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D112" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="J112" t="n">
+        <v>7</v>
       </c>
       <c r="L112" t="n">
-        <v>11</v>
-      </c>
-      <c r="U112" t="n">
-        <v>1</v>
-      </c>
-      <c r="W112" t="n">
-        <v>1</v>
-      </c>
-      <c r="X112" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="AA112" t="n">
         <v>1</v>
@@ -9182,23 +9164,23 @@
         <v>1</v>
       </c>
       <c r="AF112" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mezclas de gases, difusión y gases reales</t>
+          <t>Hidrólisis de sales y disoluciones amortiguadoras</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9207,16 +9189,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
-      </c>
-      <c r="J113" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L113" t="n">
-        <v>7.5</v>
+        <v>11</v>
+      </c>
+      <c r="U113" t="n">
+        <v>1</v>
+      </c>
+      <c r="X113" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" t="n">
         <v>1</v>
@@ -9234,23 +9222,23 @@
         <v>1</v>
       </c>
       <c r="AF113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Hidrólisis de sales y disoluciones amortiguadoras</t>
+          <t>Ecuación de los gases ideales y volumen molar</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9259,23 +9247,38 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D114" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F114" t="n">
+        <v>8</v>
+      </c>
+      <c r="I114" t="n">
+        <v>9.5</v>
       </c>
       <c r="L114" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1</v>
       </c>
       <c r="U114" t="n">
         <v>1</v>
       </c>
-      <c r="X114" t="n">
+      <c r="W114" t="n">
         <v>1</v>
       </c>
       <c r="Y114" t="n">
         <v>1</v>
       </c>
+      <c r="Z114" t="n">
+        <v>1</v>
+      </c>
       <c r="AA114" t="n">
         <v>1</v>
       </c>
@@ -9292,7 +9295,7 @@
         <v>1</v>
       </c>
       <c r="AF114" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
@@ -9308,7 +9311,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ecuación de los gases ideales y volumen molar</t>
+          <t>Energía de Gibbs y espontaneidad</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9317,32 +9320,17 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D115" t="n">
-        <v>10</v>
-      </c>
-      <c r="F115" t="n">
-        <v>8</v>
-      </c>
-      <c r="I115" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L115" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O115" t="n">
-        <v>1</v>
-      </c>
-      <c r="R115" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W115" t="n">
         <v>1</v>
       </c>
+      <c r="X115" t="n">
+        <v>1</v>
+      </c>
       <c r="Y115" t="n">
         <v>1</v>
       </c>
@@ -9355,13 +9343,7 @@
       <c r="AB115" t="n">
         <v>1</v>
       </c>
-      <c r="AC115" t="n">
-        <v>1</v>
-      </c>
       <c r="AD115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE115" t="n">
         <v>1</v>
       </c>
       <c r="AF115" t="n">
@@ -9381,7 +9363,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Energía de Gibbs y espontaneidad</t>
+          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9390,30 +9372,24 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D116" t="n">
-        <v>9</v>
-      </c>
-      <c r="W116" t="n">
+        <v>10</v>
+      </c>
+      <c r="L116" t="n">
+        <v>11</v>
+      </c>
+      <c r="U116" t="n">
         <v>1</v>
       </c>
       <c r="X116" t="n">
         <v>1</v>
       </c>
-      <c r="Y116" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>1</v>
-      </c>
       <c r="AD116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE116" t="n">
         <v>1</v>
       </c>
       <c r="AF116" t="n">
@@ -9433,7 +9409,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
+          <t>Entropía</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9447,19 +9423,16 @@
       <c r="D117" t="n">
         <v>10</v>
       </c>
-      <c r="L117" t="n">
-        <v>11</v>
-      </c>
-      <c r="U117" t="n">
-        <v>1</v>
-      </c>
       <c r="X117" t="n">
         <v>1</v>
       </c>
+      <c r="Y117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>1</v>
+      </c>
       <c r="AD117" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE117" t="n">
         <v>1</v>
       </c>
       <c r="AF117" t="n">
@@ -9479,7 +9452,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Entropía</t>
+          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9493,13 +9466,10 @@
       <c r="D118" t="n">
         <v>10</v>
       </c>
-      <c r="X118" t="n">
-        <v>1</v>
-      </c>
       <c r="Y118" t="n">
         <v>1</v>
       </c>
-      <c r="AB118" t="n">
+      <c r="Z118" t="n">
         <v>1</v>
       </c>
       <c r="AD118" t="n">
@@ -9522,7 +9492,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
+          <t>Espectrometría de masas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9531,10 +9501,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D119" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="W119" t="n">
+        <v>1</v>
       </c>
       <c r="Y119" t="n">
         <v>1</v>
@@ -9542,12 +9515,6 @@
       <c r="Z119" t="n">
         <v>1</v>
       </c>
-      <c r="AD119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF119" t="n">
-        <v>10</v>
-      </c>
       <c r="AG119" t="inlineStr">
         <is>
           <t>solo_especializacion</t>
@@ -9555,14 +9522,14 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Espectrometría de masas</t>
+          <t>Espectros atómicos y modelo de Bohr</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9571,10 +9538,19 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D120" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="H120" t="n">
+        <v>7</v>
+      </c>
+      <c r="I120" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1</v>
       </c>
       <c r="W120" t="n">
         <v>1</v>
@@ -9585,6 +9561,18 @@
       <c r="Z120" t="n">
         <v>1</v>
       </c>
+      <c r="AC120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>10</v>
+      </c>
       <c r="AG120" t="inlineStr">
         <is>
           <t>solo_especializacion</t>
@@ -9592,14 +9580,14 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Espectros atómicos y modelo de Bohr</t>
+          <t>Técnicas para determinar estructuras orgánicas</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9608,19 +9596,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
-      </c>
-      <c r="H121" t="n">
-        <v>7</v>
-      </c>
-      <c r="I121" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R121" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="W121" t="n">
         <v>1</v>
@@ -9634,15 +9613,6 @@
       <c r="AC121" t="n">
         <v>1</v>
       </c>
-      <c r="AD121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF121" t="n">
-        <v>10</v>
-      </c>
       <c r="AG121" t="inlineStr">
         <is>
           <t>solo_especializacion</t>
@@ -9650,14 +9620,14 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Técnicas para determinar estructuras orgánicas</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9666,23 +9636,44 @@
         </is>
       </c>
       <c r="C122" t="n">
+        <v>10</v>
+      </c>
+      <c r="D122" t="n">
+        <v>10</v>
+      </c>
+      <c r="L122" t="n">
         <v>11</v>
       </c>
-      <c r="D122" t="n">
+      <c r="M122" t="n">
+        <v>7</v>
+      </c>
+      <c r="U122" t="n">
+        <v>1</v>
+      </c>
+      <c r="X122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF122" t="n">
         <v>11</v>
       </c>
-      <c r="W122" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>1</v>
-      </c>
       <c r="AG122" t="inlineStr">
         <is>
           <t>solo_especializacion</t>
@@ -9690,14 +9681,14 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9706,21 +9697,33 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G123" t="n">
+        <v>6</v>
+      </c>
+      <c r="H123" t="n">
+        <v>7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>9.5</v>
       </c>
       <c r="L123" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M123" t="n">
         <v>7</v>
       </c>
+      <c r="R123" t="n">
+        <v>1</v>
+      </c>
       <c r="U123" t="n">
         <v>1</v>
       </c>
-      <c r="X123" t="n">
+      <c r="W123" t="n">
         <v>1</v>
       </c>
       <c r="Y123" t="n">
@@ -9730,9 +9733,6 @@
         <v>1</v>
       </c>
       <c r="AA123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC123" t="n">
         <v>1</v>
       </c>
       <c r="AD123" t="n">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>

--- a/internacional/Contraste_quimica.xlsx
+++ b/internacional/Contraste_quimica.xlsx
@@ -606,7 +606,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aminoácidos y estructura de las proteínas</t>
+          <t>Agentes oxidantes y reductores</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -614,27 +614,30 @@
           <t>alineado</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
       <c r="F2" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>9.5</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M2" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
@@ -656,33 +659,33 @@
       <c r="Z2" t="n">
         <v>1</v>
       </c>
-      <c r="AA2" t="n">
-        <v>1</v>
-      </c>
       <c r="AB2" t="n">
         <v>1</v>
       </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="n">
-        <v>10</v>
+      <c r="AE2" t="n">
+        <v>1</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Autoionización del agua, Kw y cálculo de pH</t>
+          <t>Aminoácidos y estructura de las proteínas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -691,13 +694,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>8.5</v>
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10.5</v>
       </c>
       <c r="I3" t="n">
         <v>9.5</v>
@@ -706,9 +709,9 @@
         <v>11</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
-      </c>
-      <c r="P3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
@@ -738,21 +741,15 @@
       <c r="AB3" t="n">
         <v>1</v>
       </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
       <c r="AD3" t="n">
         <v>1</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -764,7 +761,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Celdas galvánicas</t>
+          <t>Autoionización del agua, Kw y cálculo de pH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -773,26 +770,32 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L4" t="n">
         <v>11</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8</v>
       </c>
       <c r="M4" t="n">
         <v>7</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
@@ -824,11 +827,11 @@
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -840,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Metales, cerámicas y materiales compuestos</t>
+          <t>Celdas galvánicas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -849,26 +852,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="I5" t="n">
         <v>8</v>
       </c>
-      <c r="L5" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M5" t="n">
         <v>7</v>
       </c>
@@ -878,18 +872,24 @@
       <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>1</v>
       </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
       <c r="AB5" t="n">
         <v>1</v>
       </c>
@@ -903,11 +903,11 @@
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Conservación de la masa</t>
+          <t>Metales, cerámicas y materiales compuestos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -928,14 +928,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="n">
-        <v>8</v>
-      </c>
       <c r="F6" t="n">
         <v>8</v>
       </c>
@@ -946,39 +943,24 @@
         <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="K6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
       <c r="U6" t="n">
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
@@ -1004,7 +986,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1016,7 +998,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>El carbono y las moléculas orgánicas</t>
+          <t>Conservación de la masa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1025,22 +1007,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9</v>
       </c>
       <c r="L7" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1048,24 +1045,27 @@
       <c r="P7" t="n">
         <v>1</v>
       </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
       <c r="U7" t="n">
         <v>1</v>
       </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
       <c r="Y7" t="n">
         <v>1</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
       </c>
-      <c r="AA7" t="n">
-        <v>1</v>
-      </c>
       <c r="AB7" t="n">
         <v>1</v>
       </c>
@@ -1079,11 +1079,11 @@
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Electrólisis y celdas electrolíticas</t>
+          <t>El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1110,16 +1110,13 @@
         <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
         <v>8.5</v>
       </c>
-      <c r="H8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>8</v>
+      <c r="L8" t="n">
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
         <v>7</v>
@@ -1130,6 +1127,9 @@
       <c r="P8" t="n">
         <v>1</v>
       </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
@@ -1174,7 +1174,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Electrolitos fuertes y débiles</t>
+          <t>Electrólisis y celdas electrolíticas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1183,23 +1183,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G9" t="n">
         <v>8.5</v>
       </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
       <c r="I9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" t="n">
-        <v>11</v>
-      </c>
       <c r="M9" t="n">
         <v>7</v>
       </c>
@@ -1209,10 +1209,10 @@
       <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
@@ -1221,6 +1221,9 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
       <c r="AB9" t="n">
         <v>1</v>
       </c>
@@ -1230,8 +1233,11 @@
       <c r="AD9" t="n">
         <v>1</v>
       </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
       <c r="AF9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1247,7 +1253,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Energía de activación y perfil energético</t>
+          <t>Electrolitos fuertes y débiles</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1256,19 +1262,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
         <v>8.5</v>
       </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
       <c r="L10" t="n">
-        <v>9.5</v>
+        <v>11</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1279,10 +1291,7 @@
       <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
@@ -1300,15 +1309,12 @@
       <c r="AD10" t="n">
         <v>1</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1</v>
-      </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1320,7 +1326,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Energía de enlace</t>
+          <t>Energía de activación y perfil energético</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1329,10 +1335,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
         <v>10.5</v>
@@ -1364,7 +1370,7 @@
       <c r="Z11" t="n">
         <v>1</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>1</v>
       </c>
       <c r="AC11" t="n">
@@ -1376,21 +1382,24 @@
       <c r="AE11" t="n">
         <v>1</v>
       </c>
+      <c r="AF11" t="n">
+        <v>10</v>
+      </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
+          <t>Energía de enlace</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1399,22 +1408,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G12" t="n">
         <v>8.5</v>
       </c>
       <c r="L12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M12" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1425,9 +1431,6 @@
       <c r="U12" t="n">
         <v>1</v>
       </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
@@ -1443,9 +1446,6 @@
       <c r="AA12" t="n">
         <v>1</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
       <c r="AC12" t="n">
         <v>1</v>
       </c>
@@ -1455,24 +1455,21 @@
       <c r="AE12" t="n">
         <v>1</v>
       </c>
-      <c r="AF12" t="n">
-        <v>10</v>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Equilibrio químico dinámico</t>
+          <t>Entalpía de reacción y ecuaciones termoquímicas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1481,20 +1478,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>8.5</v>
       </c>
-      <c r="K13" t="n">
-        <v>8</v>
-      </c>
       <c r="L13" t="n">
         <v>11</v>
       </c>
@@ -1541,11 +1535,11 @@
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -1557,7 +1551,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Equilibrio y rapidez en procesos industriales</t>
+          <t>Equilibrio químico dinámico</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1566,7 +1560,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
@@ -1577,9 +1571,15 @@
       <c r="G14" t="n">
         <v>8.5</v>
       </c>
+      <c r="K14" t="n">
+        <v>8</v>
+      </c>
       <c r="L14" t="n">
         <v>11</v>
       </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
@@ -1589,12 +1589,24 @@
       <c r="U14" t="n">
         <v>1</v>
       </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
       <c r="Y14" t="n">
         <v>1</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
       <c r="AB14" t="n">
         <v>1</v>
       </c>
@@ -1608,23 +1620,23 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Esterificación e hidrólisis</t>
+          <t>Equilibrio y rapidez en procesos industriales</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,39 +1645,45 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
         <v>10.5</v>
       </c>
+      <c r="G15" t="n">
+        <v>8.5</v>
+      </c>
       <c r="L15" t="n">
         <v>11</v>
       </c>
-      <c r="M15" t="n">
-        <v>7</v>
-      </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
       <c r="U15" t="n">
         <v>1</v>
       </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
       <c r="Y15" t="n">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
       </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
       <c r="AC15" t="n">
         <v>1</v>
       </c>
       <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
@@ -1673,19 +1691,19 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fuerza de ácidos y bases: Ka y Kb</t>
+          <t>Esterificación e hidrólisis</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1694,22 +1712,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="L16" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
@@ -1717,51 +1729,30 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
       <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
       <c r="Y16" t="n">
         <v>1</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
       <c r="AC16" t="n">
         <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>1</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
       <c r="AF16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -1773,7 +1764,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Grupos funcionales</t>
+          <t>Fuerza de ácidos y bases: Ka y Kb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1793,6 +1784,9 @@
       <c r="G17" t="n">
         <v>8.5</v>
       </c>
+      <c r="I17" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L17" t="n">
         <v>9.5</v>
       </c>
@@ -1805,9 +1799,15 @@
       <c r="P17" t="n">
         <v>1</v>
       </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
@@ -1836,11 +1836,11 @@
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
+          <t>Grupos funcionales</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -1902,6 +1902,9 @@
       <c r="AA18" t="n">
         <v>1</v>
       </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
       <c r="AC18" t="n">
         <v>1</v>
       </c>
@@ -1928,7 +1931,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Indicadores ácido-base</t>
+          <t>Hidrocarburos: alcanos, alquenos y alquinos</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1937,42 +1940,27 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
-      </c>
-      <c r="H19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M19" t="n">
         <v>7</v>
       </c>
-      <c r="I19" t="n">
-        <v>5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>9</v>
-      </c>
-      <c r="L19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="P19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
@@ -1981,12 +1969,18 @@
       <c r="W19" t="n">
         <v>1</v>
       </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
       <c r="Y19" t="n">
         <v>1</v>
       </c>
       <c r="Z19" t="n">
         <v>1</v>
       </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
       <c r="AC19" t="n">
         <v>1</v>
       </c>
@@ -1997,11 +1991,11 @@
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -2013,7 +2007,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Isomería estructural</t>
+          <t>Indicadores ácido-base</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2022,41 +2016,56 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>9</v>
+      </c>
       <c r="L20" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
       <c r="Y20" t="n">
         <v>1</v>
       </c>
       <c r="Z20" t="n">
         <v>1</v>
       </c>
-      <c r="AA20" t="n">
-        <v>1</v>
-      </c>
       <c r="AC20" t="n">
         <v>1</v>
       </c>
@@ -2067,11 +2076,11 @@
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -2083,7 +2092,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Leyes ponderales y volumétricas</t>
+          <t>Isomería estructural</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2092,32 +2101,56 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="I21" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>11</v>
+      </c>
+      <c r="M21" t="n">
         <v>7</v>
       </c>
-      <c r="J21" t="n">
-        <v>7</v>
-      </c>
-      <c r="M21" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
         <v>1</v>
       </c>
       <c r="AC21" t="n">
         <v>1</v>
       </c>
+      <c r="AD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
       <c r="AF21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -2129,7 +2162,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomenclatura orgánica IUPAC</t>
+          <t>Leyes ponderales y volumétricas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2138,59 +2171,32 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n">
         <v>7</v>
       </c>
-      <c r="D22" t="n">
-        <v>11</v>
-      </c>
-      <c r="F22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="M22" t="n">
         <v>9.5</v>
       </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="AC22" t="n">
         <v>1</v>
       </c>
-      <c r="AD22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -2202,7 +2208,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Oxidación y reducción</t>
+          <t>Nomenclatura orgánica IUPAC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2211,31 +2217,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>7</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="L23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2243,18 +2237,9 @@
       <c r="P23" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
@@ -2265,9 +2250,6 @@
         <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA23" t="n">
         <v>1</v>
       </c>
       <c r="AB23" t="n">
@@ -2287,19 +2269,19 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
           <t>alineado</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Polímeros y ambiente</t>
+          <t>Oxidación y reducción</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2308,19 +2290,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
       <c r="H24" t="n">
         <v>7</v>
       </c>
+      <c r="I24" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9</v>
+      </c>
       <c r="L24" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M24" t="n">
         <v>7</v>
@@ -2328,19 +2319,46 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
       <c r="W24" t="n">
         <v>1</v>
       </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
       <c r="Z24" t="n">
         <v>1</v>
       </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
       <c r="AC24" t="n">
         <v>1</v>
       </c>
       <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
@@ -2353,14 +2371,14 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Principio de Le Chatelier</t>
+          <t>Polímeros y ambiente</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2369,19 +2387,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>8.5</v>
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7</v>
       </c>
       <c r="L25" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M25" t="n">
         <v>7</v>
@@ -2389,41 +2407,23 @@
       <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1</v>
-      </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
-      <c r="AA25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
       <c r="AC25" t="n">
         <v>1</v>
       </c>
       <c r="AD25" t="n">
         <v>1</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Factores que afectan la rapidez de reacción</t>
+          <t>Principio de Le Chatelier</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2448,32 +2448,23 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
         <v>9</v>
       </c>
-      <c r="E26" t="n">
-        <v>9</v>
-      </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G26" t="n">
         <v>8.5</v>
       </c>
-      <c r="H26" t="n">
+      <c r="L26" t="n">
+        <v>11</v>
+      </c>
+      <c r="M26" t="n">
         <v>7</v>
       </c>
-      <c r="L26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2481,9 +2472,6 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
         <v>1</v>
       </c>
       <c r="W26" t="n">
@@ -2518,7 +2506,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -2530,7 +2518,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Reacciones de precipitación e identificación de iones</t>
+          <t>Química de los carbohidratos</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2539,20 +2527,14 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" t="n">
         <v>10.5</v>
       </c>
-      <c r="G27" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H27" t="n">
-        <v>7</v>
-      </c>
       <c r="I27" t="n">
         <v>9.5</v>
       </c>
@@ -2560,7 +2542,7 @@
         <v>9.5</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -2571,42 +2553,42 @@
       <c r="U27" t="n">
         <v>1</v>
       </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
       <c r="Y27" t="n">
         <v>1</v>
       </c>
       <c r="Z27" t="n">
         <v>1</v>
       </c>
-      <c r="AC27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="AA27" t="n">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
           <t>alineado</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Reacciones exotérmicas y endotérmicas</t>
+          <t>Química de los lípidos</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2615,81 +2597,36 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E28" t="n">
-        <v>7</v>
-      </c>
       <c r="F28" t="n">
-        <v>8</v>
-      </c>
-      <c r="G28" t="n">
-        <v>6</v>
-      </c>
-      <c r="H28" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="L28" t="n">
         <v>9.5</v>
       </c>
-      <c r="M28" t="n">
-        <v>7</v>
-      </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
       </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
       <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AA28" t="n">
         <v>1</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
@@ -2697,19 +2634,19 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Semivida, series de desintegración y residuos radiactivos</t>
+          <t>Radiactividad y emisiones nucleares</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2718,12 +2655,12 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
         <v>10</v>
       </c>
-      <c r="F29" t="n">
+      <c r="E29" t="n">
         <v>8</v>
       </c>
       <c r="G29" t="n">
@@ -2732,69 +2669,33 @@
       <c r="I29" t="n">
         <v>9.5</v>
       </c>
-      <c r="L29" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
       <c r="W29" t="n">
         <v>1</v>
       </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
-      <c r="AD29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1</v>
-      </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Teoría cinética de los gases</t>
+          <t>Factores que afectan la rapidez de reacción</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2803,25 +2704,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
       </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
       <c r="F30" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
-      </c>
-      <c r="I30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7</v>
+      </c>
+      <c r="L30" t="n">
         <v>9.5</v>
       </c>
-      <c r="J30" t="n">
+      <c r="M30" t="n">
         <v>2.5</v>
       </c>
-      <c r="M30" t="n">
-        <v>4.5</v>
+      <c r="N30" t="n">
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -2829,7 +2736,7 @@
       <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>1</v>
       </c>
       <c r="V30" t="n">
@@ -2838,6 +2745,9 @@
       <c r="W30" t="n">
         <v>1</v>
       </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
       <c r="Y30" t="n">
         <v>1</v>
       </c>
@@ -2860,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -2876,7 +2786,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Teoría de colisiones</t>
+          <t>Reacciones de precipitación e identificación de iones</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2885,59 +2795,47 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G31" t="n">
         <v>8.5</v>
       </c>
+      <c r="H31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L31" t="n">
         <v>9.5</v>
       </c>
       <c r="M31" t="n">
         <v>7</v>
       </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
       <c r="W31" t="n">
         <v>1</v>
       </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
       <c r="Y31" t="n">
         <v>1</v>
       </c>
       <c r="Z31" t="n">
         <v>1</v>
       </c>
-      <c r="AA31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1</v>
-      </c>
       <c r="AC31" t="n">
         <v>1</v>
       </c>
@@ -2948,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2957,14 +2855,14 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
+          <t>Reacciones exotérmicas y endotérmicas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2973,21 +2871,30 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" t="n">
         <v>9</v>
       </c>
       <c r="L32" t="n">
@@ -3005,6 +2912,9 @@
       <c r="S32" t="n">
         <v>1</v>
       </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
@@ -3023,6 +2933,9 @@
       <c r="Z32" t="n">
         <v>1</v>
       </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
       <c r="AB32" t="n">
         <v>1</v>
       </c>
@@ -3036,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -3052,13 +2965,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Agentes oxidantes y reductores</t>
+          <t>Semivida, series de desintegración y residuos radiactivos</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>incierto</t>
-        </is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
@@ -3066,9 +2985,6 @@
       <c r="G33" t="n">
         <v>8.5</v>
       </c>
-      <c r="H33" t="n">
-        <v>7</v>
-      </c>
       <c r="I33" t="n">
         <v>9.5</v>
       </c>
@@ -3076,7 +2992,7 @@
         <v>9.5</v>
       </c>
       <c r="M33" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -3105,7 +3021,7 @@
       <c r="Z33" t="n">
         <v>1</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AA33" t="n">
         <v>1</v>
       </c>
       <c r="AC33" t="n">
@@ -3117,51 +3033,51 @@
       <c r="AE33" t="n">
         <v>1</v>
       </c>
+      <c r="AF33" t="n">
+        <v>11</v>
+      </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>faltante</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Combustibles fósiles y biocombustibles</t>
+          <t>Teoría cinética de los gases</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
         <v>9</v>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
       </c>
-      <c r="H34" t="n">
-        <v>3</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="I34" t="n">
         <v>9.5</v>
       </c>
+      <c r="J34" t="n">
+        <v>2.5</v>
+      </c>
       <c r="M34" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -3169,10 +3085,7 @@
       <c r="P34" t="n">
         <v>1</v>
       </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="R34" t="n">
         <v>1</v>
       </c>
       <c r="V34" t="n">
@@ -3181,15 +3094,15 @@
       <c r="W34" t="n">
         <v>1</v>
       </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
       <c r="Y34" t="n">
         <v>1</v>
       </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
       <c r="AB34" t="n">
         <v>1</v>
       </c>
@@ -3203,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -3212,258 +3125,258 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ecuación de Nernst</t>
+          <t>Teoría de colisiones</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>9</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
         <v>1</v>
       </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>10</v>
+      </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
+          <t>Teorías ácido-base (Arrhenius, Brønsted-Lowry, Lewis)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9</v>
       </c>
       <c r="L36" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
       </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
       <c r="X36" t="n">
         <v>1</v>
       </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
       <c r="AD36" t="n">
         <v>1</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
       </c>
+      <c r="AF36" t="n">
+        <v>9</v>
+      </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enlace químico</t>
+          <t>Ecuación de Nernst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="F37" t="n">
-        <v>8</v>
-      </c>
-      <c r="G37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" t="n">
-        <v>9</v>
-      </c>
-      <c r="L37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AD37" t="n">
         <v>1</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1</v>
-      </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>faltante</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Química de los ácidos nucleicos</t>
+          <t>Energía reticular y ciclo de Born-Haber</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>incierto</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>10</v>
+          <t>no_aplica</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>11</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Química de los carbohidratos</t>
+          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>incierto</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="F39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1</v>
+          <t>no_aplica</t>
+        </is>
       </c>
       <c r="Y39" t="n">
         <v>1</v>
@@ -3471,76 +3384,55 @@
       <c r="Z39" t="n">
         <v>1</v>
       </c>
-      <c r="AA39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>10</v>
+      <c r="AD39" t="n">
+        <v>1</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Radiactividad y emisiones nucleares</t>
+          <t>Espectrometría de masas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>incierto</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>10</v>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="n">
-        <v>8</v>
-      </c>
-      <c r="G40" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I40" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1</v>
+          <t>no_aplica</t>
+        </is>
       </c>
       <c r="W40" t="n">
         <v>1</v>
       </c>
-      <c r="AC40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>10</v>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Energía reticular y ciclo de Born-Haber</t>
+          <t>Técnicas para determinar estructuras orgánicas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3548,13 +3440,16 @@
           <t>no_aplica</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>11</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" t="n">
         <v>1</v>
       </c>
       <c r="AG41" t="inlineStr">
@@ -3571,7 +3466,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Relación entre energía de Gibbs y constante de equilibrio</t>
+          <t>Redes covalentes y alótropos del carbono</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3579,6 +3474,36 @@
           <t>no_aplica</t>
         </is>
       </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
       <c r="Y42" t="n">
         <v>1</v>
       </c>
@@ -3590,7 +3515,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
@@ -3602,19 +3527,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Redes covalentes y alótropos del carbono</t>
+          <t>Composición del aire y contaminantes atmosféricos</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -3622,48 +3547,60 @@
       <c r="G43" t="n">
         <v>8.5</v>
       </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.5</v>
+      </c>
       <c r="L43" t="n">
         <v>9.5</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
         <v>7</v>
       </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1</v>
-      </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Composición del aire y contaminantes atmosféricos</t>
+          <t>Disolución y rapidez de disolución</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3675,52 +3612,34 @@
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
-      </c>
-      <c r="F44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
       </c>
-      <c r="I44" t="n">
-        <v>5</v>
-      </c>
       <c r="J44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M44" t="n">
         <v>2.5</v>
       </c>
-      <c r="L44" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE44" t="n">
+      <c r="AA44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3736,7 +3655,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Disolución y rapidez de disolución</t>
+          <t>Materia y materiales</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3745,37 +3664,73 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>10</v>
       </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>2</v>
       </c>
+      <c r="I45" t="n">
+        <v>6</v>
+      </c>
       <c r="J45" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K45" t="n">
         <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
         <v>2.5</v>
       </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1</v>
+      </c>
       <c r="AA45" t="n">
         <v>1</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3791,7 +3746,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Materia y materiales</t>
+          <t>Minerales: composición y estructura cristalina</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3800,77 +3755,44 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>1</v>
       </c>
       <c r="U46" t="n">
         <v>1</v>
       </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1</v>
-      </c>
       <c r="Z46" t="n">
         <v>1</v>
       </c>
       <c r="AA46" t="n">
         <v>1</v>
       </c>
-      <c r="AB46" t="n">
-        <v>1</v>
-      </c>
       <c r="AD46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
@@ -3882,7 +3804,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Minerales: composición y estructura cristalina</t>
+          <t>Moléculas y fórmulas químicas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3891,44 +3813,77 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="n">
+        <v>7</v>
       </c>
       <c r="F47" t="n">
         <v>8</v>
       </c>
+      <c r="G47" t="n">
+        <v>6</v>
+      </c>
       <c r="H47" t="n">
         <v>7</v>
       </c>
+      <c r="I47" t="n">
+        <v>7</v>
+      </c>
       <c r="J47" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6</v>
       </c>
       <c r="L47" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>7</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="S47" t="n">
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
         <v>1</v>
       </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1</v>
+      </c>
       <c r="Z47" t="n">
         <v>1</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" t="n">
         <v>1</v>
       </c>
       <c r="AD47" t="n">
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -3940,7 +3895,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Moléculas y fórmulas químicas</t>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3954,29 +3909,17 @@
       <c r="D48" t="n">
         <v>10</v>
       </c>
-      <c r="E48" t="n">
-        <v>7</v>
-      </c>
       <c r="F48" t="n">
         <v>8</v>
       </c>
       <c r="G48" t="n">
         <v>6</v>
       </c>
-      <c r="H48" t="n">
-        <v>7</v>
-      </c>
       <c r="I48" t="n">
-        <v>7</v>
-      </c>
-      <c r="J48" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
-      </c>
-      <c r="L48" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="M48" t="n">
         <v>7</v>
@@ -3987,15 +3930,12 @@
       <c r="P48" t="n">
         <v>1</v>
       </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1</v>
-      </c>
       <c r="X48" t="n">
         <v>1</v>
       </c>
@@ -4005,17 +3945,17 @@
       <c r="Z48" t="n">
         <v>1</v>
       </c>
-      <c r="AB48" t="n">
-        <v>1</v>
-      </c>
       <c r="AC48" t="n">
         <v>1</v>
       </c>
       <c r="AD48" t="n">
         <v>1</v>
       </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
       <c r="AF48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -4031,7 +3971,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+          <t>Número de oxidación</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4043,33 +3983,24 @@
         <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F49" t="n">
         <v>8</v>
       </c>
-      <c r="G49" t="n">
-        <v>6</v>
-      </c>
       <c r="I49" t="n">
         <v>9.5</v>
       </c>
-      <c r="K49" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" t="n">
-        <v>7</v>
+      <c r="L49" t="n">
+        <v>9.5</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
       <c r="R49" t="n">
         <v>1</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>1</v>
       </c>
       <c r="X49" t="n">
@@ -4081,6 +4012,9 @@
       <c r="Z49" t="n">
         <v>1</v>
       </c>
+      <c r="AB49" t="n">
+        <v>1</v>
+      </c>
       <c r="AC49" t="n">
         <v>1</v>
       </c>
@@ -4091,7 +4025,7 @@
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -4107,7 +4041,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Número de oxidación</t>
+          <t>Proceso de disolución y solvatación</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4116,52 +4050,46 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>7</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="n">
         <v>8</v>
-      </c>
-      <c r="I50" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L50" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1</v>
-      </c>
-      <c r="X50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>5</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -4177,56 +4105,83 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Proceso de disolución y solvatación</t>
+          <t>Ácidos y bases: propiedades</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F51" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H51" t="n">
         <v>7</v>
       </c>
+      <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="L51" t="n">
+        <v>7.5</v>
       </c>
       <c r="M51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="n">
         <v>7</v>
       </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>8</v>
-      </c>
       <c r="AG51" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -4234,14 +4189,14 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ácidos y bases: propiedades</t>
+          <t>Átomo y partículas subatómicas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4250,11 +4205,14 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
         <v>9</v>
       </c>
+      <c r="E52" t="n">
+        <v>8</v>
+      </c>
       <c r="F52" t="n">
         <v>8</v>
       </c>
@@ -4265,19 +4223,22 @@
         <v>7</v>
       </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J52" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
         <v>7.5</v>
       </c>
       <c r="M52" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -4288,9 +4249,6 @@
       <c r="R52" t="n">
         <v>1</v>
       </c>
-      <c r="S52" t="n">
-        <v>1</v>
-      </c>
       <c r="T52" t="n">
         <v>1</v>
       </c>
@@ -4303,6 +4261,9 @@
       <c r="W52" t="n">
         <v>1</v>
       </c>
+      <c r="X52" t="n">
+        <v>1</v>
+      </c>
       <c r="Y52" t="n">
         <v>1</v>
       </c>
@@ -4315,8 +4276,11 @@
       <c r="AD52" t="n">
         <v>1</v>
       </c>
+      <c r="AE52" t="n">
+        <v>1</v>
+      </c>
       <c r="AF52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4332,7 +4296,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Átomo y partículas subatómicas</t>
+          <t>Cambios de estado</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4341,40 +4305,37 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
         <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>7</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -4385,9 +4346,6 @@
       <c r="R53" t="n">
         <v>1</v>
       </c>
-      <c r="T53" t="n">
-        <v>1</v>
-      </c>
       <c r="U53" t="n">
         <v>1</v>
       </c>
@@ -4406,17 +4364,20 @@
       <c r="Z53" t="n">
         <v>1</v>
       </c>
+      <c r="AA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1</v>
+      </c>
       <c r="AC53" t="n">
         <v>1</v>
       </c>
       <c r="AD53" t="n">
         <v>1</v>
       </c>
-      <c r="AE53" t="n">
-        <v>1</v>
-      </c>
       <c r="AF53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4432,7 +4393,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cambios de estado</t>
+          <t>Cambios físicos y químicos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4444,7 +4405,7 @@
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -4456,22 +4417,22 @@
         <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J54" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M54" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
@@ -4482,25 +4443,22 @@
       <c r="R54" t="n">
         <v>1</v>
       </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
       <c r="U54" t="n">
         <v>1</v>
       </c>
-      <c r="V54" t="n">
-        <v>1</v>
-      </c>
       <c r="W54" t="n">
         <v>1</v>
       </c>
-      <c r="X54" t="n">
-        <v>1</v>
-      </c>
       <c r="Y54" t="n">
         <v>1</v>
       </c>
       <c r="Z54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA54" t="n">
         <v>1</v>
       </c>
       <c r="AB54" t="n">
@@ -4529,7 +4487,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cambios físicos y químicos</t>
+          <t>Catalizadores</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4538,37 +4496,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
         <v>10</v>
       </c>
-      <c r="E55" t="n">
-        <v>2</v>
-      </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J55" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L55" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="M55" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -4576,27 +4519,24 @@
       <c r="P55" t="n">
         <v>1</v>
       </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
       <c r="U55" t="n">
         <v>1</v>
       </c>
       <c r="W55" t="n">
         <v>1</v>
       </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
       <c r="Y55" t="n">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
       <c r="AB55" t="n">
         <v>1</v>
       </c>
@@ -4606,8 +4546,11 @@
       <c r="AD55" t="n">
         <v>1</v>
       </c>
+      <c r="AE55" t="n">
+        <v>1</v>
+      </c>
       <c r="AF55" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4616,14 +4559,14 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Catalizadores</t>
+          <t>Combustibles fósiles y biocombustibles</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4632,19 +4575,25 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F56" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G56" t="n">
         <v>6</v>
       </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
       <c r="L56" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M56" t="n">
         <v>7</v>
@@ -4655,9 +4604,15 @@
       <c r="P56" t="n">
         <v>1</v>
       </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
       <c r="U56" t="n">
         <v>1</v>
       </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
@@ -4670,9 +4625,6 @@
       <c r="Z56" t="n">
         <v>1</v>
       </c>
-      <c r="AA56" t="n">
-        <v>1</v>
-      </c>
       <c r="AB56" t="n">
         <v>1</v>
       </c>
@@ -4686,7 +4638,7 @@
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -4695,7 +4647,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5678,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Escala de pH</t>
+          <t>Enlace químico</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5735,34 +5687,28 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F70" t="n">
         <v>8</v>
       </c>
       <c r="G70" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H70" t="n">
         <v>7</v>
       </c>
-      <c r="I70" t="n">
-        <v>9.5</v>
-      </c>
       <c r="J70" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K70" t="n">
         <v>9</v>
       </c>
       <c r="L70" t="n">
         <v>7.5</v>
       </c>
       <c r="M70" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
@@ -5770,10 +5716,7 @@
       <c r="P70" t="n">
         <v>1</v>
       </c>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" t="n">
+      <c r="S70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
@@ -5806,9 +5749,6 @@
       <c r="AE70" t="n">
         <v>1</v>
       </c>
-      <c r="AF70" t="n">
-        <v>7</v>
-      </c>
       <c r="AG70" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -5816,14 +5756,14 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Estados de la materia</t>
+          <t>Escala de pH</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5832,37 +5772,34 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D71" t="n">
         <v>9</v>
       </c>
-      <c r="E71" t="n">
-        <v>2</v>
-      </c>
       <c r="F71" t="n">
         <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J71" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L71" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M71" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -5873,18 +5810,27 @@
       <c r="R71" t="n">
         <v>1</v>
       </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
       <c r="U71" t="n">
         <v>1</v>
       </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1</v>
+      </c>
       <c r="Y71" t="n">
         <v>1</v>
       </c>
       <c r="Z71" t="n">
         <v>1</v>
       </c>
-      <c r="AA71" t="n">
-        <v>1</v>
-      </c>
       <c r="AB71" t="n">
         <v>1</v>
       </c>
@@ -5894,8 +5840,11 @@
       <c r="AD71" t="n">
         <v>1</v>
       </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
       <c r="AF71" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
@@ -5911,7 +5860,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Estados de la materia</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5920,28 +5869,37 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
         <v>9</v>
       </c>
+      <c r="E72" t="n">
+        <v>2</v>
+      </c>
       <c r="F72" t="n">
         <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
       </c>
       <c r="L72" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M72" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -5955,15 +5913,6 @@
       <c r="U72" t="n">
         <v>1</v>
       </c>
-      <c r="V72" t="n">
-        <v>1</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1</v>
-      </c>
-      <c r="X72" t="n">
-        <v>1</v>
-      </c>
       <c r="Y72" t="n">
         <v>1</v>
       </c>
@@ -5982,11 +5931,8 @@
       <c r="AD72" t="n">
         <v>1</v>
       </c>
-      <c r="AE72" t="n">
-        <v>1</v>
-      </c>
       <c r="AF72" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -6002,7 +5948,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Notación y estructuras de Lewis</t>
+          <t>Estequiometría</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6011,29 +5957,44 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G73" t="n">
         <v>8.5</v>
       </c>
+      <c r="I73" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>7</v>
+      </c>
       <c r="L73" t="n">
         <v>9.5</v>
       </c>
+      <c r="M73" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
       <c r="P73" t="n">
         <v>1</v>
       </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
       <c r="U73" t="n">
         <v>1</v>
       </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
@@ -6046,6 +6007,9 @@
       <c r="Z73" t="n">
         <v>1</v>
       </c>
+      <c r="AA73" t="n">
+        <v>1</v>
+      </c>
       <c r="AB73" t="n">
         <v>1</v>
       </c>
@@ -6055,8 +6019,11 @@
       <c r="AD73" t="n">
         <v>1</v>
       </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
       <c r="AF73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -6072,7 +6039,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares</t>
+          <t>Notación y estructuras de Lewis</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6092,15 +6059,9 @@
       <c r="G74" t="n">
         <v>8.5</v>
       </c>
-      <c r="J74" t="n">
-        <v>7</v>
-      </c>
       <c r="L74" t="n">
         <v>9.5</v>
       </c>
-      <c r="M74" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
@@ -6110,9 +6071,6 @@
       <c r="U74" t="n">
         <v>1</v>
       </c>
-      <c r="V74" t="n">
-        <v>1</v>
-      </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
@@ -6125,9 +6083,6 @@
       <c r="Z74" t="n">
         <v>1</v>
       </c>
-      <c r="AA74" t="n">
-        <v>1</v>
-      </c>
       <c r="AB74" t="n">
         <v>1</v>
       </c>
@@ -6135,9 +6090,6 @@
         <v>1</v>
       </c>
       <c r="AD74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
@@ -6157,7 +6109,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares y propiedades físicas</t>
+          <t>Fuerzas intermoleculares</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6166,36 +6118,36 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G75" t="n">
         <v>8.5</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>7</v>
-      </c>
-      <c r="I75" t="n">
-        <v>9.5</v>
       </c>
       <c r="L75" t="n">
         <v>9.5</v>
       </c>
+      <c r="M75" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O75" t="n">
         <v>1</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
       </c>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
       <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
         <v>1</v>
       </c>
       <c r="W75" t="n">
@@ -6242,7 +6194,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Geometría molecular (RPECV)</t>
+          <t>Fuerzas intermoleculares y propiedades físicas</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6251,29 +6203,38 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
         <v>10</v>
       </c>
+      <c r="F76" t="n">
+        <v>8</v>
+      </c>
       <c r="G76" t="n">
         <v>8.5</v>
       </c>
+      <c r="H76" t="n">
+        <v>7</v>
+      </c>
+      <c r="I76" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L76" t="n">
-        <v>11</v>
-      </c>
-      <c r="M76" t="n">
         <v>9.5</v>
       </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
       <c r="P76" t="n">
         <v>1</v>
       </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
       <c r="U76" t="n">
         <v>1</v>
       </c>
-      <c r="V76" t="n">
-        <v>1</v>
-      </c>
       <c r="W76" t="n">
         <v>1</v>
       </c>
@@ -6284,6 +6245,9 @@
         <v>1</v>
       </c>
       <c r="Z76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA76" t="n">
         <v>1</v>
       </c>
       <c r="AB76" t="n">
@@ -6315,7 +6279,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Iones</t>
+          <t>Geometría molecular (RPECV)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6324,44 +6288,23 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D77" t="n">
         <v>10</v>
       </c>
-      <c r="F77" t="n">
-        <v>8</v>
-      </c>
       <c r="G77" t="n">
         <v>8.5</v>
       </c>
-      <c r="I77" t="n">
-        <v>8</v>
-      </c>
-      <c r="J77" t="n">
-        <v>7</v>
-      </c>
-      <c r="K77" t="n">
-        <v>9</v>
-      </c>
       <c r="L77" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="M77" t="n">
-        <v>7</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
       </c>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" t="n">
-        <v>1</v>
-      </c>
       <c r="U77" t="n">
         <v>1</v>
       </c>
@@ -6380,14 +6323,20 @@
       <c r="Z77" t="n">
         <v>1</v>
       </c>
+      <c r="AB77" t="n">
+        <v>1</v>
+      </c>
       <c r="AC77" t="n">
         <v>1</v>
       </c>
       <c r="AD77" t="n">
         <v>1</v>
       </c>
+      <c r="AE77" t="n">
+        <v>1</v>
+      </c>
       <c r="AF77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -6403,7 +6352,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Isótopos</t>
+          <t>Iones</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6417,20 +6366,29 @@
       <c r="D78" t="n">
         <v>10</v>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>8</v>
       </c>
       <c r="G78" t="n">
         <v>8.5</v>
       </c>
       <c r="I78" t="n">
-        <v>9.5</v>
+        <v>8</v>
+      </c>
+      <c r="J78" t="n">
+        <v>7</v>
+      </c>
+      <c r="K78" t="n">
+        <v>9</v>
       </c>
       <c r="L78" t="n">
         <v>7.5</v>
       </c>
       <c r="M78" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
       </c>
       <c r="P78" t="n">
         <v>1</v>
@@ -6438,6 +6396,9 @@
       <c r="R78" t="n">
         <v>1</v>
       </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
       <c r="U78" t="n">
         <v>1</v>
       </c>
@@ -6445,6 +6406,9 @@
         <v>1</v>
       </c>
       <c r="W78" t="n">
+        <v>1</v>
+      </c>
+      <c r="X78" t="n">
         <v>1</v>
       </c>
       <c r="Y78" t="n">
@@ -6476,7 +6440,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Masa atómica relativa</t>
+          <t>Isótopos</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6490,21 +6454,33 @@
       <c r="D79" t="n">
         <v>10</v>
       </c>
+      <c r="E79" t="n">
+        <v>8</v>
+      </c>
       <c r="G79" t="n">
         <v>8.5</v>
       </c>
+      <c r="I79" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L79" t="n">
         <v>7.5</v>
       </c>
       <c r="M79" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="P79" t="n">
         <v>1</v>
       </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
       <c r="U79" t="n">
         <v>1</v>
       </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
       <c r="W79" t="n">
         <v>1</v>
       </c>
@@ -6521,7 +6497,7 @@
         <v>1</v>
       </c>
       <c r="AF79" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -6537,7 +6513,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Masa molar</t>
+          <t>Masa atómica relativa</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6546,54 +6522,33 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
         <v>10</v>
       </c>
-      <c r="F80" t="n">
-        <v>8</v>
-      </c>
       <c r="G80" t="n">
         <v>8.5</v>
       </c>
-      <c r="I80" t="n">
-        <v>9.5</v>
-      </c>
       <c r="L80" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M80" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
       <c r="U80" t="n">
         <v>1</v>
       </c>
-      <c r="V80" t="n">
-        <v>1</v>
-      </c>
       <c r="W80" t="n">
         <v>1</v>
       </c>
-      <c r="X80" t="n">
-        <v>1</v>
-      </c>
       <c r="Y80" t="n">
         <v>1</v>
       </c>
       <c r="Z80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB80" t="n">
         <v>1</v>
       </c>
       <c r="AC80" t="n">
@@ -6619,7 +6574,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Reutilización y reciclaje de materiales</t>
+          <t>Masa molar</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6628,10 +6583,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D81" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F81" t="n">
         <v>8</v>
@@ -6639,59 +6594,53 @@
       <c r="G81" t="n">
         <v>8.5</v>
       </c>
-      <c r="H81" t="n">
-        <v>7</v>
-      </c>
       <c r="I81" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L81" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M81" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="n">
+        <v>1</v>
+      </c>
+      <c r="W81" t="n">
+        <v>1</v>
+      </c>
+      <c r="X81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="n">
         <v>8</v>
-      </c>
-      <c r="J81" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K81" t="n">
-        <v>2</v>
-      </c>
-      <c r="L81" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M81" t="n">
-        <v>7</v>
-      </c>
-      <c r="O81" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
-      <c r="S81" t="n">
-        <v>1</v>
-      </c>
-      <c r="U81" t="n">
-        <v>1</v>
-      </c>
-      <c r="V81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>2</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
@@ -6707,7 +6656,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mezclas homogéneas y heterogéneas</t>
+          <t>Reutilización y reciclaje de materiales</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6719,22 +6668,19 @@
         <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
-      </c>
-      <c r="E82" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G82" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J82" t="n">
         <v>4.5</v>
@@ -6743,10 +6689,10 @@
         <v>2</v>
       </c>
       <c r="L82" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M82" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O82" t="n">
         <v>1</v>
@@ -6757,10 +6703,13 @@
       <c r="R82" t="n">
         <v>1</v>
       </c>
+      <c r="S82" t="n">
+        <v>1</v>
+      </c>
       <c r="U82" t="n">
         <v>1</v>
       </c>
-      <c r="W82" t="n">
+      <c r="V82" t="n">
         <v>1</v>
       </c>
       <c r="Y82" t="n">
@@ -6769,10 +6718,13 @@
       <c r="Z82" t="n">
         <v>1</v>
       </c>
-      <c r="AB82" t="n">
+      <c r="AC82" t="n">
         <v>1</v>
       </c>
       <c r="AD82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE82" t="n">
         <v>1</v>
       </c>
       <c r="AF82" t="n">
@@ -6792,7 +6744,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Modelo de partículas de la materia</t>
+          <t>Mezclas homogéneas y heterogéneas</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6801,37 +6753,37 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F83" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G83" t="n">
         <v>6</v>
       </c>
       <c r="H83" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L83" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M83" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
@@ -6845,9 +6797,6 @@
       <c r="U83" t="n">
         <v>1</v>
       </c>
-      <c r="V83" t="n">
-        <v>1</v>
-      </c>
       <c r="W83" t="n">
         <v>1</v>
       </c>
@@ -6857,23 +6806,14 @@
       <c r="Z83" t="n">
         <v>1</v>
       </c>
-      <c r="AA83" t="n">
-        <v>1</v>
-      </c>
       <c r="AB83" t="n">
         <v>1</v>
       </c>
-      <c r="AC83" t="n">
-        <v>1</v>
-      </c>
       <c r="AD83" t="n">
         <v>1</v>
       </c>
-      <c r="AE83" t="n">
-        <v>1</v>
-      </c>
       <c r="AF83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
@@ -6889,7 +6829,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Modelo mecanocuántico y orbitales atómicos</t>
+          <t>Modelo de partículas de la materia</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6898,23 +6838,68 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
         <v>10</v>
       </c>
+      <c r="E84" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
+      <c r="G84" t="n">
+        <v>6</v>
+      </c>
+      <c r="H84" t="n">
+        <v>7</v>
+      </c>
+      <c r="I84" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J84" t="n">
+        <v>7</v>
+      </c>
+      <c r="K84" t="n">
+        <v>4</v>
+      </c>
       <c r="L84" t="n">
-        <v>11</v>
+        <v>7.5</v>
+      </c>
+      <c r="M84" t="n">
+        <v>7</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
       </c>
       <c r="U84" t="n">
         <v>1</v>
       </c>
+      <c r="V84" t="n">
+        <v>1</v>
+      </c>
+      <c r="W84" t="n">
+        <v>1</v>
+      </c>
       <c r="Y84" t="n">
         <v>1</v>
       </c>
       <c r="Z84" t="n">
         <v>1</v>
       </c>
+      <c r="AA84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>1</v>
+      </c>
       <c r="AC84" t="n">
         <v>1</v>
       </c>
@@ -6925,7 +6910,7 @@
         <v>1</v>
       </c>
       <c r="AF84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -6941,7 +6926,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Evolución de los modelos atómicos</t>
+          <t>Modelo mecanocuántico y orbitales atómicos</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6955,43 +6940,10 @@
       <c r="D85" t="n">
         <v>10</v>
       </c>
-      <c r="E85" t="n">
-        <v>8</v>
-      </c>
-      <c r="F85" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G85" t="n">
-        <v>6</v>
-      </c>
-      <c r="J85" t="n">
-        <v>9</v>
-      </c>
-      <c r="K85" t="n">
-        <v>8</v>
-      </c>
       <c r="L85" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M85" t="n">
-        <v>7</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
-      </c>
-      <c r="P85" t="n">
-        <v>1</v>
-      </c>
-      <c r="S85" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
-      </c>
-      <c r="V85" t="n">
-        <v>1</v>
-      </c>
-      <c r="W85" t="n">
         <v>1</v>
       </c>
       <c r="Y85" t="n">
@@ -7026,7 +6978,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Evolución de los modelos atómicos</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7035,25 +6987,31 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
         <v>10</v>
       </c>
+      <c r="E86" t="n">
+        <v>8</v>
+      </c>
       <c r="F86" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>6</v>
+      </c>
+      <c r="J86" t="n">
+        <v>9</v>
+      </c>
+      <c r="K86" t="n">
         <v>8</v>
       </c>
-      <c r="G86" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I86" t="n">
-        <v>9.5</v>
-      </c>
       <c r="L86" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M86" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
@@ -7061,7 +7019,7 @@
       <c r="P86" t="n">
         <v>1</v>
       </c>
-      <c r="R86" t="n">
+      <c r="S86" t="n">
         <v>1</v>
       </c>
       <c r="U86" t="n">
@@ -7073,26 +7031,23 @@
       <c r="W86" t="n">
         <v>1</v>
       </c>
-      <c r="X86" t="n">
-        <v>1</v>
-      </c>
       <c r="Y86" t="n">
         <v>1</v>
       </c>
       <c r="Z86" t="n">
         <v>1</v>
       </c>
-      <c r="AB86" t="n">
-        <v>1</v>
-      </c>
       <c r="AC86" t="n">
         <v>1</v>
       </c>
       <c r="AD86" t="n">
         <v>1</v>
       </c>
+      <c r="AE86" t="n">
+        <v>1</v>
+      </c>
       <c r="AF86" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -7108,7 +7063,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Molaridad y unidades químicas de concentración</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7123,7 +7078,10 @@
         <v>10</v>
       </c>
       <c r="F87" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>8.5</v>
       </c>
       <c r="I87" t="n">
         <v>9.5</v>
@@ -7137,6 +7095,9 @@
       <c r="O87" t="n">
         <v>1</v>
       </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
       <c r="R87" t="n">
         <v>1</v>
       </c>
@@ -7165,9 +7126,6 @@
         <v>1</v>
       </c>
       <c r="AD87" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE87" t="n">
         <v>1</v>
       </c>
       <c r="AF87" t="n">
@@ -7187,7 +7145,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Neutralización y reacciones de los ácidos</t>
+          <t>Molaridad y unidades químicas de concentración</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7196,76 +7154,61 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I88" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M88" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" t="n">
+        <v>1</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1</v>
+      </c>
+      <c r="X88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF88" t="n">
         <v>8</v>
-      </c>
-      <c r="G88" t="n">
-        <v>6</v>
-      </c>
-      <c r="H88" t="n">
-        <v>7</v>
-      </c>
-      <c r="I88" t="n">
-        <v>8</v>
-      </c>
-      <c r="J88" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K88" t="n">
-        <v>9</v>
-      </c>
-      <c r="L88" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M88" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O88" t="n">
-        <v>1</v>
-      </c>
-      <c r="P88" t="n">
-        <v>1</v>
-      </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
-      <c r="S88" t="n">
-        <v>1</v>
-      </c>
-      <c r="T88" t="n">
-        <v>1</v>
-      </c>
-      <c r="U88" t="n">
-        <v>1</v>
-      </c>
-      <c r="W88" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>7</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -7281,7 +7224,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Números cuánticos</t>
+          <t>Neutralización y reacciones de los ácidos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7290,17 +7233,68 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F89" t="n">
+        <v>8</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6</v>
+      </c>
+      <c r="H89" t="n">
+        <v>7</v>
+      </c>
+      <c r="I89" t="n">
+        <v>8</v>
+      </c>
+      <c r="J89" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K89" t="n">
+        <v>9</v>
       </c>
       <c r="L89" t="n">
-        <v>11</v>
+        <v>7.5</v>
+      </c>
+      <c r="M89" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1</v>
       </c>
       <c r="U89" t="n">
         <v>1</v>
       </c>
+      <c r="W89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1</v>
+      </c>
       <c r="AD89" t="n">
         <v>1</v>
       </c>
@@ -7308,7 +7302,7 @@
         <v>1</v>
       </c>
       <c r="AF89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -7324,7 +7318,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Oxidación y corrosión de los metales</t>
+          <t>Números cuánticos</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7333,80 +7327,41 @@
         </is>
       </c>
       <c r="C90" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="L90" t="n">
         <v>11</v>
       </c>
-      <c r="D90" t="n">
-        <v>11</v>
-      </c>
-      <c r="F90" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H90" t="n">
-        <v>3</v>
-      </c>
-      <c r="I90" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J90" t="n">
-        <v>9</v>
-      </c>
-      <c r="K90" t="n">
-        <v>9</v>
-      </c>
-      <c r="L90" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M90" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O90" t="n">
-        <v>1</v>
-      </c>
-      <c r="R90" t="n">
-        <v>1</v>
-      </c>
-      <c r="S90" t="n">
-        <v>1</v>
-      </c>
-      <c r="T90" t="n">
-        <v>1</v>
-      </c>
       <c r="U90" t="n">
         <v>1</v>
       </c>
-      <c r="W90" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC90" t="n">
-        <v>1</v>
-      </c>
       <c r="AD90" t="n">
         <v>1</v>
       </c>
+      <c r="AE90" t="n">
+        <v>1</v>
+      </c>
       <c r="AF90" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Polaridad molecular</t>
+          <t>Oxidación y corrosión de los metales</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7415,80 +7370,80 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F91" t="n">
-        <v>8</v>
+        <v>10.5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3</v>
       </c>
       <c r="I91" t="n">
         <v>9.5</v>
       </c>
+      <c r="J91" t="n">
+        <v>9</v>
+      </c>
       <c r="K91" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L91" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="n">
         <v>11</v>
       </c>
-      <c r="M91" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="V91" t="n">
-        <v>1</v>
-      </c>
-      <c r="W91" t="n">
-        <v>1</v>
-      </c>
-      <c r="X91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>6</v>
-      </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Procesos de la industria química</t>
+          <t>Polaridad molecular</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7497,21 +7452,33 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D92" t="n">
         <v>10</v>
       </c>
-      <c r="G92" t="n">
+      <c r="F92" t="n">
+        <v>8</v>
+      </c>
+      <c r="I92" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K92" t="n">
         <v>6</v>
       </c>
-      <c r="K92" t="n">
-        <v>4</v>
+      <c r="L92" t="n">
+        <v>11</v>
       </c>
       <c r="M92" t="n">
         <v>9.5</v>
       </c>
-      <c r="P92" t="n">
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
         <v>1</v>
       </c>
       <c r="V92" t="n">
@@ -7520,6 +7487,9 @@
       <c r="W92" t="n">
         <v>1</v>
       </c>
+      <c r="X92" t="n">
+        <v>1</v>
+      </c>
       <c r="Y92" t="n">
         <v>1</v>
       </c>
@@ -7535,8 +7505,11 @@
       <c r="AD92" t="n">
         <v>1</v>
       </c>
+      <c r="AE92" t="n">
+        <v>1</v>
+      </c>
       <c r="AF92" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
@@ -7552,7 +7525,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Procesos de la industria química</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7566,19 +7539,37 @@
       <c r="D93" t="n">
         <v>10</v>
       </c>
+      <c r="G93" t="n">
+        <v>6</v>
+      </c>
+      <c r="K93" t="n">
+        <v>4</v>
+      </c>
+      <c r="M93" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1</v>
+      </c>
+      <c r="W93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1</v>
+      </c>
       <c r="Z93" t="n">
         <v>1</v>
       </c>
-      <c r="AA93" t="n">
-        <v>1</v>
-      </c>
       <c r="AB93" t="n">
         <v>1</v>
       </c>
       <c r="AC93" t="n">
         <v>1</v>
       </c>
-      <c r="AE93" t="n">
+      <c r="AD93" t="n">
         <v>1</v>
       </c>
       <c r="AF93" t="n">
@@ -7598,7 +7589,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Propiedades físicas de los materiales</t>
+          <t>Propiedades coligativas</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7607,70 +7598,28 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D94" t="n">
         <v>10</v>
       </c>
-      <c r="E94" t="n">
-        <v>2</v>
-      </c>
-      <c r="F94" t="n">
-        <v>5</v>
-      </c>
-      <c r="G94" t="n">
-        <v>2</v>
-      </c>
-      <c r="H94" t="n">
-        <v>2</v>
-      </c>
-      <c r="I94" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J94" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K94" t="n">
-        <v>2</v>
-      </c>
-      <c r="L94" t="n">
-        <v>3</v>
-      </c>
-      <c r="M94" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O94" t="n">
-        <v>1</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1</v>
-      </c>
-      <c r="R94" t="n">
-        <v>1</v>
-      </c>
-      <c r="U94" t="n">
-        <v>1</v>
-      </c>
-      <c r="W94" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>1</v>
-      </c>
       <c r="Z94" t="n">
         <v>1</v>
       </c>
+      <c r="AA94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>1</v>
+      </c>
       <c r="AC94" t="n">
         <v>1</v>
       </c>
-      <c r="AD94" t="n">
-        <v>1</v>
-      </c>
       <c r="AE94" t="n">
         <v>1</v>
       </c>
       <c r="AF94" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
@@ -7686,7 +7635,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Propiedades físicas y químicas</t>
+          <t>Propiedades físicas de los materiales</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7698,19 +7647,22 @@
         <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G95" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
         <v>2.5</v>
@@ -7719,10 +7671,10 @@
         <v>2</v>
       </c>
       <c r="L95" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M95" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -7733,28 +7685,16 @@
       <c r="R95" t="n">
         <v>1</v>
       </c>
-      <c r="T95" t="n">
-        <v>1</v>
-      </c>
       <c r="U95" t="n">
         <v>1</v>
       </c>
-      <c r="V95" t="n">
-        <v>1</v>
-      </c>
       <c r="W95" t="n">
         <v>1</v>
       </c>
-      <c r="X95" t="n">
-        <v>1</v>
-      </c>
       <c r="Y95" t="n">
         <v>1</v>
       </c>
       <c r="Z95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB95" t="n">
         <v>1</v>
       </c>
       <c r="AC95" t="n">
@@ -7783,7 +7723,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Propiedades periódicas</t>
+          <t>Propiedades físicas y químicas</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7792,37 +7732,34 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
-      </c>
-      <c r="E96" t="n">
         <v>9</v>
       </c>
       <c r="F96" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="G96" t="n">
         <v>6</v>
       </c>
+      <c r="H96" t="n">
+        <v>2</v>
+      </c>
       <c r="I96" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="K96" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="M96" t="n">
-        <v>7</v>
-      </c>
-      <c r="N96" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -7833,12 +7770,15 @@
       <c r="R96" t="n">
         <v>1</v>
       </c>
-      <c r="S96" t="n">
+      <c r="T96" t="n">
         <v>1</v>
       </c>
       <c r="U96" t="n">
         <v>1</v>
       </c>
+      <c r="V96" t="n">
+        <v>1</v>
+      </c>
       <c r="W96" t="n">
         <v>1</v>
       </c>
@@ -7851,9 +7791,6 @@
       <c r="Z96" t="n">
         <v>1</v>
       </c>
-      <c r="AA96" t="n">
-        <v>1</v>
-      </c>
       <c r="AB96" t="n">
         <v>1</v>
       </c>
@@ -7867,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="AF96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
@@ -7883,7 +7820,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Propiedades singulares del agua</t>
+          <t>Propiedades periódicas</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7892,31 +7829,46 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
         <v>10</v>
       </c>
+      <c r="E97" t="n">
+        <v>9</v>
+      </c>
       <c r="F97" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="G97" t="n">
         <v>6</v>
       </c>
-      <c r="H97" t="n">
-        <v>7</v>
-      </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J97" t="n">
         <v>9</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L97" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M97" t="n">
+        <v>7</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -7927,9 +7879,18 @@
       <c r="W97" t="n">
         <v>1</v>
       </c>
+      <c r="X97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1</v>
+      </c>
       <c r="Z97" t="n">
         <v>1</v>
       </c>
+      <c r="AA97" t="n">
+        <v>1</v>
+      </c>
       <c r="AB97" t="n">
         <v>1</v>
       </c>
@@ -7939,8 +7900,11 @@
       <c r="AD97" t="n">
         <v>1</v>
       </c>
+      <c r="AE97" t="n">
+        <v>1</v>
+      </c>
       <c r="AF97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
@@ -7956,7 +7920,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Química de los lípidos</t>
+          <t>Propiedades singulares del agua</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7965,40 +7929,55 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
         <v>10</v>
       </c>
       <c r="F98" t="n">
-        <v>10.5</v>
+        <v>5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>6</v>
+      </c>
+      <c r="H98" t="n">
+        <v>7</v>
       </c>
       <c r="I98" t="n">
-        <v>9.5</v>
+        <v>3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>9</v>
+      </c>
+      <c r="K98" t="n">
+        <v>2</v>
       </c>
       <c r="L98" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O98" t="n">
-        <v>1</v>
-      </c>
-      <c r="R98" t="n">
+        <v>11</v>
+      </c>
+      <c r="S98" t="n">
         <v>1</v>
       </c>
       <c r="U98" t="n">
         <v>1</v>
       </c>
+      <c r="W98" t="n">
+        <v>1</v>
+      </c>
       <c r="Z98" t="n">
         <v>1</v>
       </c>
-      <c r="AA98" t="n">
+      <c r="AB98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC98" t="n">
         <v>1</v>
       </c>
       <c r="AD98" t="n">
         <v>1</v>
       </c>
       <c r="AF98" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
@@ -8007,7 +7986,7 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9429,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Entropía</t>
+          <t>Teorías del enlace de valencia y de orbitales moleculares</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9459,25 +9438,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D119" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="L119" t="n">
+        <v>11</v>
+      </c>
+      <c r="U119" t="n">
+        <v>1</v>
       </c>
       <c r="X119" t="n">
         <v>1</v>
       </c>
-      <c r="Y119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB119" t="n">
-        <v>1</v>
-      </c>
       <c r="AD119" t="n">
         <v>1</v>
       </c>
-      <c r="AF119" t="n">
-        <v>10</v>
+      <c r="AE119" t="n">
+        <v>1</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
@@ -9486,14 +9465,14 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Espectrometría de masas</t>
+          <t>Entropía</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9501,23 +9480,35 @@
           <t>solo_especializacion</t>
         </is>
       </c>
-      <c r="W120" t="n">
+      <c r="C120" t="n">
+        <v>9</v>
+      </c>
+      <c r="D120" t="n">
+        <v>9</v>
+      </c>
+      <c r="X120" t="n">
         <v>1</v>
       </c>
       <c r="Y120" t="n">
         <v>1</v>
       </c>
-      <c r="Z120" t="n">
-        <v>1</v>
+      <c r="AB120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>10</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9573,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Técnicas para determinar estructuras orgánicas</t>
+          <t>Estereoquímica y quiralidad</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9590,7 +9581,22 @@
           <t>solo_especializacion</t>
         </is>
       </c>
-      <c r="W122" t="n">
+      <c r="C122" t="n">
+        <v>10</v>
+      </c>
+      <c r="D122" t="n">
+        <v>10</v>
+      </c>
+      <c r="L122" t="n">
+        <v>11</v>
+      </c>
+      <c r="M122" t="n">
+        <v>7</v>
+      </c>
+      <c r="U122" t="n">
+        <v>1</v>
+      </c>
+      <c r="X122" t="n">
         <v>1</v>
       </c>
       <c r="Y122" t="n">
@@ -9599,24 +9605,36 @@
       <c r="Z122" t="n">
         <v>1</v>
       </c>
+      <c r="AA122" t="n">
+        <v>1</v>
+      </c>
       <c r="AC122" t="n">
         <v>1</v>
       </c>
+      <c r="AD122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>11</v>
+      </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Estereoquímica y quiralidad</t>
+          <t>Estructura y propiedades de los polímeros</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9625,21 +9643,33 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D123" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G123" t="n">
+        <v>6</v>
+      </c>
+      <c r="H123" t="n">
+        <v>7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>9.5</v>
       </c>
       <c r="L123" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M123" t="n">
         <v>7</v>
       </c>
+      <c r="R123" t="n">
+        <v>1</v>
+      </c>
       <c r="U123" t="n">
         <v>1</v>
       </c>
-      <c r="X123" t="n">
+      <c r="W123" t="n">
         <v>1</v>
       </c>
       <c r="Y123" t="n">
@@ -9649,9 +9679,6 @@
         <v>1</v>
       </c>
       <c r="AA123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC123" t="n">
         <v>1</v>
       </c>
       <c r="AD123" t="n">
@@ -9670,14 +9697,14 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Estructura y propiedades de los polímeros</t>
+          <t>Fundamentos de la reactividad orgánica</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9686,33 +9713,18 @@
         </is>
       </c>
       <c r="C124" t="n">
+        <v>5</v>
+      </c>
+      <c r="D124" t="n">
+        <v>10</v>
+      </c>
+      <c r="L124" t="n">
         <v>11</v>
       </c>
-      <c r="D124" t="n">
-        <v>11</v>
-      </c>
-      <c r="G124" t="n">
-        <v>6</v>
-      </c>
-      <c r="H124" t="n">
-        <v>7</v>
-      </c>
-      <c r="I124" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L124" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M124" t="n">
-        <v>7</v>
-      </c>
-      <c r="R124" t="n">
-        <v>1</v>
-      </c>
       <c r="U124" t="n">
         <v>1</v>
       </c>
-      <c r="W124" t="n">
+      <c r="X124" t="n">
         <v>1</v>
       </c>
       <c r="Y124" t="n">
@@ -9721,13 +9733,7 @@
       <c r="Z124" t="n">
         <v>1</v>
       </c>
-      <c r="AA124" t="n">
-        <v>1</v>
-      </c>
       <c r="AD124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE124" t="n">
         <v>1</v>
       </c>
       <c r="AF124" t="n">
@@ -9735,19 +9741,19 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
+          <t>retomado</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
           <t>solo_especializacion</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Fundamentos de la reactividad orgánica</t>
+          <t>Hibridación de orbitales</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9756,10 +9762,10 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D125" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L125" t="n">
         <v>11</v>
@@ -9779,12 +9785,15 @@
       <c r="AD125" t="n">
         <v>1</v>
       </c>
+      <c r="AE125" t="n">
+        <v>1</v>
+      </c>
       <c r="AF125" t="n">
         <v>11</v>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
@@ -9796,7 +9805,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Hibridación de orbitales</t>
+          <t>Hidrocarburos aromáticos</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9810,9 +9819,21 @@
       <c r="D126" t="n">
         <v>11</v>
       </c>
+      <c r="F126" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G126" t="n">
+        <v>8.5</v>
+      </c>
       <c r="L126" t="n">
         <v>11</v>
       </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
       <c r="U126" t="n">
         <v>1</v>
       </c>
@@ -9825,10 +9846,10 @@
       <c r="Z126" t="n">
         <v>1</v>
       </c>
+      <c r="AA126" t="n">
+        <v>1</v>
+      </c>
       <c r="AD126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE126" t="n">
         <v>1</v>
       </c>
       <c r="AF126" t="n">
@@ -9848,7 +9869,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Hidrocarburos aromáticos</t>
+          <t>Ley de Hess y entalpías de formación</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9857,13 +9878,10 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D127" t="n">
-        <v>11</v>
-      </c>
-      <c r="F127" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G127" t="n">
         <v>8.5</v>
@@ -9871,8 +9889,8 @@
       <c r="L127" t="n">
         <v>11</v>
       </c>
-      <c r="O127" t="n">
-        <v>1</v>
+      <c r="M127" t="n">
+        <v>9.5</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
@@ -9880,6 +9898,12 @@
       <c r="U127" t="n">
         <v>1</v>
       </c>
+      <c r="V127" t="n">
+        <v>1</v>
+      </c>
+      <c r="W127" t="n">
+        <v>1</v>
+      </c>
       <c r="X127" t="n">
         <v>1</v>
       </c>
@@ -9892,11 +9916,20 @@
       <c r="AA127" t="n">
         <v>1</v>
       </c>
+      <c r="AB127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>1</v>
+      </c>
       <c r="AD127" t="n">
         <v>1</v>
       </c>
+      <c r="AE127" t="n">
+        <v>1</v>
+      </c>
       <c r="AF127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
@@ -9912,7 +9945,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ley de Hess y entalpías de formación</t>
+          <t>Ley de velocidad, orden de reacción y ecuación de Arrhenius</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9921,32 +9954,17 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D128" t="n">
-        <v>10</v>
-      </c>
-      <c r="G128" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L128" t="n">
         <v>11</v>
       </c>
-      <c r="M128" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P128" t="n">
-        <v>1</v>
-      </c>
       <c r="U128" t="n">
         <v>1</v>
       </c>
-      <c r="V128" t="n">
-        <v>1</v>
-      </c>
-      <c r="W128" t="n">
-        <v>1</v>
-      </c>
       <c r="X128" t="n">
         <v>1</v>
       </c>
@@ -9954,9 +9972,6 @@
         <v>1</v>
       </c>
       <c r="Z128" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA128" t="n">
         <v>1</v>
       </c>
       <c r="AB128" t="n">
@@ -9988,7 +10003,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ley de velocidad, orden de reacción y ecuación de Arrhenius</t>
+          <t>Mecanismos de reacción</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9997,40 +10012,28 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D129" t="n">
-        <v>9</v>
-      </c>
-      <c r="L129" t="n">
+        <v>10</v>
+      </c>
+      <c r="X129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF129" t="n">
         <v>11</v>
-      </c>
-      <c r="U129" t="n">
-        <v>1</v>
-      </c>
-      <c r="X129" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE129" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>10</v>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
@@ -10046,7 +10049,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mecanismos de reacción</t>
+          <t>Nanomateriales y manufactura molecular</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10055,12 +10058,15 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D130" t="n">
-        <v>10</v>
-      </c>
-      <c r="X130" t="n">
+        <v>11</v>
+      </c>
+      <c r="G130" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W130" t="n">
         <v>1</v>
       </c>
       <c r="Y130" t="n">
@@ -10069,10 +10075,7 @@
       <c r="Z130" t="n">
         <v>1</v>
       </c>
-      <c r="AC130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD130" t="n">
+      <c r="AE130" t="n">
         <v>1</v>
       </c>
       <c r="AF130" t="n">
@@ -10092,7 +10095,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Nanomateriales y manufactura molecular</t>
+          <t>Polimerización por adición y por condensación</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10106,8 +10109,17 @@
       <c r="D131" t="n">
         <v>11</v>
       </c>
-      <c r="G131" t="n">
-        <v>8.5</v>
+      <c r="F131" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L131" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" t="n">
+        <v>1</v>
       </c>
       <c r="W131" t="n">
         <v>1</v>
@@ -10116,6 +10128,18 @@
         <v>1</v>
       </c>
       <c r="Z131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD131" t="n">
         <v>1</v>
       </c>
       <c r="AE131" t="n">
@@ -10138,7 +10162,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Polimerización por adición y por condensación</t>
+          <t>Potenciales estándar de electrodo y de celda</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10153,27 +10177,33 @@
         <v>11</v>
       </c>
       <c r="F132" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L132" t="n">
+        <v>8</v>
+      </c>
+      <c r="G132" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I132" t="n">
         <v>9.5</v>
       </c>
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="U132" t="n">
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="R132" t="n">
         <v>1</v>
       </c>
       <c r="W132" t="n">
         <v>1</v>
       </c>
+      <c r="X132" t="n">
+        <v>1</v>
+      </c>
       <c r="Y132" t="n">
         <v>1</v>
       </c>
       <c r="Z132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA132" t="n">
         <v>1</v>
       </c>
       <c r="AB132" t="n">
@@ -10205,7 +10235,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Potenciales estándar de electrodo y de celda</t>
+          <t>Producto de solubilidad (Kps)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10214,42 +10244,12 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D133" t="n">
-        <v>11</v>
-      </c>
-      <c r="F133" t="n">
-        <v>8</v>
-      </c>
-      <c r="G133" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I133" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O133" t="n">
-        <v>1</v>
-      </c>
-      <c r="P133" t="n">
-        <v>1</v>
-      </c>
-      <c r="R133" t="n">
-        <v>1</v>
-      </c>
-      <c r="W133" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="X133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB133" t="n">
         <v>1</v>
       </c>
       <c r="AC133" t="n">
@@ -10278,7 +10278,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Producto de solubilidad (Kps)</t>
+          <t>Química de los ácidos nucleicos</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10287,29 +10287,29 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D134" t="n">
         <v>10</v>
       </c>
-      <c r="X134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE134" t="n">
+      <c r="Y134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" t="n">
         <v>1</v>
       </c>
       <c r="AF134" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>solo_especializacion</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH134" t="inlineStr">
